--- a/design/道具表.xlsx
+++ b/design/道具表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12060"/>
+    <workbookView windowWidth="18345" windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="道具总表|Item" sheetId="1" r:id="rId1"/>
@@ -267,12 +267,19 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">86185:	
-</t>
+          <t>86185:	
+当ToolType=1时
+  1=近战道具
+  2=枪械
+  3=医疗道具
+  4=投掷物
+ToolType=2时
+  5=医疗道具
+  6=投掷道具</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -294,7 +301,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="K1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -317,7 +324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="1">
+    <comment ref="M1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -339,7 +346,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -367,7 +374,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="89">
   <si>
     <t>道具ID</t>
   </si>
@@ -573,6 +580,9 @@
     <t>装备数量</t>
   </si>
   <si>
+    <t>体力消耗</t>
+  </si>
+  <si>
     <t>伤害&amp;恢复量</t>
   </si>
   <si>
@@ -588,6 +598,9 @@
     <t>触发延迟（Tick）</t>
   </si>
   <si>
+    <t>延迟移速减低</t>
+  </si>
+  <si>
     <t>持续时间（Tick）</t>
   </si>
   <si>
@@ -601,6 +614,9 @@
   </si>
   <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>PhysicalExhaustion</t>
   </si>
   <si>
     <t>Value</t>
@@ -7762,15 +7778,15 @@
     <cfRule type="duplicateValues" dxfId="0" priority="6775"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 0～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="堆叠上限" prompt="整数 0～2147483647。Kind=10 填 0，表示值类型不占背包格；其他道具至少为 1，装备固定为 1。" sqref="H5 H9 H13 H17 H6:H8 H10:H12 H14:H16 H18:H20 H21:H500">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 0～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="道具小类" prompt="整数 0～2147483647。按 Kind 解释。0=未细分（原四条货币已补为 0）；示例装备填 1=武器。不得留空。" sqref="E5:E15 E17:E500">
       <formula1>0</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 0～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="道具小类" prompt="整数 0～2147483647。按 Kind 解释。0=未细分（原四条货币已补为 0）；示例装备填 1=武器。不得留空。" sqref="E7 E8 E9 E10 E11 E12 E13 E17 E5:E6 E14:E15 E18:E500">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 0～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="道具子类" prompt="整数 0～2147483647。0=未细分；示例武器填 7=枪械。其他历史分类沿用既有定义，不推断职业或等级。" sqref="F5:F15 F17:F500">
       <formula1>0</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 0～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="道具子类" prompt="整数 0～2147483647。0=未细分；示例武器填 7=枪械。其他历史分类沿用既有定义，不推断职业或等级。" sqref="F7 F8 F9 F10 F11 F12 F13 F17 F5:F6 F14:F15 F18:F500">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 0～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="堆叠上限" prompt="整数 0～2147483647。Kind=10 填 0，表示值类型不占背包格；其他道具至少为 1，装备固定为 1。" sqref="H5:H500">
       <formula1>0</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
@@ -7928,14 +7944,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="13.5" spans="1:7">
+    <row r="8" spans="1:7">
       <c r="A8" s="33"/>
       <c r="B8" s="34"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
       <c r="E8" s="33"/>
     </row>
-    <row r="9" ht="13.5" spans="1:7">
+    <row r="9" spans="1:7">
       <c r="A9" s="33"/>
       <c r="B9" s="34"/>
       <c r="C9" s="33"/>
@@ -11405,17 +11421,17 @@
     <extLst/>
   </autoFilter>
   <dataValidations count="4">
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="装备ID" prompt="整数 1～2147483647。主键同时引用 Item.ItemIdx；目标 Kind 必须为 1。" sqref="A5:A7 A8:A503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="装备ID" prompt="整数 1～2147483647。主键同时引用 Item.ItemIdx；目标 Kind 必须为 1。" sqref="A5:A503">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="可选值：1、2、3、4、5、6、7、8、9、10、11。跨表引用及组合条件请对照填表说明。" promptTitle="装备位置" prompt="可选值：1、2、3、4、5、6、7、8、9、10、11。1=武器、2=防具、3=项链、4=耳环、5=手镯、6=戒指、7=腰带、8=谷玉、9=纹章、10=封印、11=灵装。原批注中划线的 12/13 为历史记录，不采用。" sqref="C5:C7 C8:C503">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="可选值：1、2、3、4、5、6、7、8、9、10、11。跨表引用及组合条件请对照填表说明。" promptTitle="装备位置" prompt="可选值：1、2、3、4、5、6、7、8、9、10、11。1=武器、2=防具、3=项链、4=耳环、5=手镯、6=戒指、7=腰带、8=谷玉、9=纹章、10=封印、11=灵装。原批注中划线的 12/13 为历史记录，不采用。" sqref="C5:C503">
       <formula1>"1,2,3,4,5,6,7,8,9,10,11"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="可选值：0、1、2、3、4、5、6、7。跨表引用及组合条件请对照填表说明。" promptTitle="武器类型" prompt="可选值：0、1、2、3、4、5、6、7。0=非武器；保留 1=剑、2=刀、3=杖、4=扇、5=手套、6=爪，新增 7=枪械。" sqref="D5:D7 D8:D503">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="可选值：0、1、2、3、4、5、6、7。跨表引用及组合条件请对照填表说明。" promptTitle="武器类型" prompt="可选值：0、1、2、3、4、5、6、7。0=非武器；保留 1=剑、2=刀、3=杖、4=扇、5=手套、6=爪，新增 7=枪械。" sqref="D5:D503">
       <formula1>"0,1,2,3,4,5,6,7"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 0～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="武器配置ID" prompt="整数 0～2147483647。0 表示无关联；非零值引用 Weapon.WeaponIdx。本轮枪械必须引用非零武器配置；非武器填 0。其他历史武器类型仅预留。" sqref="E5:E7 E8:E503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 0～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="武器配置ID" prompt="整数 0～2147483647。0 表示无关联；非零值引用 Weapon.WeaponIdx。本轮枪械必须引用非零武器配置；非武器填 0。其他历史武器类型仅预留。" sqref="E5:E503">
       <formula1>0</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
@@ -11431,23 +11447,25 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:N504"/>
+  <dimension ref="A1:P504"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="3" customWidth="1"/>
-    <col min="3" max="6" width="13.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="20.25" style="3" customWidth="1"/>
-    <col min="10" max="11" width="15.625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.625" style="4"/>
-    <col min="14" max="14" width="55" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="15.625" style="4"/>
+    <col min="3" max="5" width="13.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.25" style="3" customWidth="1"/>
+    <col min="11" max="13" width="15.625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="15.625" style="4"/>
+    <col min="16" max="16" width="55" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="15.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="40" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="40" customHeight="1" spans="1:16">
       <c r="A1" s="5" t="s">
         <v>54</v>
       </c>
@@ -11484,11 +11502,17 @@
       <c r="L1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="M1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:14">
+    <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:16">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -11525,11 +11549,17 @@
       <c r="L2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="M2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="29" customHeight="1" spans="1:14">
+    <row r="3" s="2" customFormat="1" ht="29" customHeight="1" spans="1:16">
       <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
@@ -11537,38 +11567,42 @@
         <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="N3" s="10"/>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="28" customHeight="1" spans="1:14">
+        <v>85</v>
+      </c>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A4" s="11" t="s">
         <v>20</v>
       </c>
@@ -11603,11 +11637,17 @@
         <v>21</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="10"/>
-    </row>
-    <row r="5" spans="1:14">
+        <v>88</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="13">
         <v>1</v>
       </c>
@@ -11624,23 +11664,27 @@
         <v>1</v>
       </c>
       <c r="F5" s="13">
+        <v>20</v>
+      </c>
+      <c r="G5" s="13">
         <v>100</v>
       </c>
-      <c r="G5" s="13">
+      <c r="H5" s="13">
         <v>600</v>
       </c>
-      <c r="H5" s="13"/>
       <c r="I5" s="13"/>
-      <c r="J5" s="13">
+      <c r="J5" s="13"/>
+      <c r="K5" s="13">
         <v>0</v>
       </c>
-      <c r="K5" s="13"/>
       <c r="L5" s="13"/>
-      <c r="N5" s="10" t="s">
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="P5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:16">
       <c r="A6" s="15">
         <v>2</v>
       </c>
@@ -11657,20 +11701,26 @@
         <v>3</v>
       </c>
       <c r="F6" s="15">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15">
         <v>50</v>
       </c>
-      <c r="G6" s="15">
+      <c r="H6" s="15">
         <v>0</v>
       </c>
-      <c r="H6" s="15"/>
       <c r="I6" s="15"/>
-      <c r="J6" s="15">
-        <v>0</v>
-      </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="J6" s="15"/>
+      <c r="K6" s="15">
+        <v>120</v>
+      </c>
+      <c r="L6" s="15">
+        <v>30</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="13">
         <v>3</v>
       </c>
@@ -11687,26 +11737,32 @@
         <v>5</v>
       </c>
       <c r="F7" s="13">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13">
         <v>10</v>
       </c>
-      <c r="G7" s="13">
+      <c r="H7" s="13">
         <v>600</v>
       </c>
-      <c r="H7" s="13">
+      <c r="I7" s="13">
         <v>1600</v>
       </c>
-      <c r="I7" s="13">
+      <c r="J7" s="13">
         <v>100</v>
       </c>
-      <c r="J7" s="13">
+      <c r="K7" s="13">
         <v>180</v>
       </c>
-      <c r="K7" s="13">
+      <c r="L7" s="15">
+        <v>30</v>
+      </c>
+      <c r="M7" s="13">
         <v>540</v>
       </c>
-      <c r="L7" s="13"/>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="15">
         <v>4</v>
       </c>
@@ -11723,20 +11779,26 @@
         <v>1</v>
       </c>
       <c r="F8" s="15">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15">
         <v>150</v>
       </c>
-      <c r="G8" s="15">
+      <c r="H8" s="15">
         <v>0</v>
       </c>
-      <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="15">
+      <c r="J8" s="15"/>
+      <c r="K8" s="15">
         <v>90</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="L8" s="15">
+        <v>30</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="17">
         <v>5</v>
       </c>
@@ -11753,22 +11815,28 @@
         <v>1</v>
       </c>
       <c r="F9" s="17">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17">
         <v>10</v>
       </c>
-      <c r="G9" s="17">
+      <c r="H9" s="17">
         <v>0</v>
       </c>
-      <c r="H9" s="17"/>
       <c r="I9" s="17"/>
-      <c r="J9" s="17">
+      <c r="J9" s="17"/>
+      <c r="K9" s="17">
         <v>90</v>
       </c>
-      <c r="K9" s="17">
+      <c r="L9" s="15">
+        <v>30</v>
+      </c>
+      <c r="M9" s="17">
         <v>7200</v>
       </c>
-      <c r="L9" s="17"/>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="N9" s="17"/>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="17">
         <v>6</v>
       </c>
@@ -11785,24 +11853,30 @@
         <v>1</v>
       </c>
       <c r="F10" s="17">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17">
         <v>125</v>
       </c>
-      <c r="G10" s="17">
+      <c r="H10" s="17">
         <v>1200</v>
       </c>
-      <c r="H10" s="17">
+      <c r="I10" s="17">
         <v>1600</v>
       </c>
-      <c r="I10" s="17">
+      <c r="J10" s="17">
         <v>100</v>
       </c>
-      <c r="J10" s="13">
+      <c r="K10" s="13">
         <v>180</v>
       </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="15">
+        <v>30</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="17"/>
       <c r="B11" s="18"/>
       <c r="C11" s="17"/>
@@ -11815,8 +11889,10 @@
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="17"/>
       <c r="B12" s="18"/>
       <c r="C12" s="17"/>
@@ -11829,8 +11905,10 @@
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="17"/>
       <c r="B13" s="18"/>
       <c r="C13" s="17"/>
@@ -11843,8 +11921,10 @@
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="17"/>
@@ -11857,8 +11937,10 @@
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="17"/>
       <c r="B15" s="18"/>
       <c r="C15" s="17"/>
@@ -11871,8 +11953,10 @@
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="17"/>
       <c r="B16" s="18"/>
       <c r="C16" s="17"/>
@@ -11885,8 +11969,10 @@
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="17"/>
       <c r="B17" s="18"/>
       <c r="C17" s="17"/>
@@ -11899,8 +11985,10 @@
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="17"/>
       <c r="B18" s="18"/>
       <c r="C18" s="17"/>
@@ -11913,8 +12001,10 @@
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="17"/>
       <c r="B19" s="18"/>
       <c r="C19" s="17"/>
@@ -11927,8 +12017,10 @@
       <c r="J19" s="17"/>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="17"/>
@@ -11941,8 +12033,10 @@
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="17"/>
       <c r="B21" s="18"/>
       <c r="C21" s="17"/>
@@ -11955,8 +12049,10 @@
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="17"/>
@@ -11969,8 +12065,10 @@
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
       <c r="L22" s="17"/>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="17"/>
       <c r="B23" s="18"/>
       <c r="C23" s="17"/>
@@ -11983,8 +12081,10 @@
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
       <c r="L23" s="17"/>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="17"/>
       <c r="B24" s="18"/>
       <c r="C24" s="17"/>
@@ -11997,8 +12097,10 @@
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="17"/>
       <c r="B25" s="18"/>
       <c r="C25" s="17"/>
@@ -12011,8 +12113,10 @@
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="17"/>
       <c r="B26" s="18"/>
       <c r="C26" s="17"/>
@@ -12025,8 +12129,10 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="17"/>
       <c r="B27" s="18"/>
       <c r="C27" s="17"/>
@@ -12039,8 +12145,10 @@
       <c r="J27" s="17"/>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="17"/>
       <c r="B28" s="18"/>
       <c r="C28" s="17"/>
@@ -12053,8 +12161,10 @@
       <c r="J28" s="17"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="17"/>
       <c r="B29" s="18"/>
       <c r="C29" s="17"/>
@@ -12067,8 +12177,10 @@
       <c r="J29" s="17"/>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="17"/>
       <c r="B30" s="18"/>
       <c r="C30" s="17"/>
@@ -12081,8 +12193,10 @@
       <c r="J30" s="17"/>
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="17"/>
       <c r="B31" s="18"/>
       <c r="C31" s="17"/>
@@ -12095,8 +12209,10 @@
       <c r="J31" s="17"/>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="17"/>
       <c r="B32" s="18"/>
       <c r="C32" s="17"/>
@@ -12109,8 +12225,10 @@
       <c r="J32" s="17"/>
       <c r="K32" s="17"/>
       <c r="L32" s="17"/>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="17"/>
       <c r="B33" s="18"/>
       <c r="C33" s="17"/>
@@ -12123,8 +12241,10 @@
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="17"/>
       <c r="B34" s="18"/>
       <c r="C34" s="17"/>
@@ -12137,8 +12257,10 @@
       <c r="J34" s="17"/>
       <c r="K34" s="17"/>
       <c r="L34" s="17"/>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="17"/>
       <c r="B35" s="18"/>
       <c r="C35" s="17"/>
@@ -12151,8 +12273,10 @@
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="17"/>
       <c r="B36" s="18"/>
       <c r="C36" s="17"/>
@@ -12165,8 +12289,10 @@
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="17"/>
       <c r="B37" s="18"/>
       <c r="C37" s="17"/>
@@ -12179,8 +12305,10 @@
       <c r="J37" s="17"/>
       <c r="K37" s="17"/>
       <c r="L37" s="17"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="17"/>
       <c r="B38" s="18"/>
       <c r="C38" s="17"/>
@@ -12193,8 +12321,10 @@
       <c r="J38" s="17"/>
       <c r="K38" s="17"/>
       <c r="L38" s="17"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="17"/>
       <c r="B39" s="18"/>
       <c r="C39" s="17"/>
@@ -12207,8 +12337,10 @@
       <c r="J39" s="17"/>
       <c r="K39" s="17"/>
       <c r="L39" s="17"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="17"/>
       <c r="B40" s="18"/>
       <c r="C40" s="17"/>
@@ -12221,8 +12353,10 @@
       <c r="J40" s="17"/>
       <c r="K40" s="17"/>
       <c r="L40" s="17"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="17"/>
       <c r="B41" s="18"/>
       <c r="C41" s="17"/>
@@ -12235,8 +12369,10 @@
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
       <c r="L41" s="17"/>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="17"/>
       <c r="B42" s="18"/>
       <c r="C42" s="17"/>
@@ -12249,8 +12385,10 @@
       <c r="J42" s="17"/>
       <c r="K42" s="17"/>
       <c r="L42" s="17"/>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="17"/>
       <c r="B43" s="18"/>
       <c r="C43" s="17"/>
@@ -12263,8 +12401,10 @@
       <c r="J43" s="17"/>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="17"/>
       <c r="B44" s="18"/>
       <c r="C44" s="17"/>
@@ -12277,8 +12417,10 @@
       <c r="J44" s="17"/>
       <c r="K44" s="17"/>
       <c r="L44" s="17"/>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="17"/>
       <c r="B45" s="18"/>
       <c r="C45" s="17"/>
@@ -12291,8 +12433,10 @@
       <c r="J45" s="17"/>
       <c r="K45" s="17"/>
       <c r="L45" s="17"/>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="17"/>
       <c r="B46" s="18"/>
       <c r="C46" s="17"/>
@@ -12305,8 +12449,10 @@
       <c r="J46" s="17"/>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="17"/>
       <c r="B47" s="18"/>
       <c r="C47" s="17"/>
@@ -12319,8 +12465,10 @@
       <c r="J47" s="17"/>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="17"/>
       <c r="B48" s="18"/>
       <c r="C48" s="17"/>
@@ -12333,8 +12481,10 @@
       <c r="J48" s="17"/>
       <c r="K48" s="17"/>
       <c r="L48" s="17"/>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="17"/>
       <c r="B49" s="18"/>
       <c r="C49" s="17"/>
@@ -12347,8 +12497,10 @@
       <c r="J49" s="17"/>
       <c r="K49" s="17"/>
       <c r="L49" s="17"/>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="17"/>
       <c r="B50" s="18"/>
       <c r="C50" s="17"/>
@@ -12361,8 +12513,10 @@
       <c r="J50" s="17"/>
       <c r="K50" s="17"/>
       <c r="L50" s="17"/>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="17"/>
       <c r="B51" s="18"/>
       <c r="C51" s="17"/>
@@ -12375,8 +12529,10 @@
       <c r="J51" s="17"/>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="17"/>
       <c r="B52" s="18"/>
       <c r="C52" s="17"/>
@@ -12389,8 +12545,10 @@
       <c r="J52" s="17"/>
       <c r="K52" s="17"/>
       <c r="L52" s="17"/>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="17"/>
       <c r="B53" s="18"/>
       <c r="C53" s="17"/>
@@ -12403,8 +12561,10 @@
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="17"/>
       <c r="B54" s="18"/>
       <c r="C54" s="17"/>
@@ -12417,8 +12577,10 @@
       <c r="J54" s="17"/>
       <c r="K54" s="17"/>
       <c r="L54" s="17"/>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="17"/>
       <c r="B55" s="18"/>
       <c r="C55" s="17"/>
@@ -12431,8 +12593,10 @@
       <c r="J55" s="17"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" s="17"/>
       <c r="B56" s="18"/>
       <c r="C56" s="17"/>
@@ -12445,8 +12609,10 @@
       <c r="J56" s="17"/>
       <c r="K56" s="17"/>
       <c r="L56" s="17"/>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" s="17"/>
       <c r="B57" s="18"/>
       <c r="C57" s="17"/>
@@ -12459,8 +12625,10 @@
       <c r="J57" s="17"/>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="M57" s="17"/>
+      <c r="N57" s="17"/>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" s="17"/>
       <c r="B58" s="18"/>
       <c r="C58" s="17"/>
@@ -12473,8 +12641,10 @@
       <c r="J58" s="17"/>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" s="17"/>
       <c r="B59" s="18"/>
       <c r="C59" s="17"/>
@@ -12487,8 +12657,10 @@
       <c r="J59" s="17"/>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="M59" s="17"/>
+      <c r="N59" s="17"/>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" s="17"/>
       <c r="B60" s="18"/>
       <c r="C60" s="17"/>
@@ -12501,8 +12673,10 @@
       <c r="J60" s="17"/>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="17"/>
       <c r="B61" s="18"/>
       <c r="C61" s="17"/>
@@ -12515,8 +12689,10 @@
       <c r="J61" s="17"/>
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="M61" s="17"/>
+      <c r="N61" s="17"/>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" s="17"/>
       <c r="B62" s="18"/>
       <c r="C62" s="17"/>
@@ -12529,8 +12705,10 @@
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" s="17"/>
       <c r="B63" s="18"/>
       <c r="C63" s="17"/>
@@ -12543,8 +12721,10 @@
       <c r="J63" s="17"/>
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="M63" s="17"/>
+      <c r="N63" s="17"/>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" s="17"/>
       <c r="B64" s="18"/>
       <c r="C64" s="17"/>
@@ -12557,8 +12737,10 @@
       <c r="J64" s="17"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
-    </row>
-    <row r="65" spans="1:12">
+      <c r="M64" s="17"/>
+      <c r="N64" s="17"/>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" s="17"/>
       <c r="B65" s="18"/>
       <c r="C65" s="17"/>
@@ -12571,8 +12753,10 @@
       <c r="J65" s="17"/>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
-    </row>
-    <row r="66" spans="1:12">
+      <c r="M65" s="17"/>
+      <c r="N65" s="17"/>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" s="17"/>
       <c r="B66" s="18"/>
       <c r="C66" s="17"/>
@@ -12585,8 +12769,10 @@
       <c r="J66" s="17"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
-    </row>
-    <row r="67" spans="1:12">
+      <c r="M66" s="17"/>
+      <c r="N66" s="17"/>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" s="17"/>
       <c r="B67" s="18"/>
       <c r="C67" s="17"/>
@@ -12599,8 +12785,10 @@
       <c r="J67" s="17"/>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
-    </row>
-    <row r="68" spans="1:12">
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" s="17"/>
       <c r="B68" s="18"/>
       <c r="C68" s="17"/>
@@ -12613,8 +12801,10 @@
       <c r="J68" s="17"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
-    </row>
-    <row r="69" spans="1:12">
+      <c r="M68" s="17"/>
+      <c r="N68" s="17"/>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" s="17"/>
       <c r="B69" s="18"/>
       <c r="C69" s="17"/>
@@ -12627,8 +12817,10 @@
       <c r="J69" s="17"/>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
-    </row>
-    <row r="70" spans="1:12">
+      <c r="M69" s="17"/>
+      <c r="N69" s="17"/>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" s="17"/>
       <c r="B70" s="18"/>
       <c r="C70" s="17"/>
@@ -12641,8 +12833,10 @@
       <c r="J70" s="17"/>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
-    </row>
-    <row r="71" spans="1:12">
+      <c r="M70" s="17"/>
+      <c r="N70" s="17"/>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" s="17"/>
       <c r="B71" s="18"/>
       <c r="C71" s="17"/>
@@ -12655,8 +12849,10 @@
       <c r="J71" s="17"/>
       <c r="K71" s="17"/>
       <c r="L71" s="17"/>
-    </row>
-    <row r="72" spans="1:12">
+      <c r="M71" s="17"/>
+      <c r="N71" s="17"/>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" s="17"/>
       <c r="B72" s="18"/>
       <c r="C72" s="17"/>
@@ -12669,8 +12865,10 @@
       <c r="J72" s="17"/>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
-    </row>
-    <row r="73" spans="1:12">
+      <c r="M72" s="17"/>
+      <c r="N72" s="17"/>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" s="17"/>
       <c r="B73" s="18"/>
       <c r="C73" s="17"/>
@@ -12683,8 +12881,10 @@
       <c r="J73" s="17"/>
       <c r="K73" s="17"/>
       <c r="L73" s="17"/>
-    </row>
-    <row r="74" spans="1:12">
+      <c r="M73" s="17"/>
+      <c r="N73" s="17"/>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" s="17"/>
       <c r="B74" s="18"/>
       <c r="C74" s="17"/>
@@ -12697,8 +12897,10 @@
       <c r="J74" s="17"/>
       <c r="K74" s="17"/>
       <c r="L74" s="17"/>
-    </row>
-    <row r="75" spans="1:12">
+      <c r="M74" s="17"/>
+      <c r="N74" s="17"/>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" s="17"/>
       <c r="B75" s="18"/>
       <c r="C75" s="17"/>
@@ -12711,8 +12913,10 @@
       <c r="J75" s="17"/>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
-    </row>
-    <row r="76" spans="1:12">
+      <c r="M75" s="17"/>
+      <c r="N75" s="17"/>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76" s="17"/>
       <c r="B76" s="18"/>
       <c r="C76" s="17"/>
@@ -12725,8 +12929,10 @@
       <c r="J76" s="17"/>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
-    </row>
-    <row r="77" spans="1:12">
+      <c r="M76" s="17"/>
+      <c r="N76" s="17"/>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77" s="17"/>
       <c r="B77" s="18"/>
       <c r="C77" s="17"/>
@@ -12739,8 +12945,10 @@
       <c r="J77" s="17"/>
       <c r="K77" s="17"/>
       <c r="L77" s="17"/>
-    </row>
-    <row r="78" spans="1:12">
+      <c r="M77" s="17"/>
+      <c r="N77" s="17"/>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78" s="17"/>
       <c r="B78" s="18"/>
       <c r="C78" s="17"/>
@@ -12753,8 +12961,10 @@
       <c r="J78" s="17"/>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
-    </row>
-    <row r="79" spans="1:12">
+      <c r="M78" s="17"/>
+      <c r="N78" s="17"/>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79" s="17"/>
       <c r="B79" s="18"/>
       <c r="C79" s="17"/>
@@ -12767,8 +12977,10 @@
       <c r="J79" s="17"/>
       <c r="K79" s="17"/>
       <c r="L79" s="17"/>
-    </row>
-    <row r="80" spans="1:12">
+      <c r="M79" s="17"/>
+      <c r="N79" s="17"/>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80" s="17"/>
       <c r="B80" s="18"/>
       <c r="C80" s="17"/>
@@ -12781,8 +12993,10 @@
       <c r="J80" s="17"/>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
-    </row>
-    <row r="81" spans="1:12">
+      <c r="M80" s="17"/>
+      <c r="N80" s="17"/>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" s="17"/>
       <c r="B81" s="18"/>
       <c r="C81" s="17"/>
@@ -12795,8 +13009,10 @@
       <c r="J81" s="17"/>
       <c r="K81" s="17"/>
       <c r="L81" s="17"/>
-    </row>
-    <row r="82" spans="1:12">
+      <c r="M81" s="17"/>
+      <c r="N81" s="17"/>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82" s="17"/>
       <c r="B82" s="18"/>
       <c r="C82" s="17"/>
@@ -12809,8 +13025,10 @@
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
       <c r="L82" s="17"/>
-    </row>
-    <row r="83" spans="1:12">
+      <c r="M82" s="17"/>
+      <c r="N82" s="17"/>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83" s="17"/>
       <c r="B83" s="18"/>
       <c r="C83" s="17"/>
@@ -12823,8 +13041,10 @@
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
       <c r="L83" s="17"/>
-    </row>
-    <row r="84" spans="1:12">
+      <c r="M83" s="17"/>
+      <c r="N83" s="17"/>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84" s="17"/>
       <c r="B84" s="18"/>
       <c r="C84" s="17"/>
@@ -12837,8 +13057,10 @@
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
       <c r="L84" s="17"/>
-    </row>
-    <row r="85" spans="1:12">
+      <c r="M84" s="17"/>
+      <c r="N84" s="17"/>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85" s="17"/>
       <c r="B85" s="18"/>
       <c r="C85" s="17"/>
@@ -12851,8 +13073,10 @@
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
       <c r="L85" s="17"/>
-    </row>
-    <row r="86" spans="1:12">
+      <c r="M85" s="17"/>
+      <c r="N85" s="17"/>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86" s="17"/>
       <c r="B86" s="18"/>
       <c r="C86" s="17"/>
@@ -12865,8 +13089,10 @@
       <c r="J86" s="17"/>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
-    </row>
-    <row r="87" spans="1:12">
+      <c r="M86" s="17"/>
+      <c r="N86" s="17"/>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87" s="17"/>
       <c r="B87" s="18"/>
       <c r="C87" s="17"/>
@@ -12879,8 +13105,10 @@
       <c r="J87" s="17"/>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
-    </row>
-    <row r="88" spans="1:12">
+      <c r="M87" s="17"/>
+      <c r="N87" s="17"/>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88" s="17"/>
       <c r="B88" s="18"/>
       <c r="C88" s="17"/>
@@ -12893,8 +13121,10 @@
       <c r="J88" s="17"/>
       <c r="K88" s="17"/>
       <c r="L88" s="17"/>
-    </row>
-    <row r="89" spans="1:12">
+      <c r="M88" s="17"/>
+      <c r="N88" s="17"/>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89" s="17"/>
       <c r="B89" s="18"/>
       <c r="C89" s="17"/>
@@ -12907,8 +13137,10 @@
       <c r="J89" s="17"/>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
-    </row>
-    <row r="90" spans="1:12">
+      <c r="M89" s="17"/>
+      <c r="N89" s="17"/>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90" s="17"/>
       <c r="B90" s="18"/>
       <c r="C90" s="17"/>
@@ -12921,8 +13153,10 @@
       <c r="J90" s="17"/>
       <c r="K90" s="17"/>
       <c r="L90" s="17"/>
-    </row>
-    <row r="91" spans="1:12">
+      <c r="M90" s="17"/>
+      <c r="N90" s="17"/>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91" s="17"/>
       <c r="B91" s="18"/>
       <c r="C91" s="17"/>
@@ -12935,8 +13169,10 @@
       <c r="J91" s="17"/>
       <c r="K91" s="17"/>
       <c r="L91" s="17"/>
-    </row>
-    <row r="92" spans="1:12">
+      <c r="M91" s="17"/>
+      <c r="N91" s="17"/>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92" s="17"/>
       <c r="B92" s="18"/>
       <c r="C92" s="17"/>
@@ -12949,8 +13185,10 @@
       <c r="J92" s="17"/>
       <c r="K92" s="17"/>
       <c r="L92" s="17"/>
-    </row>
-    <row r="93" spans="1:12">
+      <c r="M92" s="17"/>
+      <c r="N92" s="17"/>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93" s="17"/>
       <c r="B93" s="18"/>
       <c r="C93" s="17"/>
@@ -12963,8 +13201,10 @@
       <c r="J93" s="17"/>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
-    </row>
-    <row r="94" spans="1:12">
+      <c r="M93" s="17"/>
+      <c r="N93" s="17"/>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94" s="17"/>
       <c r="B94" s="18"/>
       <c r="C94" s="17"/>
@@ -12977,8 +13217,10 @@
       <c r="J94" s="17"/>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
-    </row>
-    <row r="95" spans="1:12">
+      <c r="M94" s="17"/>
+      <c r="N94" s="17"/>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95" s="17"/>
       <c r="B95" s="18"/>
       <c r="C95" s="17"/>
@@ -12991,8 +13233,10 @@
       <c r="J95" s="17"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
-    </row>
-    <row r="96" spans="1:12">
+      <c r="M95" s="17"/>
+      <c r="N95" s="17"/>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96" s="17"/>
       <c r="B96" s="18"/>
       <c r="C96" s="17"/>
@@ -13005,8 +13249,10 @@
       <c r="J96" s="17"/>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
-    </row>
-    <row r="97" spans="1:12">
+      <c r="M96" s="17"/>
+      <c r="N96" s="17"/>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97" s="17"/>
       <c r="B97" s="18"/>
       <c r="C97" s="17"/>
@@ -13019,8 +13265,10 @@
       <c r="J97" s="17"/>
       <c r="K97" s="17"/>
       <c r="L97" s="17"/>
-    </row>
-    <row r="98" spans="1:12">
+      <c r="M97" s="17"/>
+      <c r="N97" s="17"/>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98" s="17"/>
       <c r="B98" s="18"/>
       <c r="C98" s="17"/>
@@ -13033,8 +13281,10 @@
       <c r="J98" s="17"/>
       <c r="K98" s="17"/>
       <c r="L98" s="17"/>
-    </row>
-    <row r="99" spans="1:12">
+      <c r="M98" s="17"/>
+      <c r="N98" s="17"/>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99" s="17"/>
       <c r="B99" s="18"/>
       <c r="C99" s="17"/>
@@ -13047,8 +13297,10 @@
       <c r="J99" s="17"/>
       <c r="K99" s="17"/>
       <c r="L99" s="17"/>
-    </row>
-    <row r="100" spans="1:12">
+      <c r="M99" s="17"/>
+      <c r="N99" s="17"/>
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100" s="17"/>
       <c r="B100" s="18"/>
       <c r="C100" s="17"/>
@@ -13061,8 +13313,10 @@
       <c r="J100" s="17"/>
       <c r="K100" s="17"/>
       <c r="L100" s="17"/>
-    </row>
-    <row r="101" spans="1:12">
+      <c r="M100" s="17"/>
+      <c r="N100" s="17"/>
+    </row>
+    <row r="101" spans="1:14">
       <c r="A101" s="17"/>
       <c r="B101" s="18"/>
       <c r="C101" s="17"/>
@@ -13075,8 +13329,10 @@
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
       <c r="L101" s="17"/>
-    </row>
-    <row r="102" spans="1:12">
+      <c r="M101" s="17"/>
+      <c r="N101" s="17"/>
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102" s="17"/>
       <c r="B102" s="18"/>
       <c r="C102" s="17"/>
@@ -13089,8 +13345,10 @@
       <c r="J102" s="17"/>
       <c r="K102" s="17"/>
       <c r="L102" s="17"/>
-    </row>
-    <row r="103" spans="1:12">
+      <c r="M102" s="17"/>
+      <c r="N102" s="17"/>
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103" s="17"/>
       <c r="B103" s="18"/>
       <c r="C103" s="17"/>
@@ -13103,8 +13361,10 @@
       <c r="J103" s="17"/>
       <c r="K103" s="17"/>
       <c r="L103" s="17"/>
-    </row>
-    <row r="104" spans="1:12">
+      <c r="M103" s="17"/>
+      <c r="N103" s="17"/>
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104" s="17"/>
       <c r="B104" s="18"/>
       <c r="C104" s="17"/>
@@ -13117,8 +13377,10 @@
       <c r="J104" s="17"/>
       <c r="K104" s="17"/>
       <c r="L104" s="17"/>
-    </row>
-    <row r="105" spans="1:12">
+      <c r="M104" s="17"/>
+      <c r="N104" s="17"/>
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105" s="17"/>
       <c r="B105" s="18"/>
       <c r="C105" s="17"/>
@@ -13131,8 +13393,10 @@
       <c r="J105" s="17"/>
       <c r="K105" s="17"/>
       <c r="L105" s="17"/>
-    </row>
-    <row r="106" spans="1:12">
+      <c r="M105" s="17"/>
+      <c r="N105" s="17"/>
+    </row>
+    <row r="106" spans="1:14">
       <c r="A106" s="17"/>
       <c r="B106" s="18"/>
       <c r="C106" s="17"/>
@@ -13145,8 +13409,10 @@
       <c r="J106" s="17"/>
       <c r="K106" s="17"/>
       <c r="L106" s="17"/>
-    </row>
-    <row r="107" spans="1:12">
+      <c r="M106" s="17"/>
+      <c r="N106" s="17"/>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107" s="17"/>
       <c r="B107" s="18"/>
       <c r="C107" s="17"/>
@@ -13159,8 +13425,10 @@
       <c r="J107" s="17"/>
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
-    </row>
-    <row r="108" spans="1:12">
+      <c r="M107" s="17"/>
+      <c r="N107" s="17"/>
+    </row>
+    <row r="108" spans="1:14">
       <c r="A108" s="17"/>
       <c r="B108" s="18"/>
       <c r="C108" s="17"/>
@@ -13173,8 +13441,10 @@
       <c r="J108" s="17"/>
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
-    </row>
-    <row r="109" spans="1:12">
+      <c r="M108" s="17"/>
+      <c r="N108" s="17"/>
+    </row>
+    <row r="109" spans="1:14">
       <c r="A109" s="17"/>
       <c r="B109" s="18"/>
       <c r="C109" s="17"/>
@@ -13187,8 +13457,10 @@
       <c r="J109" s="17"/>
       <c r="K109" s="17"/>
       <c r="L109" s="17"/>
-    </row>
-    <row r="110" spans="1:12">
+      <c r="M109" s="17"/>
+      <c r="N109" s="17"/>
+    </row>
+    <row r="110" spans="1:14">
       <c r="A110" s="17"/>
       <c r="B110" s="18"/>
       <c r="C110" s="17"/>
@@ -13201,8 +13473,10 @@
       <c r="J110" s="17"/>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
-    </row>
-    <row r="111" spans="1:12">
+      <c r="M110" s="17"/>
+      <c r="N110" s="17"/>
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111" s="17"/>
       <c r="B111" s="18"/>
       <c r="C111" s="17"/>
@@ -13215,8 +13489,10 @@
       <c r="J111" s="17"/>
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
-    </row>
-    <row r="112" spans="1:12">
+      <c r="M111" s="17"/>
+      <c r="N111" s="17"/>
+    </row>
+    <row r="112" spans="1:14">
       <c r="A112" s="17"/>
       <c r="B112" s="18"/>
       <c r="C112" s="17"/>
@@ -13229,8 +13505,10 @@
       <c r="J112" s="17"/>
       <c r="K112" s="17"/>
       <c r="L112" s="17"/>
-    </row>
-    <row r="113" spans="1:12">
+      <c r="M112" s="17"/>
+      <c r="N112" s="17"/>
+    </row>
+    <row r="113" spans="1:14">
       <c r="A113" s="17"/>
       <c r="B113" s="18"/>
       <c r="C113" s="17"/>
@@ -13243,8 +13521,10 @@
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
       <c r="L113" s="17"/>
-    </row>
-    <row r="114" spans="1:12">
+      <c r="M113" s="17"/>
+      <c r="N113" s="17"/>
+    </row>
+    <row r="114" spans="1:14">
       <c r="A114" s="17"/>
       <c r="B114" s="18"/>
       <c r="C114" s="17"/>
@@ -13257,8 +13537,10 @@
       <c r="J114" s="17"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
-    </row>
-    <row r="115" spans="1:12">
+      <c r="M114" s="17"/>
+      <c r="N114" s="17"/>
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115" s="17"/>
       <c r="B115" s="18"/>
       <c r="C115" s="17"/>
@@ -13271,8 +13553,10 @@
       <c r="J115" s="17"/>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
-    </row>
-    <row r="116" spans="1:12">
+      <c r="M115" s="17"/>
+      <c r="N115" s="17"/>
+    </row>
+    <row r="116" spans="1:14">
       <c r="A116" s="17"/>
       <c r="B116" s="18"/>
       <c r="C116" s="17"/>
@@ -13285,8 +13569,10 @@
       <c r="J116" s="17"/>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
-    </row>
-    <row r="117" spans="1:12">
+      <c r="M116" s="17"/>
+      <c r="N116" s="17"/>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117" s="17"/>
       <c r="B117" s="18"/>
       <c r="C117" s="17"/>
@@ -13299,8 +13585,10 @@
       <c r="J117" s="17"/>
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
-    </row>
-    <row r="118" spans="1:12">
+      <c r="M117" s="17"/>
+      <c r="N117" s="17"/>
+    </row>
+    <row r="118" spans="1:14">
       <c r="A118" s="17"/>
       <c r="B118" s="18"/>
       <c r="C118" s="17"/>
@@ -13313,8 +13601,10 @@
       <c r="J118" s="17"/>
       <c r="K118" s="17"/>
       <c r="L118" s="17"/>
-    </row>
-    <row r="119" spans="1:12">
+      <c r="M118" s="17"/>
+      <c r="N118" s="17"/>
+    </row>
+    <row r="119" spans="1:14">
       <c r="A119" s="17"/>
       <c r="B119" s="18"/>
       <c r="C119" s="17"/>
@@ -13327,8 +13617,10 @@
       <c r="J119" s="17"/>
       <c r="K119" s="17"/>
       <c r="L119" s="17"/>
-    </row>
-    <row r="120" spans="1:12">
+      <c r="M119" s="17"/>
+      <c r="N119" s="17"/>
+    </row>
+    <row r="120" spans="1:14">
       <c r="A120" s="17"/>
       <c r="B120" s="18"/>
       <c r="C120" s="17"/>
@@ -13341,8 +13633,10 @@
       <c r="J120" s="17"/>
       <c r="K120" s="17"/>
       <c r="L120" s="17"/>
-    </row>
-    <row r="121" spans="1:12">
+      <c r="M120" s="17"/>
+      <c r="N120" s="17"/>
+    </row>
+    <row r="121" spans="1:14">
       <c r="A121" s="17"/>
       <c r="B121" s="18"/>
       <c r="C121" s="17"/>
@@ -13355,8 +13649,10 @@
       <c r="J121" s="17"/>
       <c r="K121" s="17"/>
       <c r="L121" s="17"/>
-    </row>
-    <row r="122" spans="1:12">
+      <c r="M121" s="17"/>
+      <c r="N121" s="17"/>
+    </row>
+    <row r="122" spans="1:14">
       <c r="A122" s="17"/>
       <c r="B122" s="18"/>
       <c r="C122" s="17"/>
@@ -13369,8 +13665,10 @@
       <c r="J122" s="17"/>
       <c r="K122" s="17"/>
       <c r="L122" s="17"/>
-    </row>
-    <row r="123" spans="1:12">
+      <c r="M122" s="17"/>
+      <c r="N122" s="17"/>
+    </row>
+    <row r="123" spans="1:14">
       <c r="A123" s="17"/>
       <c r="B123" s="18"/>
       <c r="C123" s="17"/>
@@ -13383,8 +13681,10 @@
       <c r="J123" s="17"/>
       <c r="K123" s="17"/>
       <c r="L123" s="17"/>
-    </row>
-    <row r="124" spans="1:12">
+      <c r="M123" s="17"/>
+      <c r="N123" s="17"/>
+    </row>
+    <row r="124" spans="1:14">
       <c r="A124" s="17"/>
       <c r="B124" s="18"/>
       <c r="C124" s="17"/>
@@ -13397,8 +13697,10 @@
       <c r="J124" s="17"/>
       <c r="K124" s="17"/>
       <c r="L124" s="17"/>
-    </row>
-    <row r="125" spans="1:12">
+      <c r="M124" s="17"/>
+      <c r="N124" s="17"/>
+    </row>
+    <row r="125" spans="1:14">
       <c r="A125" s="17"/>
       <c r="B125" s="18"/>
       <c r="C125" s="17"/>
@@ -13411,8 +13713,10 @@
       <c r="J125" s="17"/>
       <c r="K125" s="17"/>
       <c r="L125" s="17"/>
-    </row>
-    <row r="126" spans="1:12">
+      <c r="M125" s="17"/>
+      <c r="N125" s="17"/>
+    </row>
+    <row r="126" spans="1:14">
       <c r="A126" s="17"/>
       <c r="B126" s="18"/>
       <c r="C126" s="17"/>
@@ -13425,8 +13729,10 @@
       <c r="J126" s="17"/>
       <c r="K126" s="17"/>
       <c r="L126" s="17"/>
-    </row>
-    <row r="127" spans="1:12">
+      <c r="M126" s="17"/>
+      <c r="N126" s="17"/>
+    </row>
+    <row r="127" spans="1:14">
       <c r="A127" s="17"/>
       <c r="B127" s="18"/>
       <c r="C127" s="17"/>
@@ -13439,8 +13745,10 @@
       <c r="J127" s="17"/>
       <c r="K127" s="17"/>
       <c r="L127" s="17"/>
-    </row>
-    <row r="128" spans="1:12">
+      <c r="M127" s="17"/>
+      <c r="N127" s="17"/>
+    </row>
+    <row r="128" spans="1:14">
       <c r="A128" s="17"/>
       <c r="B128" s="18"/>
       <c r="C128" s="17"/>
@@ -13453,8 +13761,10 @@
       <c r="J128" s="17"/>
       <c r="K128" s="17"/>
       <c r="L128" s="17"/>
-    </row>
-    <row r="129" spans="1:12">
+      <c r="M128" s="17"/>
+      <c r="N128" s="17"/>
+    </row>
+    <row r="129" spans="1:14">
       <c r="A129" s="17"/>
       <c r="B129" s="18"/>
       <c r="C129" s="17"/>
@@ -13467,8 +13777,10 @@
       <c r="J129" s="17"/>
       <c r="K129" s="17"/>
       <c r="L129" s="17"/>
-    </row>
-    <row r="130" spans="1:12">
+      <c r="M129" s="17"/>
+      <c r="N129" s="17"/>
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130" s="17"/>
       <c r="B130" s="18"/>
       <c r="C130" s="17"/>
@@ -13481,8 +13793,10 @@
       <c r="J130" s="17"/>
       <c r="K130" s="17"/>
       <c r="L130" s="17"/>
-    </row>
-    <row r="131" spans="1:12">
+      <c r="M130" s="17"/>
+      <c r="N130" s="17"/>
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131" s="17"/>
       <c r="B131" s="18"/>
       <c r="C131" s="17"/>
@@ -13495,8 +13809,10 @@
       <c r="J131" s="17"/>
       <c r="K131" s="17"/>
       <c r="L131" s="17"/>
-    </row>
-    <row r="132" spans="1:12">
+      <c r="M131" s="17"/>
+      <c r="N131" s="17"/>
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132" s="17"/>
       <c r="B132" s="18"/>
       <c r="C132" s="17"/>
@@ -13509,8 +13825,10 @@
       <c r="J132" s="17"/>
       <c r="K132" s="17"/>
       <c r="L132" s="17"/>
-    </row>
-    <row r="133" spans="1:12">
+      <c r="M132" s="17"/>
+      <c r="N132" s="17"/>
+    </row>
+    <row r="133" spans="1:14">
       <c r="A133" s="17"/>
       <c r="B133" s="18"/>
       <c r="C133" s="17"/>
@@ -13523,8 +13841,10 @@
       <c r="J133" s="17"/>
       <c r="K133" s="17"/>
       <c r="L133" s="17"/>
-    </row>
-    <row r="134" spans="1:12">
+      <c r="M133" s="17"/>
+      <c r="N133" s="17"/>
+    </row>
+    <row r="134" spans="1:14">
       <c r="A134" s="17"/>
       <c r="B134" s="18"/>
       <c r="C134" s="17"/>
@@ -13537,8 +13857,10 @@
       <c r="J134" s="17"/>
       <c r="K134" s="17"/>
       <c r="L134" s="17"/>
-    </row>
-    <row r="135" spans="1:12">
+      <c r="M134" s="17"/>
+      <c r="N134" s="17"/>
+    </row>
+    <row r="135" spans="1:14">
       <c r="A135" s="17"/>
       <c r="B135" s="18"/>
       <c r="C135" s="17"/>
@@ -13551,8 +13873,10 @@
       <c r="J135" s="17"/>
       <c r="K135" s="17"/>
       <c r="L135" s="17"/>
-    </row>
-    <row r="136" spans="1:12">
+      <c r="M135" s="17"/>
+      <c r="N135" s="17"/>
+    </row>
+    <row r="136" spans="1:14">
       <c r="A136" s="17"/>
       <c r="B136" s="18"/>
       <c r="C136" s="17"/>
@@ -13565,8 +13889,10 @@
       <c r="J136" s="17"/>
       <c r="K136" s="17"/>
       <c r="L136" s="17"/>
-    </row>
-    <row r="137" spans="1:12">
+      <c r="M136" s="17"/>
+      <c r="N136" s="17"/>
+    </row>
+    <row r="137" spans="1:14">
       <c r="A137" s="17"/>
       <c r="B137" s="18"/>
       <c r="C137" s="17"/>
@@ -13579,8 +13905,10 @@
       <c r="J137" s="17"/>
       <c r="K137" s="17"/>
       <c r="L137" s="17"/>
-    </row>
-    <row r="138" spans="1:12">
+      <c r="M137" s="17"/>
+      <c r="N137" s="17"/>
+    </row>
+    <row r="138" spans="1:14">
       <c r="A138" s="17"/>
       <c r="B138" s="18"/>
       <c r="C138" s="17"/>
@@ -13593,8 +13921,10 @@
       <c r="J138" s="17"/>
       <c r="K138" s="17"/>
       <c r="L138" s="17"/>
-    </row>
-    <row r="139" spans="1:12">
+      <c r="M138" s="17"/>
+      <c r="N138" s="17"/>
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139" s="17"/>
       <c r="B139" s="18"/>
       <c r="C139" s="17"/>
@@ -13607,8 +13937,10 @@
       <c r="J139" s="17"/>
       <c r="K139" s="17"/>
       <c r="L139" s="17"/>
-    </row>
-    <row r="140" spans="1:12">
+      <c r="M139" s="17"/>
+      <c r="N139" s="17"/>
+    </row>
+    <row r="140" spans="1:14">
       <c r="A140" s="17"/>
       <c r="B140" s="18"/>
       <c r="C140" s="17"/>
@@ -13621,8 +13953,10 @@
       <c r="J140" s="17"/>
       <c r="K140" s="17"/>
       <c r="L140" s="17"/>
-    </row>
-    <row r="141" spans="1:12">
+      <c r="M140" s="17"/>
+      <c r="N140" s="17"/>
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141" s="17"/>
       <c r="B141" s="18"/>
       <c r="C141" s="17"/>
@@ -13635,8 +13969,10 @@
       <c r="J141" s="17"/>
       <c r="K141" s="17"/>
       <c r="L141" s="17"/>
-    </row>
-    <row r="142" spans="1:12">
+      <c r="M141" s="17"/>
+      <c r="N141" s="17"/>
+    </row>
+    <row r="142" spans="1:14">
       <c r="A142" s="17"/>
       <c r="B142" s="18"/>
       <c r="C142" s="17"/>
@@ -13649,8 +13985,10 @@
       <c r="J142" s="17"/>
       <c r="K142" s="17"/>
       <c r="L142" s="17"/>
-    </row>
-    <row r="143" spans="1:12">
+      <c r="M142" s="17"/>
+      <c r="N142" s="17"/>
+    </row>
+    <row r="143" spans="1:14">
       <c r="A143" s="17"/>
       <c r="B143" s="18"/>
       <c r="C143" s="17"/>
@@ -13663,8 +14001,10 @@
       <c r="J143" s="17"/>
       <c r="K143" s="17"/>
       <c r="L143" s="17"/>
-    </row>
-    <row r="144" spans="1:12">
+      <c r="M143" s="17"/>
+      <c r="N143" s="17"/>
+    </row>
+    <row r="144" spans="1:14">
       <c r="A144" s="17"/>
       <c r="B144" s="18"/>
       <c r="C144" s="17"/>
@@ -13677,8 +14017,10 @@
       <c r="J144" s="17"/>
       <c r="K144" s="17"/>
       <c r="L144" s="17"/>
-    </row>
-    <row r="145" spans="1:12">
+      <c r="M144" s="17"/>
+      <c r="N144" s="17"/>
+    </row>
+    <row r="145" spans="1:14">
       <c r="A145" s="17"/>
       <c r="B145" s="18"/>
       <c r="C145" s="17"/>
@@ -13691,8 +14033,10 @@
       <c r="J145" s="17"/>
       <c r="K145" s="17"/>
       <c r="L145" s="17"/>
-    </row>
-    <row r="146" spans="1:12">
+      <c r="M145" s="17"/>
+      <c r="N145" s="17"/>
+    </row>
+    <row r="146" spans="1:14">
       <c r="A146" s="17"/>
       <c r="B146" s="18"/>
       <c r="C146" s="17"/>
@@ -13705,8 +14049,10 @@
       <c r="J146" s="17"/>
       <c r="K146" s="17"/>
       <c r="L146" s="17"/>
-    </row>
-    <row r="147" spans="1:12">
+      <c r="M146" s="17"/>
+      <c r="N146" s="17"/>
+    </row>
+    <row r="147" spans="1:14">
       <c r="A147" s="17"/>
       <c r="B147" s="18"/>
       <c r="C147" s="17"/>
@@ -13719,8 +14065,10 @@
       <c r="J147" s="17"/>
       <c r="K147" s="17"/>
       <c r="L147" s="17"/>
-    </row>
-    <row r="148" spans="1:12">
+      <c r="M147" s="17"/>
+      <c r="N147" s="17"/>
+    </row>
+    <row r="148" spans="1:14">
       <c r="A148" s="17"/>
       <c r="B148" s="18"/>
       <c r="C148" s="17"/>
@@ -13733,8 +14081,10 @@
       <c r="J148" s="17"/>
       <c r="K148" s="17"/>
       <c r="L148" s="17"/>
-    </row>
-    <row r="149" spans="1:12">
+      <c r="M148" s="17"/>
+      <c r="N148" s="17"/>
+    </row>
+    <row r="149" spans="1:14">
       <c r="A149" s="17"/>
       <c r="B149" s="18"/>
       <c r="C149" s="17"/>
@@ -13747,8 +14097,10 @@
       <c r="J149" s="17"/>
       <c r="K149" s="17"/>
       <c r="L149" s="17"/>
-    </row>
-    <row r="150" spans="1:12">
+      <c r="M149" s="17"/>
+      <c r="N149" s="17"/>
+    </row>
+    <row r="150" spans="1:14">
       <c r="A150" s="17"/>
       <c r="B150" s="18"/>
       <c r="C150" s="17"/>
@@ -13761,8 +14113,10 @@
       <c r="J150" s="17"/>
       <c r="K150" s="17"/>
       <c r="L150" s="17"/>
-    </row>
-    <row r="151" spans="1:12">
+      <c r="M150" s="17"/>
+      <c r="N150" s="17"/>
+    </row>
+    <row r="151" spans="1:14">
       <c r="A151" s="17"/>
       <c r="B151" s="18"/>
       <c r="C151" s="17"/>
@@ -13775,8 +14129,10 @@
       <c r="J151" s="17"/>
       <c r="K151" s="17"/>
       <c r="L151" s="17"/>
-    </row>
-    <row r="152" spans="1:12">
+      <c r="M151" s="17"/>
+      <c r="N151" s="17"/>
+    </row>
+    <row r="152" spans="1:14">
       <c r="A152" s="17"/>
       <c r="B152" s="18"/>
       <c r="C152" s="17"/>
@@ -13789,8 +14145,10 @@
       <c r="J152" s="17"/>
       <c r="K152" s="17"/>
       <c r="L152" s="17"/>
-    </row>
-    <row r="153" spans="1:12">
+      <c r="M152" s="17"/>
+      <c r="N152" s="17"/>
+    </row>
+    <row r="153" spans="1:14">
       <c r="A153" s="17"/>
       <c r="B153" s="18"/>
       <c r="C153" s="17"/>
@@ -13803,8 +14161,10 @@
       <c r="J153" s="17"/>
       <c r="K153" s="17"/>
       <c r="L153" s="17"/>
-    </row>
-    <row r="154" spans="1:12">
+      <c r="M153" s="17"/>
+      <c r="N153" s="17"/>
+    </row>
+    <row r="154" spans="1:14">
       <c r="A154" s="17"/>
       <c r="B154" s="18"/>
       <c r="C154" s="17"/>
@@ -13817,8 +14177,10 @@
       <c r="J154" s="17"/>
       <c r="K154" s="17"/>
       <c r="L154" s="17"/>
-    </row>
-    <row r="155" spans="1:12">
+      <c r="M154" s="17"/>
+      <c r="N154" s="17"/>
+    </row>
+    <row r="155" spans="1:14">
       <c r="A155" s="17"/>
       <c r="B155" s="18"/>
       <c r="C155" s="17"/>
@@ -13831,8 +14193,10 @@
       <c r="J155" s="17"/>
       <c r="K155" s="17"/>
       <c r="L155" s="17"/>
-    </row>
-    <row r="156" spans="1:12">
+      <c r="M155" s="17"/>
+      <c r="N155" s="17"/>
+    </row>
+    <row r="156" spans="1:14">
       <c r="A156" s="17"/>
       <c r="B156" s="18"/>
       <c r="C156" s="17"/>
@@ -13845,8 +14209,10 @@
       <c r="J156" s="17"/>
       <c r="K156" s="17"/>
       <c r="L156" s="17"/>
-    </row>
-    <row r="157" spans="1:12">
+      <c r="M156" s="17"/>
+      <c r="N156" s="17"/>
+    </row>
+    <row r="157" spans="1:14">
       <c r="A157" s="17"/>
       <c r="B157" s="18"/>
       <c r="C157" s="17"/>
@@ -13859,8 +14225,10 @@
       <c r="J157" s="17"/>
       <c r="K157" s="17"/>
       <c r="L157" s="17"/>
-    </row>
-    <row r="158" spans="1:12">
+      <c r="M157" s="17"/>
+      <c r="N157" s="17"/>
+    </row>
+    <row r="158" spans="1:14">
       <c r="A158" s="17"/>
       <c r="B158" s="18"/>
       <c r="C158" s="17"/>
@@ -13873,8 +14241,10 @@
       <c r="J158" s="17"/>
       <c r="K158" s="17"/>
       <c r="L158" s="17"/>
-    </row>
-    <row r="159" spans="1:12">
+      <c r="M158" s="17"/>
+      <c r="N158" s="17"/>
+    </row>
+    <row r="159" spans="1:14">
       <c r="A159" s="17"/>
       <c r="B159" s="18"/>
       <c r="C159" s="17"/>
@@ -13887,8 +14257,10 @@
       <c r="J159" s="17"/>
       <c r="K159" s="17"/>
       <c r="L159" s="17"/>
-    </row>
-    <row r="160" spans="1:12">
+      <c r="M159" s="17"/>
+      <c r="N159" s="17"/>
+    </row>
+    <row r="160" spans="1:14">
       <c r="A160" s="17"/>
       <c r="B160" s="18"/>
       <c r="C160" s="17"/>
@@ -13901,8 +14273,10 @@
       <c r="J160" s="17"/>
       <c r="K160" s="17"/>
       <c r="L160" s="17"/>
-    </row>
-    <row r="161" spans="1:12">
+      <c r="M160" s="17"/>
+      <c r="N160" s="17"/>
+    </row>
+    <row r="161" spans="1:14">
       <c r="A161" s="17"/>
       <c r="B161" s="18"/>
       <c r="C161" s="17"/>
@@ -13915,8 +14289,10 @@
       <c r="J161" s="17"/>
       <c r="K161" s="17"/>
       <c r="L161" s="17"/>
-    </row>
-    <row r="162" spans="1:12">
+      <c r="M161" s="17"/>
+      <c r="N161" s="17"/>
+    </row>
+    <row r="162" spans="1:14">
       <c r="A162" s="17"/>
       <c r="B162" s="18"/>
       <c r="C162" s="17"/>
@@ -13929,8 +14305,10 @@
       <c r="J162" s="17"/>
       <c r="K162" s="17"/>
       <c r="L162" s="17"/>
-    </row>
-    <row r="163" spans="1:12">
+      <c r="M162" s="17"/>
+      <c r="N162" s="17"/>
+    </row>
+    <row r="163" spans="1:14">
       <c r="A163" s="17"/>
       <c r="B163" s="18"/>
       <c r="C163" s="17"/>
@@ -13943,8 +14321,10 @@
       <c r="J163" s="17"/>
       <c r="K163" s="17"/>
       <c r="L163" s="17"/>
-    </row>
-    <row r="164" spans="1:12">
+      <c r="M163" s="17"/>
+      <c r="N163" s="17"/>
+    </row>
+    <row r="164" spans="1:14">
       <c r="A164" s="17"/>
       <c r="B164" s="18"/>
       <c r="C164" s="17"/>
@@ -13957,8 +14337,10 @@
       <c r="J164" s="17"/>
       <c r="K164" s="17"/>
       <c r="L164" s="17"/>
-    </row>
-    <row r="165" spans="1:12">
+      <c r="M164" s="17"/>
+      <c r="N164" s="17"/>
+    </row>
+    <row r="165" spans="1:14">
       <c r="A165" s="17"/>
       <c r="B165" s="18"/>
       <c r="C165" s="17"/>
@@ -13971,8 +14353,10 @@
       <c r="J165" s="17"/>
       <c r="K165" s="17"/>
       <c r="L165" s="17"/>
-    </row>
-    <row r="166" spans="1:12">
+      <c r="M165" s="17"/>
+      <c r="N165" s="17"/>
+    </row>
+    <row r="166" spans="1:14">
       <c r="A166" s="17"/>
       <c r="B166" s="18"/>
       <c r="C166" s="17"/>
@@ -13985,8 +14369,10 @@
       <c r="J166" s="17"/>
       <c r="K166" s="17"/>
       <c r="L166" s="17"/>
-    </row>
-    <row r="167" spans="1:12">
+      <c r="M166" s="17"/>
+      <c r="N166" s="17"/>
+    </row>
+    <row r="167" spans="1:14">
       <c r="A167" s="17"/>
       <c r="B167" s="18"/>
       <c r="C167" s="17"/>
@@ -13999,8 +14385,10 @@
       <c r="J167" s="17"/>
       <c r="K167" s="17"/>
       <c r="L167" s="17"/>
-    </row>
-    <row r="168" spans="1:12">
+      <c r="M167" s="17"/>
+      <c r="N167" s="17"/>
+    </row>
+    <row r="168" spans="1:14">
       <c r="A168" s="17"/>
       <c r="B168" s="18"/>
       <c r="C168" s="17"/>
@@ -14013,8 +14401,10 @@
       <c r="J168" s="17"/>
       <c r="K168" s="17"/>
       <c r="L168" s="17"/>
-    </row>
-    <row r="169" spans="1:12">
+      <c r="M168" s="17"/>
+      <c r="N168" s="17"/>
+    </row>
+    <row r="169" spans="1:14">
       <c r="A169" s="17"/>
       <c r="B169" s="18"/>
       <c r="C169" s="17"/>
@@ -14027,8 +14417,10 @@
       <c r="J169" s="17"/>
       <c r="K169" s="17"/>
       <c r="L169" s="17"/>
-    </row>
-    <row r="170" spans="1:12">
+      <c r="M169" s="17"/>
+      <c r="N169" s="17"/>
+    </row>
+    <row r="170" spans="1:14">
       <c r="A170" s="17"/>
       <c r="B170" s="18"/>
       <c r="C170" s="17"/>
@@ -14041,8 +14433,10 @@
       <c r="J170" s="17"/>
       <c r="K170" s="17"/>
       <c r="L170" s="17"/>
-    </row>
-    <row r="171" spans="1:12">
+      <c r="M170" s="17"/>
+      <c r="N170" s="17"/>
+    </row>
+    <row r="171" spans="1:14">
       <c r="A171" s="17"/>
       <c r="B171" s="18"/>
       <c r="C171" s="17"/>
@@ -14055,8 +14449,10 @@
       <c r="J171" s="17"/>
       <c r="K171" s="17"/>
       <c r="L171" s="17"/>
-    </row>
-    <row r="172" spans="1:12">
+      <c r="M171" s="17"/>
+      <c r="N171" s="17"/>
+    </row>
+    <row r="172" spans="1:14">
       <c r="A172" s="17"/>
       <c r="B172" s="18"/>
       <c r="C172" s="17"/>
@@ -14069,8 +14465,10 @@
       <c r="J172" s="17"/>
       <c r="K172" s="17"/>
       <c r="L172" s="17"/>
-    </row>
-    <row r="173" spans="1:12">
+      <c r="M172" s="17"/>
+      <c r="N172" s="17"/>
+    </row>
+    <row r="173" spans="1:14">
       <c r="A173" s="17"/>
       <c r="B173" s="18"/>
       <c r="C173" s="17"/>
@@ -14083,8 +14481,10 @@
       <c r="J173" s="17"/>
       <c r="K173" s="17"/>
       <c r="L173" s="17"/>
-    </row>
-    <row r="174" spans="1:12">
+      <c r="M173" s="17"/>
+      <c r="N173" s="17"/>
+    </row>
+    <row r="174" spans="1:14">
       <c r="A174" s="17"/>
       <c r="B174" s="18"/>
       <c r="C174" s="17"/>
@@ -14097,8 +14497,10 @@
       <c r="J174" s="17"/>
       <c r="K174" s="17"/>
       <c r="L174" s="17"/>
-    </row>
-    <row r="175" spans="1:12">
+      <c r="M174" s="17"/>
+      <c r="N174" s="17"/>
+    </row>
+    <row r="175" spans="1:14">
       <c r="A175" s="17"/>
       <c r="B175" s="18"/>
       <c r="C175" s="17"/>
@@ -14111,8 +14513,10 @@
       <c r="J175" s="17"/>
       <c r="K175" s="17"/>
       <c r="L175" s="17"/>
-    </row>
-    <row r="176" spans="1:12">
+      <c r="M175" s="17"/>
+      <c r="N175" s="17"/>
+    </row>
+    <row r="176" spans="1:14">
       <c r="A176" s="17"/>
       <c r="B176" s="18"/>
       <c r="C176" s="17"/>
@@ -14125,8 +14529,10 @@
       <c r="J176" s="17"/>
       <c r="K176" s="17"/>
       <c r="L176" s="17"/>
-    </row>
-    <row r="177" spans="1:12">
+      <c r="M176" s="17"/>
+      <c r="N176" s="17"/>
+    </row>
+    <row r="177" spans="1:14">
       <c r="A177" s="17"/>
       <c r="B177" s="18"/>
       <c r="C177" s="17"/>
@@ -14139,8 +14545,10 @@
       <c r="J177" s="17"/>
       <c r="K177" s="17"/>
       <c r="L177" s="17"/>
-    </row>
-    <row r="178" spans="1:12">
+      <c r="M177" s="17"/>
+      <c r="N177" s="17"/>
+    </row>
+    <row r="178" spans="1:14">
       <c r="A178" s="17"/>
       <c r="B178" s="18"/>
       <c r="C178" s="17"/>
@@ -14153,8 +14561,10 @@
       <c r="J178" s="17"/>
       <c r="K178" s="17"/>
       <c r="L178" s="17"/>
-    </row>
-    <row r="179" spans="1:12">
+      <c r="M178" s="17"/>
+      <c r="N178" s="17"/>
+    </row>
+    <row r="179" spans="1:14">
       <c r="A179" s="17"/>
       <c r="B179" s="18"/>
       <c r="C179" s="17"/>
@@ -14167,8 +14577,10 @@
       <c r="J179" s="17"/>
       <c r="K179" s="17"/>
       <c r="L179" s="17"/>
-    </row>
-    <row r="180" spans="1:12">
+      <c r="M179" s="17"/>
+      <c r="N179" s="17"/>
+    </row>
+    <row r="180" spans="1:14">
       <c r="A180" s="17"/>
       <c r="B180" s="18"/>
       <c r="C180" s="17"/>
@@ -14181,8 +14593,10 @@
       <c r="J180" s="17"/>
       <c r="K180" s="17"/>
       <c r="L180" s="17"/>
-    </row>
-    <row r="181" spans="1:12">
+      <c r="M180" s="17"/>
+      <c r="N180" s="17"/>
+    </row>
+    <row r="181" spans="1:14">
       <c r="A181" s="17"/>
       <c r="B181" s="18"/>
       <c r="C181" s="17"/>
@@ -14195,8 +14609,10 @@
       <c r="J181" s="17"/>
       <c r="K181" s="17"/>
       <c r="L181" s="17"/>
-    </row>
-    <row r="182" spans="1:12">
+      <c r="M181" s="17"/>
+      <c r="N181" s="17"/>
+    </row>
+    <row r="182" spans="1:14">
       <c r="A182" s="17"/>
       <c r="B182" s="18"/>
       <c r="C182" s="17"/>
@@ -14209,8 +14625,10 @@
       <c r="J182" s="17"/>
       <c r="K182" s="17"/>
       <c r="L182" s="17"/>
-    </row>
-    <row r="183" spans="1:12">
+      <c r="M182" s="17"/>
+      <c r="N182" s="17"/>
+    </row>
+    <row r="183" spans="1:14">
       <c r="A183" s="17"/>
       <c r="B183" s="18"/>
       <c r="C183" s="17"/>
@@ -14223,8 +14641,10 @@
       <c r="J183" s="17"/>
       <c r="K183" s="17"/>
       <c r="L183" s="17"/>
-    </row>
-    <row r="184" spans="1:12">
+      <c r="M183" s="17"/>
+      <c r="N183" s="17"/>
+    </row>
+    <row r="184" spans="1:14">
       <c r="A184" s="17"/>
       <c r="B184" s="18"/>
       <c r="C184" s="17"/>
@@ -14237,8 +14657,10 @@
       <c r="J184" s="17"/>
       <c r="K184" s="17"/>
       <c r="L184" s="17"/>
-    </row>
-    <row r="185" spans="1:12">
+      <c r="M184" s="17"/>
+      <c r="N184" s="17"/>
+    </row>
+    <row r="185" spans="1:14">
       <c r="A185" s="17"/>
       <c r="B185" s="18"/>
       <c r="C185" s="17"/>
@@ -14251,8 +14673,10 @@
       <c r="J185" s="17"/>
       <c r="K185" s="17"/>
       <c r="L185" s="17"/>
-    </row>
-    <row r="186" spans="1:12">
+      <c r="M185" s="17"/>
+      <c r="N185" s="17"/>
+    </row>
+    <row r="186" spans="1:14">
       <c r="A186" s="17"/>
       <c r="B186" s="18"/>
       <c r="C186" s="17"/>
@@ -14265,8 +14689,10 @@
       <c r="J186" s="17"/>
       <c r="K186" s="17"/>
       <c r="L186" s="17"/>
-    </row>
-    <row r="187" spans="1:12">
+      <c r="M186" s="17"/>
+      <c r="N186" s="17"/>
+    </row>
+    <row r="187" spans="1:14">
       <c r="A187" s="17"/>
       <c r="B187" s="18"/>
       <c r="C187" s="17"/>
@@ -14279,8 +14705,10 @@
       <c r="J187" s="17"/>
       <c r="K187" s="17"/>
       <c r="L187" s="17"/>
-    </row>
-    <row r="188" spans="1:12">
+      <c r="M187" s="17"/>
+      <c r="N187" s="17"/>
+    </row>
+    <row r="188" spans="1:14">
       <c r="A188" s="17"/>
       <c r="B188" s="18"/>
       <c r="C188" s="17"/>
@@ -14293,8 +14721,10 @@
       <c r="J188" s="17"/>
       <c r="K188" s="17"/>
       <c r="L188" s="17"/>
-    </row>
-    <row r="189" spans="1:12">
+      <c r="M188" s="17"/>
+      <c r="N188" s="17"/>
+    </row>
+    <row r="189" spans="1:14">
       <c r="A189" s="17"/>
       <c r="B189" s="18"/>
       <c r="C189" s="17"/>
@@ -14307,8 +14737,10 @@
       <c r="J189" s="17"/>
       <c r="K189" s="17"/>
       <c r="L189" s="17"/>
-    </row>
-    <row r="190" spans="1:12">
+      <c r="M189" s="17"/>
+      <c r="N189" s="17"/>
+    </row>
+    <row r="190" spans="1:14">
       <c r="A190" s="17"/>
       <c r="B190" s="18"/>
       <c r="C190" s="17"/>
@@ -14321,8 +14753,10 @@
       <c r="J190" s="17"/>
       <c r="K190" s="17"/>
       <c r="L190" s="17"/>
-    </row>
-    <row r="191" spans="1:12">
+      <c r="M190" s="17"/>
+      <c r="N190" s="17"/>
+    </row>
+    <row r="191" spans="1:14">
       <c r="A191" s="17"/>
       <c r="B191" s="18"/>
       <c r="C191" s="17"/>
@@ -14335,8 +14769,10 @@
       <c r="J191" s="17"/>
       <c r="K191" s="17"/>
       <c r="L191" s="17"/>
-    </row>
-    <row r="192" spans="1:12">
+      <c r="M191" s="17"/>
+      <c r="N191" s="17"/>
+    </row>
+    <row r="192" spans="1:14">
       <c r="A192" s="17"/>
       <c r="B192" s="18"/>
       <c r="C192" s="17"/>
@@ -14349,8 +14785,10 @@
       <c r="J192" s="17"/>
       <c r="K192" s="17"/>
       <c r="L192" s="17"/>
-    </row>
-    <row r="193" spans="1:12">
+      <c r="M192" s="17"/>
+      <c r="N192" s="17"/>
+    </row>
+    <row r="193" spans="1:14">
       <c r="A193" s="17"/>
       <c r="B193" s="18"/>
       <c r="C193" s="17"/>
@@ -14363,8 +14801,10 @@
       <c r="J193" s="17"/>
       <c r="K193" s="17"/>
       <c r="L193" s="17"/>
-    </row>
-    <row r="194" spans="1:12">
+      <c r="M193" s="17"/>
+      <c r="N193" s="17"/>
+    </row>
+    <row r="194" spans="1:14">
       <c r="A194" s="17"/>
       <c r="B194" s="18"/>
       <c r="C194" s="17"/>
@@ -14377,8 +14817,10 @@
       <c r="J194" s="17"/>
       <c r="K194" s="17"/>
       <c r="L194" s="17"/>
-    </row>
-    <row r="195" spans="1:12">
+      <c r="M194" s="17"/>
+      <c r="N194" s="17"/>
+    </row>
+    <row r="195" spans="1:14">
       <c r="A195" s="17"/>
       <c r="B195" s="18"/>
       <c r="C195" s="17"/>
@@ -14391,8 +14833,10 @@
       <c r="J195" s="17"/>
       <c r="K195" s="17"/>
       <c r="L195" s="17"/>
-    </row>
-    <row r="196" spans="1:12">
+      <c r="M195" s="17"/>
+      <c r="N195" s="17"/>
+    </row>
+    <row r="196" spans="1:14">
       <c r="A196" s="17"/>
       <c r="B196" s="18"/>
       <c r="C196" s="17"/>
@@ -14405,8 +14849,10 @@
       <c r="J196" s="17"/>
       <c r="K196" s="17"/>
       <c r="L196" s="17"/>
-    </row>
-    <row r="197" spans="1:12">
+      <c r="M196" s="17"/>
+      <c r="N196" s="17"/>
+    </row>
+    <row r="197" spans="1:14">
       <c r="A197" s="17"/>
       <c r="B197" s="18"/>
       <c r="C197" s="17"/>
@@ -14419,8 +14865,10 @@
       <c r="J197" s="17"/>
       <c r="K197" s="17"/>
       <c r="L197" s="17"/>
-    </row>
-    <row r="198" spans="1:12">
+      <c r="M197" s="17"/>
+      <c r="N197" s="17"/>
+    </row>
+    <row r="198" spans="1:14">
       <c r="A198" s="17"/>
       <c r="B198" s="18"/>
       <c r="C198" s="17"/>
@@ -14433,8 +14881,10 @@
       <c r="J198" s="17"/>
       <c r="K198" s="17"/>
       <c r="L198" s="17"/>
-    </row>
-    <row r="199" spans="1:12">
+      <c r="M198" s="17"/>
+      <c r="N198" s="17"/>
+    </row>
+    <row r="199" spans="1:14">
       <c r="A199" s="17"/>
       <c r="B199" s="18"/>
       <c r="C199" s="17"/>
@@ -14447,8 +14897,10 @@
       <c r="J199" s="17"/>
       <c r="K199" s="17"/>
       <c r="L199" s="17"/>
-    </row>
-    <row r="200" spans="1:12">
+      <c r="M199" s="17"/>
+      <c r="N199" s="17"/>
+    </row>
+    <row r="200" spans="1:14">
       <c r="A200" s="17"/>
       <c r="B200" s="18"/>
       <c r="C200" s="17"/>
@@ -14461,8 +14913,10 @@
       <c r="J200" s="17"/>
       <c r="K200" s="17"/>
       <c r="L200" s="17"/>
-    </row>
-    <row r="201" spans="1:12">
+      <c r="M200" s="17"/>
+      <c r="N200" s="17"/>
+    </row>
+    <row r="201" spans="1:14">
       <c r="A201" s="17"/>
       <c r="B201" s="18"/>
       <c r="C201" s="17"/>
@@ -14475,8 +14929,10 @@
       <c r="J201" s="17"/>
       <c r="K201" s="17"/>
       <c r="L201" s="17"/>
-    </row>
-    <row r="202" spans="1:12">
+      <c r="M201" s="17"/>
+      <c r="N201" s="17"/>
+    </row>
+    <row r="202" spans="1:14">
       <c r="A202" s="17"/>
       <c r="B202" s="18"/>
       <c r="C202" s="17"/>
@@ -14489,8 +14945,10 @@
       <c r="J202" s="17"/>
       <c r="K202" s="17"/>
       <c r="L202" s="17"/>
-    </row>
-    <row r="203" spans="1:12">
+      <c r="M202" s="17"/>
+      <c r="N202" s="17"/>
+    </row>
+    <row r="203" spans="1:14">
       <c r="A203" s="17"/>
       <c r="B203" s="18"/>
       <c r="C203" s="17"/>
@@ -14503,8 +14961,10 @@
       <c r="J203" s="17"/>
       <c r="K203" s="17"/>
       <c r="L203" s="17"/>
-    </row>
-    <row r="204" spans="1:12">
+      <c r="M203" s="17"/>
+      <c r="N203" s="17"/>
+    </row>
+    <row r="204" spans="1:14">
       <c r="A204" s="17"/>
       <c r="B204" s="18"/>
       <c r="C204" s="17"/>
@@ -14517,8 +14977,10 @@
       <c r="J204" s="17"/>
       <c r="K204" s="17"/>
       <c r="L204" s="17"/>
-    </row>
-    <row r="205" spans="1:12">
+      <c r="M204" s="17"/>
+      <c r="N204" s="17"/>
+    </row>
+    <row r="205" spans="1:14">
       <c r="A205" s="17"/>
       <c r="B205" s="18"/>
       <c r="C205" s="17"/>
@@ -14531,8 +14993,10 @@
       <c r="J205" s="17"/>
       <c r="K205" s="17"/>
       <c r="L205" s="17"/>
-    </row>
-    <row r="206" spans="1:12">
+      <c r="M205" s="17"/>
+      <c r="N205" s="17"/>
+    </row>
+    <row r="206" spans="1:14">
       <c r="A206" s="17"/>
       <c r="B206" s="18"/>
       <c r="C206" s="17"/>
@@ -14545,8 +15009,10 @@
       <c r="J206" s="17"/>
       <c r="K206" s="17"/>
       <c r="L206" s="17"/>
-    </row>
-    <row r="207" spans="1:12">
+      <c r="M206" s="17"/>
+      <c r="N206" s="17"/>
+    </row>
+    <row r="207" spans="1:14">
       <c r="A207" s="17"/>
       <c r="B207" s="18"/>
       <c r="C207" s="17"/>
@@ -14559,8 +15025,10 @@
       <c r="J207" s="17"/>
       <c r="K207" s="17"/>
       <c r="L207" s="17"/>
-    </row>
-    <row r="208" spans="1:12">
+      <c r="M207" s="17"/>
+      <c r="N207" s="17"/>
+    </row>
+    <row r="208" spans="1:14">
       <c r="A208" s="17"/>
       <c r="B208" s="18"/>
       <c r="C208" s="17"/>
@@ -14573,8 +15041,10 @@
       <c r="J208" s="17"/>
       <c r="K208" s="17"/>
       <c r="L208" s="17"/>
-    </row>
-    <row r="209" spans="1:12">
+      <c r="M208" s="17"/>
+      <c r="N208" s="17"/>
+    </row>
+    <row r="209" spans="1:14">
       <c r="A209" s="17"/>
       <c r="B209" s="18"/>
       <c r="C209" s="17"/>
@@ -14587,8 +15057,10 @@
       <c r="J209" s="17"/>
       <c r="K209" s="17"/>
       <c r="L209" s="17"/>
-    </row>
-    <row r="210" spans="1:12">
+      <c r="M209" s="17"/>
+      <c r="N209" s="17"/>
+    </row>
+    <row r="210" spans="1:14">
       <c r="A210" s="17"/>
       <c r="B210" s="18"/>
       <c r="C210" s="17"/>
@@ -14601,8 +15073,10 @@
       <c r="J210" s="17"/>
       <c r="K210" s="17"/>
       <c r="L210" s="17"/>
-    </row>
-    <row r="211" spans="1:12">
+      <c r="M210" s="17"/>
+      <c r="N210" s="17"/>
+    </row>
+    <row r="211" spans="1:14">
       <c r="A211" s="17"/>
       <c r="B211" s="18"/>
       <c r="C211" s="17"/>
@@ -14615,8 +15089,10 @@
       <c r="J211" s="17"/>
       <c r="K211" s="17"/>
       <c r="L211" s="17"/>
-    </row>
-    <row r="212" spans="1:12">
+      <c r="M211" s="17"/>
+      <c r="N211" s="17"/>
+    </row>
+    <row r="212" spans="1:14">
       <c r="A212" s="17"/>
       <c r="B212" s="18"/>
       <c r="C212" s="17"/>
@@ -14629,8 +15105,10 @@
       <c r="J212" s="17"/>
       <c r="K212" s="17"/>
       <c r="L212" s="17"/>
-    </row>
-    <row r="213" spans="1:12">
+      <c r="M212" s="17"/>
+      <c r="N212" s="17"/>
+    </row>
+    <row r="213" spans="1:14">
       <c r="A213" s="17"/>
       <c r="B213" s="18"/>
       <c r="C213" s="17"/>
@@ -14643,8 +15121,10 @@
       <c r="J213" s="17"/>
       <c r="K213" s="17"/>
       <c r="L213" s="17"/>
-    </row>
-    <row r="214" spans="1:12">
+      <c r="M213" s="17"/>
+      <c r="N213" s="17"/>
+    </row>
+    <row r="214" spans="1:14">
       <c r="A214" s="17"/>
       <c r="B214" s="18"/>
       <c r="C214" s="17"/>
@@ -14657,8 +15137,10 @@
       <c r="J214" s="17"/>
       <c r="K214" s="17"/>
       <c r="L214" s="17"/>
-    </row>
-    <row r="215" spans="1:12">
+      <c r="M214" s="17"/>
+      <c r="N214" s="17"/>
+    </row>
+    <row r="215" spans="1:14">
       <c r="A215" s="17"/>
       <c r="B215" s="18"/>
       <c r="C215" s="17"/>
@@ -14671,8 +15153,10 @@
       <c r="J215" s="17"/>
       <c r="K215" s="17"/>
       <c r="L215" s="17"/>
-    </row>
-    <row r="216" spans="1:12">
+      <c r="M215" s="17"/>
+      <c r="N215" s="17"/>
+    </row>
+    <row r="216" spans="1:14">
       <c r="A216" s="17"/>
       <c r="B216" s="18"/>
       <c r="C216" s="17"/>
@@ -14685,8 +15169,10 @@
       <c r="J216" s="17"/>
       <c r="K216" s="17"/>
       <c r="L216" s="17"/>
-    </row>
-    <row r="217" spans="1:12">
+      <c r="M216" s="17"/>
+      <c r="N216" s="17"/>
+    </row>
+    <row r="217" spans="1:14">
       <c r="A217" s="17"/>
       <c r="B217" s="18"/>
       <c r="C217" s="17"/>
@@ -14699,8 +15185,10 @@
       <c r="J217" s="17"/>
       <c r="K217" s="17"/>
       <c r="L217" s="17"/>
-    </row>
-    <row r="218" spans="1:12">
+      <c r="M217" s="17"/>
+      <c r="N217" s="17"/>
+    </row>
+    <row r="218" spans="1:14">
       <c r="A218" s="17"/>
       <c r="B218" s="18"/>
       <c r="C218" s="17"/>
@@ -14713,8 +15201,10 @@
       <c r="J218" s="17"/>
       <c r="K218" s="17"/>
       <c r="L218" s="17"/>
-    </row>
-    <row r="219" spans="1:12">
+      <c r="M218" s="17"/>
+      <c r="N218" s="17"/>
+    </row>
+    <row r="219" spans="1:14">
       <c r="A219" s="17"/>
       <c r="B219" s="18"/>
       <c r="C219" s="17"/>
@@ -14727,8 +15217,10 @@
       <c r="J219" s="17"/>
       <c r="K219" s="17"/>
       <c r="L219" s="17"/>
-    </row>
-    <row r="220" spans="1:12">
+      <c r="M219" s="17"/>
+      <c r="N219" s="17"/>
+    </row>
+    <row r="220" spans="1:14">
       <c r="A220" s="17"/>
       <c r="B220" s="18"/>
       <c r="C220" s="17"/>
@@ -14741,8 +15233,10 @@
       <c r="J220" s="17"/>
       <c r="K220" s="17"/>
       <c r="L220" s="17"/>
-    </row>
-    <row r="221" spans="1:12">
+      <c r="M220" s="17"/>
+      <c r="N220" s="17"/>
+    </row>
+    <row r="221" spans="1:14">
       <c r="A221" s="17"/>
       <c r="B221" s="18"/>
       <c r="C221" s="17"/>
@@ -14755,8 +15249,10 @@
       <c r="J221" s="17"/>
       <c r="K221" s="17"/>
       <c r="L221" s="17"/>
-    </row>
-    <row r="222" spans="1:12">
+      <c r="M221" s="17"/>
+      <c r="N221" s="17"/>
+    </row>
+    <row r="222" spans="1:14">
       <c r="A222" s="17"/>
       <c r="B222" s="18"/>
       <c r="C222" s="17"/>
@@ -14769,8 +15265,10 @@
       <c r="J222" s="17"/>
       <c r="K222" s="17"/>
       <c r="L222" s="17"/>
-    </row>
-    <row r="223" spans="1:12">
+      <c r="M222" s="17"/>
+      <c r="N222" s="17"/>
+    </row>
+    <row r="223" spans="1:14">
       <c r="A223" s="17"/>
       <c r="B223" s="18"/>
       <c r="C223" s="17"/>
@@ -14783,8 +15281,10 @@
       <c r="J223" s="17"/>
       <c r="K223" s="17"/>
       <c r="L223" s="17"/>
-    </row>
-    <row r="224" spans="1:12">
+      <c r="M223" s="17"/>
+      <c r="N223" s="17"/>
+    </row>
+    <row r="224" spans="1:14">
       <c r="A224" s="17"/>
       <c r="B224" s="18"/>
       <c r="C224" s="17"/>
@@ -14797,8 +15297,10 @@
       <c r="J224" s="17"/>
       <c r="K224" s="17"/>
       <c r="L224" s="17"/>
-    </row>
-    <row r="225" spans="1:12">
+      <c r="M224" s="17"/>
+      <c r="N224" s="17"/>
+    </row>
+    <row r="225" spans="1:14">
       <c r="A225" s="17"/>
       <c r="B225" s="18"/>
       <c r="C225" s="17"/>
@@ -14811,8 +15313,10 @@
       <c r="J225" s="17"/>
       <c r="K225" s="17"/>
       <c r="L225" s="17"/>
-    </row>
-    <row r="226" spans="1:12">
+      <c r="M225" s="17"/>
+      <c r="N225" s="17"/>
+    </row>
+    <row r="226" spans="1:14">
       <c r="A226" s="17"/>
       <c r="B226" s="18"/>
       <c r="C226" s="17"/>
@@ -14825,8 +15329,10 @@
       <c r="J226" s="17"/>
       <c r="K226" s="17"/>
       <c r="L226" s="17"/>
-    </row>
-    <row r="227" spans="1:12">
+      <c r="M226" s="17"/>
+      <c r="N226" s="17"/>
+    </row>
+    <row r="227" spans="1:14">
       <c r="A227" s="17"/>
       <c r="B227" s="18"/>
       <c r="C227" s="17"/>
@@ -14839,8 +15345,10 @@
       <c r="J227" s="17"/>
       <c r="K227" s="17"/>
       <c r="L227" s="17"/>
-    </row>
-    <row r="228" spans="1:12">
+      <c r="M227" s="17"/>
+      <c r="N227" s="17"/>
+    </row>
+    <row r="228" spans="1:14">
       <c r="A228" s="17"/>
       <c r="B228" s="18"/>
       <c r="C228" s="17"/>
@@ -14853,8 +15361,10 @@
       <c r="J228" s="17"/>
       <c r="K228" s="17"/>
       <c r="L228" s="17"/>
-    </row>
-    <row r="229" spans="1:12">
+      <c r="M228" s="17"/>
+      <c r="N228" s="17"/>
+    </row>
+    <row r="229" spans="1:14">
       <c r="A229" s="17"/>
       <c r="B229" s="18"/>
       <c r="C229" s="17"/>
@@ -14867,8 +15377,10 @@
       <c r="J229" s="17"/>
       <c r="K229" s="17"/>
       <c r="L229" s="17"/>
-    </row>
-    <row r="230" spans="1:12">
+      <c r="M229" s="17"/>
+      <c r="N229" s="17"/>
+    </row>
+    <row r="230" spans="1:14">
       <c r="A230" s="17"/>
       <c r="B230" s="18"/>
       <c r="C230" s="17"/>
@@ -14881,8 +15393,10 @@
       <c r="J230" s="17"/>
       <c r="K230" s="17"/>
       <c r="L230" s="17"/>
-    </row>
-    <row r="231" spans="1:12">
+      <c r="M230" s="17"/>
+      <c r="N230" s="17"/>
+    </row>
+    <row r="231" spans="1:14">
       <c r="A231" s="17"/>
       <c r="B231" s="18"/>
       <c r="C231" s="17"/>
@@ -14895,8 +15409,10 @@
       <c r="J231" s="17"/>
       <c r="K231" s="17"/>
       <c r="L231" s="17"/>
-    </row>
-    <row r="232" spans="1:12">
+      <c r="M231" s="17"/>
+      <c r="N231" s="17"/>
+    </row>
+    <row r="232" spans="1:14">
       <c r="A232" s="17"/>
       <c r="B232" s="18"/>
       <c r="C232" s="17"/>
@@ -14909,8 +15425,10 @@
       <c r="J232" s="17"/>
       <c r="K232" s="17"/>
       <c r="L232" s="17"/>
-    </row>
-    <row r="233" spans="1:12">
+      <c r="M232" s="17"/>
+      <c r="N232" s="17"/>
+    </row>
+    <row r="233" spans="1:14">
       <c r="A233" s="17"/>
       <c r="B233" s="18"/>
       <c r="C233" s="17"/>
@@ -14923,8 +15441,10 @@
       <c r="J233" s="17"/>
       <c r="K233" s="17"/>
       <c r="L233" s="17"/>
-    </row>
-    <row r="234" spans="1:12">
+      <c r="M233" s="17"/>
+      <c r="N233" s="17"/>
+    </row>
+    <row r="234" spans="1:14">
       <c r="A234" s="17"/>
       <c r="B234" s="18"/>
       <c r="C234" s="17"/>
@@ -14937,8 +15457,10 @@
       <c r="J234" s="17"/>
       <c r="K234" s="17"/>
       <c r="L234" s="17"/>
-    </row>
-    <row r="235" spans="1:12">
+      <c r="M234" s="17"/>
+      <c r="N234" s="17"/>
+    </row>
+    <row r="235" spans="1:14">
       <c r="A235" s="17"/>
       <c r="B235" s="18"/>
       <c r="C235" s="17"/>
@@ -14951,8 +15473,10 @@
       <c r="J235" s="17"/>
       <c r="K235" s="17"/>
       <c r="L235" s="17"/>
-    </row>
-    <row r="236" spans="1:12">
+      <c r="M235" s="17"/>
+      <c r="N235" s="17"/>
+    </row>
+    <row r="236" spans="1:14">
       <c r="A236" s="17"/>
       <c r="B236" s="18"/>
       <c r="C236" s="17"/>
@@ -14965,8 +15489,10 @@
       <c r="J236" s="17"/>
       <c r="K236" s="17"/>
       <c r="L236" s="17"/>
-    </row>
-    <row r="237" spans="1:12">
+      <c r="M236" s="17"/>
+      <c r="N236" s="17"/>
+    </row>
+    <row r="237" spans="1:14">
       <c r="A237" s="17"/>
       <c r="B237" s="18"/>
       <c r="C237" s="17"/>
@@ -14979,8 +15505,10 @@
       <c r="J237" s="17"/>
       <c r="K237" s="17"/>
       <c r="L237" s="17"/>
-    </row>
-    <row r="238" spans="1:12">
+      <c r="M237" s="17"/>
+      <c r="N237" s="17"/>
+    </row>
+    <row r="238" spans="1:14">
       <c r="A238" s="17"/>
       <c r="B238" s="18"/>
       <c r="C238" s="17"/>
@@ -14993,8 +15521,10 @@
       <c r="J238" s="17"/>
       <c r="K238" s="17"/>
       <c r="L238" s="17"/>
-    </row>
-    <row r="239" spans="1:12">
+      <c r="M238" s="17"/>
+      <c r="N238" s="17"/>
+    </row>
+    <row r="239" spans="1:14">
       <c r="A239" s="17"/>
       <c r="B239" s="18"/>
       <c r="C239" s="17"/>
@@ -15007,8 +15537,10 @@
       <c r="J239" s="17"/>
       <c r="K239" s="17"/>
       <c r="L239" s="17"/>
-    </row>
-    <row r="240" spans="1:12">
+      <c r="M239" s="17"/>
+      <c r="N239" s="17"/>
+    </row>
+    <row r="240" spans="1:14">
       <c r="A240" s="17"/>
       <c r="B240" s="18"/>
       <c r="C240" s="17"/>
@@ -15021,8 +15553,10 @@
       <c r="J240" s="17"/>
       <c r="K240" s="17"/>
       <c r="L240" s="17"/>
-    </row>
-    <row r="241" spans="1:12">
+      <c r="M240" s="17"/>
+      <c r="N240" s="17"/>
+    </row>
+    <row r="241" spans="1:14">
       <c r="A241" s="17"/>
       <c r="B241" s="18"/>
       <c r="C241" s="17"/>
@@ -15035,8 +15569,10 @@
       <c r="J241" s="17"/>
       <c r="K241" s="17"/>
       <c r="L241" s="17"/>
-    </row>
-    <row r="242" spans="1:12">
+      <c r="M241" s="17"/>
+      <c r="N241" s="17"/>
+    </row>
+    <row r="242" spans="1:14">
       <c r="A242" s="17"/>
       <c r="B242" s="18"/>
       <c r="C242" s="17"/>
@@ -15049,8 +15585,10 @@
       <c r="J242" s="17"/>
       <c r="K242" s="17"/>
       <c r="L242" s="17"/>
-    </row>
-    <row r="243" spans="1:12">
+      <c r="M242" s="17"/>
+      <c r="N242" s="17"/>
+    </row>
+    <row r="243" spans="1:14">
       <c r="A243" s="17"/>
       <c r="B243" s="18"/>
       <c r="C243" s="17"/>
@@ -15063,8 +15601,10 @@
       <c r="J243" s="17"/>
       <c r="K243" s="17"/>
       <c r="L243" s="17"/>
-    </row>
-    <row r="244" spans="1:12">
+      <c r="M243" s="17"/>
+      <c r="N243" s="17"/>
+    </row>
+    <row r="244" spans="1:14">
       <c r="A244" s="17"/>
       <c r="B244" s="18"/>
       <c r="C244" s="17"/>
@@ -15077,8 +15617,10 @@
       <c r="J244" s="17"/>
       <c r="K244" s="17"/>
       <c r="L244" s="17"/>
-    </row>
-    <row r="245" spans="1:12">
+      <c r="M244" s="17"/>
+      <c r="N244" s="17"/>
+    </row>
+    <row r="245" spans="1:14">
       <c r="A245" s="17"/>
       <c r="B245" s="18"/>
       <c r="C245" s="17"/>
@@ -15091,8 +15633,10 @@
       <c r="J245" s="17"/>
       <c r="K245" s="17"/>
       <c r="L245" s="17"/>
-    </row>
-    <row r="246" spans="1:12">
+      <c r="M245" s="17"/>
+      <c r="N245" s="17"/>
+    </row>
+    <row r="246" spans="1:14">
       <c r="A246" s="17"/>
       <c r="B246" s="18"/>
       <c r="C246" s="17"/>
@@ -15105,8 +15649,10 @@
       <c r="J246" s="17"/>
       <c r="K246" s="17"/>
       <c r="L246" s="17"/>
-    </row>
-    <row r="247" spans="1:12">
+      <c r="M246" s="17"/>
+      <c r="N246" s="17"/>
+    </row>
+    <row r="247" spans="1:14">
       <c r="A247" s="17"/>
       <c r="B247" s="18"/>
       <c r="C247" s="17"/>
@@ -15119,8 +15665,10 @@
       <c r="J247" s="17"/>
       <c r="K247" s="17"/>
       <c r="L247" s="17"/>
-    </row>
-    <row r="248" spans="1:12">
+      <c r="M247" s="17"/>
+      <c r="N247" s="17"/>
+    </row>
+    <row r="248" spans="1:14">
       <c r="A248" s="17"/>
       <c r="B248" s="18"/>
       <c r="C248" s="17"/>
@@ -15133,8 +15681,10 @@
       <c r="J248" s="17"/>
       <c r="K248" s="17"/>
       <c r="L248" s="17"/>
-    </row>
-    <row r="249" spans="1:12">
+      <c r="M248" s="17"/>
+      <c r="N248" s="17"/>
+    </row>
+    <row r="249" spans="1:14">
       <c r="A249" s="17"/>
       <c r="B249" s="18"/>
       <c r="C249" s="17"/>
@@ -15147,8 +15697,10 @@
       <c r="J249" s="17"/>
       <c r="K249" s="17"/>
       <c r="L249" s="17"/>
-    </row>
-    <row r="250" spans="1:12">
+      <c r="M249" s="17"/>
+      <c r="N249" s="17"/>
+    </row>
+    <row r="250" spans="1:14">
       <c r="A250" s="17"/>
       <c r="B250" s="18"/>
       <c r="C250" s="17"/>
@@ -15161,8 +15713,10 @@
       <c r="J250" s="17"/>
       <c r="K250" s="17"/>
       <c r="L250" s="17"/>
-    </row>
-    <row r="251" spans="1:12">
+      <c r="M250" s="17"/>
+      <c r="N250" s="17"/>
+    </row>
+    <row r="251" spans="1:14">
       <c r="A251" s="17"/>
       <c r="B251" s="18"/>
       <c r="C251" s="17"/>
@@ -15175,8 +15729,10 @@
       <c r="J251" s="17"/>
       <c r="K251" s="17"/>
       <c r="L251" s="17"/>
-    </row>
-    <row r="252" spans="1:12">
+      <c r="M251" s="17"/>
+      <c r="N251" s="17"/>
+    </row>
+    <row r="252" spans="1:14">
       <c r="A252" s="17"/>
       <c r="B252" s="18"/>
       <c r="C252" s="17"/>
@@ -15189,8 +15745,10 @@
       <c r="J252" s="17"/>
       <c r="K252" s="17"/>
       <c r="L252" s="17"/>
-    </row>
-    <row r="253" spans="1:12">
+      <c r="M252" s="17"/>
+      <c r="N252" s="17"/>
+    </row>
+    <row r="253" spans="1:14">
       <c r="A253" s="17"/>
       <c r="B253" s="18"/>
       <c r="C253" s="17"/>
@@ -15203,8 +15761,10 @@
       <c r="J253" s="17"/>
       <c r="K253" s="17"/>
       <c r="L253" s="17"/>
-    </row>
-    <row r="254" spans="1:12">
+      <c r="M253" s="17"/>
+      <c r="N253" s="17"/>
+    </row>
+    <row r="254" spans="1:14">
       <c r="A254" s="17"/>
       <c r="B254" s="18"/>
       <c r="C254" s="17"/>
@@ -15217,8 +15777,10 @@
       <c r="J254" s="17"/>
       <c r="K254" s="17"/>
       <c r="L254" s="17"/>
-    </row>
-    <row r="255" spans="1:12">
+      <c r="M254" s="17"/>
+      <c r="N254" s="17"/>
+    </row>
+    <row r="255" spans="1:14">
       <c r="A255" s="17"/>
       <c r="B255" s="18"/>
       <c r="C255" s="17"/>
@@ -15231,8 +15793,10 @@
       <c r="J255" s="17"/>
       <c r="K255" s="17"/>
       <c r="L255" s="17"/>
-    </row>
-    <row r="256" spans="1:12">
+      <c r="M255" s="17"/>
+      <c r="N255" s="17"/>
+    </row>
+    <row r="256" spans="1:14">
       <c r="A256" s="17"/>
       <c r="B256" s="18"/>
       <c r="C256" s="17"/>
@@ -15245,8 +15809,10 @@
       <c r="J256" s="17"/>
       <c r="K256" s="17"/>
       <c r="L256" s="17"/>
-    </row>
-    <row r="257" spans="1:12">
+      <c r="M256" s="17"/>
+      <c r="N256" s="17"/>
+    </row>
+    <row r="257" spans="1:14">
       <c r="A257" s="17"/>
       <c r="B257" s="18"/>
       <c r="C257" s="17"/>
@@ -15259,8 +15825,10 @@
       <c r="J257" s="17"/>
       <c r="K257" s="17"/>
       <c r="L257" s="17"/>
-    </row>
-    <row r="258" spans="1:12">
+      <c r="M257" s="17"/>
+      <c r="N257" s="17"/>
+    </row>
+    <row r="258" spans="1:14">
       <c r="A258" s="17"/>
       <c r="B258" s="18"/>
       <c r="C258" s="17"/>
@@ -15273,8 +15841,10 @@
       <c r="J258" s="17"/>
       <c r="K258" s="17"/>
       <c r="L258" s="17"/>
-    </row>
-    <row r="259" spans="1:12">
+      <c r="M258" s="17"/>
+      <c r="N258" s="17"/>
+    </row>
+    <row r="259" spans="1:14">
       <c r="A259" s="17"/>
       <c r="B259" s="18"/>
       <c r="C259" s="17"/>
@@ -15287,8 +15857,10 @@
       <c r="J259" s="17"/>
       <c r="K259" s="17"/>
       <c r="L259" s="17"/>
-    </row>
-    <row r="260" spans="1:12">
+      <c r="M259" s="17"/>
+      <c r="N259" s="17"/>
+    </row>
+    <row r="260" spans="1:14">
       <c r="A260" s="17"/>
       <c r="B260" s="18"/>
       <c r="C260" s="17"/>
@@ -15301,8 +15873,10 @@
       <c r="J260" s="17"/>
       <c r="K260" s="17"/>
       <c r="L260" s="17"/>
-    </row>
-    <row r="261" spans="1:12">
+      <c r="M260" s="17"/>
+      <c r="N260" s="17"/>
+    </row>
+    <row r="261" spans="1:14">
       <c r="A261" s="17"/>
       <c r="B261" s="18"/>
       <c r="C261" s="17"/>
@@ -15315,8 +15889,10 @@
       <c r="J261" s="17"/>
       <c r="K261" s="17"/>
       <c r="L261" s="17"/>
-    </row>
-    <row r="262" spans="1:12">
+      <c r="M261" s="17"/>
+      <c r="N261" s="17"/>
+    </row>
+    <row r="262" spans="1:14">
       <c r="A262" s="17"/>
       <c r="B262" s="18"/>
       <c r="C262" s="17"/>
@@ -15329,8 +15905,10 @@
       <c r="J262" s="17"/>
       <c r="K262" s="17"/>
       <c r="L262" s="17"/>
-    </row>
-    <row r="263" spans="1:12">
+      <c r="M262" s="17"/>
+      <c r="N262" s="17"/>
+    </row>
+    <row r="263" spans="1:14">
       <c r="A263" s="17"/>
       <c r="B263" s="18"/>
       <c r="C263" s="17"/>
@@ -15343,8 +15921,10 @@
       <c r="J263" s="17"/>
       <c r="K263" s="17"/>
       <c r="L263" s="17"/>
-    </row>
-    <row r="264" spans="1:12">
+      <c r="M263" s="17"/>
+      <c r="N263" s="17"/>
+    </row>
+    <row r="264" spans="1:14">
       <c r="A264" s="17"/>
       <c r="B264" s="18"/>
       <c r="C264" s="17"/>
@@ -15357,8 +15937,10 @@
       <c r="J264" s="17"/>
       <c r="K264" s="17"/>
       <c r="L264" s="17"/>
-    </row>
-    <row r="265" spans="1:12">
+      <c r="M264" s="17"/>
+      <c r="N264" s="17"/>
+    </row>
+    <row r="265" spans="1:14">
       <c r="A265" s="17"/>
       <c r="B265" s="18"/>
       <c r="C265" s="17"/>
@@ -15371,8 +15953,10 @@
       <c r="J265" s="17"/>
       <c r="K265" s="17"/>
       <c r="L265" s="17"/>
-    </row>
-    <row r="266" spans="1:12">
+      <c r="M265" s="17"/>
+      <c r="N265" s="17"/>
+    </row>
+    <row r="266" spans="1:14">
       <c r="A266" s="17"/>
       <c r="B266" s="18"/>
       <c r="C266" s="17"/>
@@ -15385,8 +15969,10 @@
       <c r="J266" s="17"/>
       <c r="K266" s="17"/>
       <c r="L266" s="17"/>
-    </row>
-    <row r="267" spans="1:12">
+      <c r="M266" s="17"/>
+      <c r="N266" s="17"/>
+    </row>
+    <row r="267" spans="1:14">
       <c r="A267" s="17"/>
       <c r="B267" s="18"/>
       <c r="C267" s="17"/>
@@ -15399,8 +15985,10 @@
       <c r="J267" s="17"/>
       <c r="K267" s="17"/>
       <c r="L267" s="17"/>
-    </row>
-    <row r="268" spans="1:12">
+      <c r="M267" s="17"/>
+      <c r="N267" s="17"/>
+    </row>
+    <row r="268" spans="1:14">
       <c r="A268" s="17"/>
       <c r="B268" s="18"/>
       <c r="C268" s="17"/>
@@ -15413,8 +16001,10 @@
       <c r="J268" s="17"/>
       <c r="K268" s="17"/>
       <c r="L268" s="17"/>
-    </row>
-    <row r="269" spans="1:12">
+      <c r="M268" s="17"/>
+      <c r="N268" s="17"/>
+    </row>
+    <row r="269" spans="1:14">
       <c r="A269" s="17"/>
       <c r="B269" s="18"/>
       <c r="C269" s="17"/>
@@ -15427,8 +16017,10 @@
       <c r="J269" s="17"/>
       <c r="K269" s="17"/>
       <c r="L269" s="17"/>
-    </row>
-    <row r="270" spans="1:12">
+      <c r="M269" s="17"/>
+      <c r="N269" s="17"/>
+    </row>
+    <row r="270" spans="1:14">
       <c r="A270" s="17"/>
       <c r="B270" s="18"/>
       <c r="C270" s="17"/>
@@ -15441,8 +16033,10 @@
       <c r="J270" s="17"/>
       <c r="K270" s="17"/>
       <c r="L270" s="17"/>
-    </row>
-    <row r="271" spans="1:12">
+      <c r="M270" s="17"/>
+      <c r="N270" s="17"/>
+    </row>
+    <row r="271" spans="1:14">
       <c r="A271" s="17"/>
       <c r="B271" s="18"/>
       <c r="C271" s="17"/>
@@ -15455,8 +16049,10 @@
       <c r="J271" s="17"/>
       <c r="K271" s="17"/>
       <c r="L271" s="17"/>
-    </row>
-    <row r="272" spans="1:12">
+      <c r="M271" s="17"/>
+      <c r="N271" s="17"/>
+    </row>
+    <row r="272" spans="1:14">
       <c r="A272" s="17"/>
       <c r="B272" s="18"/>
       <c r="C272" s="17"/>
@@ -15469,8 +16065,10 @@
       <c r="J272" s="17"/>
       <c r="K272" s="17"/>
       <c r="L272" s="17"/>
-    </row>
-    <row r="273" spans="1:12">
+      <c r="M272" s="17"/>
+      <c r="N272" s="17"/>
+    </row>
+    <row r="273" spans="1:14">
       <c r="A273" s="17"/>
       <c r="B273" s="18"/>
       <c r="C273" s="17"/>
@@ -15483,8 +16081,10 @@
       <c r="J273" s="17"/>
       <c r="K273" s="17"/>
       <c r="L273" s="17"/>
-    </row>
-    <row r="274" spans="1:12">
+      <c r="M273" s="17"/>
+      <c r="N273" s="17"/>
+    </row>
+    <row r="274" spans="1:14">
       <c r="A274" s="17"/>
       <c r="B274" s="18"/>
       <c r="C274" s="17"/>
@@ -15497,8 +16097,10 @@
       <c r="J274" s="17"/>
       <c r="K274" s="17"/>
       <c r="L274" s="17"/>
-    </row>
-    <row r="275" spans="1:12">
+      <c r="M274" s="17"/>
+      <c r="N274" s="17"/>
+    </row>
+    <row r="275" spans="1:14">
       <c r="A275" s="17"/>
       <c r="B275" s="18"/>
       <c r="C275" s="17"/>
@@ -15511,8 +16113,10 @@
       <c r="J275" s="17"/>
       <c r="K275" s="17"/>
       <c r="L275" s="17"/>
-    </row>
-    <row r="276" spans="1:12">
+      <c r="M275" s="17"/>
+      <c r="N275" s="17"/>
+    </row>
+    <row r="276" spans="1:14">
       <c r="A276" s="17"/>
       <c r="B276" s="18"/>
       <c r="C276" s="17"/>
@@ -15525,8 +16129,10 @@
       <c r="J276" s="17"/>
       <c r="K276" s="17"/>
       <c r="L276" s="17"/>
-    </row>
-    <row r="277" spans="1:12">
+      <c r="M276" s="17"/>
+      <c r="N276" s="17"/>
+    </row>
+    <row r="277" spans="1:14">
       <c r="A277" s="17"/>
       <c r="B277" s="18"/>
       <c r="C277" s="17"/>
@@ -15539,8 +16145,10 @@
       <c r="J277" s="17"/>
       <c r="K277" s="17"/>
       <c r="L277" s="17"/>
-    </row>
-    <row r="278" spans="1:12">
+      <c r="M277" s="17"/>
+      <c r="N277" s="17"/>
+    </row>
+    <row r="278" spans="1:14">
       <c r="A278" s="17"/>
       <c r="B278" s="18"/>
       <c r="C278" s="17"/>
@@ -15553,8 +16161,10 @@
       <c r="J278" s="17"/>
       <c r="K278" s="17"/>
       <c r="L278" s="17"/>
-    </row>
-    <row r="279" spans="1:12">
+      <c r="M278" s="17"/>
+      <c r="N278" s="17"/>
+    </row>
+    <row r="279" spans="1:14">
       <c r="A279" s="17"/>
       <c r="B279" s="18"/>
       <c r="C279" s="17"/>
@@ -15567,8 +16177,10 @@
       <c r="J279" s="17"/>
       <c r="K279" s="17"/>
       <c r="L279" s="17"/>
-    </row>
-    <row r="280" spans="1:12">
+      <c r="M279" s="17"/>
+      <c r="N279" s="17"/>
+    </row>
+    <row r="280" spans="1:14">
       <c r="A280" s="17"/>
       <c r="B280" s="18"/>
       <c r="C280" s="17"/>
@@ -15581,8 +16193,10 @@
       <c r="J280" s="17"/>
       <c r="K280" s="17"/>
       <c r="L280" s="17"/>
-    </row>
-    <row r="281" spans="1:12">
+      <c r="M280" s="17"/>
+      <c r="N280" s="17"/>
+    </row>
+    <row r="281" spans="1:14">
       <c r="A281" s="17"/>
       <c r="B281" s="18"/>
       <c r="C281" s="17"/>
@@ -15595,8 +16209,10 @@
       <c r="J281" s="17"/>
       <c r="K281" s="17"/>
       <c r="L281" s="17"/>
-    </row>
-    <row r="282" spans="1:12">
+      <c r="M281" s="17"/>
+      <c r="N281" s="17"/>
+    </row>
+    <row r="282" spans="1:14">
       <c r="A282" s="17"/>
       <c r="B282" s="18"/>
       <c r="C282" s="17"/>
@@ -15609,8 +16225,10 @@
       <c r="J282" s="17"/>
       <c r="K282" s="17"/>
       <c r="L282" s="17"/>
-    </row>
-    <row r="283" spans="1:12">
+      <c r="M282" s="17"/>
+      <c r="N282" s="17"/>
+    </row>
+    <row r="283" spans="1:14">
       <c r="A283" s="17"/>
       <c r="B283" s="18"/>
       <c r="C283" s="17"/>
@@ -15623,8 +16241,10 @@
       <c r="J283" s="17"/>
       <c r="K283" s="17"/>
       <c r="L283" s="17"/>
-    </row>
-    <row r="284" spans="1:12">
+      <c r="M283" s="17"/>
+      <c r="N283" s="17"/>
+    </row>
+    <row r="284" spans="1:14">
       <c r="A284" s="17"/>
       <c r="B284" s="18"/>
       <c r="C284" s="17"/>
@@ -15637,8 +16257,10 @@
       <c r="J284" s="17"/>
       <c r="K284" s="17"/>
       <c r="L284" s="17"/>
-    </row>
-    <row r="285" spans="1:12">
+      <c r="M284" s="17"/>
+      <c r="N284" s="17"/>
+    </row>
+    <row r="285" spans="1:14">
       <c r="A285" s="17"/>
       <c r="B285" s="18"/>
       <c r="C285" s="17"/>
@@ -15651,8 +16273,10 @@
       <c r="J285" s="17"/>
       <c r="K285" s="17"/>
       <c r="L285" s="17"/>
-    </row>
-    <row r="286" spans="1:12">
+      <c r="M285" s="17"/>
+      <c r="N285" s="17"/>
+    </row>
+    <row r="286" spans="1:14">
       <c r="A286" s="17"/>
       <c r="B286" s="18"/>
       <c r="C286" s="17"/>
@@ -15665,8 +16289,10 @@
       <c r="J286" s="17"/>
       <c r="K286" s="17"/>
       <c r="L286" s="17"/>
-    </row>
-    <row r="287" spans="1:12">
+      <c r="M286" s="17"/>
+      <c r="N286" s="17"/>
+    </row>
+    <row r="287" spans="1:14">
       <c r="A287" s="17"/>
       <c r="B287" s="18"/>
       <c r="C287" s="17"/>
@@ -15679,8 +16305,10 @@
       <c r="J287" s="17"/>
       <c r="K287" s="17"/>
       <c r="L287" s="17"/>
-    </row>
-    <row r="288" spans="1:12">
+      <c r="M287" s="17"/>
+      <c r="N287" s="17"/>
+    </row>
+    <row r="288" spans="1:14">
       <c r="A288" s="17"/>
       <c r="B288" s="18"/>
       <c r="C288" s="17"/>
@@ -15693,8 +16321,10 @@
       <c r="J288" s="17"/>
       <c r="K288" s="17"/>
       <c r="L288" s="17"/>
-    </row>
-    <row r="289" spans="1:12">
+      <c r="M288" s="17"/>
+      <c r="N288" s="17"/>
+    </row>
+    <row r="289" spans="1:14">
       <c r="A289" s="17"/>
       <c r="B289" s="18"/>
       <c r="C289" s="17"/>
@@ -15707,8 +16337,10 @@
       <c r="J289" s="17"/>
       <c r="K289" s="17"/>
       <c r="L289" s="17"/>
-    </row>
-    <row r="290" spans="1:12">
+      <c r="M289" s="17"/>
+      <c r="N289" s="17"/>
+    </row>
+    <row r="290" spans="1:14">
       <c r="A290" s="17"/>
       <c r="B290" s="18"/>
       <c r="C290" s="17"/>
@@ -15721,8 +16353,10 @@
       <c r="J290" s="17"/>
       <c r="K290" s="17"/>
       <c r="L290" s="17"/>
-    </row>
-    <row r="291" spans="1:12">
+      <c r="M290" s="17"/>
+      <c r="N290" s="17"/>
+    </row>
+    <row r="291" spans="1:14">
       <c r="A291" s="17"/>
       <c r="B291" s="18"/>
       <c r="C291" s="17"/>
@@ -15735,8 +16369,10 @@
       <c r="J291" s="17"/>
       <c r="K291" s="17"/>
       <c r="L291" s="17"/>
-    </row>
-    <row r="292" spans="1:12">
+      <c r="M291" s="17"/>
+      <c r="N291" s="17"/>
+    </row>
+    <row r="292" spans="1:14">
       <c r="A292" s="17"/>
       <c r="B292" s="18"/>
       <c r="C292" s="17"/>
@@ -15749,8 +16385,10 @@
       <c r="J292" s="17"/>
       <c r="K292" s="17"/>
       <c r="L292" s="17"/>
-    </row>
-    <row r="293" spans="1:12">
+      <c r="M292" s="17"/>
+      <c r="N292" s="17"/>
+    </row>
+    <row r="293" spans="1:14">
       <c r="A293" s="17"/>
       <c r="B293" s="18"/>
       <c r="C293" s="17"/>
@@ -15763,8 +16401,10 @@
       <c r="J293" s="17"/>
       <c r="K293" s="17"/>
       <c r="L293" s="17"/>
-    </row>
-    <row r="294" spans="1:12">
+      <c r="M293" s="17"/>
+      <c r="N293" s="17"/>
+    </row>
+    <row r="294" spans="1:14">
       <c r="A294" s="17"/>
       <c r="B294" s="18"/>
       <c r="C294" s="17"/>
@@ -15777,8 +16417,10 @@
       <c r="J294" s="17"/>
       <c r="K294" s="17"/>
       <c r="L294" s="17"/>
-    </row>
-    <row r="295" spans="1:12">
+      <c r="M294" s="17"/>
+      <c r="N294" s="17"/>
+    </row>
+    <row r="295" spans="1:14">
       <c r="A295" s="17"/>
       <c r="B295" s="18"/>
       <c r="C295" s="17"/>
@@ -15791,8 +16433,10 @@
       <c r="J295" s="17"/>
       <c r="K295" s="17"/>
       <c r="L295" s="17"/>
-    </row>
-    <row r="296" spans="1:12">
+      <c r="M295" s="17"/>
+      <c r="N295" s="17"/>
+    </row>
+    <row r="296" spans="1:14">
       <c r="A296" s="17"/>
       <c r="B296" s="18"/>
       <c r="C296" s="17"/>
@@ -15805,8 +16449,10 @@
       <c r="J296" s="17"/>
       <c r="K296" s="17"/>
       <c r="L296" s="17"/>
-    </row>
-    <row r="297" spans="1:12">
+      <c r="M296" s="17"/>
+      <c r="N296" s="17"/>
+    </row>
+    <row r="297" spans="1:14">
       <c r="A297" s="17"/>
       <c r="B297" s="18"/>
       <c r="C297" s="17"/>
@@ -15819,8 +16465,10 @@
       <c r="J297" s="17"/>
       <c r="K297" s="17"/>
       <c r="L297" s="17"/>
-    </row>
-    <row r="298" spans="1:12">
+      <c r="M297" s="17"/>
+      <c r="N297" s="17"/>
+    </row>
+    <row r="298" spans="1:14">
       <c r="A298" s="17"/>
       <c r="B298" s="18"/>
       <c r="C298" s="17"/>
@@ -15833,8 +16481,10 @@
       <c r="J298" s="17"/>
       <c r="K298" s="17"/>
       <c r="L298" s="17"/>
-    </row>
-    <row r="299" spans="1:12">
+      <c r="M298" s="17"/>
+      <c r="N298" s="17"/>
+    </row>
+    <row r="299" spans="1:14">
       <c r="A299" s="17"/>
       <c r="B299" s="18"/>
       <c r="C299" s="17"/>
@@ -15847,8 +16497,10 @@
       <c r="J299" s="17"/>
       <c r="K299" s="17"/>
       <c r="L299" s="17"/>
-    </row>
-    <row r="300" spans="1:12">
+      <c r="M299" s="17"/>
+      <c r="N299" s="17"/>
+    </row>
+    <row r="300" spans="1:14">
       <c r="A300" s="17"/>
       <c r="B300" s="18"/>
       <c r="C300" s="17"/>
@@ -15861,8 +16513,10 @@
       <c r="J300" s="17"/>
       <c r="K300" s="17"/>
       <c r="L300" s="17"/>
-    </row>
-    <row r="301" spans="1:12">
+      <c r="M300" s="17"/>
+      <c r="N300" s="17"/>
+    </row>
+    <row r="301" spans="1:14">
       <c r="A301" s="17"/>
       <c r="B301" s="18"/>
       <c r="C301" s="17"/>
@@ -15875,8 +16529,10 @@
       <c r="J301" s="17"/>
       <c r="K301" s="17"/>
       <c r="L301" s="17"/>
-    </row>
-    <row r="302" spans="1:12">
+      <c r="M301" s="17"/>
+      <c r="N301" s="17"/>
+    </row>
+    <row r="302" spans="1:14">
       <c r="A302" s="17"/>
       <c r="B302" s="18"/>
       <c r="C302" s="17"/>
@@ -15889,8 +16545,10 @@
       <c r="J302" s="17"/>
       <c r="K302" s="17"/>
       <c r="L302" s="17"/>
-    </row>
-    <row r="303" spans="1:12">
+      <c r="M302" s="17"/>
+      <c r="N302" s="17"/>
+    </row>
+    <row r="303" spans="1:14">
       <c r="A303" s="17"/>
       <c r="B303" s="18"/>
       <c r="C303" s="17"/>
@@ -15903,8 +16561,10 @@
       <c r="J303" s="17"/>
       <c r="K303" s="17"/>
       <c r="L303" s="17"/>
-    </row>
-    <row r="304" spans="1:12">
+      <c r="M303" s="17"/>
+      <c r="N303" s="17"/>
+    </row>
+    <row r="304" spans="1:14">
       <c r="A304" s="17"/>
       <c r="B304" s="18"/>
       <c r="C304" s="17"/>
@@ -15917,8 +16577,10 @@
       <c r="J304" s="17"/>
       <c r="K304" s="17"/>
       <c r="L304" s="17"/>
-    </row>
-    <row r="305" spans="1:12">
+      <c r="M304" s="17"/>
+      <c r="N304" s="17"/>
+    </row>
+    <row r="305" spans="1:14">
       <c r="A305" s="17"/>
       <c r="B305" s="18"/>
       <c r="C305" s="17"/>
@@ -15931,8 +16593,10 @@
       <c r="J305" s="17"/>
       <c r="K305" s="17"/>
       <c r="L305" s="17"/>
-    </row>
-    <row r="306" spans="1:12">
+      <c r="M305" s="17"/>
+      <c r="N305" s="17"/>
+    </row>
+    <row r="306" spans="1:14">
       <c r="A306" s="17"/>
       <c r="B306" s="18"/>
       <c r="C306" s="17"/>
@@ -15945,8 +16609,10 @@
       <c r="J306" s="17"/>
       <c r="K306" s="17"/>
       <c r="L306" s="17"/>
-    </row>
-    <row r="307" spans="1:12">
+      <c r="M306" s="17"/>
+      <c r="N306" s="17"/>
+    </row>
+    <row r="307" spans="1:14">
       <c r="A307" s="17"/>
       <c r="B307" s="18"/>
       <c r="C307" s="17"/>
@@ -15959,8 +16625,10 @@
       <c r="J307" s="17"/>
       <c r="K307" s="17"/>
       <c r="L307" s="17"/>
-    </row>
-    <row r="308" spans="1:12">
+      <c r="M307" s="17"/>
+      <c r="N307" s="17"/>
+    </row>
+    <row r="308" spans="1:14">
       <c r="A308" s="17"/>
       <c r="B308" s="18"/>
       <c r="C308" s="17"/>
@@ -15973,8 +16641,10 @@
       <c r="J308" s="17"/>
       <c r="K308" s="17"/>
       <c r="L308" s="17"/>
-    </row>
-    <row r="309" spans="1:12">
+      <c r="M308" s="17"/>
+      <c r="N308" s="17"/>
+    </row>
+    <row r="309" spans="1:14">
       <c r="A309" s="17"/>
       <c r="B309" s="18"/>
       <c r="C309" s="17"/>
@@ -15987,8 +16657,10 @@
       <c r="J309" s="17"/>
       <c r="K309" s="17"/>
       <c r="L309" s="17"/>
-    </row>
-    <row r="310" spans="1:12">
+      <c r="M309" s="17"/>
+      <c r="N309" s="17"/>
+    </row>
+    <row r="310" spans="1:14">
       <c r="A310" s="17"/>
       <c r="B310" s="18"/>
       <c r="C310" s="17"/>
@@ -16001,8 +16673,10 @@
       <c r="J310" s="17"/>
       <c r="K310" s="17"/>
       <c r="L310" s="17"/>
-    </row>
-    <row r="311" spans="1:12">
+      <c r="M310" s="17"/>
+      <c r="N310" s="17"/>
+    </row>
+    <row r="311" spans="1:14">
       <c r="A311" s="17"/>
       <c r="B311" s="18"/>
       <c r="C311" s="17"/>
@@ -16015,8 +16689,10 @@
       <c r="J311" s="17"/>
       <c r="K311" s="17"/>
       <c r="L311" s="17"/>
-    </row>
-    <row r="312" spans="1:12">
+      <c r="M311" s="17"/>
+      <c r="N311" s="17"/>
+    </row>
+    <row r="312" spans="1:14">
       <c r="A312" s="17"/>
       <c r="B312" s="18"/>
       <c r="C312" s="17"/>
@@ -16029,8 +16705,10 @@
       <c r="J312" s="17"/>
       <c r="K312" s="17"/>
       <c r="L312" s="17"/>
-    </row>
-    <row r="313" spans="1:12">
+      <c r="M312" s="17"/>
+      <c r="N312" s="17"/>
+    </row>
+    <row r="313" spans="1:14">
       <c r="A313" s="17"/>
       <c r="B313" s="18"/>
       <c r="C313" s="17"/>
@@ -16043,8 +16721,10 @@
       <c r="J313" s="17"/>
       <c r="K313" s="17"/>
       <c r="L313" s="17"/>
-    </row>
-    <row r="314" spans="1:12">
+      <c r="M313" s="17"/>
+      <c r="N313" s="17"/>
+    </row>
+    <row r="314" spans="1:14">
       <c r="A314" s="17"/>
       <c r="B314" s="18"/>
       <c r="C314" s="17"/>
@@ -16057,8 +16737,10 @@
       <c r="J314" s="17"/>
       <c r="K314" s="17"/>
       <c r="L314" s="17"/>
-    </row>
-    <row r="315" spans="1:12">
+      <c r="M314" s="17"/>
+      <c r="N314" s="17"/>
+    </row>
+    <row r="315" spans="1:14">
       <c r="A315" s="17"/>
       <c r="B315" s="18"/>
       <c r="C315" s="17"/>
@@ -16071,8 +16753,10 @@
       <c r="J315" s="17"/>
       <c r="K315" s="17"/>
       <c r="L315" s="17"/>
-    </row>
-    <row r="316" spans="1:12">
+      <c r="M315" s="17"/>
+      <c r="N315" s="17"/>
+    </row>
+    <row r="316" spans="1:14">
       <c r="A316" s="17"/>
       <c r="B316" s="18"/>
       <c r="C316" s="17"/>
@@ -16085,8 +16769,10 @@
       <c r="J316" s="17"/>
       <c r="K316" s="17"/>
       <c r="L316" s="17"/>
-    </row>
-    <row r="317" spans="1:12">
+      <c r="M316" s="17"/>
+      <c r="N316" s="17"/>
+    </row>
+    <row r="317" spans="1:14">
       <c r="A317" s="17"/>
       <c r="B317" s="18"/>
       <c r="C317" s="17"/>
@@ -16099,8 +16785,10 @@
       <c r="J317" s="17"/>
       <c r="K317" s="17"/>
       <c r="L317" s="17"/>
-    </row>
-    <row r="318" spans="1:12">
+      <c r="M317" s="17"/>
+      <c r="N317" s="17"/>
+    </row>
+    <row r="318" spans="1:14">
       <c r="A318" s="17"/>
       <c r="B318" s="18"/>
       <c r="C318" s="17"/>
@@ -16113,8 +16801,10 @@
       <c r="J318" s="17"/>
       <c r="K318" s="17"/>
       <c r="L318" s="17"/>
-    </row>
-    <row r="319" spans="1:12">
+      <c r="M318" s="17"/>
+      <c r="N318" s="17"/>
+    </row>
+    <row r="319" spans="1:14">
       <c r="A319" s="17"/>
       <c r="B319" s="18"/>
       <c r="C319" s="17"/>
@@ -16127,8 +16817,10 @@
       <c r="J319" s="17"/>
       <c r="K319" s="17"/>
       <c r="L319" s="17"/>
-    </row>
-    <row r="320" spans="1:12">
+      <c r="M319" s="17"/>
+      <c r="N319" s="17"/>
+    </row>
+    <row r="320" spans="1:14">
       <c r="A320" s="17"/>
       <c r="B320" s="18"/>
       <c r="C320" s="17"/>
@@ -16141,8 +16833,10 @@
       <c r="J320" s="17"/>
       <c r="K320" s="17"/>
       <c r="L320" s="17"/>
-    </row>
-    <row r="321" spans="1:12">
+      <c r="M320" s="17"/>
+      <c r="N320" s="17"/>
+    </row>
+    <row r="321" spans="1:14">
       <c r="A321" s="17"/>
       <c r="B321" s="18"/>
       <c r="C321" s="17"/>
@@ -16155,8 +16849,10 @@
       <c r="J321" s="17"/>
       <c r="K321" s="17"/>
       <c r="L321" s="17"/>
-    </row>
-    <row r="322" spans="1:12">
+      <c r="M321" s="17"/>
+      <c r="N321" s="17"/>
+    </row>
+    <row r="322" spans="1:14">
       <c r="A322" s="17"/>
       <c r="B322" s="18"/>
       <c r="C322" s="17"/>
@@ -16169,8 +16865,10 @@
       <c r="J322" s="17"/>
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
-    </row>
-    <row r="323" spans="1:12">
+      <c r="M322" s="17"/>
+      <c r="N322" s="17"/>
+    </row>
+    <row r="323" spans="1:14">
       <c r="A323" s="17"/>
       <c r="B323" s="18"/>
       <c r="C323" s="17"/>
@@ -16183,8 +16881,10 @@
       <c r="J323" s="17"/>
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
-    </row>
-    <row r="324" spans="1:12">
+      <c r="M323" s="17"/>
+      <c r="N323" s="17"/>
+    </row>
+    <row r="324" spans="1:14">
       <c r="A324" s="17"/>
       <c r="B324" s="18"/>
       <c r="C324" s="17"/>
@@ -16197,8 +16897,10 @@
       <c r="J324" s="17"/>
       <c r="K324" s="17"/>
       <c r="L324" s="17"/>
-    </row>
-    <row r="325" spans="1:12">
+      <c r="M324" s="17"/>
+      <c r="N324" s="17"/>
+    </row>
+    <row r="325" spans="1:14">
       <c r="A325" s="17"/>
       <c r="B325" s="18"/>
       <c r="C325" s="17"/>
@@ -16211,8 +16913,10 @@
       <c r="J325" s="17"/>
       <c r="K325" s="17"/>
       <c r="L325" s="17"/>
-    </row>
-    <row r="326" spans="1:12">
+      <c r="M325" s="17"/>
+      <c r="N325" s="17"/>
+    </row>
+    <row r="326" spans="1:14">
       <c r="A326" s="17"/>
       <c r="B326" s="18"/>
       <c r="C326" s="17"/>
@@ -16225,8 +16929,10 @@
       <c r="J326" s="17"/>
       <c r="K326" s="17"/>
       <c r="L326" s="17"/>
-    </row>
-    <row r="327" spans="1:12">
+      <c r="M326" s="17"/>
+      <c r="N326" s="17"/>
+    </row>
+    <row r="327" spans="1:14">
       <c r="A327" s="17"/>
       <c r="B327" s="18"/>
       <c r="C327" s="17"/>
@@ -16239,8 +16945,10 @@
       <c r="J327" s="17"/>
       <c r="K327" s="17"/>
       <c r="L327" s="17"/>
-    </row>
-    <row r="328" spans="1:12">
+      <c r="M327" s="17"/>
+      <c r="N327" s="17"/>
+    </row>
+    <row r="328" spans="1:14">
       <c r="A328" s="17"/>
       <c r="B328" s="18"/>
       <c r="C328" s="17"/>
@@ -16253,8 +16961,10 @@
       <c r="J328" s="17"/>
       <c r="K328" s="17"/>
       <c r="L328" s="17"/>
-    </row>
-    <row r="329" spans="1:12">
+      <c r="M328" s="17"/>
+      <c r="N328" s="17"/>
+    </row>
+    <row r="329" spans="1:14">
       <c r="A329" s="17"/>
       <c r="B329" s="18"/>
       <c r="C329" s="17"/>
@@ -16267,8 +16977,10 @@
       <c r="J329" s="17"/>
       <c r="K329" s="17"/>
       <c r="L329" s="17"/>
-    </row>
-    <row r="330" spans="1:12">
+      <c r="M329" s="17"/>
+      <c r="N329" s="17"/>
+    </row>
+    <row r="330" spans="1:14">
       <c r="A330" s="17"/>
       <c r="B330" s="18"/>
       <c r="C330" s="17"/>
@@ -16281,8 +16993,10 @@
       <c r="J330" s="17"/>
       <c r="K330" s="17"/>
       <c r="L330" s="17"/>
-    </row>
-    <row r="331" spans="1:12">
+      <c r="M330" s="17"/>
+      <c r="N330" s="17"/>
+    </row>
+    <row r="331" spans="1:14">
       <c r="A331" s="17"/>
       <c r="B331" s="18"/>
       <c r="C331" s="17"/>
@@ -16295,8 +17009,10 @@
       <c r="J331" s="17"/>
       <c r="K331" s="17"/>
       <c r="L331" s="17"/>
-    </row>
-    <row r="332" spans="1:12">
+      <c r="M331" s="17"/>
+      <c r="N331" s="17"/>
+    </row>
+    <row r="332" spans="1:14">
       <c r="A332" s="17"/>
       <c r="B332" s="18"/>
       <c r="C332" s="17"/>
@@ -16309,8 +17025,10 @@
       <c r="J332" s="17"/>
       <c r="K332" s="17"/>
       <c r="L332" s="17"/>
-    </row>
-    <row r="333" spans="1:12">
+      <c r="M332" s="17"/>
+      <c r="N332" s="17"/>
+    </row>
+    <row r="333" spans="1:14">
       <c r="A333" s="17"/>
       <c r="B333" s="18"/>
       <c r="C333" s="17"/>
@@ -16323,8 +17041,10 @@
       <c r="J333" s="17"/>
       <c r="K333" s="17"/>
       <c r="L333" s="17"/>
-    </row>
-    <row r="334" spans="1:12">
+      <c r="M333" s="17"/>
+      <c r="N333" s="17"/>
+    </row>
+    <row r="334" spans="1:14">
       <c r="A334" s="17"/>
       <c r="B334" s="18"/>
       <c r="C334" s="17"/>
@@ -16337,8 +17057,10 @@
       <c r="J334" s="17"/>
       <c r="K334" s="17"/>
       <c r="L334" s="17"/>
-    </row>
-    <row r="335" spans="1:12">
+      <c r="M334" s="17"/>
+      <c r="N334" s="17"/>
+    </row>
+    <row r="335" spans="1:14">
       <c r="A335" s="17"/>
       <c r="B335" s="18"/>
       <c r="C335" s="17"/>
@@ -16351,8 +17073,10 @@
       <c r="J335" s="17"/>
       <c r="K335" s="17"/>
       <c r="L335" s="17"/>
-    </row>
-    <row r="336" spans="1:12">
+      <c r="M335" s="17"/>
+      <c r="N335" s="17"/>
+    </row>
+    <row r="336" spans="1:14">
       <c r="A336" s="17"/>
       <c r="B336" s="18"/>
       <c r="C336" s="17"/>
@@ -16365,8 +17089,10 @@
       <c r="J336" s="17"/>
       <c r="K336" s="17"/>
       <c r="L336" s="17"/>
-    </row>
-    <row r="337" spans="1:12">
+      <c r="M336" s="17"/>
+      <c r="N336" s="17"/>
+    </row>
+    <row r="337" spans="1:14">
       <c r="A337" s="17"/>
       <c r="B337" s="18"/>
       <c r="C337" s="17"/>
@@ -16379,8 +17105,10 @@
       <c r="J337" s="17"/>
       <c r="K337" s="17"/>
       <c r="L337" s="17"/>
-    </row>
-    <row r="338" spans="1:12">
+      <c r="M337" s="17"/>
+      <c r="N337" s="17"/>
+    </row>
+    <row r="338" spans="1:14">
       <c r="A338" s="17"/>
       <c r="B338" s="18"/>
       <c r="C338" s="17"/>
@@ -16393,8 +17121,10 @@
       <c r="J338" s="17"/>
       <c r="K338" s="17"/>
       <c r="L338" s="17"/>
-    </row>
-    <row r="339" spans="1:12">
+      <c r="M338" s="17"/>
+      <c r="N338" s="17"/>
+    </row>
+    <row r="339" spans="1:14">
       <c r="A339" s="17"/>
       <c r="B339" s="18"/>
       <c r="C339" s="17"/>
@@ -16407,8 +17137,10 @@
       <c r="J339" s="17"/>
       <c r="K339" s="17"/>
       <c r="L339" s="17"/>
-    </row>
-    <row r="340" spans="1:12">
+      <c r="M339" s="17"/>
+      <c r="N339" s="17"/>
+    </row>
+    <row r="340" spans="1:14">
       <c r="A340" s="17"/>
       <c r="B340" s="18"/>
       <c r="C340" s="17"/>
@@ -16421,8 +17153,10 @@
       <c r="J340" s="17"/>
       <c r="K340" s="17"/>
       <c r="L340" s="17"/>
-    </row>
-    <row r="341" spans="1:12">
+      <c r="M340" s="17"/>
+      <c r="N340" s="17"/>
+    </row>
+    <row r="341" spans="1:14">
       <c r="A341" s="17"/>
       <c r="B341" s="18"/>
       <c r="C341" s="17"/>
@@ -16435,8 +17169,10 @@
       <c r="J341" s="17"/>
       <c r="K341" s="17"/>
       <c r="L341" s="17"/>
-    </row>
-    <row r="342" spans="1:12">
+      <c r="M341" s="17"/>
+      <c r="N341" s="17"/>
+    </row>
+    <row r="342" spans="1:14">
       <c r="A342" s="17"/>
       <c r="B342" s="18"/>
       <c r="C342" s="17"/>
@@ -16449,8 +17185,10 @@
       <c r="J342" s="17"/>
       <c r="K342" s="17"/>
       <c r="L342" s="17"/>
-    </row>
-    <row r="343" spans="1:12">
+      <c r="M342" s="17"/>
+      <c r="N342" s="17"/>
+    </row>
+    <row r="343" spans="1:14">
       <c r="A343" s="17"/>
       <c r="B343" s="18"/>
       <c r="C343" s="17"/>
@@ -16463,8 +17201,10 @@
       <c r="J343" s="17"/>
       <c r="K343" s="17"/>
       <c r="L343" s="17"/>
-    </row>
-    <row r="344" spans="1:12">
+      <c r="M343" s="17"/>
+      <c r="N343" s="17"/>
+    </row>
+    <row r="344" spans="1:14">
       <c r="A344" s="17"/>
       <c r="B344" s="18"/>
       <c r="C344" s="17"/>
@@ -16477,8 +17217,10 @@
       <c r="J344" s="17"/>
       <c r="K344" s="17"/>
       <c r="L344" s="17"/>
-    </row>
-    <row r="345" spans="1:12">
+      <c r="M344" s="17"/>
+      <c r="N344" s="17"/>
+    </row>
+    <row r="345" spans="1:14">
       <c r="A345" s="17"/>
       <c r="B345" s="18"/>
       <c r="C345" s="17"/>
@@ -16491,8 +17233,10 @@
       <c r="J345" s="17"/>
       <c r="K345" s="17"/>
       <c r="L345" s="17"/>
-    </row>
-    <row r="346" spans="1:12">
+      <c r="M345" s="17"/>
+      <c r="N345" s="17"/>
+    </row>
+    <row r="346" spans="1:14">
       <c r="A346" s="17"/>
       <c r="B346" s="18"/>
       <c r="C346" s="17"/>
@@ -16505,8 +17249,10 @@
       <c r="J346" s="17"/>
       <c r="K346" s="17"/>
       <c r="L346" s="17"/>
-    </row>
-    <row r="347" spans="1:12">
+      <c r="M346" s="17"/>
+      <c r="N346" s="17"/>
+    </row>
+    <row r="347" spans="1:14">
       <c r="A347" s="17"/>
       <c r="B347" s="18"/>
       <c r="C347" s="17"/>
@@ -16519,8 +17265,10 @@
       <c r="J347" s="17"/>
       <c r="K347" s="17"/>
       <c r="L347" s="17"/>
-    </row>
-    <row r="348" spans="1:12">
+      <c r="M347" s="17"/>
+      <c r="N347" s="17"/>
+    </row>
+    <row r="348" spans="1:14">
       <c r="A348" s="17"/>
       <c r="B348" s="18"/>
       <c r="C348" s="17"/>
@@ -16533,8 +17281,10 @@
       <c r="J348" s="17"/>
       <c r="K348" s="17"/>
       <c r="L348" s="17"/>
-    </row>
-    <row r="349" spans="1:12">
+      <c r="M348" s="17"/>
+      <c r="N348" s="17"/>
+    </row>
+    <row r="349" spans="1:14">
       <c r="A349" s="17"/>
       <c r="B349" s="18"/>
       <c r="C349" s="17"/>
@@ -16547,8 +17297,10 @@
       <c r="J349" s="17"/>
       <c r="K349" s="17"/>
       <c r="L349" s="17"/>
-    </row>
-    <row r="350" spans="1:12">
+      <c r="M349" s="17"/>
+      <c r="N349" s="17"/>
+    </row>
+    <row r="350" spans="1:14">
       <c r="A350" s="17"/>
       <c r="B350" s="18"/>
       <c r="C350" s="17"/>
@@ -16561,8 +17313,10 @@
       <c r="J350" s="17"/>
       <c r="K350" s="17"/>
       <c r="L350" s="17"/>
-    </row>
-    <row r="351" spans="1:12">
+      <c r="M350" s="17"/>
+      <c r="N350" s="17"/>
+    </row>
+    <row r="351" spans="1:14">
       <c r="A351" s="17"/>
       <c r="B351" s="18"/>
       <c r="C351" s="17"/>
@@ -16575,8 +17329,10 @@
       <c r="J351" s="17"/>
       <c r="K351" s="17"/>
       <c r="L351" s="17"/>
-    </row>
-    <row r="352" spans="1:12">
+      <c r="M351" s="17"/>
+      <c r="N351" s="17"/>
+    </row>
+    <row r="352" spans="1:14">
       <c r="A352" s="17"/>
       <c r="B352" s="18"/>
       <c r="C352" s="17"/>
@@ -16589,8 +17345,10 @@
       <c r="J352" s="17"/>
       <c r="K352" s="17"/>
       <c r="L352" s="17"/>
-    </row>
-    <row r="353" spans="1:12">
+      <c r="M352" s="17"/>
+      <c r="N352" s="17"/>
+    </row>
+    <row r="353" spans="1:14">
       <c r="A353" s="17"/>
       <c r="B353" s="18"/>
       <c r="C353" s="17"/>
@@ -16603,8 +17361,10 @@
       <c r="J353" s="17"/>
       <c r="K353" s="17"/>
       <c r="L353" s="17"/>
-    </row>
-    <row r="354" spans="1:12">
+      <c r="M353" s="17"/>
+      <c r="N353" s="17"/>
+    </row>
+    <row r="354" spans="1:14">
       <c r="A354" s="17"/>
       <c r="B354" s="18"/>
       <c r="C354" s="17"/>
@@ -16617,8 +17377,10 @@
       <c r="J354" s="17"/>
       <c r="K354" s="17"/>
       <c r="L354" s="17"/>
-    </row>
-    <row r="355" spans="1:12">
+      <c r="M354" s="17"/>
+      <c r="N354" s="17"/>
+    </row>
+    <row r="355" spans="1:14">
       <c r="A355" s="17"/>
       <c r="B355" s="18"/>
       <c r="C355" s="17"/>
@@ -16631,8 +17393,10 @@
       <c r="J355" s="17"/>
       <c r="K355" s="17"/>
       <c r="L355" s="17"/>
-    </row>
-    <row r="356" spans="1:12">
+      <c r="M355" s="17"/>
+      <c r="N355" s="17"/>
+    </row>
+    <row r="356" spans="1:14">
       <c r="A356" s="17"/>
       <c r="B356" s="18"/>
       <c r="C356" s="17"/>
@@ -16645,8 +17409,10 @@
       <c r="J356" s="17"/>
       <c r="K356" s="17"/>
       <c r="L356" s="17"/>
-    </row>
-    <row r="357" spans="1:12">
+      <c r="M356" s="17"/>
+      <c r="N356" s="17"/>
+    </row>
+    <row r="357" spans="1:14">
       <c r="A357" s="17"/>
       <c r="B357" s="18"/>
       <c r="C357" s="17"/>
@@ -16659,8 +17425,10 @@
       <c r="J357" s="17"/>
       <c r="K357" s="17"/>
       <c r="L357" s="17"/>
-    </row>
-    <row r="358" spans="1:12">
+      <c r="M357" s="17"/>
+      <c r="N357" s="17"/>
+    </row>
+    <row r="358" spans="1:14">
       <c r="A358" s="17"/>
       <c r="B358" s="18"/>
       <c r="C358" s="17"/>
@@ -16673,8 +17441,10 @@
       <c r="J358" s="17"/>
       <c r="K358" s="17"/>
       <c r="L358" s="17"/>
-    </row>
-    <row r="359" spans="1:12">
+      <c r="M358" s="17"/>
+      <c r="N358" s="17"/>
+    </row>
+    <row r="359" spans="1:14">
       <c r="A359" s="17"/>
       <c r="B359" s="18"/>
       <c r="C359" s="17"/>
@@ -16687,8 +17457,10 @@
       <c r="J359" s="17"/>
       <c r="K359" s="17"/>
       <c r="L359" s="17"/>
-    </row>
-    <row r="360" spans="1:12">
+      <c r="M359" s="17"/>
+      <c r="N359" s="17"/>
+    </row>
+    <row r="360" spans="1:14">
       <c r="A360" s="17"/>
       <c r="B360" s="18"/>
       <c r="C360" s="17"/>
@@ -16701,8 +17473,10 @@
       <c r="J360" s="17"/>
       <c r="K360" s="17"/>
       <c r="L360" s="17"/>
-    </row>
-    <row r="361" spans="1:12">
+      <c r="M360" s="17"/>
+      <c r="N360" s="17"/>
+    </row>
+    <row r="361" spans="1:14">
       <c r="A361" s="17"/>
       <c r="B361" s="18"/>
       <c r="C361" s="17"/>
@@ -16715,8 +17489,10 @@
       <c r="J361" s="17"/>
       <c r="K361" s="17"/>
       <c r="L361" s="17"/>
-    </row>
-    <row r="362" spans="1:12">
+      <c r="M361" s="17"/>
+      <c r="N361" s="17"/>
+    </row>
+    <row r="362" spans="1:14">
       <c r="A362" s="17"/>
       <c r="B362" s="18"/>
       <c r="C362" s="17"/>
@@ -16729,8 +17505,10 @@
       <c r="J362" s="17"/>
       <c r="K362" s="17"/>
       <c r="L362" s="17"/>
-    </row>
-    <row r="363" spans="1:12">
+      <c r="M362" s="17"/>
+      <c r="N362" s="17"/>
+    </row>
+    <row r="363" spans="1:14">
       <c r="A363" s="17"/>
       <c r="B363" s="18"/>
       <c r="C363" s="17"/>
@@ -16743,8 +17521,10 @@
       <c r="J363" s="17"/>
       <c r="K363" s="17"/>
       <c r="L363" s="17"/>
-    </row>
-    <row r="364" spans="1:12">
+      <c r="M363" s="17"/>
+      <c r="N363" s="17"/>
+    </row>
+    <row r="364" spans="1:14">
       <c r="A364" s="17"/>
       <c r="B364" s="18"/>
       <c r="C364" s="17"/>
@@ -16757,8 +17537,10 @@
       <c r="J364" s="17"/>
       <c r="K364" s="17"/>
       <c r="L364" s="17"/>
-    </row>
-    <row r="365" spans="1:12">
+      <c r="M364" s="17"/>
+      <c r="N364" s="17"/>
+    </row>
+    <row r="365" spans="1:14">
       <c r="A365" s="17"/>
       <c r="B365" s="18"/>
       <c r="C365" s="17"/>
@@ -16771,8 +17553,10 @@
       <c r="J365" s="17"/>
       <c r="K365" s="17"/>
       <c r="L365" s="17"/>
-    </row>
-    <row r="366" spans="1:12">
+      <c r="M365" s="17"/>
+      <c r="N365" s="17"/>
+    </row>
+    <row r="366" spans="1:14">
       <c r="A366" s="17"/>
       <c r="B366" s="18"/>
       <c r="C366" s="17"/>
@@ -16785,8 +17569,10 @@
       <c r="J366" s="17"/>
       <c r="K366" s="17"/>
       <c r="L366" s="17"/>
-    </row>
-    <row r="367" spans="1:12">
+      <c r="M366" s="17"/>
+      <c r="N366" s="17"/>
+    </row>
+    <row r="367" spans="1:14">
       <c r="A367" s="17"/>
       <c r="B367" s="18"/>
       <c r="C367" s="17"/>
@@ -16799,8 +17585,10 @@
       <c r="J367" s="17"/>
       <c r="K367" s="17"/>
       <c r="L367" s="17"/>
-    </row>
-    <row r="368" spans="1:12">
+      <c r="M367" s="17"/>
+      <c r="N367" s="17"/>
+    </row>
+    <row r="368" spans="1:14">
       <c r="A368" s="17"/>
       <c r="B368" s="18"/>
       <c r="C368" s="17"/>
@@ -16813,8 +17601,10 @@
       <c r="J368" s="17"/>
       <c r="K368" s="17"/>
       <c r="L368" s="17"/>
-    </row>
-    <row r="369" spans="1:12">
+      <c r="M368" s="17"/>
+      <c r="N368" s="17"/>
+    </row>
+    <row r="369" spans="1:14">
       <c r="A369" s="17"/>
       <c r="B369" s="18"/>
       <c r="C369" s="17"/>
@@ -16827,8 +17617,10 @@
       <c r="J369" s="17"/>
       <c r="K369" s="17"/>
       <c r="L369" s="17"/>
-    </row>
-    <row r="370" spans="1:12">
+      <c r="M369" s="17"/>
+      <c r="N369" s="17"/>
+    </row>
+    <row r="370" spans="1:14">
       <c r="A370" s="17"/>
       <c r="B370" s="18"/>
       <c r="C370" s="17"/>
@@ -16841,8 +17633,10 @@
       <c r="J370" s="17"/>
       <c r="K370" s="17"/>
       <c r="L370" s="17"/>
-    </row>
-    <row r="371" spans="1:12">
+      <c r="M370" s="17"/>
+      <c r="N370" s="17"/>
+    </row>
+    <row r="371" spans="1:14">
       <c r="A371" s="17"/>
       <c r="B371" s="18"/>
       <c r="C371" s="17"/>
@@ -16855,8 +17649,10 @@
       <c r="J371" s="17"/>
       <c r="K371" s="17"/>
       <c r="L371" s="17"/>
-    </row>
-    <row r="372" spans="1:12">
+      <c r="M371" s="17"/>
+      <c r="N371" s="17"/>
+    </row>
+    <row r="372" spans="1:14">
       <c r="A372" s="17"/>
       <c r="B372" s="18"/>
       <c r="C372" s="17"/>
@@ -16869,8 +17665,10 @@
       <c r="J372" s="17"/>
       <c r="K372" s="17"/>
       <c r="L372" s="17"/>
-    </row>
-    <row r="373" spans="1:12">
+      <c r="M372" s="17"/>
+      <c r="N372" s="17"/>
+    </row>
+    <row r="373" spans="1:14">
       <c r="A373" s="17"/>
       <c r="B373" s="18"/>
       <c r="C373" s="17"/>
@@ -16883,8 +17681,10 @@
       <c r="J373" s="17"/>
       <c r="K373" s="17"/>
       <c r="L373" s="17"/>
-    </row>
-    <row r="374" spans="1:12">
+      <c r="M373" s="17"/>
+      <c r="N373" s="17"/>
+    </row>
+    <row r="374" spans="1:14">
       <c r="A374" s="17"/>
       <c r="B374" s="18"/>
       <c r="C374" s="17"/>
@@ -16897,8 +17697,10 @@
       <c r="J374" s="17"/>
       <c r="K374" s="17"/>
       <c r="L374" s="17"/>
-    </row>
-    <row r="375" spans="1:12">
+      <c r="M374" s="17"/>
+      <c r="N374" s="17"/>
+    </row>
+    <row r="375" spans="1:14">
       <c r="A375" s="17"/>
       <c r="B375" s="18"/>
       <c r="C375" s="17"/>
@@ -16911,8 +17713,10 @@
       <c r="J375" s="17"/>
       <c r="K375" s="17"/>
       <c r="L375" s="17"/>
-    </row>
-    <row r="376" spans="1:12">
+      <c r="M375" s="17"/>
+      <c r="N375" s="17"/>
+    </row>
+    <row r="376" spans="1:14">
       <c r="A376" s="17"/>
       <c r="B376" s="18"/>
       <c r="C376" s="17"/>
@@ -16925,8 +17729,10 @@
       <c r="J376" s="17"/>
       <c r="K376" s="17"/>
       <c r="L376" s="17"/>
-    </row>
-    <row r="377" spans="1:12">
+      <c r="M376" s="17"/>
+      <c r="N376" s="17"/>
+    </row>
+    <row r="377" spans="1:14">
       <c r="A377" s="17"/>
       <c r="B377" s="18"/>
       <c r="C377" s="17"/>
@@ -16939,8 +17745,10 @@
       <c r="J377" s="17"/>
       <c r="K377" s="17"/>
       <c r="L377" s="17"/>
-    </row>
-    <row r="378" spans="1:12">
+      <c r="M377" s="17"/>
+      <c r="N377" s="17"/>
+    </row>
+    <row r="378" spans="1:14">
       <c r="A378" s="17"/>
       <c r="B378" s="18"/>
       <c r="C378" s="17"/>
@@ -16953,8 +17761,10 @@
       <c r="J378" s="17"/>
       <c r="K378" s="17"/>
       <c r="L378" s="17"/>
-    </row>
-    <row r="379" spans="1:12">
+      <c r="M378" s="17"/>
+      <c r="N378" s="17"/>
+    </row>
+    <row r="379" spans="1:14">
       <c r="A379" s="17"/>
       <c r="B379" s="18"/>
       <c r="C379" s="17"/>
@@ -16967,8 +17777,10 @@
       <c r="J379" s="17"/>
       <c r="K379" s="17"/>
       <c r="L379" s="17"/>
-    </row>
-    <row r="380" spans="1:12">
+      <c r="M379" s="17"/>
+      <c r="N379" s="17"/>
+    </row>
+    <row r="380" spans="1:14">
       <c r="A380" s="17"/>
       <c r="B380" s="18"/>
       <c r="C380" s="17"/>
@@ -16981,8 +17793,10 @@
       <c r="J380" s="17"/>
       <c r="K380" s="17"/>
       <c r="L380" s="17"/>
-    </row>
-    <row r="381" spans="1:12">
+      <c r="M380" s="17"/>
+      <c r="N380" s="17"/>
+    </row>
+    <row r="381" spans="1:14">
       <c r="A381" s="17"/>
       <c r="B381" s="18"/>
       <c r="C381" s="17"/>
@@ -16995,8 +17809,10 @@
       <c r="J381" s="17"/>
       <c r="K381" s="17"/>
       <c r="L381" s="17"/>
-    </row>
-    <row r="382" spans="1:12">
+      <c r="M381" s="17"/>
+      <c r="N381" s="17"/>
+    </row>
+    <row r="382" spans="1:14">
       <c r="A382" s="17"/>
       <c r="B382" s="18"/>
       <c r="C382" s="17"/>
@@ -17009,8 +17825,10 @@
       <c r="J382" s="17"/>
       <c r="K382" s="17"/>
       <c r="L382" s="17"/>
-    </row>
-    <row r="383" spans="1:12">
+      <c r="M382" s="17"/>
+      <c r="N382" s="17"/>
+    </row>
+    <row r="383" spans="1:14">
       <c r="A383" s="17"/>
       <c r="B383" s="18"/>
       <c r="C383" s="17"/>
@@ -17023,8 +17841,10 @@
       <c r="J383" s="17"/>
       <c r="K383" s="17"/>
       <c r="L383" s="17"/>
-    </row>
-    <row r="384" spans="1:12">
+      <c r="M383" s="17"/>
+      <c r="N383" s="17"/>
+    </row>
+    <row r="384" spans="1:14">
       <c r="A384" s="17"/>
       <c r="B384" s="18"/>
       <c r="C384" s="17"/>
@@ -17037,8 +17857,10 @@
       <c r="J384" s="17"/>
       <c r="K384" s="17"/>
       <c r="L384" s="17"/>
-    </row>
-    <row r="385" spans="1:12">
+      <c r="M384" s="17"/>
+      <c r="N384" s="17"/>
+    </row>
+    <row r="385" spans="1:14">
       <c r="A385" s="17"/>
       <c r="B385" s="18"/>
       <c r="C385" s="17"/>
@@ -17051,8 +17873,10 @@
       <c r="J385" s="17"/>
       <c r="K385" s="17"/>
       <c r="L385" s="17"/>
-    </row>
-    <row r="386" spans="1:12">
+      <c r="M385" s="17"/>
+      <c r="N385" s="17"/>
+    </row>
+    <row r="386" spans="1:14">
       <c r="A386" s="17"/>
       <c r="B386" s="18"/>
       <c r="C386" s="17"/>
@@ -17065,8 +17889,10 @@
       <c r="J386" s="17"/>
       <c r="K386" s="17"/>
       <c r="L386" s="17"/>
-    </row>
-    <row r="387" spans="1:12">
+      <c r="M386" s="17"/>
+      <c r="N386" s="17"/>
+    </row>
+    <row r="387" spans="1:14">
       <c r="A387" s="17"/>
       <c r="B387" s="18"/>
       <c r="C387" s="17"/>
@@ -17079,8 +17905,10 @@
       <c r="J387" s="17"/>
       <c r="K387" s="17"/>
       <c r="L387" s="17"/>
-    </row>
-    <row r="388" spans="1:12">
+      <c r="M387" s="17"/>
+      <c r="N387" s="17"/>
+    </row>
+    <row r="388" spans="1:14">
       <c r="A388" s="17"/>
       <c r="B388" s="18"/>
       <c r="C388" s="17"/>
@@ -17093,8 +17921,10 @@
       <c r="J388" s="17"/>
       <c r="K388" s="17"/>
       <c r="L388" s="17"/>
-    </row>
-    <row r="389" spans="1:12">
+      <c r="M388" s="17"/>
+      <c r="N388" s="17"/>
+    </row>
+    <row r="389" spans="1:14">
       <c r="A389" s="17"/>
       <c r="B389" s="18"/>
       <c r="C389" s="17"/>
@@ -17107,8 +17937,10 @@
       <c r="J389" s="17"/>
       <c r="K389" s="17"/>
       <c r="L389" s="17"/>
-    </row>
-    <row r="390" spans="1:12">
+      <c r="M389" s="17"/>
+      <c r="N389" s="17"/>
+    </row>
+    <row r="390" spans="1:14">
       <c r="A390" s="17"/>
       <c r="B390" s="18"/>
       <c r="C390" s="17"/>
@@ -17121,8 +17953,10 @@
       <c r="J390" s="17"/>
       <c r="K390" s="17"/>
       <c r="L390" s="17"/>
-    </row>
-    <row r="391" spans="1:12">
+      <c r="M390" s="17"/>
+      <c r="N390" s="17"/>
+    </row>
+    <row r="391" spans="1:14">
       <c r="A391" s="17"/>
       <c r="B391" s="18"/>
       <c r="C391" s="17"/>
@@ -17135,8 +17969,10 @@
       <c r="J391" s="17"/>
       <c r="K391" s="17"/>
       <c r="L391" s="17"/>
-    </row>
-    <row r="392" spans="1:12">
+      <c r="M391" s="17"/>
+      <c r="N391" s="17"/>
+    </row>
+    <row r="392" spans="1:14">
       <c r="A392" s="17"/>
       <c r="B392" s="18"/>
       <c r="C392" s="17"/>
@@ -17149,8 +17985,10 @@
       <c r="J392" s="17"/>
       <c r="K392" s="17"/>
       <c r="L392" s="17"/>
-    </row>
-    <row r="393" spans="1:12">
+      <c r="M392" s="17"/>
+      <c r="N392" s="17"/>
+    </row>
+    <row r="393" spans="1:14">
       <c r="A393" s="17"/>
       <c r="B393" s="18"/>
       <c r="C393" s="17"/>
@@ -17163,8 +18001,10 @@
       <c r="J393" s="17"/>
       <c r="K393" s="17"/>
       <c r="L393" s="17"/>
-    </row>
-    <row r="394" spans="1:12">
+      <c r="M393" s="17"/>
+      <c r="N393" s="17"/>
+    </row>
+    <row r="394" spans="1:14">
       <c r="A394" s="17"/>
       <c r="B394" s="18"/>
       <c r="C394" s="17"/>
@@ -17177,8 +18017,10 @@
       <c r="J394" s="17"/>
       <c r="K394" s="17"/>
       <c r="L394" s="17"/>
-    </row>
-    <row r="395" spans="1:12">
+      <c r="M394" s="17"/>
+      <c r="N394" s="17"/>
+    </row>
+    <row r="395" spans="1:14">
       <c r="A395" s="17"/>
       <c r="B395" s="18"/>
       <c r="C395" s="17"/>
@@ -17191,8 +18033,10 @@
       <c r="J395" s="17"/>
       <c r="K395" s="17"/>
       <c r="L395" s="17"/>
-    </row>
-    <row r="396" spans="1:12">
+      <c r="M395" s="17"/>
+      <c r="N395" s="17"/>
+    </row>
+    <row r="396" spans="1:14">
       <c r="A396" s="17"/>
       <c r="B396" s="18"/>
       <c r="C396" s="17"/>
@@ -17205,8 +18049,10 @@
       <c r="J396" s="17"/>
       <c r="K396" s="17"/>
       <c r="L396" s="17"/>
-    </row>
-    <row r="397" spans="1:12">
+      <c r="M396" s="17"/>
+      <c r="N396" s="17"/>
+    </row>
+    <row r="397" spans="1:14">
       <c r="A397" s="17"/>
       <c r="B397" s="18"/>
       <c r="C397" s="17"/>
@@ -17219,8 +18065,10 @@
       <c r="J397" s="17"/>
       <c r="K397" s="17"/>
       <c r="L397" s="17"/>
-    </row>
-    <row r="398" spans="1:12">
+      <c r="M397" s="17"/>
+      <c r="N397" s="17"/>
+    </row>
+    <row r="398" spans="1:14">
       <c r="A398" s="17"/>
       <c r="B398" s="18"/>
       <c r="C398" s="17"/>
@@ -17233,8 +18081,10 @@
       <c r="J398" s="17"/>
       <c r="K398" s="17"/>
       <c r="L398" s="17"/>
-    </row>
-    <row r="399" spans="1:12">
+      <c r="M398" s="17"/>
+      <c r="N398" s="17"/>
+    </row>
+    <row r="399" spans="1:14">
       <c r="A399" s="17"/>
       <c r="B399" s="18"/>
       <c r="C399" s="17"/>
@@ -17247,8 +18097,10 @@
       <c r="J399" s="17"/>
       <c r="K399" s="17"/>
       <c r="L399" s="17"/>
-    </row>
-    <row r="400" spans="1:12">
+      <c r="M399" s="17"/>
+      <c r="N399" s="17"/>
+    </row>
+    <row r="400" spans="1:14">
       <c r="A400" s="17"/>
       <c r="B400" s="18"/>
       <c r="C400" s="17"/>
@@ -17261,8 +18113,10 @@
       <c r="J400" s="17"/>
       <c r="K400" s="17"/>
       <c r="L400" s="17"/>
-    </row>
-    <row r="401" spans="1:12">
+      <c r="M400" s="17"/>
+      <c r="N400" s="17"/>
+    </row>
+    <row r="401" spans="1:14">
       <c r="A401" s="17"/>
       <c r="B401" s="18"/>
       <c r="C401" s="17"/>
@@ -17275,8 +18129,10 @@
       <c r="J401" s="17"/>
       <c r="K401" s="17"/>
       <c r="L401" s="17"/>
-    </row>
-    <row r="402" spans="1:12">
+      <c r="M401" s="17"/>
+      <c r="N401" s="17"/>
+    </row>
+    <row r="402" spans="1:14">
       <c r="A402" s="17"/>
       <c r="B402" s="18"/>
       <c r="C402" s="17"/>
@@ -17289,8 +18145,10 @@
       <c r="J402" s="17"/>
       <c r="K402" s="17"/>
       <c r="L402" s="17"/>
-    </row>
-    <row r="403" spans="1:12">
+      <c r="M402" s="17"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14">
       <c r="A403" s="17"/>
       <c r="B403" s="18"/>
       <c r="C403" s="17"/>
@@ -17303,8 +18161,10 @@
       <c r="J403" s="17"/>
       <c r="K403" s="17"/>
       <c r="L403" s="17"/>
-    </row>
-    <row r="404" spans="1:12">
+      <c r="M403" s="17"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14">
       <c r="A404" s="17"/>
       <c r="B404" s="18"/>
       <c r="C404" s="17"/>
@@ -17317,8 +18177,10 @@
       <c r="J404" s="17"/>
       <c r="K404" s="17"/>
       <c r="L404" s="17"/>
-    </row>
-    <row r="405" spans="1:12">
+      <c r="M404" s="17"/>
+      <c r="N404" s="17"/>
+    </row>
+    <row r="405" spans="1:14">
       <c r="A405" s="17"/>
       <c r="B405" s="18"/>
       <c r="C405" s="17"/>
@@ -17331,8 +18193,10 @@
       <c r="J405" s="17"/>
       <c r="K405" s="17"/>
       <c r="L405" s="17"/>
-    </row>
-    <row r="406" spans="1:12">
+      <c r="M405" s="17"/>
+      <c r="N405" s="17"/>
+    </row>
+    <row r="406" spans="1:14">
       <c r="A406" s="17"/>
       <c r="B406" s="18"/>
       <c r="C406" s="17"/>
@@ -17345,8 +18209,10 @@
       <c r="J406" s="17"/>
       <c r="K406" s="17"/>
       <c r="L406" s="17"/>
-    </row>
-    <row r="407" spans="1:12">
+      <c r="M406" s="17"/>
+      <c r="N406" s="17"/>
+    </row>
+    <row r="407" spans="1:14">
       <c r="A407" s="17"/>
       <c r="B407" s="18"/>
       <c r="C407" s="17"/>
@@ -17359,8 +18225,10 @@
       <c r="J407" s="17"/>
       <c r="K407" s="17"/>
       <c r="L407" s="17"/>
-    </row>
-    <row r="408" spans="1:12">
+      <c r="M407" s="17"/>
+      <c r="N407" s="17"/>
+    </row>
+    <row r="408" spans="1:14">
       <c r="A408" s="17"/>
       <c r="B408" s="18"/>
       <c r="C408" s="17"/>
@@ -17373,8 +18241,10 @@
       <c r="J408" s="17"/>
       <c r="K408" s="17"/>
       <c r="L408" s="17"/>
-    </row>
-    <row r="409" spans="1:12">
+      <c r="M408" s="17"/>
+      <c r="N408" s="17"/>
+    </row>
+    <row r="409" spans="1:14">
       <c r="A409" s="17"/>
       <c r="B409" s="18"/>
       <c r="C409" s="17"/>
@@ -17387,8 +18257,10 @@
       <c r="J409" s="17"/>
       <c r="K409" s="17"/>
       <c r="L409" s="17"/>
-    </row>
-    <row r="410" spans="1:12">
+      <c r="M409" s="17"/>
+      <c r="N409" s="17"/>
+    </row>
+    <row r="410" spans="1:14">
       <c r="A410" s="17"/>
       <c r="B410" s="18"/>
       <c r="C410" s="17"/>
@@ -17401,8 +18273,10 @@
       <c r="J410" s="17"/>
       <c r="K410" s="17"/>
       <c r="L410" s="17"/>
-    </row>
-    <row r="411" spans="1:12">
+      <c r="M410" s="17"/>
+      <c r="N410" s="17"/>
+    </row>
+    <row r="411" spans="1:14">
       <c r="A411" s="17"/>
       <c r="B411" s="18"/>
       <c r="C411" s="17"/>
@@ -17415,8 +18289,10 @@
       <c r="J411" s="17"/>
       <c r="K411" s="17"/>
       <c r="L411" s="17"/>
-    </row>
-    <row r="412" spans="1:12">
+      <c r="M411" s="17"/>
+      <c r="N411" s="17"/>
+    </row>
+    <row r="412" spans="1:14">
       <c r="A412" s="17"/>
       <c r="B412" s="18"/>
       <c r="C412" s="17"/>
@@ -17429,8 +18305,10 @@
       <c r="J412" s="17"/>
       <c r="K412" s="17"/>
       <c r="L412" s="17"/>
-    </row>
-    <row r="413" spans="1:12">
+      <c r="M412" s="17"/>
+      <c r="N412" s="17"/>
+    </row>
+    <row r="413" spans="1:14">
       <c r="A413" s="17"/>
       <c r="B413" s="18"/>
       <c r="C413" s="17"/>
@@ -17443,8 +18321,10 @@
       <c r="J413" s="17"/>
       <c r="K413" s="17"/>
       <c r="L413" s="17"/>
-    </row>
-    <row r="414" spans="1:12">
+      <c r="M413" s="17"/>
+      <c r="N413" s="17"/>
+    </row>
+    <row r="414" spans="1:14">
       <c r="A414" s="17"/>
       <c r="B414" s="18"/>
       <c r="C414" s="17"/>
@@ -17457,8 +18337,10 @@
       <c r="J414" s="17"/>
       <c r="K414" s="17"/>
       <c r="L414" s="17"/>
-    </row>
-    <row r="415" spans="1:12">
+      <c r="M414" s="17"/>
+      <c r="N414" s="17"/>
+    </row>
+    <row r="415" spans="1:14">
       <c r="A415" s="17"/>
       <c r="B415" s="18"/>
       <c r="C415" s="17"/>
@@ -17471,8 +18353,10 @@
       <c r="J415" s="17"/>
       <c r="K415" s="17"/>
       <c r="L415" s="17"/>
-    </row>
-    <row r="416" spans="1:12">
+      <c r="M415" s="17"/>
+      <c r="N415" s="17"/>
+    </row>
+    <row r="416" spans="1:14">
       <c r="A416" s="17"/>
       <c r="B416" s="18"/>
       <c r="C416" s="17"/>
@@ -17485,8 +18369,10 @@
       <c r="J416" s="17"/>
       <c r="K416" s="17"/>
       <c r="L416" s="17"/>
-    </row>
-    <row r="417" spans="1:12">
+      <c r="M416" s="17"/>
+      <c r="N416" s="17"/>
+    </row>
+    <row r="417" spans="1:14">
       <c r="A417" s="17"/>
       <c r="B417" s="18"/>
       <c r="C417" s="17"/>
@@ -17499,8 +18385,10 @@
       <c r="J417" s="17"/>
       <c r="K417" s="17"/>
       <c r="L417" s="17"/>
-    </row>
-    <row r="418" spans="1:12">
+      <c r="M417" s="17"/>
+      <c r="N417" s="17"/>
+    </row>
+    <row r="418" spans="1:14">
       <c r="A418" s="17"/>
       <c r="B418" s="18"/>
       <c r="C418" s="17"/>
@@ -17513,8 +18401,10 @@
       <c r="J418" s="17"/>
       <c r="K418" s="17"/>
       <c r="L418" s="17"/>
-    </row>
-    <row r="419" spans="1:12">
+      <c r="M418" s="17"/>
+      <c r="N418" s="17"/>
+    </row>
+    <row r="419" spans="1:14">
       <c r="A419" s="17"/>
       <c r="B419" s="18"/>
       <c r="C419" s="17"/>
@@ -17527,8 +18417,10 @@
       <c r="J419" s="17"/>
       <c r="K419" s="17"/>
       <c r="L419" s="17"/>
-    </row>
-    <row r="420" spans="1:12">
+      <c r="M419" s="17"/>
+      <c r="N419" s="17"/>
+    </row>
+    <row r="420" spans="1:14">
       <c r="A420" s="17"/>
       <c r="B420" s="18"/>
       <c r="C420" s="17"/>
@@ -17541,8 +18433,10 @@
       <c r="J420" s="17"/>
       <c r="K420" s="17"/>
       <c r="L420" s="17"/>
-    </row>
-    <row r="421" spans="1:12">
+      <c r="M420" s="17"/>
+      <c r="N420" s="17"/>
+    </row>
+    <row r="421" spans="1:14">
       <c r="A421" s="17"/>
       <c r="B421" s="18"/>
       <c r="C421" s="17"/>
@@ -17555,8 +18449,10 @@
       <c r="J421" s="17"/>
       <c r="K421" s="17"/>
       <c r="L421" s="17"/>
-    </row>
-    <row r="422" spans="1:12">
+      <c r="M421" s="17"/>
+      <c r="N421" s="17"/>
+    </row>
+    <row r="422" spans="1:14">
       <c r="A422" s="17"/>
       <c r="B422" s="18"/>
       <c r="C422" s="17"/>
@@ -17569,8 +18465,10 @@
       <c r="J422" s="17"/>
       <c r="K422" s="17"/>
       <c r="L422" s="17"/>
-    </row>
-    <row r="423" spans="1:12">
+      <c r="M422" s="17"/>
+      <c r="N422" s="17"/>
+    </row>
+    <row r="423" spans="1:14">
       <c r="A423" s="17"/>
       <c r="B423" s="18"/>
       <c r="C423" s="17"/>
@@ -17583,8 +18481,10 @@
       <c r="J423" s="17"/>
       <c r="K423" s="17"/>
       <c r="L423" s="17"/>
-    </row>
-    <row r="424" spans="1:12">
+      <c r="M423" s="17"/>
+      <c r="N423" s="17"/>
+    </row>
+    <row r="424" spans="1:14">
       <c r="A424" s="17"/>
       <c r="B424" s="18"/>
       <c r="C424" s="17"/>
@@ -17597,8 +18497,10 @@
       <c r="J424" s="17"/>
       <c r="K424" s="17"/>
       <c r="L424" s="17"/>
-    </row>
-    <row r="425" spans="1:12">
+      <c r="M424" s="17"/>
+      <c r="N424" s="17"/>
+    </row>
+    <row r="425" spans="1:14">
       <c r="A425" s="17"/>
       <c r="B425" s="18"/>
       <c r="C425" s="17"/>
@@ -17611,8 +18513,10 @@
       <c r="J425" s="17"/>
       <c r="K425" s="17"/>
       <c r="L425" s="17"/>
-    </row>
-    <row r="426" spans="1:12">
+      <c r="M425" s="17"/>
+      <c r="N425" s="17"/>
+    </row>
+    <row r="426" spans="1:14">
       <c r="A426" s="17"/>
       <c r="B426" s="18"/>
       <c r="C426" s="17"/>
@@ -17625,8 +18529,10 @@
       <c r="J426" s="17"/>
       <c r="K426" s="17"/>
       <c r="L426" s="17"/>
-    </row>
-    <row r="427" spans="1:12">
+      <c r="M426" s="17"/>
+      <c r="N426" s="17"/>
+    </row>
+    <row r="427" spans="1:14">
       <c r="A427" s="17"/>
       <c r="B427" s="18"/>
       <c r="C427" s="17"/>
@@ -17639,8 +18545,10 @@
       <c r="J427" s="17"/>
       <c r="K427" s="17"/>
       <c r="L427" s="17"/>
-    </row>
-    <row r="428" spans="1:12">
+      <c r="M427" s="17"/>
+      <c r="N427" s="17"/>
+    </row>
+    <row r="428" spans="1:14">
       <c r="A428" s="17"/>
       <c r="B428" s="18"/>
       <c r="C428" s="17"/>
@@ -17653,8 +18561,10 @@
       <c r="J428" s="17"/>
       <c r="K428" s="17"/>
       <c r="L428" s="17"/>
-    </row>
-    <row r="429" spans="1:12">
+      <c r="M428" s="17"/>
+      <c r="N428" s="17"/>
+    </row>
+    <row r="429" spans="1:14">
       <c r="A429" s="17"/>
       <c r="B429" s="18"/>
       <c r="C429" s="17"/>
@@ -17667,8 +18577,10 @@
       <c r="J429" s="17"/>
       <c r="K429" s="17"/>
       <c r="L429" s="17"/>
-    </row>
-    <row r="430" spans="1:12">
+      <c r="M429" s="17"/>
+      <c r="N429" s="17"/>
+    </row>
+    <row r="430" spans="1:14">
       <c r="A430" s="17"/>
       <c r="B430" s="18"/>
       <c r="C430" s="17"/>
@@ -17681,8 +18593,10 @@
       <c r="J430" s="17"/>
       <c r="K430" s="17"/>
       <c r="L430" s="17"/>
-    </row>
-    <row r="431" spans="1:12">
+      <c r="M430" s="17"/>
+      <c r="N430" s="17"/>
+    </row>
+    <row r="431" spans="1:14">
       <c r="A431" s="17"/>
       <c r="B431" s="18"/>
       <c r="C431" s="17"/>
@@ -17695,8 +18609,10 @@
       <c r="J431" s="17"/>
       <c r="K431" s="17"/>
       <c r="L431" s="17"/>
-    </row>
-    <row r="432" spans="1:12">
+      <c r="M431" s="17"/>
+      <c r="N431" s="17"/>
+    </row>
+    <row r="432" spans="1:14">
       <c r="A432" s="17"/>
       <c r="B432" s="18"/>
       <c r="C432" s="17"/>
@@ -17709,8 +18625,10 @@
       <c r="J432" s="17"/>
       <c r="K432" s="17"/>
       <c r="L432" s="17"/>
-    </row>
-    <row r="433" spans="1:12">
+      <c r="M432" s="17"/>
+      <c r="N432" s="17"/>
+    </row>
+    <row r="433" spans="1:14">
       <c r="A433" s="17"/>
       <c r="B433" s="18"/>
       <c r="C433" s="17"/>
@@ -17723,8 +18641,10 @@
       <c r="J433" s="17"/>
       <c r="K433" s="17"/>
       <c r="L433" s="17"/>
-    </row>
-    <row r="434" spans="1:12">
+      <c r="M433" s="17"/>
+      <c r="N433" s="17"/>
+    </row>
+    <row r="434" spans="1:14">
       <c r="A434" s="17"/>
       <c r="B434" s="18"/>
       <c r="C434" s="17"/>
@@ -17737,8 +18657,10 @@
       <c r="J434" s="17"/>
       <c r="K434" s="17"/>
       <c r="L434" s="17"/>
-    </row>
-    <row r="435" spans="1:12">
+      <c r="M434" s="17"/>
+      <c r="N434" s="17"/>
+    </row>
+    <row r="435" spans="1:14">
       <c r="A435" s="17"/>
       <c r="B435" s="18"/>
       <c r="C435" s="17"/>
@@ -17751,8 +18673,10 @@
       <c r="J435" s="17"/>
       <c r="K435" s="17"/>
       <c r="L435" s="17"/>
-    </row>
-    <row r="436" spans="1:12">
+      <c r="M435" s="17"/>
+      <c r="N435" s="17"/>
+    </row>
+    <row r="436" spans="1:14">
       <c r="A436" s="17"/>
       <c r="B436" s="18"/>
       <c r="C436" s="17"/>
@@ -17765,8 +18689,10 @@
       <c r="J436" s="17"/>
       <c r="K436" s="17"/>
       <c r="L436" s="17"/>
-    </row>
-    <row r="437" spans="1:12">
+      <c r="M436" s="17"/>
+      <c r="N436" s="17"/>
+    </row>
+    <row r="437" spans="1:14">
       <c r="A437" s="17"/>
       <c r="B437" s="18"/>
       <c r="C437" s="17"/>
@@ -17779,8 +18705,10 @@
       <c r="J437" s="17"/>
       <c r="K437" s="17"/>
       <c r="L437" s="17"/>
-    </row>
-    <row r="438" spans="1:12">
+      <c r="M437" s="17"/>
+      <c r="N437" s="17"/>
+    </row>
+    <row r="438" spans="1:14">
       <c r="A438" s="17"/>
       <c r="B438" s="18"/>
       <c r="C438" s="17"/>
@@ -17793,8 +18721,10 @@
       <c r="J438" s="17"/>
       <c r="K438" s="17"/>
       <c r="L438" s="17"/>
-    </row>
-    <row r="439" spans="1:12">
+      <c r="M438" s="17"/>
+      <c r="N438" s="17"/>
+    </row>
+    <row r="439" spans="1:14">
       <c r="A439" s="17"/>
       <c r="B439" s="18"/>
       <c r="C439" s="17"/>
@@ -17807,8 +18737,10 @@
       <c r="J439" s="17"/>
       <c r="K439" s="17"/>
       <c r="L439" s="17"/>
-    </row>
-    <row r="440" spans="1:12">
+      <c r="M439" s="17"/>
+      <c r="N439" s="17"/>
+    </row>
+    <row r="440" spans="1:14">
       <c r="A440" s="17"/>
       <c r="B440" s="18"/>
       <c r="C440" s="17"/>
@@ -17821,8 +18753,10 @@
       <c r="J440" s="17"/>
       <c r="K440" s="17"/>
       <c r="L440" s="17"/>
-    </row>
-    <row r="441" spans="1:12">
+      <c r="M440" s="17"/>
+      <c r="N440" s="17"/>
+    </row>
+    <row r="441" spans="1:14">
       <c r="A441" s="17"/>
       <c r="B441" s="18"/>
       <c r="C441" s="17"/>
@@ -17835,8 +18769,10 @@
       <c r="J441" s="17"/>
       <c r="K441" s="17"/>
       <c r="L441" s="17"/>
-    </row>
-    <row r="442" spans="1:12">
+      <c r="M441" s="17"/>
+      <c r="N441" s="17"/>
+    </row>
+    <row r="442" spans="1:14">
       <c r="A442" s="17"/>
       <c r="B442" s="18"/>
       <c r="C442" s="17"/>
@@ -17849,8 +18785,10 @@
       <c r="J442" s="17"/>
       <c r="K442" s="17"/>
       <c r="L442" s="17"/>
-    </row>
-    <row r="443" spans="1:12">
+      <c r="M442" s="17"/>
+      <c r="N442" s="17"/>
+    </row>
+    <row r="443" spans="1:14">
       <c r="A443" s="17"/>
       <c r="B443" s="18"/>
       <c r="C443" s="17"/>
@@ -17863,8 +18801,10 @@
       <c r="J443" s="17"/>
       <c r="K443" s="17"/>
       <c r="L443" s="17"/>
-    </row>
-    <row r="444" spans="1:12">
+      <c r="M443" s="17"/>
+      <c r="N443" s="17"/>
+    </row>
+    <row r="444" spans="1:14">
       <c r="A444" s="17"/>
       <c r="B444" s="18"/>
       <c r="C444" s="17"/>
@@ -17877,8 +18817,10 @@
       <c r="J444" s="17"/>
       <c r="K444" s="17"/>
       <c r="L444" s="17"/>
-    </row>
-    <row r="445" spans="1:12">
+      <c r="M444" s="17"/>
+      <c r="N444" s="17"/>
+    </row>
+    <row r="445" spans="1:14">
       <c r="A445" s="17"/>
       <c r="B445" s="18"/>
       <c r="C445" s="17"/>
@@ -17891,8 +18833,10 @@
       <c r="J445" s="17"/>
       <c r="K445" s="17"/>
       <c r="L445" s="17"/>
-    </row>
-    <row r="446" spans="1:12">
+      <c r="M445" s="17"/>
+      <c r="N445" s="17"/>
+    </row>
+    <row r="446" spans="1:14">
       <c r="A446" s="17"/>
       <c r="B446" s="18"/>
       <c r="C446" s="17"/>
@@ -17905,8 +18849,10 @@
       <c r="J446" s="17"/>
       <c r="K446" s="17"/>
       <c r="L446" s="17"/>
-    </row>
-    <row r="447" spans="1:12">
+      <c r="M446" s="17"/>
+      <c r="N446" s="17"/>
+    </row>
+    <row r="447" spans="1:14">
       <c r="A447" s="17"/>
       <c r="B447" s="18"/>
       <c r="C447" s="17"/>
@@ -17919,8 +18865,10 @@
       <c r="J447" s="17"/>
       <c r="K447" s="17"/>
       <c r="L447" s="17"/>
-    </row>
-    <row r="448" spans="1:12">
+      <c r="M447" s="17"/>
+      <c r="N447" s="17"/>
+    </row>
+    <row r="448" spans="1:14">
       <c r="A448" s="17"/>
       <c r="B448" s="18"/>
       <c r="C448" s="17"/>
@@ -17933,8 +18881,10 @@
       <c r="J448" s="17"/>
       <c r="K448" s="17"/>
       <c r="L448" s="17"/>
-    </row>
-    <row r="449" spans="1:12">
+      <c r="M448" s="17"/>
+      <c r="N448" s="17"/>
+    </row>
+    <row r="449" spans="1:14">
       <c r="A449" s="17"/>
       <c r="B449" s="18"/>
       <c r="C449" s="17"/>
@@ -17947,8 +18897,10 @@
       <c r="J449" s="17"/>
       <c r="K449" s="17"/>
       <c r="L449" s="17"/>
-    </row>
-    <row r="450" spans="1:12">
+      <c r="M449" s="17"/>
+      <c r="N449" s="17"/>
+    </row>
+    <row r="450" spans="1:14">
       <c r="A450" s="17"/>
       <c r="B450" s="18"/>
       <c r="C450" s="17"/>
@@ -17961,8 +18913,10 @@
       <c r="J450" s="17"/>
       <c r="K450" s="17"/>
       <c r="L450" s="17"/>
-    </row>
-    <row r="451" spans="1:12">
+      <c r="M450" s="17"/>
+      <c r="N450" s="17"/>
+    </row>
+    <row r="451" spans="1:14">
       <c r="A451" s="17"/>
       <c r="B451" s="18"/>
       <c r="C451" s="17"/>
@@ -17975,8 +18929,10 @@
       <c r="J451" s="17"/>
       <c r="K451" s="17"/>
       <c r="L451" s="17"/>
-    </row>
-    <row r="452" spans="1:12">
+      <c r="M451" s="17"/>
+      <c r="N451" s="17"/>
+    </row>
+    <row r="452" spans="1:14">
       <c r="A452" s="17"/>
       <c r="B452" s="18"/>
       <c r="C452" s="17"/>
@@ -17989,8 +18945,10 @@
       <c r="J452" s="17"/>
       <c r="K452" s="17"/>
       <c r="L452" s="17"/>
-    </row>
-    <row r="453" spans="1:12">
+      <c r="M452" s="17"/>
+      <c r="N452" s="17"/>
+    </row>
+    <row r="453" spans="1:14">
       <c r="A453" s="17"/>
       <c r="B453" s="18"/>
       <c r="C453" s="17"/>
@@ -18003,8 +18961,10 @@
       <c r="J453" s="17"/>
       <c r="K453" s="17"/>
       <c r="L453" s="17"/>
-    </row>
-    <row r="454" spans="1:12">
+      <c r="M453" s="17"/>
+      <c r="N453" s="17"/>
+    </row>
+    <row r="454" spans="1:14">
       <c r="A454" s="17"/>
       <c r="B454" s="18"/>
       <c r="C454" s="17"/>
@@ -18017,8 +18977,10 @@
       <c r="J454" s="17"/>
       <c r="K454" s="17"/>
       <c r="L454" s="17"/>
-    </row>
-    <row r="455" spans="1:12">
+      <c r="M454" s="17"/>
+      <c r="N454" s="17"/>
+    </row>
+    <row r="455" spans="1:14">
       <c r="A455" s="17"/>
       <c r="B455" s="18"/>
       <c r="C455" s="17"/>
@@ -18031,8 +18993,10 @@
       <c r="J455" s="17"/>
       <c r="K455" s="17"/>
       <c r="L455" s="17"/>
-    </row>
-    <row r="456" spans="1:12">
+      <c r="M455" s="17"/>
+      <c r="N455" s="17"/>
+    </row>
+    <row r="456" spans="1:14">
       <c r="A456" s="17"/>
       <c r="B456" s="18"/>
       <c r="C456" s="17"/>
@@ -18045,8 +19009,10 @@
       <c r="J456" s="17"/>
       <c r="K456" s="17"/>
       <c r="L456" s="17"/>
-    </row>
-    <row r="457" spans="1:12">
+      <c r="M456" s="17"/>
+      <c r="N456" s="17"/>
+    </row>
+    <row r="457" spans="1:14">
       <c r="A457" s="17"/>
       <c r="B457" s="18"/>
       <c r="C457" s="17"/>
@@ -18059,8 +19025,10 @@
       <c r="J457" s="17"/>
       <c r="K457" s="17"/>
       <c r="L457" s="17"/>
-    </row>
-    <row r="458" spans="1:12">
+      <c r="M457" s="17"/>
+      <c r="N457" s="17"/>
+    </row>
+    <row r="458" spans="1:14">
       <c r="A458" s="17"/>
       <c r="B458" s="18"/>
       <c r="C458" s="17"/>
@@ -18073,8 +19041,10 @@
       <c r="J458" s="17"/>
       <c r="K458" s="17"/>
       <c r="L458" s="17"/>
-    </row>
-    <row r="459" spans="1:12">
+      <c r="M458" s="17"/>
+      <c r="N458" s="17"/>
+    </row>
+    <row r="459" spans="1:14">
       <c r="A459" s="17"/>
       <c r="B459" s="18"/>
       <c r="C459" s="17"/>
@@ -18087,8 +19057,10 @@
       <c r="J459" s="17"/>
       <c r="K459" s="17"/>
       <c r="L459" s="17"/>
-    </row>
-    <row r="460" spans="1:12">
+      <c r="M459" s="17"/>
+      <c r="N459" s="17"/>
+    </row>
+    <row r="460" spans="1:14">
       <c r="A460" s="17"/>
       <c r="B460" s="18"/>
       <c r="C460" s="17"/>
@@ -18101,8 +19073,10 @@
       <c r="J460" s="17"/>
       <c r="K460" s="17"/>
       <c r="L460" s="17"/>
-    </row>
-    <row r="461" spans="1:12">
+      <c r="M460" s="17"/>
+      <c r="N460" s="17"/>
+    </row>
+    <row r="461" spans="1:14">
       <c r="A461" s="17"/>
       <c r="B461" s="18"/>
       <c r="C461" s="17"/>
@@ -18115,8 +19089,10 @@
       <c r="J461" s="17"/>
       <c r="K461" s="17"/>
       <c r="L461" s="17"/>
-    </row>
-    <row r="462" spans="1:12">
+      <c r="M461" s="17"/>
+      <c r="N461" s="17"/>
+    </row>
+    <row r="462" spans="1:14">
       <c r="A462" s="17"/>
       <c r="B462" s="18"/>
       <c r="C462" s="17"/>
@@ -18129,8 +19105,10 @@
       <c r="J462" s="17"/>
       <c r="K462" s="17"/>
       <c r="L462" s="17"/>
-    </row>
-    <row r="463" spans="1:12">
+      <c r="M462" s="17"/>
+      <c r="N462" s="17"/>
+    </row>
+    <row r="463" spans="1:14">
       <c r="A463" s="17"/>
       <c r="B463" s="18"/>
       <c r="C463" s="17"/>
@@ -18143,8 +19121,10 @@
       <c r="J463" s="17"/>
       <c r="K463" s="17"/>
       <c r="L463" s="17"/>
-    </row>
-    <row r="464" spans="1:12">
+      <c r="M463" s="17"/>
+      <c r="N463" s="17"/>
+    </row>
+    <row r="464" spans="1:14">
       <c r="A464" s="17"/>
       <c r="B464" s="18"/>
       <c r="C464" s="17"/>
@@ -18157,8 +19137,10 @@
       <c r="J464" s="17"/>
       <c r="K464" s="17"/>
       <c r="L464" s="17"/>
-    </row>
-    <row r="465" spans="1:12">
+      <c r="M464" s="17"/>
+      <c r="N464" s="17"/>
+    </row>
+    <row r="465" spans="1:14">
       <c r="A465" s="17"/>
       <c r="B465" s="18"/>
       <c r="C465" s="17"/>
@@ -18171,8 +19153,10 @@
       <c r="J465" s="17"/>
       <c r="K465" s="17"/>
       <c r="L465" s="17"/>
-    </row>
-    <row r="466" spans="1:12">
+      <c r="M465" s="17"/>
+      <c r="N465" s="17"/>
+    </row>
+    <row r="466" spans="1:14">
       <c r="A466" s="17"/>
       <c r="B466" s="18"/>
       <c r="C466" s="17"/>
@@ -18185,8 +19169,10 @@
       <c r="J466" s="17"/>
       <c r="K466" s="17"/>
       <c r="L466" s="17"/>
-    </row>
-    <row r="467" spans="1:12">
+      <c r="M466" s="17"/>
+      <c r="N466" s="17"/>
+    </row>
+    <row r="467" spans="1:14">
       <c r="A467" s="17"/>
       <c r="B467" s="18"/>
       <c r="C467" s="17"/>
@@ -18199,8 +19185,10 @@
       <c r="J467" s="17"/>
       <c r="K467" s="17"/>
       <c r="L467" s="17"/>
-    </row>
-    <row r="468" spans="1:12">
+      <c r="M467" s="17"/>
+      <c r="N467" s="17"/>
+    </row>
+    <row r="468" spans="1:14">
       <c r="A468" s="17"/>
       <c r="B468" s="18"/>
       <c r="C468" s="17"/>
@@ -18213,8 +19201,10 @@
       <c r="J468" s="17"/>
       <c r="K468" s="17"/>
       <c r="L468" s="17"/>
-    </row>
-    <row r="469" spans="1:12">
+      <c r="M468" s="17"/>
+      <c r="N468" s="17"/>
+    </row>
+    <row r="469" spans="1:14">
       <c r="A469" s="17"/>
       <c r="B469" s="18"/>
       <c r="C469" s="17"/>
@@ -18227,8 +19217,10 @@
       <c r="J469" s="17"/>
       <c r="K469" s="17"/>
       <c r="L469" s="17"/>
-    </row>
-    <row r="470" spans="1:12">
+      <c r="M469" s="17"/>
+      <c r="N469" s="17"/>
+    </row>
+    <row r="470" spans="1:14">
       <c r="A470" s="17"/>
       <c r="B470" s="18"/>
       <c r="C470" s="17"/>
@@ -18241,8 +19233,10 @@
       <c r="J470" s="17"/>
       <c r="K470" s="17"/>
       <c r="L470" s="17"/>
-    </row>
-    <row r="471" spans="1:12">
+      <c r="M470" s="17"/>
+      <c r="N470" s="17"/>
+    </row>
+    <row r="471" spans="1:14">
       <c r="A471" s="17"/>
       <c r="B471" s="18"/>
       <c r="C471" s="17"/>
@@ -18255,8 +19249,10 @@
       <c r="J471" s="17"/>
       <c r="K471" s="17"/>
       <c r="L471" s="17"/>
-    </row>
-    <row r="472" spans="1:12">
+      <c r="M471" s="17"/>
+      <c r="N471" s="17"/>
+    </row>
+    <row r="472" spans="1:14">
       <c r="A472" s="17"/>
       <c r="B472" s="18"/>
       <c r="C472" s="17"/>
@@ -18269,8 +19265,10 @@
       <c r="J472" s="17"/>
       <c r="K472" s="17"/>
       <c r="L472" s="17"/>
-    </row>
-    <row r="473" spans="1:12">
+      <c r="M472" s="17"/>
+      <c r="N472" s="17"/>
+    </row>
+    <row r="473" spans="1:14">
       <c r="A473" s="17"/>
       <c r="B473" s="18"/>
       <c r="C473" s="17"/>
@@ -18283,8 +19281,10 @@
       <c r="J473" s="17"/>
       <c r="K473" s="17"/>
       <c r="L473" s="17"/>
-    </row>
-    <row r="474" spans="1:12">
+      <c r="M473" s="17"/>
+      <c r="N473" s="17"/>
+    </row>
+    <row r="474" spans="1:14">
       <c r="A474" s="17"/>
       <c r="B474" s="18"/>
       <c r="C474" s="17"/>
@@ -18297,8 +19297,10 @@
       <c r="J474" s="17"/>
       <c r="K474" s="17"/>
       <c r="L474" s="17"/>
-    </row>
-    <row r="475" spans="1:12">
+      <c r="M474" s="17"/>
+      <c r="N474" s="17"/>
+    </row>
+    <row r="475" spans="1:14">
       <c r="A475" s="17"/>
       <c r="B475" s="18"/>
       <c r="C475" s="17"/>
@@ -18311,8 +19313,10 @@
       <c r="J475" s="17"/>
       <c r="K475" s="17"/>
       <c r="L475" s="17"/>
-    </row>
-    <row r="476" spans="1:12">
+      <c r="M475" s="17"/>
+      <c r="N475" s="17"/>
+    </row>
+    <row r="476" spans="1:14">
       <c r="A476" s="17"/>
       <c r="B476" s="18"/>
       <c r="C476" s="17"/>
@@ -18325,8 +19329,10 @@
       <c r="J476" s="17"/>
       <c r="K476" s="17"/>
       <c r="L476" s="17"/>
-    </row>
-    <row r="477" spans="1:12">
+      <c r="M476" s="17"/>
+      <c r="N476" s="17"/>
+    </row>
+    <row r="477" spans="1:14">
       <c r="A477" s="17"/>
       <c r="B477" s="18"/>
       <c r="C477" s="17"/>
@@ -18339,8 +19345,10 @@
       <c r="J477" s="17"/>
       <c r="K477" s="17"/>
       <c r="L477" s="17"/>
-    </row>
-    <row r="478" spans="1:12">
+      <c r="M477" s="17"/>
+      <c r="N477" s="17"/>
+    </row>
+    <row r="478" spans="1:14">
       <c r="A478" s="17"/>
       <c r="B478" s="18"/>
       <c r="C478" s="17"/>
@@ -18353,8 +19361,10 @@
       <c r="J478" s="17"/>
       <c r="K478" s="17"/>
       <c r="L478" s="17"/>
-    </row>
-    <row r="479" spans="1:12">
+      <c r="M478" s="17"/>
+      <c r="N478" s="17"/>
+    </row>
+    <row r="479" spans="1:14">
       <c r="A479" s="17"/>
       <c r="B479" s="18"/>
       <c r="C479" s="17"/>
@@ -18367,8 +19377,10 @@
       <c r="J479" s="17"/>
       <c r="K479" s="17"/>
       <c r="L479" s="17"/>
-    </row>
-    <row r="480" spans="1:12">
+      <c r="M479" s="17"/>
+      <c r="N479" s="17"/>
+    </row>
+    <row r="480" spans="1:14">
       <c r="A480" s="17"/>
       <c r="B480" s="18"/>
       <c r="C480" s="17"/>
@@ -18381,8 +19393,10 @@
       <c r="J480" s="17"/>
       <c r="K480" s="17"/>
       <c r="L480" s="17"/>
-    </row>
-    <row r="481" spans="1:12">
+      <c r="M480" s="17"/>
+      <c r="N480" s="17"/>
+    </row>
+    <row r="481" spans="1:14">
       <c r="A481" s="17"/>
       <c r="B481" s="18"/>
       <c r="C481" s="17"/>
@@ -18395,8 +19409,10 @@
       <c r="J481" s="17"/>
       <c r="K481" s="17"/>
       <c r="L481" s="17"/>
-    </row>
-    <row r="482" spans="1:12">
+      <c r="M481" s="17"/>
+      <c r="N481" s="17"/>
+    </row>
+    <row r="482" spans="1:14">
       <c r="A482" s="17"/>
       <c r="B482" s="18"/>
       <c r="C482" s="17"/>
@@ -18409,8 +19425,10 @@
       <c r="J482" s="17"/>
       <c r="K482" s="17"/>
       <c r="L482" s="17"/>
-    </row>
-    <row r="483" spans="1:12">
+      <c r="M482" s="17"/>
+      <c r="N482" s="17"/>
+    </row>
+    <row r="483" spans="1:14">
       <c r="A483" s="17"/>
       <c r="B483" s="18"/>
       <c r="C483" s="17"/>
@@ -18423,8 +19441,10 @@
       <c r="J483" s="17"/>
       <c r="K483" s="17"/>
       <c r="L483" s="17"/>
-    </row>
-    <row r="484" spans="1:12">
+      <c r="M483" s="17"/>
+      <c r="N483" s="17"/>
+    </row>
+    <row r="484" spans="1:14">
       <c r="A484" s="17"/>
       <c r="B484" s="18"/>
       <c r="C484" s="17"/>
@@ -18437,8 +19457,10 @@
       <c r="J484" s="17"/>
       <c r="K484" s="17"/>
       <c r="L484" s="17"/>
-    </row>
-    <row r="485" spans="1:12">
+      <c r="M484" s="17"/>
+      <c r="N484" s="17"/>
+    </row>
+    <row r="485" spans="1:14">
       <c r="A485" s="17"/>
       <c r="B485" s="18"/>
       <c r="C485" s="17"/>
@@ -18451,8 +19473,10 @@
       <c r="J485" s="17"/>
       <c r="K485" s="17"/>
       <c r="L485" s="17"/>
-    </row>
-    <row r="486" spans="1:12">
+      <c r="M485" s="17"/>
+      <c r="N485" s="17"/>
+    </row>
+    <row r="486" spans="1:14">
       <c r="A486" s="17"/>
       <c r="B486" s="18"/>
       <c r="C486" s="17"/>
@@ -18465,8 +19489,10 @@
       <c r="J486" s="17"/>
       <c r="K486" s="17"/>
       <c r="L486" s="17"/>
-    </row>
-    <row r="487" spans="1:12">
+      <c r="M486" s="17"/>
+      <c r="N486" s="17"/>
+    </row>
+    <row r="487" spans="1:14">
       <c r="A487" s="17"/>
       <c r="B487" s="18"/>
       <c r="C487" s="17"/>
@@ -18479,8 +19505,10 @@
       <c r="J487" s="17"/>
       <c r="K487" s="17"/>
       <c r="L487" s="17"/>
-    </row>
-    <row r="488" spans="1:12">
+      <c r="M487" s="17"/>
+      <c r="N487" s="17"/>
+    </row>
+    <row r="488" spans="1:14">
       <c r="A488" s="17"/>
       <c r="B488" s="18"/>
       <c r="C488" s="17"/>
@@ -18493,8 +19521,10 @@
       <c r="J488" s="17"/>
       <c r="K488" s="17"/>
       <c r="L488" s="17"/>
-    </row>
-    <row r="489" spans="1:12">
+      <c r="M488" s="17"/>
+      <c r="N488" s="17"/>
+    </row>
+    <row r="489" spans="1:14">
       <c r="A489" s="17"/>
       <c r="B489" s="18"/>
       <c r="C489" s="17"/>
@@ -18507,8 +19537,10 @@
       <c r="J489" s="17"/>
       <c r="K489" s="17"/>
       <c r="L489" s="17"/>
-    </row>
-    <row r="490" spans="1:12">
+      <c r="M489" s="17"/>
+      <c r="N489" s="17"/>
+    </row>
+    <row r="490" spans="1:14">
       <c r="A490" s="17"/>
       <c r="B490" s="18"/>
       <c r="C490" s="17"/>
@@ -18521,8 +19553,10 @@
       <c r="J490" s="17"/>
       <c r="K490" s="17"/>
       <c r="L490" s="17"/>
-    </row>
-    <row r="491" spans="1:12">
+      <c r="M490" s="17"/>
+      <c r="N490" s="17"/>
+    </row>
+    <row r="491" spans="1:14">
       <c r="A491" s="17"/>
       <c r="B491" s="18"/>
       <c r="C491" s="17"/>
@@ -18535,8 +19569,10 @@
       <c r="J491" s="17"/>
       <c r="K491" s="17"/>
       <c r="L491" s="17"/>
-    </row>
-    <row r="492" spans="1:12">
+      <c r="M491" s="17"/>
+      <c r="N491" s="17"/>
+    </row>
+    <row r="492" spans="1:14">
       <c r="A492" s="17"/>
       <c r="B492" s="18"/>
       <c r="C492" s="17"/>
@@ -18549,8 +19585,10 @@
       <c r="J492" s="17"/>
       <c r="K492" s="17"/>
       <c r="L492" s="17"/>
-    </row>
-    <row r="493" spans="1:12">
+      <c r="M492" s="17"/>
+      <c r="N492" s="17"/>
+    </row>
+    <row r="493" spans="1:14">
       <c r="A493" s="17"/>
       <c r="B493" s="18"/>
       <c r="C493" s="17"/>
@@ -18563,8 +19601,10 @@
       <c r="J493" s="17"/>
       <c r="K493" s="17"/>
       <c r="L493" s="17"/>
-    </row>
-    <row r="494" spans="1:12">
+      <c r="M493" s="17"/>
+      <c r="N493" s="17"/>
+    </row>
+    <row r="494" spans="1:14">
       <c r="A494" s="17"/>
       <c r="B494" s="18"/>
       <c r="C494" s="17"/>
@@ -18577,8 +19617,10 @@
       <c r="J494" s="17"/>
       <c r="K494" s="17"/>
       <c r="L494" s="17"/>
-    </row>
-    <row r="495" spans="1:12">
+      <c r="M494" s="17"/>
+      <c r="N494" s="17"/>
+    </row>
+    <row r="495" spans="1:14">
       <c r="A495" s="17"/>
       <c r="B495" s="18"/>
       <c r="C495" s="17"/>
@@ -18591,8 +19633,10 @@
       <c r="J495" s="17"/>
       <c r="K495" s="17"/>
       <c r="L495" s="17"/>
-    </row>
-    <row r="496" spans="1:12">
+      <c r="M495" s="17"/>
+      <c r="N495" s="17"/>
+    </row>
+    <row r="496" spans="1:14">
       <c r="A496" s="17"/>
       <c r="B496" s="18"/>
       <c r="C496" s="17"/>
@@ -18605,8 +19649,10 @@
       <c r="J496" s="17"/>
       <c r="K496" s="17"/>
       <c r="L496" s="17"/>
-    </row>
-    <row r="497" spans="1:12">
+      <c r="M496" s="17"/>
+      <c r="N496" s="17"/>
+    </row>
+    <row r="497" spans="1:14">
       <c r="A497" s="17"/>
       <c r="B497" s="18"/>
       <c r="C497" s="17"/>
@@ -18619,8 +19665,10 @@
       <c r="J497" s="17"/>
       <c r="K497" s="17"/>
       <c r="L497" s="17"/>
-    </row>
-    <row r="498" spans="1:12">
+      <c r="M497" s="17"/>
+      <c r="N497" s="17"/>
+    </row>
+    <row r="498" spans="1:14">
       <c r="A498" s="17"/>
       <c r="B498" s="18"/>
       <c r="C498" s="17"/>
@@ -18633,8 +19681,10 @@
       <c r="J498" s="17"/>
       <c r="K498" s="17"/>
       <c r="L498" s="17"/>
-    </row>
-    <row r="499" spans="1:12">
+      <c r="M498" s="17"/>
+      <c r="N498" s="17"/>
+    </row>
+    <row r="499" spans="1:14">
       <c r="A499" s="17"/>
       <c r="B499" s="18"/>
       <c r="C499" s="17"/>
@@ -18647,8 +19697,10 @@
       <c r="J499" s="17"/>
       <c r="K499" s="17"/>
       <c r="L499" s="17"/>
-    </row>
-    <row r="500" spans="1:12">
+      <c r="M499" s="17"/>
+      <c r="N499" s="17"/>
+    </row>
+    <row r="500" spans="1:14">
       <c r="A500" s="17"/>
       <c r="B500" s="18"/>
       <c r="C500" s="17"/>
@@ -18661,8 +19713,10 @@
       <c r="J500" s="17"/>
       <c r="K500" s="17"/>
       <c r="L500" s="17"/>
-    </row>
-    <row r="501" spans="1:12">
+      <c r="M500" s="17"/>
+      <c r="N500" s="17"/>
+    </row>
+    <row r="501" spans="1:14">
       <c r="A501" s="17"/>
       <c r="B501" s="18"/>
       <c r="C501" s="17"/>
@@ -18675,8 +19729,10 @@
       <c r="J501" s="17"/>
       <c r="K501" s="17"/>
       <c r="L501" s="17"/>
-    </row>
-    <row r="502" spans="1:12">
+      <c r="M501" s="17"/>
+      <c r="N501" s="17"/>
+    </row>
+    <row r="502" spans="1:14">
       <c r="A502" s="17"/>
       <c r="B502" s="18"/>
       <c r="C502" s="17"/>
@@ -18689,8 +19745,10 @@
       <c r="J502" s="17"/>
       <c r="K502" s="17"/>
       <c r="L502" s="17"/>
-    </row>
-    <row r="503" spans="1:12">
+      <c r="M502" s="17"/>
+      <c r="N502" s="17"/>
+    </row>
+    <row r="503" spans="1:14">
       <c r="A503" s="17"/>
       <c r="B503" s="18"/>
       <c r="C503" s="17"/>
@@ -18703,8 +19761,10 @@
       <c r="J503" s="17"/>
       <c r="K503" s="17"/>
       <c r="L503" s="17"/>
-    </row>
-    <row r="504" spans="1:12">
+      <c r="M503" s="17"/>
+      <c r="N503" s="17"/>
+    </row>
+    <row r="504" spans="1:14">
       <c r="A504" s="17"/>
       <c r="B504" s="18"/>
       <c r="C504" s="17"/>
@@ -18717,6 +19777,8 @@
       <c r="J504" s="17"/>
       <c r="K504" s="17"/>
       <c r="L504" s="17"/>
+      <c r="M504" s="17"/>
+      <c r="N504" s="17"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/design/道具表.xlsx
+++ b/design/道具表.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\聚光灯\Hunter\design\"/>
+      <x15ac:absPath url="E:\聚光灯\Hunter\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -646,14 +646,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="71">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -872,8 +872,197 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF12283F"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202C3A"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF12283F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202C3A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.25"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="83">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1120,8 +1309,213 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CEE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.25"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.25"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.25"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD3E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1403,8 +1797,250 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="53">
+  <cellStyleXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1560,8 +2196,160 @@
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="35" fillId="0" borderId="21" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="35" fillId="0" borderId="21" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="35" fillId="0" borderId="21" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="35" fillId="0" borderId="21" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="35" fillId="0" borderId="21" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="51" borderId="34" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="52" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="53" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="53" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="54" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="55" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="56" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="57" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="58" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="59" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="60" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="61" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="62" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="63" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="64" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="65" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="66" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="67" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="68" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="69" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="70" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="71" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="72" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="73" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="74" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="75" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="76" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="77" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="78" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="79" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="80" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="81" borderId="21" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="21"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="21">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1765,6 +2553,231 @@
     </xf>
     <xf numFmtId="1" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="21" xfId="53">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="42" borderId="22" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="42" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="22" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="22" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="23" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="24" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="44" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="25" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="26" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="27" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="41" fillId="45" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="45" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="41" fillId="46" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="46" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="37" fillId="0" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="23" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="24" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="29" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="25" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="26" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="30" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="27" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="31" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="43" fillId="45" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="45" borderId="21" xfId="104" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="43" fillId="46" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="46" borderId="21" xfId="104" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="21" xfId="104" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="47" borderId="21" xfId="53" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="21" xfId="53" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="21" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="22" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="44" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="22" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="41" fillId="0" borderId="22" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="22" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="41" fillId="0" borderId="32" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="32" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="45" fillId="48" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="48" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="48" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="48" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="41" fillId="0" borderId="33" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="33" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="22" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="37" fillId="0" borderId="22" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="32" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="37" fillId="0" borderId="32" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="45" fillId="49" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="49" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="49" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="49" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="33" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="37" fillId="0" borderId="33" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="32" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="45" fillId="50" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="50" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="50" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="50" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="82" borderId="24" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="82" borderId="26" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="82" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="82" borderId="24" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="82" borderId="26" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="82" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="82" borderId="26" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="82" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="53">
@@ -2045,7 +3058,7 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
@@ -2270,7 +3283,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:AM500"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="24" style="3" customWidth="1"/>
@@ -2715,7 +3728,9 @@
       <c r="E10" s="51">
         <v>1</v>
       </c>
-      <c r="F10" s="51"/>
+      <c r="F10" s="118" t="n">
+        <v>0</v>
+      </c>
       <c r="G10" s="52" t="s">
         <v>32</v>
       </c>
@@ -2737,7 +3752,9 @@
       <c r="E11" s="54">
         <v>2</v>
       </c>
-      <c r="F11" s="54"/>
+      <c r="F11" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="G11" s="53" t="s">
         <v>34</v>
       </c>
@@ -2759,7 +3776,9 @@
       <c r="E12" s="56">
         <v>3</v>
       </c>
-      <c r="F12" s="56"/>
+      <c r="F12" s="123" t="n">
+        <v>0</v>
+      </c>
       <c r="G12" s="55" t="s">
         <v>36</v>
       </c>
@@ -2795,7 +3814,9 @@
       <c r="E14" s="62">
         <v>1</v>
       </c>
-      <c r="F14" s="62"/>
+      <c r="F14" s="129" t="n">
+        <v>0</v>
+      </c>
       <c r="G14" s="61" t="s">
         <v>39</v>
       </c>
@@ -2817,7 +3838,9 @@
       <c r="E15" s="54">
         <v>2</v>
       </c>
-      <c r="F15" s="54"/>
+      <c r="F15" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" s="53" t="s">
         <v>41</v>
       </c>
@@ -2839,7 +3862,9 @@
       <c r="E16" s="63">
         <v>3</v>
       </c>
-      <c r="F16" s="63"/>
+      <c r="F16" s="130" t="n">
+        <v>0</v>
+      </c>
       <c r="G16" s="63" t="s">
         <v>43</v>
       </c>
@@ -2875,7 +3900,9 @@
       <c r="E18" s="62">
         <v>1</v>
       </c>
-      <c r="F18" s="62"/>
+      <c r="F18" s="129" t="n">
+        <v>0</v>
+      </c>
       <c r="G18" s="61" t="s">
         <v>47</v>
       </c>
@@ -2897,7 +3924,9 @@
       <c r="E19" s="54">
         <v>1</v>
       </c>
-      <c r="F19" s="54"/>
+      <c r="F19" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="G19" s="61" t="s">
         <v>47</v>
       </c>
@@ -2941,7 +3970,9 @@
       <c r="E21" s="54">
         <v>2</v>
       </c>
-      <c r="F21" s="54"/>
+      <c r="F21" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="G21" s="53" t="s">
         <v>51</v>
       </c>
@@ -2982,8 +4013,12 @@
       <c r="D23" s="62">
         <v>4</v>
       </c>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
+      <c r="E23" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="G23" s="53" t="s">
         <v>51</v>
       </c>
@@ -2992,24 +4027,52 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="54"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="54"/>
+      <c r="A24" s="121" t="n">
+        <v>2800001</v>
+      </c>
+      <c r="B24" s="120" t="str">
+        <v>废铁（示例）</v>
+      </c>
+      <c r="C24" s="120" t="str"/>
+      <c r="D24" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="120" t="str">
+        <v>撤离战利品</v>
+      </c>
+      <c r="H24" s="121" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="54"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="54"/>
+      <c r="A25" s="121" t="n">
+        <v>2800002</v>
+      </c>
+      <c r="B25" s="120" t="str">
+        <v>首领徽记（示例）</v>
+      </c>
+      <c r="C25" s="120" t="str"/>
+      <c r="D25" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="120" t="str">
+        <v>首领撤离战利品</v>
+      </c>
+      <c r="H25" s="121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="54"/>
@@ -7798,11 +8861,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:G503"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="24" style="4" customWidth="1"/>
@@ -7891,8 +8954,8 @@
       <c r="G4" s="10"/>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:7">
-      <c r="A5" s="28">
-        <v>100000001</v>
+      <c r="A5" s="96" t="n">
+        <v>10001</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>31</v>
@@ -7911,8 +8974,8 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:7">
-      <c r="A6" s="30">
-        <v>100000002</v>
+      <c r="A6" s="98" t="n">
+        <v>10002</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>33</v>
@@ -7928,8 +8991,8 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:7">
-      <c r="A7" s="28">
-        <v>100000003</v>
+      <c r="A7" s="96" t="n">
+        <v>10003</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>35</v>
@@ -11417,7 +12480,7 @@
       <c r="E503" s="33"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:E7" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A4:E7" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <dataValidations count="4">
@@ -11447,7 +12510,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:P504"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.25" style="3" customWidth="1"/>
@@ -11499,8 +12562,8 @@
       <c r="K1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>74</v>
+      <c r="L1" s="138" t="str">
+        <v>使用时移速降低（百分比）</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>75</v>
@@ -11593,7 +12656,9 @@
       <c r="K3" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="L3" s="9"/>
+      <c r="L3" s="141" t="str">
+        <v>SlowPercent</v>
+      </c>
       <c r="M3" s="9" t="s">
         <v>86</v>
       </c>
@@ -11636,8 +12701,8 @@
       <c r="K4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="12" t="s">
-        <v>88</v>
+      <c r="L4" s="142" t="str">
+        <v>server/client</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>21</v>
@@ -11648,8 +12713,8 @@
       <c r="P4" s="10"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="13">
-        <v>1</v>
+      <c r="A5" s="81" t="n">
+        <v>30001</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>46</v>
@@ -11672,21 +12737,31 @@
       <c r="H5" s="13">
         <v>600</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
+      <c r="I5" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="81" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" s="13">
         <v>0</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
+      <c r="L5" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="81" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="15">
-        <v>2</v>
+      <c r="A6" s="83" t="n">
+        <v>30002</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>48</v>
@@ -11709,16 +12784,24 @@
       <c r="H6" s="15">
         <v>0</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
+      <c r="I6" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="83" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" s="15">
         <v>120</v>
       </c>
       <c r="L6" s="15">
         <v>30</v>
       </c>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
+      <c r="M6" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="13">
@@ -11763,8 +12846,8 @@
       <c r="N7" s="13"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="15">
-        <v>4</v>
+      <c r="A8" s="83" t="n">
+        <v>30004</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>50</v>
@@ -11787,16 +12870,24 @@
       <c r="H8" s="15">
         <v>0</v>
       </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
+      <c r="I8" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="83" t="n">
+        <v>0</v>
+      </c>
       <c r="K8" s="15">
         <v>90</v>
       </c>
       <c r="L8" s="15">
         <v>30</v>
       </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
+      <c r="M8" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="17">
@@ -11837,8 +12928,8 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="17">
-        <v>6</v>
+      <c r="A10" s="85" t="n">
+        <v>30006</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>53</v>
@@ -11873,8 +12964,12 @@
       <c r="L10" s="15">
         <v>30</v>
       </c>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
+      <c r="M10" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="17"/>

--- a/design/道具表.xlsx
+++ b/design/道具表.xlsx
@@ -43,6 +43,7 @@
   <authors>
     <author>Administrator</author>
     <author>86185</author>
+    <author>User</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -71,6 +72,11 @@
 示例：100000001=训练步枪；2800001=废铁；2800002=首领徽记。
 保留历史预留约定：时装可使用 3000000+时装ID，精灵可使用 2502000+精灵ID；均非本轮实现范围，不用于推断运行时属性。</t>
         </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+本行记录在 Item 表中的唯一正整数 ID，不使用行号、名称或数字位推断关联。不同配置表的 ID 空间相互独立。是否参与当前运行内容，由生产清单显式选中的记录决定。</t>
+        </r>
       </text>
     </comment>
     <comment ref="D1" authorId="1">
@@ -96,6 +102,11 @@
 3=弹药
 4=工具
 消耗品</t>
+        </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+当前分类使用 1=值道具、2=枪械、3=弹药、4=工具、5=本版撤离战利品。枪械、弹药、工具各自关联扩展表；旧批注的 ID 区间和分类不能覆盖当前显式关联。</t>
         </r>
       </text>
     </comment>
@@ -140,6 +151,27 @@
         XiaoLei_SoulPetEquip = 11,//灵物装备
 Hunter 填写规则：Type=0 表示未细分，所有道具均须填写整数。原四条货币的历史空值已补为 0。</t>
         </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+在 Kind 分类内解释的小类值，0 表示未细分。当前生产仍保留该字段，但不通过它推断枪械、弹药或工具的跨表引用。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+历史细分分类字段，含义依赖 Kind 与 Type。当前正式玩法未读取此字段，不应据此推断已实现的职业、品质或武器行为。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+单格物品的最大堆叠数，当前生产选中物品必须填写正整数。战利品超过上限时拆堆；历史货币说明不能当作当前生产允许填 0 的规则。</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -151,6 +183,7 @@
   <authors>
     <author>Administrator</author>
     <author>xb21cn</author>
+    <author>User</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -163,6 +196,11 @@
           </rPr>
           <t>Administrator:
 装备id需要和道具表的id对应，切记</t>
+        </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+主键同时引用 Item.ItemIdx，关联物品共同属性；本表补充装备与武器关联。当前正式用法要求物品 Kind=2，不能另编一个无对应物品的 ID。是否参与当前运行内容，由生产清单显式选中的记录决定。</t>
         </r>
       </text>
     </comment>
@@ -189,6 +227,11 @@
 ----------12 = 谷玉
 ----------13 = 封印装备</t>
         </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+沿用旧装备位置枚举，当前枪械行使用 1=武器。当前正式配装的槽位数量由 Rules.WeaponSlots 决定，其他装备位置不代表已有对应系统。</t>
+        </r>
       </text>
     </comment>
     <comment ref="D1" authorId="1">
@@ -209,6 +252,19 @@
 0=非武器；原 1～6 数值保持不变。
 枪械必须填写 WeaponIdx，非武器填 0。</t>
         </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+当前枪械填写 7，原 1～6 为保留武器分类。正式枪械行为由 WeaponIdx 关联的武器表提供，不能仅凭类型枚举生成攻击规则。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+引用 Weapon.WeaponIdx，连接装备物品与枪械行为。物品 ID 与武器配置 ID 属于不同命名空间，必须显式关联。</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -220,6 +276,7 @@
   <authors>
     <author>Administrator</author>
     <author>86185</author>
+    <author>User</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -232,6 +289,11 @@
           </rPr>
           <t>Administrator:
 装备id需要和道具表的id对应，切记</t>
+        </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+主键同时引用 Item.ItemIdx，关联物品共同属性；本表补充工具行为。当前正式用法要求物品 Kind=4，不能另编一个无对应物品的 ID。是否参与当前运行内容，由生产清单显式选中的记录决定。</t>
         </r>
       </text>
     </comment>
@@ -256,6 +318,11 @@
 1=常规工具
 2=消耗品</t>
         </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+1=常规工具，2=消耗品；需要结合 Subdivision 解释。常规工具和消耗品分别占用 Rules.ToolSlots、Rules.ConsumableSlots。</t>
+        </r>
       </text>
     </comment>
     <comment ref="D1" authorId="1">
@@ -276,6 +343,35 @@
 ToolType=2时
   5=医疗道具
   6=投掷道具</t>
+        </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+当前生产支持 (ToolType, Subdivision)=(1,1) 匕首、(1,3) 急救包、(2,5) 生命针剂、(2,6) 炸药束。原批注中其他组合为预留设计，并不代表已经接入。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+当前映射为工具可使用次数，不是 Item.MaxStack。匕首填 1 表示可用且使用不扣次数，医疗与投掷工具会消耗剩余次数。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+工具设计中的体力消耗字段，当前会保留到工具配置。匕首与枪托近战实际共用 Rules.MeleeStamina，调整匕首本列不能单独改变近战体耗。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+按工具种类解释：匕首和炸药束为伤害，急救包和生命针剂为恢复生命量。此值表示绝对点数，不是生命百分比。</t>
         </r>
       </text>
     </comment>
@@ -298,6 +394,27 @@
           </rPr>
           <t xml:space="preserve">
 填0则代表仅对自己生效</t>
+        </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+单位为毫米；匕首表示近战距离，炸药束表示爆炸半径。当前医疗工具作用于自己，使用范围填 0；不代表已实现范围治疗。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+投掷物可到达的最大投掷距离，单位为毫米。炸药束必须大于 0，并与 Speed 一起决定投掷推进。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+投掷物每 Tick 的移动距离，单位为毫米/Tick。炸药束必须大于 0，60 Tick=1 秒。</t>
         </r>
       </text>
     </comment>
@@ -322,6 +439,19 @@
 90 Tick = 1.5 秒。
 </t>
         </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+工具使用读条耗时，单位为 Tick，60 Tick=1 秒。医疗读条完成后恢复生命，投掷工具读条完成后生成投掷物；不是投掷物飞行耗时。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="2">
+      <text>
+        <r>
+          <t>补充说明：
+使用时降低的移速百分比，与 Rules.ToolMovePercent 的“保留比例”相反。当前非匕首工具必须满足 SlowPercent=100-ToolMovePercent，例如降低 30% 对应保留 70%。</t>
+        </r>
       </text>
     </comment>
     <comment ref="M1" authorId="1">
@@ -343,6 +473,11 @@
           </rPr>
           <t xml:space="preserve">
 填写0则为瞬发效果</t>
+        </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+保留的持续效果时长，单位为 Tick，旧约定 0 表示瞬发效果。当前正式工具执行器未读取本列，使用读条由 Lag 控制。</t>
         </r>
       </text>
     </comment>
@@ -366,6 +501,11 @@
           <t xml:space="preserve">
 仅当Subdivision=2是需要填写枪械id
 </t>
+        </r>
+        <r>
+          <t xml:space="preserve">
+补充说明：
+旧设计中供 Subdivision=2 关联枪械配置的字段，不是本工具主键。当前正式版本未启用该工具类型，工具身份以 ItemIdx 为准。</t>
         </r>
       </text>
     </comment>
@@ -2349,7 +2489,7 @@
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2778,6 +2918,36 @@
     </xf>
     <xf numFmtId="0" fontId="70" fillId="82" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="43" fillId="45" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="43" fillId="46" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="53">
@@ -3283,7 +3453,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:AM500"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="24" style="3" customWidth="1"/>
@@ -3706,7 +3876,7 @@
       </c>
       <c r="B9" s="48"/>
       <c r="C9" s="48"/>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="143" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="50"/>
@@ -3792,7 +3962,7 @@
       </c>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="144" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="60"/>
@@ -3878,7 +4048,7 @@
       </c>
       <c r="B17" s="65"/>
       <c r="C17" s="65"/>
-      <c r="D17" s="66" t="s">
+      <c r="D17" s="145" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="67"/>
@@ -8865,7 +9035,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G503"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="24" style="4" customWidth="1"/>
@@ -8954,19 +9124,19 @@
       <c r="G4" s="10"/>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:7">
-      <c r="A5" s="96" t="n">
+      <c r="A5" s="146" t="n">
         <v>10001</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="147">
         <v>1</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="147">
         <v>7</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="147">
         <v>1</v>
       </c>
       <c r="G5" s="10" t="s">
@@ -8974,3510 +9144,3510 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:7">
-      <c r="A6" s="98" t="n">
+      <c r="A6" s="148" t="n">
         <v>10002</v>
       </c>
       <c r="B6" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="149">
         <v>1</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="149">
         <v>7</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="149">
         <v>2</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:7">
-      <c r="A7" s="96" t="n">
+      <c r="A7" s="146" t="n">
         <v>10003</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="150" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="147">
         <v>1</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="147">
         <v>7</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="147">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="33"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
+      <c r="A8" s="151"/>
+      <c r="B8" s="152"/>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="33"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
+      <c r="A9" s="151"/>
+      <c r="B9" s="152"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="151"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
+      <c r="A10" s="151"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="151"/>
+      <c r="D10" s="151"/>
+      <c r="E10" s="151"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="33"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
+      <c r="A11" s="151"/>
+      <c r="B11" s="152"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
+      <c r="A12" s="151"/>
+      <c r="B12" s="152"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
+      <c r="A13" s="151"/>
+      <c r="B13" s="152"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="33"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
+      <c r="A14" s="151"/>
+      <c r="B14" s="152"/>
+      <c r="C14" s="151"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="33"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
+      <c r="A15" s="151"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="151"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
+      <c r="A16" s="151"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="151"/>
+      <c r="D16" s="151"/>
+      <c r="E16" s="151"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="33"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
+      <c r="A17" s="151"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="151"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="33"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
+      <c r="A18" s="151"/>
+      <c r="B18" s="152"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="33"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
+      <c r="A19" s="151"/>
+      <c r="B19" s="152"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="151"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="33"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
+      <c r="A20" s="151"/>
+      <c r="B20" s="152"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="151"/>
+      <c r="E20" s="151"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="33"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="152"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="33"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
+      <c r="A22" s="151"/>
+      <c r="B22" s="152"/>
+      <c r="C22" s="151"/>
+      <c r="D22" s="151"/>
+      <c r="E22" s="151"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="33"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
+      <c r="A23" s="151"/>
+      <c r="B23" s="152"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="33"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
+      <c r="A24" s="151"/>
+      <c r="B24" s="152"/>
+      <c r="C24" s="151"/>
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="33"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
+      <c r="A25" s="151"/>
+      <c r="B25" s="152"/>
+      <c r="C25" s="151"/>
+      <c r="D25" s="151"/>
+      <c r="E25" s="151"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="33"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
+      <c r="A26" s="151"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="151"/>
+      <c r="E26" s="151"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="33"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
+      <c r="A27" s="151"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="151"/>
+      <c r="E27" s="151"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="33"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
+      <c r="A28" s="151"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="151"/>
+      <c r="D28" s="151"/>
+      <c r="E28" s="151"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="33"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
+      <c r="A29" s="151"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="151"/>
+      <c r="D29" s="151"/>
+      <c r="E29" s="151"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="33"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
+      <c r="A30" s="151"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="151"/>
+      <c r="D30" s="151"/>
+      <c r="E30" s="151"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="33"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
+      <c r="A31" s="151"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="151"/>
+      <c r="E31" s="151"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="33"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
+      <c r="A32" s="151"/>
+      <c r="B32" s="152"/>
+      <c r="C32" s="151"/>
+      <c r="D32" s="151"/>
+      <c r="E32" s="151"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="33"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
+      <c r="A33" s="151"/>
+      <c r="B33" s="152"/>
+      <c r="C33" s="151"/>
+      <c r="D33" s="151"/>
+      <c r="E33" s="151"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="33"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
+      <c r="A34" s="151"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="151"/>
+      <c r="D34" s="151"/>
+      <c r="E34" s="151"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="33"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
+      <c r="A35" s="151"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="33"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
+      <c r="A36" s="151"/>
+      <c r="B36" s="152"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="151"/>
+      <c r="E36" s="151"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="33"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
+      <c r="A37" s="151"/>
+      <c r="B37" s="152"/>
+      <c r="C37" s="151"/>
+      <c r="D37" s="151"/>
+      <c r="E37" s="151"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="33"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
+      <c r="A38" s="151"/>
+      <c r="B38" s="152"/>
+      <c r="C38" s="151"/>
+      <c r="D38" s="151"/>
+      <c r="E38" s="151"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="33"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
+      <c r="A39" s="151"/>
+      <c r="B39" s="152"/>
+      <c r="C39" s="151"/>
+      <c r="D39" s="151"/>
+      <c r="E39" s="151"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="33"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
+      <c r="A40" s="151"/>
+      <c r="B40" s="152"/>
+      <c r="C40" s="151"/>
+      <c r="D40" s="151"/>
+      <c r="E40" s="151"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="33"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
+      <c r="A41" s="151"/>
+      <c r="B41" s="152"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="151"/>
+      <c r="E41" s="151"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="33"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
+      <c r="A42" s="151"/>
+      <c r="B42" s="152"/>
+      <c r="C42" s="151"/>
+      <c r="D42" s="151"/>
+      <c r="E42" s="151"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="33"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
+      <c r="A43" s="151"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="151"/>
+      <c r="D43" s="151"/>
+      <c r="E43" s="151"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="33"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
+      <c r="A44" s="151"/>
+      <c r="B44" s="152"/>
+      <c r="C44" s="151"/>
+      <c r="D44" s="151"/>
+      <c r="E44" s="151"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="33"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
+      <c r="A45" s="151"/>
+      <c r="B45" s="152"/>
+      <c r="C45" s="151"/>
+      <c r="D45" s="151"/>
+      <c r="E45" s="151"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="33"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
+      <c r="A46" s="151"/>
+      <c r="B46" s="152"/>
+      <c r="C46" s="151"/>
+      <c r="D46" s="151"/>
+      <c r="E46" s="151"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="33"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
+      <c r="A47" s="151"/>
+      <c r="B47" s="152"/>
+      <c r="C47" s="151"/>
+      <c r="D47" s="151"/>
+      <c r="E47" s="151"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="33"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
+      <c r="A48" s="151"/>
+      <c r="B48" s="152"/>
+      <c r="C48" s="151"/>
+      <c r="D48" s="151"/>
+      <c r="E48" s="151"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="33"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
+      <c r="A49" s="151"/>
+      <c r="B49" s="152"/>
+      <c r="C49" s="151"/>
+      <c r="D49" s="151"/>
+      <c r="E49" s="151"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="33"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
+      <c r="A50" s="151"/>
+      <c r="B50" s="152"/>
+      <c r="C50" s="151"/>
+      <c r="D50" s="151"/>
+      <c r="E50" s="151"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="33"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
+      <c r="A51" s="151"/>
+      <c r="B51" s="152"/>
+      <c r="C51" s="151"/>
+      <c r="D51" s="151"/>
+      <c r="E51" s="151"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="33"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
+      <c r="A52" s="151"/>
+      <c r="B52" s="152"/>
+      <c r="C52" s="151"/>
+      <c r="D52" s="151"/>
+      <c r="E52" s="151"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="33"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
+      <c r="A53" s="151"/>
+      <c r="B53" s="152"/>
+      <c r="C53" s="151"/>
+      <c r="D53" s="151"/>
+      <c r="E53" s="151"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="33"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
+      <c r="A54" s="151"/>
+      <c r="B54" s="152"/>
+      <c r="C54" s="151"/>
+      <c r="D54" s="151"/>
+      <c r="E54" s="151"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="33"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
+      <c r="A55" s="151"/>
+      <c r="B55" s="152"/>
+      <c r="C55" s="151"/>
+      <c r="D55" s="151"/>
+      <c r="E55" s="151"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="33"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
+      <c r="A56" s="151"/>
+      <c r="B56" s="152"/>
+      <c r="C56" s="151"/>
+      <c r="D56" s="151"/>
+      <c r="E56" s="151"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="33"/>
-      <c r="B57" s="34"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
+      <c r="A57" s="151"/>
+      <c r="B57" s="152"/>
+      <c r="C57" s="151"/>
+      <c r="D57" s="151"/>
+      <c r="E57" s="151"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="33"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
+      <c r="A58" s="151"/>
+      <c r="B58" s="152"/>
+      <c r="C58" s="151"/>
+      <c r="D58" s="151"/>
+      <c r="E58" s="151"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="33"/>
-      <c r="B59" s="34"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
+      <c r="A59" s="151"/>
+      <c r="B59" s="152"/>
+      <c r="C59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="33"/>
-      <c r="B60" s="34"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
+      <c r="A60" s="151"/>
+      <c r="B60" s="152"/>
+      <c r="C60" s="151"/>
+      <c r="D60" s="151"/>
+      <c r="E60" s="151"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="33"/>
-      <c r="B61" s="34"/>
-      <c r="C61" s="33"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
+      <c r="A61" s="151"/>
+      <c r="B61" s="152"/>
+      <c r="C61" s="151"/>
+      <c r="D61" s="151"/>
+      <c r="E61" s="151"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="33"/>
-      <c r="B62" s="34"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
+      <c r="A62" s="151"/>
+      <c r="B62" s="152"/>
+      <c r="C62" s="151"/>
+      <c r="D62" s="151"/>
+      <c r="E62" s="151"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="33"/>
-      <c r="B63" s="34"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="151"/>
+      <c r="D63" s="151"/>
+      <c r="E63" s="151"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="33"/>
-      <c r="B64" s="34"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
+      <c r="A64" s="151"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="151"/>
+      <c r="D64" s="151"/>
+      <c r="E64" s="151"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="33"/>
-      <c r="B65" s="34"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="33"/>
+      <c r="A65" s="151"/>
+      <c r="B65" s="152"/>
+      <c r="C65" s="151"/>
+      <c r="D65" s="151"/>
+      <c r="E65" s="151"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="33"/>
-      <c r="B66" s="34"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
+      <c r="A66" s="151"/>
+      <c r="B66" s="152"/>
+      <c r="C66" s="151"/>
+      <c r="D66" s="151"/>
+      <c r="E66" s="151"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="33"/>
-      <c r="B67" s="34"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
+      <c r="A67" s="151"/>
+      <c r="B67" s="152"/>
+      <c r="C67" s="151"/>
+      <c r="D67" s="151"/>
+      <c r="E67" s="151"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="33"/>
-      <c r="B68" s="34"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="33"/>
-      <c r="E68" s="33"/>
+      <c r="A68" s="151"/>
+      <c r="B68" s="152"/>
+      <c r="C68" s="151"/>
+      <c r="D68" s="151"/>
+      <c r="E68" s="151"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="33"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="33"/>
+      <c r="A69" s="151"/>
+      <c r="B69" s="152"/>
+      <c r="C69" s="151"/>
+      <c r="D69" s="151"/>
+      <c r="E69" s="151"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="33"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="33"/>
-      <c r="E70" s="33"/>
+      <c r="A70" s="151"/>
+      <c r="B70" s="152"/>
+      <c r="C70" s="151"/>
+      <c r="D70" s="151"/>
+      <c r="E70" s="151"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="33"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="33"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
+      <c r="A71" s="151"/>
+      <c r="B71" s="152"/>
+      <c r="C71" s="151"/>
+      <c r="D71" s="151"/>
+      <c r="E71" s="151"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="33"/>
-      <c r="B72" s="34"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
+      <c r="A72" s="151"/>
+      <c r="B72" s="152"/>
+      <c r="C72" s="151"/>
+      <c r="D72" s="151"/>
+      <c r="E72" s="151"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="33"/>
-      <c r="B73" s="34"/>
-      <c r="C73" s="33"/>
-      <c r="D73" s="33"/>
-      <c r="E73" s="33"/>
+      <c r="A73" s="151"/>
+      <c r="B73" s="152"/>
+      <c r="C73" s="151"/>
+      <c r="D73" s="151"/>
+      <c r="E73" s="151"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="33"/>
-      <c r="B74" s="34"/>
-      <c r="C74" s="33"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="33"/>
+      <c r="A74" s="151"/>
+      <c r="B74" s="152"/>
+      <c r="C74" s="151"/>
+      <c r="D74" s="151"/>
+      <c r="E74" s="151"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="33"/>
-      <c r="B75" s="34"/>
-      <c r="C75" s="33"/>
-      <c r="D75" s="33"/>
-      <c r="E75" s="33"/>
+      <c r="A75" s="151"/>
+      <c r="B75" s="152"/>
+      <c r="C75" s="151"/>
+      <c r="D75" s="151"/>
+      <c r="E75" s="151"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="33"/>
-      <c r="B76" s="34"/>
-      <c r="C76" s="33"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="33"/>
+      <c r="A76" s="151"/>
+      <c r="B76" s="152"/>
+      <c r="C76" s="151"/>
+      <c r="D76" s="151"/>
+      <c r="E76" s="151"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="33"/>
-      <c r="B77" s="34"/>
-      <c r="C77" s="33"/>
-      <c r="D77" s="33"/>
-      <c r="E77" s="33"/>
+      <c r="A77" s="151"/>
+      <c r="B77" s="152"/>
+      <c r="C77" s="151"/>
+      <c r="D77" s="151"/>
+      <c r="E77" s="151"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="33"/>
-      <c r="B78" s="34"/>
-      <c r="C78" s="33"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
+      <c r="A78" s="151"/>
+      <c r="B78" s="152"/>
+      <c r="C78" s="151"/>
+      <c r="D78" s="151"/>
+      <c r="E78" s="151"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="33"/>
-      <c r="B79" s="34"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="33"/>
-      <c r="E79" s="33"/>
+      <c r="A79" s="151"/>
+      <c r="B79" s="152"/>
+      <c r="C79" s="151"/>
+      <c r="D79" s="151"/>
+      <c r="E79" s="151"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="33"/>
-      <c r="B80" s="34"/>
-      <c r="C80" s="33"/>
-      <c r="D80" s="33"/>
-      <c r="E80" s="33"/>
+      <c r="A80" s="151"/>
+      <c r="B80" s="152"/>
+      <c r="C80" s="151"/>
+      <c r="D80" s="151"/>
+      <c r="E80" s="151"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="33"/>
-      <c r="B81" s="34"/>
-      <c r="C81" s="33"/>
-      <c r="D81" s="33"/>
-      <c r="E81" s="33"/>
+      <c r="A81" s="151"/>
+      <c r="B81" s="152"/>
+      <c r="C81" s="151"/>
+      <c r="D81" s="151"/>
+      <c r="E81" s="151"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="33"/>
-      <c r="B82" s="34"/>
-      <c r="C82" s="33"/>
-      <c r="D82" s="33"/>
-      <c r="E82" s="33"/>
+      <c r="A82" s="151"/>
+      <c r="B82" s="152"/>
+      <c r="C82" s="151"/>
+      <c r="D82" s="151"/>
+      <c r="E82" s="151"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="33"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="33"/>
-      <c r="D83" s="33"/>
-      <c r="E83" s="33"/>
+      <c r="A83" s="151"/>
+      <c r="B83" s="152"/>
+      <c r="C83" s="151"/>
+      <c r="D83" s="151"/>
+      <c r="E83" s="151"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="33"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="33"/>
-      <c r="D84" s="33"/>
-      <c r="E84" s="33"/>
+      <c r="A84" s="151"/>
+      <c r="B84" s="152"/>
+      <c r="C84" s="151"/>
+      <c r="D84" s="151"/>
+      <c r="E84" s="151"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="33"/>
-      <c r="B85" s="34"/>
-      <c r="C85" s="33"/>
-      <c r="D85" s="33"/>
-      <c r="E85" s="33"/>
+      <c r="A85" s="151"/>
+      <c r="B85" s="152"/>
+      <c r="C85" s="151"/>
+      <c r="D85" s="151"/>
+      <c r="E85" s="151"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="33"/>
-      <c r="B86" s="34"/>
-      <c r="C86" s="33"/>
-      <c r="D86" s="33"/>
-      <c r="E86" s="33"/>
+      <c r="A86" s="151"/>
+      <c r="B86" s="152"/>
+      <c r="C86" s="151"/>
+      <c r="D86" s="151"/>
+      <c r="E86" s="151"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="33"/>
-      <c r="B87" s="34"/>
-      <c r="C87" s="33"/>
-      <c r="D87" s="33"/>
-      <c r="E87" s="33"/>
+      <c r="A87" s="151"/>
+      <c r="B87" s="152"/>
+      <c r="C87" s="151"/>
+      <c r="D87" s="151"/>
+      <c r="E87" s="151"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="33"/>
-      <c r="B88" s="34"/>
-      <c r="C88" s="33"/>
-      <c r="D88" s="33"/>
-      <c r="E88" s="33"/>
+      <c r="A88" s="151"/>
+      <c r="B88" s="152"/>
+      <c r="C88" s="151"/>
+      <c r="D88" s="151"/>
+      <c r="E88" s="151"/>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="33"/>
-      <c r="B89" s="34"/>
-      <c r="C89" s="33"/>
-      <c r="D89" s="33"/>
-      <c r="E89" s="33"/>
+      <c r="A89" s="151"/>
+      <c r="B89" s="152"/>
+      <c r="C89" s="151"/>
+      <c r="D89" s="151"/>
+      <c r="E89" s="151"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="33"/>
-      <c r="B90" s="34"/>
-      <c r="C90" s="33"/>
-      <c r="D90" s="33"/>
-      <c r="E90" s="33"/>
+      <c r="A90" s="151"/>
+      <c r="B90" s="152"/>
+      <c r="C90" s="151"/>
+      <c r="D90" s="151"/>
+      <c r="E90" s="151"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="33"/>
-      <c r="B91" s="34"/>
-      <c r="C91" s="33"/>
-      <c r="D91" s="33"/>
-      <c r="E91" s="33"/>
+      <c r="A91" s="151"/>
+      <c r="B91" s="152"/>
+      <c r="C91" s="151"/>
+      <c r="D91" s="151"/>
+      <c r="E91" s="151"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="33"/>
-      <c r="B92" s="34"/>
-      <c r="C92" s="33"/>
-      <c r="D92" s="33"/>
-      <c r="E92" s="33"/>
+      <c r="A92" s="151"/>
+      <c r="B92" s="152"/>
+      <c r="C92" s="151"/>
+      <c r="D92" s="151"/>
+      <c r="E92" s="151"/>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="33"/>
-      <c r="B93" s="34"/>
-      <c r="C93" s="33"/>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33"/>
+      <c r="A93" s="151"/>
+      <c r="B93" s="152"/>
+      <c r="C93" s="151"/>
+      <c r="D93" s="151"/>
+      <c r="E93" s="151"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="33"/>
-      <c r="B94" s="34"/>
-      <c r="C94" s="33"/>
-      <c r="D94" s="33"/>
-      <c r="E94" s="33"/>
+      <c r="A94" s="151"/>
+      <c r="B94" s="152"/>
+      <c r="C94" s="151"/>
+      <c r="D94" s="151"/>
+      <c r="E94" s="151"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="33"/>
-      <c r="B95" s="34"/>
-      <c r="C95" s="33"/>
-      <c r="D95" s="33"/>
-      <c r="E95" s="33"/>
+      <c r="A95" s="151"/>
+      <c r="B95" s="152"/>
+      <c r="C95" s="151"/>
+      <c r="D95" s="151"/>
+      <c r="E95" s="151"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="33"/>
-      <c r="B96" s="34"/>
-      <c r="C96" s="33"/>
-      <c r="D96" s="33"/>
-      <c r="E96" s="33"/>
+      <c r="A96" s="151"/>
+      <c r="B96" s="152"/>
+      <c r="C96" s="151"/>
+      <c r="D96" s="151"/>
+      <c r="E96" s="151"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="33"/>
-      <c r="B97" s="34"/>
-      <c r="C97" s="33"/>
-      <c r="D97" s="33"/>
-      <c r="E97" s="33"/>
+      <c r="A97" s="151"/>
+      <c r="B97" s="152"/>
+      <c r="C97" s="151"/>
+      <c r="D97" s="151"/>
+      <c r="E97" s="151"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="33"/>
-      <c r="B98" s="34"/>
-      <c r="C98" s="33"/>
-      <c r="D98" s="33"/>
-      <c r="E98" s="33"/>
+      <c r="A98" s="151"/>
+      <c r="B98" s="152"/>
+      <c r="C98" s="151"/>
+      <c r="D98" s="151"/>
+      <c r="E98" s="151"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="33"/>
-      <c r="B99" s="34"/>
-      <c r="C99" s="33"/>
-      <c r="D99" s="33"/>
-      <c r="E99" s="33"/>
+      <c r="A99" s="151"/>
+      <c r="B99" s="152"/>
+      <c r="C99" s="151"/>
+      <c r="D99" s="151"/>
+      <c r="E99" s="151"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="33"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="33"/>
-      <c r="D100" s="33"/>
-      <c r="E100" s="33"/>
+      <c r="A100" s="151"/>
+      <c r="B100" s="152"/>
+      <c r="C100" s="151"/>
+      <c r="D100" s="151"/>
+      <c r="E100" s="151"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="33"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="33"/>
-      <c r="D101" s="33"/>
-      <c r="E101" s="33"/>
+      <c r="A101" s="151"/>
+      <c r="B101" s="152"/>
+      <c r="C101" s="151"/>
+      <c r="D101" s="151"/>
+      <c r="E101" s="151"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="33"/>
-      <c r="B102" s="34"/>
-      <c r="C102" s="33"/>
-      <c r="D102" s="33"/>
-      <c r="E102" s="33"/>
+      <c r="A102" s="151"/>
+      <c r="B102" s="152"/>
+      <c r="C102" s="151"/>
+      <c r="D102" s="151"/>
+      <c r="E102" s="151"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="33"/>
-      <c r="B103" s="34"/>
-      <c r="C103" s="33"/>
-      <c r="D103" s="33"/>
-      <c r="E103" s="33"/>
+      <c r="A103" s="151"/>
+      <c r="B103" s="152"/>
+      <c r="C103" s="151"/>
+      <c r="D103" s="151"/>
+      <c r="E103" s="151"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="33"/>
-      <c r="B104" s="34"/>
-      <c r="C104" s="33"/>
-      <c r="D104" s="33"/>
-      <c r="E104" s="33"/>
+      <c r="A104" s="151"/>
+      <c r="B104" s="152"/>
+      <c r="C104" s="151"/>
+      <c r="D104" s="151"/>
+      <c r="E104" s="151"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="33"/>
-      <c r="B105" s="34"/>
-      <c r="C105" s="33"/>
-      <c r="D105" s="33"/>
-      <c r="E105" s="33"/>
+      <c r="A105" s="151"/>
+      <c r="B105" s="152"/>
+      <c r="C105" s="151"/>
+      <c r="D105" s="151"/>
+      <c r="E105" s="151"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="33"/>
-      <c r="B106" s="34"/>
-      <c r="C106" s="33"/>
-      <c r="D106" s="33"/>
-      <c r="E106" s="33"/>
+      <c r="A106" s="151"/>
+      <c r="B106" s="152"/>
+      <c r="C106" s="151"/>
+      <c r="D106" s="151"/>
+      <c r="E106" s="151"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="33"/>
-      <c r="B107" s="34"/>
-      <c r="C107" s="33"/>
-      <c r="D107" s="33"/>
-      <c r="E107" s="33"/>
+      <c r="A107" s="151"/>
+      <c r="B107" s="152"/>
+      <c r="C107" s="151"/>
+      <c r="D107" s="151"/>
+      <c r="E107" s="151"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="33"/>
-      <c r="B108" s="34"/>
-      <c r="C108" s="33"/>
-      <c r="D108" s="33"/>
-      <c r="E108" s="33"/>
+      <c r="A108" s="151"/>
+      <c r="B108" s="152"/>
+      <c r="C108" s="151"/>
+      <c r="D108" s="151"/>
+      <c r="E108" s="151"/>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="33"/>
-      <c r="B109" s="34"/>
-      <c r="C109" s="33"/>
-      <c r="D109" s="33"/>
-      <c r="E109" s="33"/>
+      <c r="A109" s="151"/>
+      <c r="B109" s="152"/>
+      <c r="C109" s="151"/>
+      <c r="D109" s="151"/>
+      <c r="E109" s="151"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="33"/>
-      <c r="B110" s="34"/>
-      <c r="C110" s="33"/>
-      <c r="D110" s="33"/>
-      <c r="E110" s="33"/>
+      <c r="A110" s="151"/>
+      <c r="B110" s="152"/>
+      <c r="C110" s="151"/>
+      <c r="D110" s="151"/>
+      <c r="E110" s="151"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="33"/>
-      <c r="B111" s="34"/>
-      <c r="C111" s="33"/>
-      <c r="D111" s="33"/>
-      <c r="E111" s="33"/>
+      <c r="A111" s="151"/>
+      <c r="B111" s="152"/>
+      <c r="C111" s="151"/>
+      <c r="D111" s="151"/>
+      <c r="E111" s="151"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="33"/>
-      <c r="B112" s="34"/>
-      <c r="C112" s="33"/>
-      <c r="D112" s="33"/>
-      <c r="E112" s="33"/>
+      <c r="A112" s="151"/>
+      <c r="B112" s="152"/>
+      <c r="C112" s="151"/>
+      <c r="D112" s="151"/>
+      <c r="E112" s="151"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="33"/>
-      <c r="B113" s="34"/>
-      <c r="C113" s="33"/>
-      <c r="D113" s="33"/>
-      <c r="E113" s="33"/>
+      <c r="A113" s="151"/>
+      <c r="B113" s="152"/>
+      <c r="C113" s="151"/>
+      <c r="D113" s="151"/>
+      <c r="E113" s="151"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="33"/>
-      <c r="B114" s="34"/>
-      <c r="C114" s="33"/>
-      <c r="D114" s="33"/>
-      <c r="E114" s="33"/>
+      <c r="A114" s="151"/>
+      <c r="B114" s="152"/>
+      <c r="C114" s="151"/>
+      <c r="D114" s="151"/>
+      <c r="E114" s="151"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="33"/>
-      <c r="B115" s="34"/>
-      <c r="C115" s="33"/>
-      <c r="D115" s="33"/>
-      <c r="E115" s="33"/>
+      <c r="A115" s="151"/>
+      <c r="B115" s="152"/>
+      <c r="C115" s="151"/>
+      <c r="D115" s="151"/>
+      <c r="E115" s="151"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="33"/>
-      <c r="B116" s="34"/>
-      <c r="C116" s="33"/>
-      <c r="D116" s="33"/>
-      <c r="E116" s="33"/>
+      <c r="A116" s="151"/>
+      <c r="B116" s="152"/>
+      <c r="C116" s="151"/>
+      <c r="D116" s="151"/>
+      <c r="E116" s="151"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="33"/>
-      <c r="B117" s="34"/>
-      <c r="C117" s="33"/>
-      <c r="D117" s="33"/>
-      <c r="E117" s="33"/>
+      <c r="A117" s="151"/>
+      <c r="B117" s="152"/>
+      <c r="C117" s="151"/>
+      <c r="D117" s="151"/>
+      <c r="E117" s="151"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="33"/>
-      <c r="B118" s="34"/>
-      <c r="C118" s="33"/>
-      <c r="D118" s="33"/>
-      <c r="E118" s="33"/>
+      <c r="A118" s="151"/>
+      <c r="B118" s="152"/>
+      <c r="C118" s="151"/>
+      <c r="D118" s="151"/>
+      <c r="E118" s="151"/>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="33"/>
-      <c r="B119" s="34"/>
-      <c r="C119" s="33"/>
-      <c r="D119" s="33"/>
-      <c r="E119" s="33"/>
+      <c r="A119" s="151"/>
+      <c r="B119" s="152"/>
+      <c r="C119" s="151"/>
+      <c r="D119" s="151"/>
+      <c r="E119" s="151"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="33"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="33"/>
-      <c r="D120" s="33"/>
-      <c r="E120" s="33"/>
+      <c r="A120" s="151"/>
+      <c r="B120" s="152"/>
+      <c r="C120" s="151"/>
+      <c r="D120" s="151"/>
+      <c r="E120" s="151"/>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="33"/>
-      <c r="B121" s="34"/>
-      <c r="C121" s="33"/>
-      <c r="D121" s="33"/>
-      <c r="E121" s="33"/>
+      <c r="A121" s="151"/>
+      <c r="B121" s="152"/>
+      <c r="C121" s="151"/>
+      <c r="D121" s="151"/>
+      <c r="E121" s="151"/>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="33"/>
-      <c r="B122" s="34"/>
-      <c r="C122" s="33"/>
-      <c r="D122" s="33"/>
-      <c r="E122" s="33"/>
+      <c r="A122" s="151"/>
+      <c r="B122" s="152"/>
+      <c r="C122" s="151"/>
+      <c r="D122" s="151"/>
+      <c r="E122" s="151"/>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="33"/>
-      <c r="B123" s="34"/>
-      <c r="C123" s="33"/>
-      <c r="D123" s="33"/>
-      <c r="E123" s="33"/>
+      <c r="A123" s="151"/>
+      <c r="B123" s="152"/>
+      <c r="C123" s="151"/>
+      <c r="D123" s="151"/>
+      <c r="E123" s="151"/>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="33"/>
-      <c r="B124" s="34"/>
-      <c r="C124" s="33"/>
-      <c r="D124" s="33"/>
-      <c r="E124" s="33"/>
+      <c r="A124" s="151"/>
+      <c r="B124" s="152"/>
+      <c r="C124" s="151"/>
+      <c r="D124" s="151"/>
+      <c r="E124" s="151"/>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="33"/>
-      <c r="B125" s="34"/>
-      <c r="C125" s="33"/>
-      <c r="D125" s="33"/>
-      <c r="E125" s="33"/>
+      <c r="A125" s="151"/>
+      <c r="B125" s="152"/>
+      <c r="C125" s="151"/>
+      <c r="D125" s="151"/>
+      <c r="E125" s="151"/>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="33"/>
-      <c r="B126" s="34"/>
-      <c r="C126" s="33"/>
-      <c r="D126" s="33"/>
-      <c r="E126" s="33"/>
+      <c r="A126" s="151"/>
+      <c r="B126" s="152"/>
+      <c r="C126" s="151"/>
+      <c r="D126" s="151"/>
+      <c r="E126" s="151"/>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="33"/>
-      <c r="B127" s="34"/>
-      <c r="C127" s="33"/>
-      <c r="D127" s="33"/>
-      <c r="E127" s="33"/>
+      <c r="A127" s="151"/>
+      <c r="B127" s="152"/>
+      <c r="C127" s="151"/>
+      <c r="D127" s="151"/>
+      <c r="E127" s="151"/>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="33"/>
-      <c r="B128" s="34"/>
-      <c r="C128" s="33"/>
-      <c r="D128" s="33"/>
-      <c r="E128" s="33"/>
+      <c r="A128" s="151"/>
+      <c r="B128" s="152"/>
+      <c r="C128" s="151"/>
+      <c r="D128" s="151"/>
+      <c r="E128" s="151"/>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="33"/>
-      <c r="B129" s="34"/>
-      <c r="C129" s="33"/>
-      <c r="D129" s="33"/>
-      <c r="E129" s="33"/>
+      <c r="A129" s="151"/>
+      <c r="B129" s="152"/>
+      <c r="C129" s="151"/>
+      <c r="D129" s="151"/>
+      <c r="E129" s="151"/>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="33"/>
-      <c r="B130" s="34"/>
-      <c r="C130" s="33"/>
-      <c r="D130" s="33"/>
-      <c r="E130" s="33"/>
+      <c r="A130" s="151"/>
+      <c r="B130" s="152"/>
+      <c r="C130" s="151"/>
+      <c r="D130" s="151"/>
+      <c r="E130" s="151"/>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="33"/>
-      <c r="B131" s="34"/>
-      <c r="C131" s="33"/>
-      <c r="D131" s="33"/>
-      <c r="E131" s="33"/>
+      <c r="A131" s="151"/>
+      <c r="B131" s="152"/>
+      <c r="C131" s="151"/>
+      <c r="D131" s="151"/>
+      <c r="E131" s="151"/>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="33"/>
-      <c r="B132" s="34"/>
-      <c r="C132" s="33"/>
-      <c r="D132" s="33"/>
-      <c r="E132" s="33"/>
+      <c r="A132" s="151"/>
+      <c r="B132" s="152"/>
+      <c r="C132" s="151"/>
+      <c r="D132" s="151"/>
+      <c r="E132" s="151"/>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="33"/>
-      <c r="B133" s="34"/>
-      <c r="C133" s="33"/>
-      <c r="D133" s="33"/>
-      <c r="E133" s="33"/>
+      <c r="A133" s="151"/>
+      <c r="B133" s="152"/>
+      <c r="C133" s="151"/>
+      <c r="D133" s="151"/>
+      <c r="E133" s="151"/>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="33"/>
-      <c r="B134" s="34"/>
-      <c r="C134" s="33"/>
-      <c r="D134" s="33"/>
-      <c r="E134" s="33"/>
+      <c r="A134" s="151"/>
+      <c r="B134" s="152"/>
+      <c r="C134" s="151"/>
+      <c r="D134" s="151"/>
+      <c r="E134" s="151"/>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="33"/>
-      <c r="B135" s="34"/>
-      <c r="C135" s="33"/>
-      <c r="D135" s="33"/>
-      <c r="E135" s="33"/>
+      <c r="A135" s="151"/>
+      <c r="B135" s="152"/>
+      <c r="C135" s="151"/>
+      <c r="D135" s="151"/>
+      <c r="E135" s="151"/>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="33"/>
-      <c r="B136" s="34"/>
-      <c r="C136" s="33"/>
-      <c r="D136" s="33"/>
-      <c r="E136" s="33"/>
+      <c r="A136" s="151"/>
+      <c r="B136" s="152"/>
+      <c r="C136" s="151"/>
+      <c r="D136" s="151"/>
+      <c r="E136" s="151"/>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="33"/>
-      <c r="B137" s="34"/>
-      <c r="C137" s="33"/>
-      <c r="D137" s="33"/>
-      <c r="E137" s="33"/>
+      <c r="A137" s="151"/>
+      <c r="B137" s="152"/>
+      <c r="C137" s="151"/>
+      <c r="D137" s="151"/>
+      <c r="E137" s="151"/>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="33"/>
-      <c r="B138" s="34"/>
-      <c r="C138" s="33"/>
-      <c r="D138" s="33"/>
-      <c r="E138" s="33"/>
+      <c r="A138" s="151"/>
+      <c r="B138" s="152"/>
+      <c r="C138" s="151"/>
+      <c r="D138" s="151"/>
+      <c r="E138" s="151"/>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="33"/>
-      <c r="B139" s="34"/>
-      <c r="C139" s="33"/>
-      <c r="D139" s="33"/>
-      <c r="E139" s="33"/>
+      <c r="A139" s="151"/>
+      <c r="B139" s="152"/>
+      <c r="C139" s="151"/>
+      <c r="D139" s="151"/>
+      <c r="E139" s="151"/>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="33"/>
-      <c r="B140" s="34"/>
-      <c r="C140" s="33"/>
-      <c r="D140" s="33"/>
-      <c r="E140" s="33"/>
+      <c r="A140" s="151"/>
+      <c r="B140" s="152"/>
+      <c r="C140" s="151"/>
+      <c r="D140" s="151"/>
+      <c r="E140" s="151"/>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="33"/>
-      <c r="B141" s="34"/>
-      <c r="C141" s="33"/>
-      <c r="D141" s="33"/>
-      <c r="E141" s="33"/>
+      <c r="A141" s="151"/>
+      <c r="B141" s="152"/>
+      <c r="C141" s="151"/>
+      <c r="D141" s="151"/>
+      <c r="E141" s="151"/>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="33"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="33"/>
-      <c r="D142" s="33"/>
-      <c r="E142" s="33"/>
+      <c r="A142" s="151"/>
+      <c r="B142" s="152"/>
+      <c r="C142" s="151"/>
+      <c r="D142" s="151"/>
+      <c r="E142" s="151"/>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="33"/>
-      <c r="B143" s="34"/>
-      <c r="C143" s="33"/>
-      <c r="D143" s="33"/>
-      <c r="E143" s="33"/>
+      <c r="A143" s="151"/>
+      <c r="B143" s="152"/>
+      <c r="C143" s="151"/>
+      <c r="D143" s="151"/>
+      <c r="E143" s="151"/>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="33"/>
-      <c r="B144" s="34"/>
-      <c r="C144" s="33"/>
-      <c r="D144" s="33"/>
-      <c r="E144" s="33"/>
+      <c r="A144" s="151"/>
+      <c r="B144" s="152"/>
+      <c r="C144" s="151"/>
+      <c r="D144" s="151"/>
+      <c r="E144" s="151"/>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="33"/>
-      <c r="B145" s="34"/>
-      <c r="C145" s="33"/>
-      <c r="D145" s="33"/>
-      <c r="E145" s="33"/>
+      <c r="A145" s="151"/>
+      <c r="B145" s="152"/>
+      <c r="C145" s="151"/>
+      <c r="D145" s="151"/>
+      <c r="E145" s="151"/>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="33"/>
-      <c r="B146" s="34"/>
-      <c r="C146" s="33"/>
-      <c r="D146" s="33"/>
-      <c r="E146" s="33"/>
+      <c r="A146" s="151"/>
+      <c r="B146" s="152"/>
+      <c r="C146" s="151"/>
+      <c r="D146" s="151"/>
+      <c r="E146" s="151"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="33"/>
-      <c r="B147" s="34"/>
-      <c r="C147" s="33"/>
-      <c r="D147" s="33"/>
-      <c r="E147" s="33"/>
+      <c r="A147" s="151"/>
+      <c r="B147" s="152"/>
+      <c r="C147" s="151"/>
+      <c r="D147" s="151"/>
+      <c r="E147" s="151"/>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="33"/>
-      <c r="B148" s="34"/>
-      <c r="C148" s="33"/>
-      <c r="D148" s="33"/>
-      <c r="E148" s="33"/>
+      <c r="A148" s="151"/>
+      <c r="B148" s="152"/>
+      <c r="C148" s="151"/>
+      <c r="D148" s="151"/>
+      <c r="E148" s="151"/>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="33"/>
-      <c r="B149" s="34"/>
-      <c r="C149" s="33"/>
-      <c r="D149" s="33"/>
-      <c r="E149" s="33"/>
+      <c r="A149" s="151"/>
+      <c r="B149" s="152"/>
+      <c r="C149" s="151"/>
+      <c r="D149" s="151"/>
+      <c r="E149" s="151"/>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="33"/>
-      <c r="B150" s="34"/>
-      <c r="C150" s="33"/>
-      <c r="D150" s="33"/>
-      <c r="E150" s="33"/>
+      <c r="A150" s="151"/>
+      <c r="B150" s="152"/>
+      <c r="C150" s="151"/>
+      <c r="D150" s="151"/>
+      <c r="E150" s="151"/>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="33"/>
-      <c r="B151" s="34"/>
-      <c r="C151" s="33"/>
-      <c r="D151" s="33"/>
-      <c r="E151" s="33"/>
+      <c r="A151" s="151"/>
+      <c r="B151" s="152"/>
+      <c r="C151" s="151"/>
+      <c r="D151" s="151"/>
+      <c r="E151" s="151"/>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="33"/>
-      <c r="B152" s="34"/>
-      <c r="C152" s="33"/>
-      <c r="D152" s="33"/>
-      <c r="E152" s="33"/>
+      <c r="A152" s="151"/>
+      <c r="B152" s="152"/>
+      <c r="C152" s="151"/>
+      <c r="D152" s="151"/>
+      <c r="E152" s="151"/>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="33"/>
-      <c r="B153" s="34"/>
-      <c r="C153" s="33"/>
-      <c r="D153" s="33"/>
-      <c r="E153" s="33"/>
+      <c r="A153" s="151"/>
+      <c r="B153" s="152"/>
+      <c r="C153" s="151"/>
+      <c r="D153" s="151"/>
+      <c r="E153" s="151"/>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="33"/>
-      <c r="B154" s="34"/>
-      <c r="C154" s="33"/>
-      <c r="D154" s="33"/>
-      <c r="E154" s="33"/>
+      <c r="A154" s="151"/>
+      <c r="B154" s="152"/>
+      <c r="C154" s="151"/>
+      <c r="D154" s="151"/>
+      <c r="E154" s="151"/>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="33"/>
-      <c r="B155" s="34"/>
-      <c r="C155" s="33"/>
-      <c r="D155" s="33"/>
-      <c r="E155" s="33"/>
+      <c r="A155" s="151"/>
+      <c r="B155" s="152"/>
+      <c r="C155" s="151"/>
+      <c r="D155" s="151"/>
+      <c r="E155" s="151"/>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="33"/>
-      <c r="B156" s="34"/>
-      <c r="C156" s="33"/>
-      <c r="D156" s="33"/>
-      <c r="E156" s="33"/>
+      <c r="A156" s="151"/>
+      <c r="B156" s="152"/>
+      <c r="C156" s="151"/>
+      <c r="D156" s="151"/>
+      <c r="E156" s="151"/>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="33"/>
-      <c r="B157" s="34"/>
-      <c r="C157" s="33"/>
-      <c r="D157" s="33"/>
-      <c r="E157" s="33"/>
+      <c r="A157" s="151"/>
+      <c r="B157" s="152"/>
+      <c r="C157" s="151"/>
+      <c r="D157" s="151"/>
+      <c r="E157" s="151"/>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="33"/>
-      <c r="B158" s="34"/>
-      <c r="C158" s="33"/>
-      <c r="D158" s="33"/>
-      <c r="E158" s="33"/>
+      <c r="A158" s="151"/>
+      <c r="B158" s="152"/>
+      <c r="C158" s="151"/>
+      <c r="D158" s="151"/>
+      <c r="E158" s="151"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="33"/>
-      <c r="B159" s="34"/>
-      <c r="C159" s="33"/>
-      <c r="D159" s="33"/>
-      <c r="E159" s="33"/>
+      <c r="A159" s="151"/>
+      <c r="B159" s="152"/>
+      <c r="C159" s="151"/>
+      <c r="D159" s="151"/>
+      <c r="E159" s="151"/>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="33"/>
-      <c r="B160" s="34"/>
-      <c r="C160" s="33"/>
-      <c r="D160" s="33"/>
-      <c r="E160" s="33"/>
+      <c r="A160" s="151"/>
+      <c r="B160" s="152"/>
+      <c r="C160" s="151"/>
+      <c r="D160" s="151"/>
+      <c r="E160" s="151"/>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="33"/>
-      <c r="B161" s="34"/>
-      <c r="C161" s="33"/>
-      <c r="D161" s="33"/>
-      <c r="E161" s="33"/>
+      <c r="A161" s="151"/>
+      <c r="B161" s="152"/>
+      <c r="C161" s="151"/>
+      <c r="D161" s="151"/>
+      <c r="E161" s="151"/>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="33"/>
-      <c r="B162" s="34"/>
-      <c r="C162" s="33"/>
-      <c r="D162" s="33"/>
-      <c r="E162" s="33"/>
+      <c r="A162" s="151"/>
+      <c r="B162" s="152"/>
+      <c r="C162" s="151"/>
+      <c r="D162" s="151"/>
+      <c r="E162" s="151"/>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="33"/>
-      <c r="B163" s="34"/>
-      <c r="C163" s="33"/>
-      <c r="D163" s="33"/>
-      <c r="E163" s="33"/>
+      <c r="A163" s="151"/>
+      <c r="B163" s="152"/>
+      <c r="C163" s="151"/>
+      <c r="D163" s="151"/>
+      <c r="E163" s="151"/>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="33"/>
-      <c r="B164" s="34"/>
-      <c r="C164" s="33"/>
-      <c r="D164" s="33"/>
-      <c r="E164" s="33"/>
+      <c r="A164" s="151"/>
+      <c r="B164" s="152"/>
+      <c r="C164" s="151"/>
+      <c r="D164" s="151"/>
+      <c r="E164" s="151"/>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="33"/>
-      <c r="B165" s="34"/>
-      <c r="C165" s="33"/>
-      <c r="D165" s="33"/>
-      <c r="E165" s="33"/>
+      <c r="A165" s="151"/>
+      <c r="B165" s="152"/>
+      <c r="C165" s="151"/>
+      <c r="D165" s="151"/>
+      <c r="E165" s="151"/>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="33"/>
-      <c r="B166" s="34"/>
-      <c r="C166" s="33"/>
-      <c r="D166" s="33"/>
-      <c r="E166" s="33"/>
+      <c r="A166" s="151"/>
+      <c r="B166" s="152"/>
+      <c r="C166" s="151"/>
+      <c r="D166" s="151"/>
+      <c r="E166" s="151"/>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="33"/>
-      <c r="B167" s="34"/>
-      <c r="C167" s="33"/>
-      <c r="D167" s="33"/>
-      <c r="E167" s="33"/>
+      <c r="A167" s="151"/>
+      <c r="B167" s="152"/>
+      <c r="C167" s="151"/>
+      <c r="D167" s="151"/>
+      <c r="E167" s="151"/>
     </row>
     <row r="168" spans="1:5">
-      <c r="A168" s="33"/>
-      <c r="B168" s="34"/>
-      <c r="C168" s="33"/>
-      <c r="D168" s="33"/>
-      <c r="E168" s="33"/>
+      <c r="A168" s="151"/>
+      <c r="B168" s="152"/>
+      <c r="C168" s="151"/>
+      <c r="D168" s="151"/>
+      <c r="E168" s="151"/>
     </row>
     <row r="169" spans="1:5">
-      <c r="A169" s="33"/>
-      <c r="B169" s="34"/>
-      <c r="C169" s="33"/>
-      <c r="D169" s="33"/>
-      <c r="E169" s="33"/>
+      <c r="A169" s="151"/>
+      <c r="B169" s="152"/>
+      <c r="C169" s="151"/>
+      <c r="D169" s="151"/>
+      <c r="E169" s="151"/>
     </row>
     <row r="170" spans="1:5">
-      <c r="A170" s="33"/>
-      <c r="B170" s="34"/>
-      <c r="C170" s="33"/>
-      <c r="D170" s="33"/>
-      <c r="E170" s="33"/>
+      <c r="A170" s="151"/>
+      <c r="B170" s="152"/>
+      <c r="C170" s="151"/>
+      <c r="D170" s="151"/>
+      <c r="E170" s="151"/>
     </row>
     <row r="171" spans="1:5">
-      <c r="A171" s="33"/>
-      <c r="B171" s="34"/>
-      <c r="C171" s="33"/>
-      <c r="D171" s="33"/>
-      <c r="E171" s="33"/>
+      <c r="A171" s="151"/>
+      <c r="B171" s="152"/>
+      <c r="C171" s="151"/>
+      <c r="D171" s="151"/>
+      <c r="E171" s="151"/>
     </row>
     <row r="172" spans="1:5">
-      <c r="A172" s="33"/>
-      <c r="B172" s="34"/>
-      <c r="C172" s="33"/>
-      <c r="D172" s="33"/>
-      <c r="E172" s="33"/>
+      <c r="A172" s="151"/>
+      <c r="B172" s="152"/>
+      <c r="C172" s="151"/>
+      <c r="D172" s="151"/>
+      <c r="E172" s="151"/>
     </row>
     <row r="173" spans="1:5">
-      <c r="A173" s="33"/>
-      <c r="B173" s="34"/>
-      <c r="C173" s="33"/>
-      <c r="D173" s="33"/>
-      <c r="E173" s="33"/>
+      <c r="A173" s="151"/>
+      <c r="B173" s="152"/>
+      <c r="C173" s="151"/>
+      <c r="D173" s="151"/>
+      <c r="E173" s="151"/>
     </row>
     <row r="174" spans="1:5">
-      <c r="A174" s="33"/>
-      <c r="B174" s="34"/>
-      <c r="C174" s="33"/>
-      <c r="D174" s="33"/>
-      <c r="E174" s="33"/>
+      <c r="A174" s="151"/>
+      <c r="B174" s="152"/>
+      <c r="C174" s="151"/>
+      <c r="D174" s="151"/>
+      <c r="E174" s="151"/>
     </row>
     <row r="175" spans="1:5">
-      <c r="A175" s="33"/>
-      <c r="B175" s="34"/>
-      <c r="C175" s="33"/>
-      <c r="D175" s="33"/>
-      <c r="E175" s="33"/>
+      <c r="A175" s="151"/>
+      <c r="B175" s="152"/>
+      <c r="C175" s="151"/>
+      <c r="D175" s="151"/>
+      <c r="E175" s="151"/>
     </row>
     <row r="176" spans="1:5">
-      <c r="A176" s="33"/>
-      <c r="B176" s="34"/>
-      <c r="C176" s="33"/>
-      <c r="D176" s="33"/>
-      <c r="E176" s="33"/>
+      <c r="A176" s="151"/>
+      <c r="B176" s="152"/>
+      <c r="C176" s="151"/>
+      <c r="D176" s="151"/>
+      <c r="E176" s="151"/>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" s="33"/>
-      <c r="B177" s="34"/>
-      <c r="C177" s="33"/>
-      <c r="D177" s="33"/>
-      <c r="E177" s="33"/>
+      <c r="A177" s="151"/>
+      <c r="B177" s="152"/>
+      <c r="C177" s="151"/>
+      <c r="D177" s="151"/>
+      <c r="E177" s="151"/>
     </row>
     <row r="178" spans="1:5">
-      <c r="A178" s="33"/>
-      <c r="B178" s="34"/>
-      <c r="C178" s="33"/>
-      <c r="D178" s="33"/>
-      <c r="E178" s="33"/>
+      <c r="A178" s="151"/>
+      <c r="B178" s="152"/>
+      <c r="C178" s="151"/>
+      <c r="D178" s="151"/>
+      <c r="E178" s="151"/>
     </row>
     <row r="179" spans="1:5">
-      <c r="A179" s="33"/>
-      <c r="B179" s="34"/>
-      <c r="C179" s="33"/>
-      <c r="D179" s="33"/>
-      <c r="E179" s="33"/>
+      <c r="A179" s="151"/>
+      <c r="B179" s="152"/>
+      <c r="C179" s="151"/>
+      <c r="D179" s="151"/>
+      <c r="E179" s="151"/>
     </row>
     <row r="180" spans="1:5">
-      <c r="A180" s="33"/>
-      <c r="B180" s="34"/>
-      <c r="C180" s="33"/>
-      <c r="D180" s="33"/>
-      <c r="E180" s="33"/>
+      <c r="A180" s="151"/>
+      <c r="B180" s="152"/>
+      <c r="C180" s="151"/>
+      <c r="D180" s="151"/>
+      <c r="E180" s="151"/>
     </row>
     <row r="181" spans="1:5">
-      <c r="A181" s="33"/>
-      <c r="B181" s="34"/>
-      <c r="C181" s="33"/>
-      <c r="D181" s="33"/>
-      <c r="E181" s="33"/>
+      <c r="A181" s="151"/>
+      <c r="B181" s="152"/>
+      <c r="C181" s="151"/>
+      <c r="D181" s="151"/>
+      <c r="E181" s="151"/>
     </row>
     <row r="182" spans="1:5">
-      <c r="A182" s="33"/>
-      <c r="B182" s="34"/>
-      <c r="C182" s="33"/>
-      <c r="D182" s="33"/>
-      <c r="E182" s="33"/>
+      <c r="A182" s="151"/>
+      <c r="B182" s="152"/>
+      <c r="C182" s="151"/>
+      <c r="D182" s="151"/>
+      <c r="E182" s="151"/>
     </row>
     <row r="183" spans="1:5">
-      <c r="A183" s="33"/>
-      <c r="B183" s="34"/>
-      <c r="C183" s="33"/>
-      <c r="D183" s="33"/>
-      <c r="E183" s="33"/>
+      <c r="A183" s="151"/>
+      <c r="B183" s="152"/>
+      <c r="C183" s="151"/>
+      <c r="D183" s="151"/>
+      <c r="E183" s="151"/>
     </row>
     <row r="184" spans="1:5">
-      <c r="A184" s="33"/>
-      <c r="B184" s="34"/>
-      <c r="C184" s="33"/>
-      <c r="D184" s="33"/>
-      <c r="E184" s="33"/>
+      <c r="A184" s="151"/>
+      <c r="B184" s="152"/>
+      <c r="C184" s="151"/>
+      <c r="D184" s="151"/>
+      <c r="E184" s="151"/>
     </row>
     <row r="185" spans="1:5">
-      <c r="A185" s="33"/>
-      <c r="B185" s="34"/>
-      <c r="C185" s="33"/>
-      <c r="D185" s="33"/>
-      <c r="E185" s="33"/>
+      <c r="A185" s="151"/>
+      <c r="B185" s="152"/>
+      <c r="C185" s="151"/>
+      <c r="D185" s="151"/>
+      <c r="E185" s="151"/>
     </row>
     <row r="186" spans="1:5">
-      <c r="A186" s="33"/>
-      <c r="B186" s="34"/>
-      <c r="C186" s="33"/>
-      <c r="D186" s="33"/>
-      <c r="E186" s="33"/>
+      <c r="A186" s="151"/>
+      <c r="B186" s="152"/>
+      <c r="C186" s="151"/>
+      <c r="D186" s="151"/>
+      <c r="E186" s="151"/>
     </row>
     <row r="187" spans="1:5">
-      <c r="A187" s="33"/>
-      <c r="B187" s="34"/>
-      <c r="C187" s="33"/>
-      <c r="D187" s="33"/>
-      <c r="E187" s="33"/>
+      <c r="A187" s="151"/>
+      <c r="B187" s="152"/>
+      <c r="C187" s="151"/>
+      <c r="D187" s="151"/>
+      <c r="E187" s="151"/>
     </row>
     <row r="188" spans="1:5">
-      <c r="A188" s="33"/>
-      <c r="B188" s="34"/>
-      <c r="C188" s="33"/>
-      <c r="D188" s="33"/>
-      <c r="E188" s="33"/>
+      <c r="A188" s="151"/>
+      <c r="B188" s="152"/>
+      <c r="C188" s="151"/>
+      <c r="D188" s="151"/>
+      <c r="E188" s="151"/>
     </row>
     <row r="189" spans="1:5">
-      <c r="A189" s="33"/>
-      <c r="B189" s="34"/>
-      <c r="C189" s="33"/>
-      <c r="D189" s="33"/>
-      <c r="E189" s="33"/>
+      <c r="A189" s="151"/>
+      <c r="B189" s="152"/>
+      <c r="C189" s="151"/>
+      <c r="D189" s="151"/>
+      <c r="E189" s="151"/>
     </row>
     <row r="190" spans="1:5">
-      <c r="A190" s="33"/>
-      <c r="B190" s="34"/>
-      <c r="C190" s="33"/>
-      <c r="D190" s="33"/>
-      <c r="E190" s="33"/>
+      <c r="A190" s="151"/>
+      <c r="B190" s="152"/>
+      <c r="C190" s="151"/>
+      <c r="D190" s="151"/>
+      <c r="E190" s="151"/>
     </row>
     <row r="191" spans="1:5">
-      <c r="A191" s="33"/>
-      <c r="B191" s="34"/>
-      <c r="C191" s="33"/>
-      <c r="D191" s="33"/>
-      <c r="E191" s="33"/>
+      <c r="A191" s="151"/>
+      <c r="B191" s="152"/>
+      <c r="C191" s="151"/>
+      <c r="D191" s="151"/>
+      <c r="E191" s="151"/>
     </row>
     <row r="192" spans="1:5">
-      <c r="A192" s="33"/>
-      <c r="B192" s="34"/>
-      <c r="C192" s="33"/>
-      <c r="D192" s="33"/>
-      <c r="E192" s="33"/>
+      <c r="A192" s="151"/>
+      <c r="B192" s="152"/>
+      <c r="C192" s="151"/>
+      <c r="D192" s="151"/>
+      <c r="E192" s="151"/>
     </row>
     <row r="193" spans="1:5">
-      <c r="A193" s="33"/>
-      <c r="B193" s="34"/>
-      <c r="C193" s="33"/>
-      <c r="D193" s="33"/>
-      <c r="E193" s="33"/>
+      <c r="A193" s="151"/>
+      <c r="B193" s="152"/>
+      <c r="C193" s="151"/>
+      <c r="D193" s="151"/>
+      <c r="E193" s="151"/>
     </row>
     <row r="194" spans="1:5">
-      <c r="A194" s="33"/>
-      <c r="B194" s="34"/>
-      <c r="C194" s="33"/>
-      <c r="D194" s="33"/>
-      <c r="E194" s="33"/>
+      <c r="A194" s="151"/>
+      <c r="B194" s="152"/>
+      <c r="C194" s="151"/>
+      <c r="D194" s="151"/>
+      <c r="E194" s="151"/>
     </row>
     <row r="195" spans="1:5">
-      <c r="A195" s="33"/>
-      <c r="B195" s="34"/>
-      <c r="C195" s="33"/>
-      <c r="D195" s="33"/>
-      <c r="E195" s="33"/>
+      <c r="A195" s="151"/>
+      <c r="B195" s="152"/>
+      <c r="C195" s="151"/>
+      <c r="D195" s="151"/>
+      <c r="E195" s="151"/>
     </row>
     <row r="196" spans="1:5">
-      <c r="A196" s="33"/>
-      <c r="B196" s="34"/>
-      <c r="C196" s="33"/>
-      <c r="D196" s="33"/>
-      <c r="E196" s="33"/>
+      <c r="A196" s="151"/>
+      <c r="B196" s="152"/>
+      <c r="C196" s="151"/>
+      <c r="D196" s="151"/>
+      <c r="E196" s="151"/>
     </row>
     <row r="197" spans="1:5">
-      <c r="A197" s="33"/>
-      <c r="B197" s="34"/>
-      <c r="C197" s="33"/>
-      <c r="D197" s="33"/>
-      <c r="E197" s="33"/>
+      <c r="A197" s="151"/>
+      <c r="B197" s="152"/>
+      <c r="C197" s="151"/>
+      <c r="D197" s="151"/>
+      <c r="E197" s="151"/>
     </row>
     <row r="198" spans="1:5">
-      <c r="A198" s="33"/>
-      <c r="B198" s="34"/>
-      <c r="C198" s="33"/>
-      <c r="D198" s="33"/>
-      <c r="E198" s="33"/>
+      <c r="A198" s="151"/>
+      <c r="B198" s="152"/>
+      <c r="C198" s="151"/>
+      <c r="D198" s="151"/>
+      <c r="E198" s="151"/>
     </row>
     <row r="199" spans="1:5">
-      <c r="A199" s="33"/>
-      <c r="B199" s="34"/>
-      <c r="C199" s="33"/>
-      <c r="D199" s="33"/>
-      <c r="E199" s="33"/>
+      <c r="A199" s="151"/>
+      <c r="B199" s="152"/>
+      <c r="C199" s="151"/>
+      <c r="D199" s="151"/>
+      <c r="E199" s="151"/>
     </row>
     <row r="200" spans="1:5">
-      <c r="A200" s="33"/>
-      <c r="B200" s="34"/>
-      <c r="C200" s="33"/>
-      <c r="D200" s="33"/>
-      <c r="E200" s="33"/>
+      <c r="A200" s="151"/>
+      <c r="B200" s="152"/>
+      <c r="C200" s="151"/>
+      <c r="D200" s="151"/>
+      <c r="E200" s="151"/>
     </row>
     <row r="201" spans="1:5">
-      <c r="A201" s="33"/>
-      <c r="B201" s="34"/>
-      <c r="C201" s="33"/>
-      <c r="D201" s="33"/>
-      <c r="E201" s="33"/>
+      <c r="A201" s="151"/>
+      <c r="B201" s="152"/>
+      <c r="C201" s="151"/>
+      <c r="D201" s="151"/>
+      <c r="E201" s="151"/>
     </row>
     <row r="202" spans="1:5">
-      <c r="A202" s="33"/>
-      <c r="B202" s="34"/>
-      <c r="C202" s="33"/>
-      <c r="D202" s="33"/>
-      <c r="E202" s="33"/>
+      <c r="A202" s="151"/>
+      <c r="B202" s="152"/>
+      <c r="C202" s="151"/>
+      <c r="D202" s="151"/>
+      <c r="E202" s="151"/>
     </row>
     <row r="203" spans="1:5">
-      <c r="A203" s="33"/>
-      <c r="B203" s="34"/>
-      <c r="C203" s="33"/>
-      <c r="D203" s="33"/>
-      <c r="E203" s="33"/>
+      <c r="A203" s="151"/>
+      <c r="B203" s="152"/>
+      <c r="C203" s="151"/>
+      <c r="D203" s="151"/>
+      <c r="E203" s="151"/>
     </row>
     <row r="204" spans="1:5">
-      <c r="A204" s="33"/>
-      <c r="B204" s="34"/>
-      <c r="C204" s="33"/>
-      <c r="D204" s="33"/>
-      <c r="E204" s="33"/>
+      <c r="A204" s="151"/>
+      <c r="B204" s="152"/>
+      <c r="C204" s="151"/>
+      <c r="D204" s="151"/>
+      <c r="E204" s="151"/>
     </row>
     <row r="205" spans="1:5">
-      <c r="A205" s="33"/>
-      <c r="B205" s="34"/>
-      <c r="C205" s="33"/>
-      <c r="D205" s="33"/>
-      <c r="E205" s="33"/>
+      <c r="A205" s="151"/>
+      <c r="B205" s="152"/>
+      <c r="C205" s="151"/>
+      <c r="D205" s="151"/>
+      <c r="E205" s="151"/>
     </row>
     <row r="206" spans="1:5">
-      <c r="A206" s="33"/>
-      <c r="B206" s="34"/>
-      <c r="C206" s="33"/>
-      <c r="D206" s="33"/>
-      <c r="E206" s="33"/>
+      <c r="A206" s="151"/>
+      <c r="B206" s="152"/>
+      <c r="C206" s="151"/>
+      <c r="D206" s="151"/>
+      <c r="E206" s="151"/>
     </row>
     <row r="207" spans="1:5">
-      <c r="A207" s="33"/>
-      <c r="B207" s="34"/>
-      <c r="C207" s="33"/>
-      <c r="D207" s="33"/>
-      <c r="E207" s="33"/>
+      <c r="A207" s="151"/>
+      <c r="B207" s="152"/>
+      <c r="C207" s="151"/>
+      <c r="D207" s="151"/>
+      <c r="E207" s="151"/>
     </row>
     <row r="208" spans="1:5">
-      <c r="A208" s="33"/>
-      <c r="B208" s="34"/>
-      <c r="C208" s="33"/>
-      <c r="D208" s="33"/>
-      <c r="E208" s="33"/>
+      <c r="A208" s="151"/>
+      <c r="B208" s="152"/>
+      <c r="C208" s="151"/>
+      <c r="D208" s="151"/>
+      <c r="E208" s="151"/>
     </row>
     <row r="209" spans="1:5">
-      <c r="A209" s="33"/>
-      <c r="B209" s="34"/>
-      <c r="C209" s="33"/>
-      <c r="D209" s="33"/>
-      <c r="E209" s="33"/>
+      <c r="A209" s="151"/>
+      <c r="B209" s="152"/>
+      <c r="C209" s="151"/>
+      <c r="D209" s="151"/>
+      <c r="E209" s="151"/>
     </row>
     <row r="210" spans="1:5">
-      <c r="A210" s="33"/>
-      <c r="B210" s="34"/>
-      <c r="C210" s="33"/>
-      <c r="D210" s="33"/>
-      <c r="E210" s="33"/>
+      <c r="A210" s="151"/>
+      <c r="B210" s="152"/>
+      <c r="C210" s="151"/>
+      <c r="D210" s="151"/>
+      <c r="E210" s="151"/>
     </row>
     <row r="211" spans="1:5">
-      <c r="A211" s="33"/>
-      <c r="B211" s="34"/>
-      <c r="C211" s="33"/>
-      <c r="D211" s="33"/>
-      <c r="E211" s="33"/>
+      <c r="A211" s="151"/>
+      <c r="B211" s="152"/>
+      <c r="C211" s="151"/>
+      <c r="D211" s="151"/>
+      <c r="E211" s="151"/>
     </row>
     <row r="212" spans="1:5">
-      <c r="A212" s="33"/>
-      <c r="B212" s="34"/>
-      <c r="C212" s="33"/>
-      <c r="D212" s="33"/>
-      <c r="E212" s="33"/>
+      <c r="A212" s="151"/>
+      <c r="B212" s="152"/>
+      <c r="C212" s="151"/>
+      <c r="D212" s="151"/>
+      <c r="E212" s="151"/>
     </row>
     <row r="213" spans="1:5">
-      <c r="A213" s="33"/>
-      <c r="B213" s="34"/>
-      <c r="C213" s="33"/>
-      <c r="D213" s="33"/>
-      <c r="E213" s="33"/>
+      <c r="A213" s="151"/>
+      <c r="B213" s="152"/>
+      <c r="C213" s="151"/>
+      <c r="D213" s="151"/>
+      <c r="E213" s="151"/>
     </row>
     <row r="214" spans="1:5">
-      <c r="A214" s="33"/>
-      <c r="B214" s="34"/>
-      <c r="C214" s="33"/>
-      <c r="D214" s="33"/>
-      <c r="E214" s="33"/>
+      <c r="A214" s="151"/>
+      <c r="B214" s="152"/>
+      <c r="C214" s="151"/>
+      <c r="D214" s="151"/>
+      <c r="E214" s="151"/>
     </row>
     <row r="215" spans="1:5">
-      <c r="A215" s="33"/>
-      <c r="B215" s="34"/>
-      <c r="C215" s="33"/>
-      <c r="D215" s="33"/>
-      <c r="E215" s="33"/>
+      <c r="A215" s="151"/>
+      <c r="B215" s="152"/>
+      <c r="C215" s="151"/>
+      <c r="D215" s="151"/>
+      <c r="E215" s="151"/>
     </row>
     <row r="216" spans="1:5">
-      <c r="A216" s="33"/>
-      <c r="B216" s="34"/>
-      <c r="C216" s="33"/>
-      <c r="D216" s="33"/>
-      <c r="E216" s="33"/>
+      <c r="A216" s="151"/>
+      <c r="B216" s="152"/>
+      <c r="C216" s="151"/>
+      <c r="D216" s="151"/>
+      <c r="E216" s="151"/>
     </row>
     <row r="217" spans="1:5">
-      <c r="A217" s="33"/>
-      <c r="B217" s="34"/>
-      <c r="C217" s="33"/>
-      <c r="D217" s="33"/>
-      <c r="E217" s="33"/>
+      <c r="A217" s="151"/>
+      <c r="B217" s="152"/>
+      <c r="C217" s="151"/>
+      <c r="D217" s="151"/>
+      <c r="E217" s="151"/>
     </row>
     <row r="218" spans="1:5">
-      <c r="A218" s="33"/>
-      <c r="B218" s="34"/>
-      <c r="C218" s="33"/>
-      <c r="D218" s="33"/>
-      <c r="E218" s="33"/>
+      <c r="A218" s="151"/>
+      <c r="B218" s="152"/>
+      <c r="C218" s="151"/>
+      <c r="D218" s="151"/>
+      <c r="E218" s="151"/>
     </row>
     <row r="219" spans="1:5">
-      <c r="A219" s="33"/>
-      <c r="B219" s="34"/>
-      <c r="C219" s="33"/>
-      <c r="D219" s="33"/>
-      <c r="E219" s="33"/>
+      <c r="A219" s="151"/>
+      <c r="B219" s="152"/>
+      <c r="C219" s="151"/>
+      <c r="D219" s="151"/>
+      <c r="E219" s="151"/>
     </row>
     <row r="220" spans="1:5">
-      <c r="A220" s="33"/>
-      <c r="B220" s="34"/>
-      <c r="C220" s="33"/>
-      <c r="D220" s="33"/>
-      <c r="E220" s="33"/>
+      <c r="A220" s="151"/>
+      <c r="B220" s="152"/>
+      <c r="C220" s="151"/>
+      <c r="D220" s="151"/>
+      <c r="E220" s="151"/>
     </row>
     <row r="221" spans="1:5">
-      <c r="A221" s="33"/>
-      <c r="B221" s="34"/>
-      <c r="C221" s="33"/>
-      <c r="D221" s="33"/>
-      <c r="E221" s="33"/>
+      <c r="A221" s="151"/>
+      <c r="B221" s="152"/>
+      <c r="C221" s="151"/>
+      <c r="D221" s="151"/>
+      <c r="E221" s="151"/>
     </row>
     <row r="222" spans="1:5">
-      <c r="A222" s="33"/>
-      <c r="B222" s="34"/>
-      <c r="C222" s="33"/>
-      <c r="D222" s="33"/>
-      <c r="E222" s="33"/>
+      <c r="A222" s="151"/>
+      <c r="B222" s="152"/>
+      <c r="C222" s="151"/>
+      <c r="D222" s="151"/>
+      <c r="E222" s="151"/>
     </row>
     <row r="223" spans="1:5">
-      <c r="A223" s="33"/>
-      <c r="B223" s="34"/>
-      <c r="C223" s="33"/>
-      <c r="D223" s="33"/>
-      <c r="E223" s="33"/>
+      <c r="A223" s="151"/>
+      <c r="B223" s="152"/>
+      <c r="C223" s="151"/>
+      <c r="D223" s="151"/>
+      <c r="E223" s="151"/>
     </row>
     <row r="224" spans="1:5">
-      <c r="A224" s="33"/>
-      <c r="B224" s="34"/>
-      <c r="C224" s="33"/>
-      <c r="D224" s="33"/>
-      <c r="E224" s="33"/>
+      <c r="A224" s="151"/>
+      <c r="B224" s="152"/>
+      <c r="C224" s="151"/>
+      <c r="D224" s="151"/>
+      <c r="E224" s="151"/>
     </row>
     <row r="225" spans="1:5">
-      <c r="A225" s="33"/>
-      <c r="B225" s="34"/>
-      <c r="C225" s="33"/>
-      <c r="D225" s="33"/>
-      <c r="E225" s="33"/>
+      <c r="A225" s="151"/>
+      <c r="B225" s="152"/>
+      <c r="C225" s="151"/>
+      <c r="D225" s="151"/>
+      <c r="E225" s="151"/>
     </row>
     <row r="226" spans="1:5">
-      <c r="A226" s="33"/>
-      <c r="B226" s="34"/>
-      <c r="C226" s="33"/>
-      <c r="D226" s="33"/>
-      <c r="E226" s="33"/>
+      <c r="A226" s="151"/>
+      <c r="B226" s="152"/>
+      <c r="C226" s="151"/>
+      <c r="D226" s="151"/>
+      <c r="E226" s="151"/>
     </row>
     <row r="227" spans="1:5">
-      <c r="A227" s="33"/>
-      <c r="B227" s="34"/>
-      <c r="C227" s="33"/>
-      <c r="D227" s="33"/>
-      <c r="E227" s="33"/>
+      <c r="A227" s="151"/>
+      <c r="B227" s="152"/>
+      <c r="C227" s="151"/>
+      <c r="D227" s="151"/>
+      <c r="E227" s="151"/>
     </row>
     <row r="228" spans="1:5">
-      <c r="A228" s="33"/>
-      <c r="B228" s="34"/>
-      <c r="C228" s="33"/>
-      <c r="D228" s="33"/>
-      <c r="E228" s="33"/>
+      <c r="A228" s="151"/>
+      <c r="B228" s="152"/>
+      <c r="C228" s="151"/>
+      <c r="D228" s="151"/>
+      <c r="E228" s="151"/>
     </row>
     <row r="229" spans="1:5">
-      <c r="A229" s="33"/>
-      <c r="B229" s="34"/>
-      <c r="C229" s="33"/>
-      <c r="D229" s="33"/>
-      <c r="E229" s="33"/>
+      <c r="A229" s="151"/>
+      <c r="B229" s="152"/>
+      <c r="C229" s="151"/>
+      <c r="D229" s="151"/>
+      <c r="E229" s="151"/>
     </row>
     <row r="230" spans="1:5">
-      <c r="A230" s="33"/>
-      <c r="B230" s="34"/>
-      <c r="C230" s="33"/>
-      <c r="D230" s="33"/>
-      <c r="E230" s="33"/>
+      <c r="A230" s="151"/>
+      <c r="B230" s="152"/>
+      <c r="C230" s="151"/>
+      <c r="D230" s="151"/>
+      <c r="E230" s="151"/>
     </row>
     <row r="231" spans="1:5">
-      <c r="A231" s="33"/>
-      <c r="B231" s="34"/>
-      <c r="C231" s="33"/>
-      <c r="D231" s="33"/>
-      <c r="E231" s="33"/>
+      <c r="A231" s="151"/>
+      <c r="B231" s="152"/>
+      <c r="C231" s="151"/>
+      <c r="D231" s="151"/>
+      <c r="E231" s="151"/>
     </row>
     <row r="232" spans="1:5">
-      <c r="A232" s="33"/>
-      <c r="B232" s="34"/>
-      <c r="C232" s="33"/>
-      <c r="D232" s="33"/>
-      <c r="E232" s="33"/>
+      <c r="A232" s="151"/>
+      <c r="B232" s="152"/>
+      <c r="C232" s="151"/>
+      <c r="D232" s="151"/>
+      <c r="E232" s="151"/>
     </row>
     <row r="233" spans="1:5">
-      <c r="A233" s="33"/>
-      <c r="B233" s="34"/>
-      <c r="C233" s="33"/>
-      <c r="D233" s="33"/>
-      <c r="E233" s="33"/>
+      <c r="A233" s="151"/>
+      <c r="B233" s="152"/>
+      <c r="C233" s="151"/>
+      <c r="D233" s="151"/>
+      <c r="E233" s="151"/>
     </row>
     <row r="234" spans="1:5">
-      <c r="A234" s="33"/>
-      <c r="B234" s="34"/>
-      <c r="C234" s="33"/>
-      <c r="D234" s="33"/>
-      <c r="E234" s="33"/>
+      <c r="A234" s="151"/>
+      <c r="B234" s="152"/>
+      <c r="C234" s="151"/>
+      <c r="D234" s="151"/>
+      <c r="E234" s="151"/>
     </row>
     <row r="235" spans="1:5">
-      <c r="A235" s="33"/>
-      <c r="B235" s="34"/>
-      <c r="C235" s="33"/>
-      <c r="D235" s="33"/>
-      <c r="E235" s="33"/>
+      <c r="A235" s="151"/>
+      <c r="B235" s="152"/>
+      <c r="C235" s="151"/>
+      <c r="D235" s="151"/>
+      <c r="E235" s="151"/>
     </row>
     <row r="236" spans="1:5">
-      <c r="A236" s="33"/>
-      <c r="B236" s="34"/>
-      <c r="C236" s="33"/>
-      <c r="D236" s="33"/>
-      <c r="E236" s="33"/>
+      <c r="A236" s="151"/>
+      <c r="B236" s="152"/>
+      <c r="C236" s="151"/>
+      <c r="D236" s="151"/>
+      <c r="E236" s="151"/>
     </row>
     <row r="237" spans="1:5">
-      <c r="A237" s="33"/>
-      <c r="B237" s="34"/>
-      <c r="C237" s="33"/>
-      <c r="D237" s="33"/>
-      <c r="E237" s="33"/>
+      <c r="A237" s="151"/>
+      <c r="B237" s="152"/>
+      <c r="C237" s="151"/>
+      <c r="D237" s="151"/>
+      <c r="E237" s="151"/>
     </row>
     <row r="238" spans="1:5">
-      <c r="A238" s="33"/>
-      <c r="B238" s="34"/>
-      <c r="C238" s="33"/>
-      <c r="D238" s="33"/>
-      <c r="E238" s="33"/>
+      <c r="A238" s="151"/>
+      <c r="B238" s="152"/>
+      <c r="C238" s="151"/>
+      <c r="D238" s="151"/>
+      <c r="E238" s="151"/>
     </row>
     <row r="239" spans="1:5">
-      <c r="A239" s="33"/>
-      <c r="B239" s="34"/>
-      <c r="C239" s="33"/>
-      <c r="D239" s="33"/>
-      <c r="E239" s="33"/>
+      <c r="A239" s="151"/>
+      <c r="B239" s="152"/>
+      <c r="C239" s="151"/>
+      <c r="D239" s="151"/>
+      <c r="E239" s="151"/>
     </row>
     <row r="240" spans="1:5">
-      <c r="A240" s="33"/>
-      <c r="B240" s="34"/>
-      <c r="C240" s="33"/>
-      <c r="D240" s="33"/>
-      <c r="E240" s="33"/>
+      <c r="A240" s="151"/>
+      <c r="B240" s="152"/>
+      <c r="C240" s="151"/>
+      <c r="D240" s="151"/>
+      <c r="E240" s="151"/>
     </row>
     <row r="241" spans="1:5">
-      <c r="A241" s="33"/>
-      <c r="B241" s="34"/>
-      <c r="C241" s="33"/>
-      <c r="D241" s="33"/>
-      <c r="E241" s="33"/>
+      <c r="A241" s="151"/>
+      <c r="B241" s="152"/>
+      <c r="C241" s="151"/>
+      <c r="D241" s="151"/>
+      <c r="E241" s="151"/>
     </row>
     <row r="242" spans="1:5">
-      <c r="A242" s="33"/>
-      <c r="B242" s="34"/>
-      <c r="C242" s="33"/>
-      <c r="D242" s="33"/>
-      <c r="E242" s="33"/>
+      <c r="A242" s="151"/>
+      <c r="B242" s="152"/>
+      <c r="C242" s="151"/>
+      <c r="D242" s="151"/>
+      <c r="E242" s="151"/>
     </row>
     <row r="243" spans="1:5">
-      <c r="A243" s="33"/>
-      <c r="B243" s="34"/>
-      <c r="C243" s="33"/>
-      <c r="D243" s="33"/>
-      <c r="E243" s="33"/>
+      <c r="A243" s="151"/>
+      <c r="B243" s="152"/>
+      <c r="C243" s="151"/>
+      <c r="D243" s="151"/>
+      <c r="E243" s="151"/>
     </row>
     <row r="244" spans="1:5">
-      <c r="A244" s="33"/>
-      <c r="B244" s="34"/>
-      <c r="C244" s="33"/>
-      <c r="D244" s="33"/>
-      <c r="E244" s="33"/>
+      <c r="A244" s="151"/>
+      <c r="B244" s="152"/>
+      <c r="C244" s="151"/>
+      <c r="D244" s="151"/>
+      <c r="E244" s="151"/>
     </row>
     <row r="245" spans="1:5">
-      <c r="A245" s="33"/>
-      <c r="B245" s="34"/>
-      <c r="C245" s="33"/>
-      <c r="D245" s="33"/>
-      <c r="E245" s="33"/>
+      <c r="A245" s="151"/>
+      <c r="B245" s="152"/>
+      <c r="C245" s="151"/>
+      <c r="D245" s="151"/>
+      <c r="E245" s="151"/>
     </row>
     <row r="246" spans="1:5">
-      <c r="A246" s="33"/>
-      <c r="B246" s="34"/>
-      <c r="C246" s="33"/>
-      <c r="D246" s="33"/>
-      <c r="E246" s="33"/>
+      <c r="A246" s="151"/>
+      <c r="B246" s="152"/>
+      <c r="C246" s="151"/>
+      <c r="D246" s="151"/>
+      <c r="E246" s="151"/>
     </row>
     <row r="247" spans="1:5">
-      <c r="A247" s="33"/>
-      <c r="B247" s="34"/>
-      <c r="C247" s="33"/>
-      <c r="D247" s="33"/>
-      <c r="E247" s="33"/>
+      <c r="A247" s="151"/>
+      <c r="B247" s="152"/>
+      <c r="C247" s="151"/>
+      <c r="D247" s="151"/>
+      <c r="E247" s="151"/>
     </row>
     <row r="248" spans="1:5">
-      <c r="A248" s="33"/>
-      <c r="B248" s="34"/>
-      <c r="C248" s="33"/>
-      <c r="D248" s="33"/>
-      <c r="E248" s="33"/>
+      <c r="A248" s="151"/>
+      <c r="B248" s="152"/>
+      <c r="C248" s="151"/>
+      <c r="D248" s="151"/>
+      <c r="E248" s="151"/>
     </row>
     <row r="249" spans="1:5">
-      <c r="A249" s="33"/>
-      <c r="B249" s="34"/>
-      <c r="C249" s="33"/>
-      <c r="D249" s="33"/>
-      <c r="E249" s="33"/>
+      <c r="A249" s="151"/>
+      <c r="B249" s="152"/>
+      <c r="C249" s="151"/>
+      <c r="D249" s="151"/>
+      <c r="E249" s="151"/>
     </row>
     <row r="250" spans="1:5">
-      <c r="A250" s="33"/>
-      <c r="B250" s="34"/>
-      <c r="C250" s="33"/>
-      <c r="D250" s="33"/>
-      <c r="E250" s="33"/>
+      <c r="A250" s="151"/>
+      <c r="B250" s="152"/>
+      <c r="C250" s="151"/>
+      <c r="D250" s="151"/>
+      <c r="E250" s="151"/>
     </row>
     <row r="251" spans="1:5">
-      <c r="A251" s="33"/>
-      <c r="B251" s="34"/>
-      <c r="C251" s="33"/>
-      <c r="D251" s="33"/>
-      <c r="E251" s="33"/>
+      <c r="A251" s="151"/>
+      <c r="B251" s="152"/>
+      <c r="C251" s="151"/>
+      <c r="D251" s="151"/>
+      <c r="E251" s="151"/>
     </row>
     <row r="252" spans="1:5">
-      <c r="A252" s="33"/>
-      <c r="B252" s="34"/>
-      <c r="C252" s="33"/>
-      <c r="D252" s="33"/>
-      <c r="E252" s="33"/>
+      <c r="A252" s="151"/>
+      <c r="B252" s="152"/>
+      <c r="C252" s="151"/>
+      <c r="D252" s="151"/>
+      <c r="E252" s="151"/>
     </row>
     <row r="253" spans="1:5">
-      <c r="A253" s="33"/>
-      <c r="B253" s="34"/>
-      <c r="C253" s="33"/>
-      <c r="D253" s="33"/>
-      <c r="E253" s="33"/>
+      <c r="A253" s="151"/>
+      <c r="B253" s="152"/>
+      <c r="C253" s="151"/>
+      <c r="D253" s="151"/>
+      <c r="E253" s="151"/>
     </row>
     <row r="254" spans="1:5">
-      <c r="A254" s="33"/>
-      <c r="B254" s="34"/>
-      <c r="C254" s="33"/>
-      <c r="D254" s="33"/>
-      <c r="E254" s="33"/>
+      <c r="A254" s="151"/>
+      <c r="B254" s="152"/>
+      <c r="C254" s="151"/>
+      <c r="D254" s="151"/>
+      <c r="E254" s="151"/>
     </row>
     <row r="255" spans="1:5">
-      <c r="A255" s="33"/>
-      <c r="B255" s="34"/>
-      <c r="C255" s="33"/>
-      <c r="D255" s="33"/>
-      <c r="E255" s="33"/>
+      <c r="A255" s="151"/>
+      <c r="B255" s="152"/>
+      <c r="C255" s="151"/>
+      <c r="D255" s="151"/>
+      <c r="E255" s="151"/>
     </row>
     <row r="256" spans="1:5">
-      <c r="A256" s="33"/>
-      <c r="B256" s="34"/>
-      <c r="C256" s="33"/>
-      <c r="D256" s="33"/>
-      <c r="E256" s="33"/>
+      <c r="A256" s="151"/>
+      <c r="B256" s="152"/>
+      <c r="C256" s="151"/>
+      <c r="D256" s="151"/>
+      <c r="E256" s="151"/>
     </row>
     <row r="257" spans="1:5">
-      <c r="A257" s="33"/>
-      <c r="B257" s="34"/>
-      <c r="C257" s="33"/>
-      <c r="D257" s="33"/>
-      <c r="E257" s="33"/>
+      <c r="A257" s="151"/>
+      <c r="B257" s="152"/>
+      <c r="C257" s="151"/>
+      <c r="D257" s="151"/>
+      <c r="E257" s="151"/>
     </row>
     <row r="258" spans="1:5">
-      <c r="A258" s="33"/>
-      <c r="B258" s="34"/>
-      <c r="C258" s="33"/>
-      <c r="D258" s="33"/>
-      <c r="E258" s="33"/>
+      <c r="A258" s="151"/>
+      <c r="B258" s="152"/>
+      <c r="C258" s="151"/>
+      <c r="D258" s="151"/>
+      <c r="E258" s="151"/>
     </row>
     <row r="259" spans="1:5">
-      <c r="A259" s="33"/>
-      <c r="B259" s="34"/>
-      <c r="C259" s="33"/>
-      <c r="D259" s="33"/>
-      <c r="E259" s="33"/>
+      <c r="A259" s="151"/>
+      <c r="B259" s="152"/>
+      <c r="C259" s="151"/>
+      <c r="D259" s="151"/>
+      <c r="E259" s="151"/>
     </row>
     <row r="260" spans="1:5">
-      <c r="A260" s="33"/>
-      <c r="B260" s="34"/>
-      <c r="C260" s="33"/>
-      <c r="D260" s="33"/>
-      <c r="E260" s="33"/>
+      <c r="A260" s="151"/>
+      <c r="B260" s="152"/>
+      <c r="C260" s="151"/>
+      <c r="D260" s="151"/>
+      <c r="E260" s="151"/>
     </row>
     <row r="261" spans="1:5">
-      <c r="A261" s="33"/>
-      <c r="B261" s="34"/>
-      <c r="C261" s="33"/>
-      <c r="D261" s="33"/>
-      <c r="E261" s="33"/>
+      <c r="A261" s="151"/>
+      <c r="B261" s="152"/>
+      <c r="C261" s="151"/>
+      <c r="D261" s="151"/>
+      <c r="E261" s="151"/>
     </row>
     <row r="262" spans="1:5">
-      <c r="A262" s="33"/>
-      <c r="B262" s="34"/>
-      <c r="C262" s="33"/>
-      <c r="D262" s="33"/>
-      <c r="E262" s="33"/>
+      <c r="A262" s="151"/>
+      <c r="B262" s="152"/>
+      <c r="C262" s="151"/>
+      <c r="D262" s="151"/>
+      <c r="E262" s="151"/>
     </row>
     <row r="263" spans="1:5">
-      <c r="A263" s="33"/>
-      <c r="B263" s="34"/>
-      <c r="C263" s="33"/>
-      <c r="D263" s="33"/>
-      <c r="E263" s="33"/>
+      <c r="A263" s="151"/>
+      <c r="B263" s="152"/>
+      <c r="C263" s="151"/>
+      <c r="D263" s="151"/>
+      <c r="E263" s="151"/>
     </row>
     <row r="264" spans="1:5">
-      <c r="A264" s="33"/>
-      <c r="B264" s="34"/>
-      <c r="C264" s="33"/>
-      <c r="D264" s="33"/>
-      <c r="E264" s="33"/>
+      <c r="A264" s="151"/>
+      <c r="B264" s="152"/>
+      <c r="C264" s="151"/>
+      <c r="D264" s="151"/>
+      <c r="E264" s="151"/>
     </row>
     <row r="265" spans="1:5">
-      <c r="A265" s="33"/>
-      <c r="B265" s="34"/>
-      <c r="C265" s="33"/>
-      <c r="D265" s="33"/>
-      <c r="E265" s="33"/>
+      <c r="A265" s="151"/>
+      <c r="B265" s="152"/>
+      <c r="C265" s="151"/>
+      <c r="D265" s="151"/>
+      <c r="E265" s="151"/>
     </row>
     <row r="266" spans="1:5">
-      <c r="A266" s="33"/>
-      <c r="B266" s="34"/>
-      <c r="C266" s="33"/>
-      <c r="D266" s="33"/>
-      <c r="E266" s="33"/>
+      <c r="A266" s="151"/>
+      <c r="B266" s="152"/>
+      <c r="C266" s="151"/>
+      <c r="D266" s="151"/>
+      <c r="E266" s="151"/>
     </row>
     <row r="267" spans="1:5">
-      <c r="A267" s="33"/>
-      <c r="B267" s="34"/>
-      <c r="C267" s="33"/>
-      <c r="D267" s="33"/>
-      <c r="E267" s="33"/>
+      <c r="A267" s="151"/>
+      <c r="B267" s="152"/>
+      <c r="C267" s="151"/>
+      <c r="D267" s="151"/>
+      <c r="E267" s="151"/>
     </row>
     <row r="268" spans="1:5">
-      <c r="A268" s="33"/>
-      <c r="B268" s="34"/>
-      <c r="C268" s="33"/>
-      <c r="D268" s="33"/>
-      <c r="E268" s="33"/>
+      <c r="A268" s="151"/>
+      <c r="B268" s="152"/>
+      <c r="C268" s="151"/>
+      <c r="D268" s="151"/>
+      <c r="E268" s="151"/>
     </row>
     <row r="269" spans="1:5">
-      <c r="A269" s="33"/>
-      <c r="B269" s="34"/>
-      <c r="C269" s="33"/>
-      <c r="D269" s="33"/>
-      <c r="E269" s="33"/>
+      <c r="A269" s="151"/>
+      <c r="B269" s="152"/>
+      <c r="C269" s="151"/>
+      <c r="D269" s="151"/>
+      <c r="E269" s="151"/>
     </row>
     <row r="270" spans="1:5">
-      <c r="A270" s="33"/>
-      <c r="B270" s="34"/>
-      <c r="C270" s="33"/>
-      <c r="D270" s="33"/>
-      <c r="E270" s="33"/>
+      <c r="A270" s="151"/>
+      <c r="B270" s="152"/>
+      <c r="C270" s="151"/>
+      <c r="D270" s="151"/>
+      <c r="E270" s="151"/>
     </row>
     <row r="271" spans="1:5">
-      <c r="A271" s="33"/>
-      <c r="B271" s="34"/>
-      <c r="C271" s="33"/>
-      <c r="D271" s="33"/>
-      <c r="E271" s="33"/>
+      <c r="A271" s="151"/>
+      <c r="B271" s="152"/>
+      <c r="C271" s="151"/>
+      <c r="D271" s="151"/>
+      <c r="E271" s="151"/>
     </row>
     <row r="272" spans="1:5">
-      <c r="A272" s="33"/>
-      <c r="B272" s="34"/>
-      <c r="C272" s="33"/>
-      <c r="D272" s="33"/>
-      <c r="E272" s="33"/>
+      <c r="A272" s="151"/>
+      <c r="B272" s="152"/>
+      <c r="C272" s="151"/>
+      <c r="D272" s="151"/>
+      <c r="E272" s="151"/>
     </row>
     <row r="273" spans="1:5">
-      <c r="A273" s="33"/>
-      <c r="B273" s="34"/>
-      <c r="C273" s="33"/>
-      <c r="D273" s="33"/>
-      <c r="E273" s="33"/>
+      <c r="A273" s="151"/>
+      <c r="B273" s="152"/>
+      <c r="C273" s="151"/>
+      <c r="D273" s="151"/>
+      <c r="E273" s="151"/>
     </row>
     <row r="274" spans="1:5">
-      <c r="A274" s="33"/>
-      <c r="B274" s="34"/>
-      <c r="C274" s="33"/>
-      <c r="D274" s="33"/>
-      <c r="E274" s="33"/>
+      <c r="A274" s="151"/>
+      <c r="B274" s="152"/>
+      <c r="C274" s="151"/>
+      <c r="D274" s="151"/>
+      <c r="E274" s="151"/>
     </row>
     <row r="275" spans="1:5">
-      <c r="A275" s="33"/>
-      <c r="B275" s="34"/>
-      <c r="C275" s="33"/>
-      <c r="D275" s="33"/>
-      <c r="E275" s="33"/>
+      <c r="A275" s="151"/>
+      <c r="B275" s="152"/>
+      <c r="C275" s="151"/>
+      <c r="D275" s="151"/>
+      <c r="E275" s="151"/>
     </row>
     <row r="276" spans="1:5">
-      <c r="A276" s="33"/>
-      <c r="B276" s="34"/>
-      <c r="C276" s="33"/>
-      <c r="D276" s="33"/>
-      <c r="E276" s="33"/>
+      <c r="A276" s="151"/>
+      <c r="B276" s="152"/>
+      <c r="C276" s="151"/>
+      <c r="D276" s="151"/>
+      <c r="E276" s="151"/>
     </row>
     <row r="277" spans="1:5">
-      <c r="A277" s="33"/>
-      <c r="B277" s="34"/>
-      <c r="C277" s="33"/>
-      <c r="D277" s="33"/>
-      <c r="E277" s="33"/>
+      <c r="A277" s="151"/>
+      <c r="B277" s="152"/>
+      <c r="C277" s="151"/>
+      <c r="D277" s="151"/>
+      <c r="E277" s="151"/>
     </row>
     <row r="278" spans="1:5">
-      <c r="A278" s="33"/>
-      <c r="B278" s="34"/>
-      <c r="C278" s="33"/>
-      <c r="D278" s="33"/>
-      <c r="E278" s="33"/>
+      <c r="A278" s="151"/>
+      <c r="B278" s="152"/>
+      <c r="C278" s="151"/>
+      <c r="D278" s="151"/>
+      <c r="E278" s="151"/>
     </row>
     <row r="279" spans="1:5">
-      <c r="A279" s="33"/>
-      <c r="B279" s="34"/>
-      <c r="C279" s="33"/>
-      <c r="D279" s="33"/>
-      <c r="E279" s="33"/>
+      <c r="A279" s="151"/>
+      <c r="B279" s="152"/>
+      <c r="C279" s="151"/>
+      <c r="D279" s="151"/>
+      <c r="E279" s="151"/>
     </row>
     <row r="280" spans="1:5">
-      <c r="A280" s="33"/>
-      <c r="B280" s="34"/>
-      <c r="C280" s="33"/>
-      <c r="D280" s="33"/>
-      <c r="E280" s="33"/>
+      <c r="A280" s="151"/>
+      <c r="B280" s="152"/>
+      <c r="C280" s="151"/>
+      <c r="D280" s="151"/>
+      <c r="E280" s="151"/>
     </row>
     <row r="281" spans="1:5">
-      <c r="A281" s="33"/>
-      <c r="B281" s="34"/>
-      <c r="C281" s="33"/>
-      <c r="D281" s="33"/>
-      <c r="E281" s="33"/>
+      <c r="A281" s="151"/>
+      <c r="B281" s="152"/>
+      <c r="C281" s="151"/>
+      <c r="D281" s="151"/>
+      <c r="E281" s="151"/>
     </row>
     <row r="282" spans="1:5">
-      <c r="A282" s="33"/>
-      <c r="B282" s="34"/>
-      <c r="C282" s="33"/>
-      <c r="D282" s="33"/>
-      <c r="E282" s="33"/>
+      <c r="A282" s="151"/>
+      <c r="B282" s="152"/>
+      <c r="C282" s="151"/>
+      <c r="D282" s="151"/>
+      <c r="E282" s="151"/>
     </row>
     <row r="283" spans="1:5">
-      <c r="A283" s="33"/>
-      <c r="B283" s="34"/>
-      <c r="C283" s="33"/>
-      <c r="D283" s="33"/>
-      <c r="E283" s="33"/>
+      <c r="A283" s="151"/>
+      <c r="B283" s="152"/>
+      <c r="C283" s="151"/>
+      <c r="D283" s="151"/>
+      <c r="E283" s="151"/>
     </row>
     <row r="284" spans="1:5">
-      <c r="A284" s="33"/>
-      <c r="B284" s="34"/>
-      <c r="C284" s="33"/>
-      <c r="D284" s="33"/>
-      <c r="E284" s="33"/>
+      <c r="A284" s="151"/>
+      <c r="B284" s="152"/>
+      <c r="C284" s="151"/>
+      <c r="D284" s="151"/>
+      <c r="E284" s="151"/>
     </row>
     <row r="285" spans="1:5">
-      <c r="A285" s="33"/>
-      <c r="B285" s="34"/>
-      <c r="C285" s="33"/>
-      <c r="D285" s="33"/>
-      <c r="E285" s="33"/>
+      <c r="A285" s="151"/>
+      <c r="B285" s="152"/>
+      <c r="C285" s="151"/>
+      <c r="D285" s="151"/>
+      <c r="E285" s="151"/>
     </row>
     <row r="286" spans="1:5">
-      <c r="A286" s="33"/>
-      <c r="B286" s="34"/>
-      <c r="C286" s="33"/>
-      <c r="D286" s="33"/>
-      <c r="E286" s="33"/>
+      <c r="A286" s="151"/>
+      <c r="B286" s="152"/>
+      <c r="C286" s="151"/>
+      <c r="D286" s="151"/>
+      <c r="E286" s="151"/>
     </row>
     <row r="287" spans="1:5">
-      <c r="A287" s="33"/>
-      <c r="B287" s="34"/>
-      <c r="C287" s="33"/>
-      <c r="D287" s="33"/>
-      <c r="E287" s="33"/>
+      <c r="A287" s="151"/>
+      <c r="B287" s="152"/>
+      <c r="C287" s="151"/>
+      <c r="D287" s="151"/>
+      <c r="E287" s="151"/>
     </row>
     <row r="288" spans="1:5">
-      <c r="A288" s="33"/>
-      <c r="B288" s="34"/>
-      <c r="C288" s="33"/>
-      <c r="D288" s="33"/>
-      <c r="E288" s="33"/>
+      <c r="A288" s="151"/>
+      <c r="B288" s="152"/>
+      <c r="C288" s="151"/>
+      <c r="D288" s="151"/>
+      <c r="E288" s="151"/>
     </row>
     <row r="289" spans="1:5">
-      <c r="A289" s="33"/>
-      <c r="B289" s="34"/>
-      <c r="C289" s="33"/>
-      <c r="D289" s="33"/>
-      <c r="E289" s="33"/>
+      <c r="A289" s="151"/>
+      <c r="B289" s="152"/>
+      <c r="C289" s="151"/>
+      <c r="D289" s="151"/>
+      <c r="E289" s="151"/>
     </row>
     <row r="290" spans="1:5">
-      <c r="A290" s="33"/>
-      <c r="B290" s="34"/>
-      <c r="C290" s="33"/>
-      <c r="D290" s="33"/>
-      <c r="E290" s="33"/>
+      <c r="A290" s="151"/>
+      <c r="B290" s="152"/>
+      <c r="C290" s="151"/>
+      <c r="D290" s="151"/>
+      <c r="E290" s="151"/>
     </row>
     <row r="291" spans="1:5">
-      <c r="A291" s="33"/>
-      <c r="B291" s="34"/>
-      <c r="C291" s="33"/>
-      <c r="D291" s="33"/>
-      <c r="E291" s="33"/>
+      <c r="A291" s="151"/>
+      <c r="B291" s="152"/>
+      <c r="C291" s="151"/>
+      <c r="D291" s="151"/>
+      <c r="E291" s="151"/>
     </row>
     <row r="292" spans="1:5">
-      <c r="A292" s="33"/>
-      <c r="B292" s="34"/>
-      <c r="C292" s="33"/>
-      <c r="D292" s="33"/>
-      <c r="E292" s="33"/>
+      <c r="A292" s="151"/>
+      <c r="B292" s="152"/>
+      <c r="C292" s="151"/>
+      <c r="D292" s="151"/>
+      <c r="E292" s="151"/>
     </row>
     <row r="293" spans="1:5">
-      <c r="A293" s="33"/>
-      <c r="B293" s="34"/>
-      <c r="C293" s="33"/>
-      <c r="D293" s="33"/>
-      <c r="E293" s="33"/>
+      <c r="A293" s="151"/>
+      <c r="B293" s="152"/>
+      <c r="C293" s="151"/>
+      <c r="D293" s="151"/>
+      <c r="E293" s="151"/>
     </row>
     <row r="294" spans="1:5">
-      <c r="A294" s="33"/>
-      <c r="B294" s="34"/>
-      <c r="C294" s="33"/>
-      <c r="D294" s="33"/>
-      <c r="E294" s="33"/>
+      <c r="A294" s="151"/>
+      <c r="B294" s="152"/>
+      <c r="C294" s="151"/>
+      <c r="D294" s="151"/>
+      <c r="E294" s="151"/>
     </row>
     <row r="295" spans="1:5">
-      <c r="A295" s="33"/>
-      <c r="B295" s="34"/>
-      <c r="C295" s="33"/>
-      <c r="D295" s="33"/>
-      <c r="E295" s="33"/>
+      <c r="A295" s="151"/>
+      <c r="B295" s="152"/>
+      <c r="C295" s="151"/>
+      <c r="D295" s="151"/>
+      <c r="E295" s="151"/>
     </row>
     <row r="296" spans="1:5">
-      <c r="A296" s="33"/>
-      <c r="B296" s="34"/>
-      <c r="C296" s="33"/>
-      <c r="D296" s="33"/>
-      <c r="E296" s="33"/>
+      <c r="A296" s="151"/>
+      <c r="B296" s="152"/>
+      <c r="C296" s="151"/>
+      <c r="D296" s="151"/>
+      <c r="E296" s="151"/>
     </row>
     <row r="297" spans="1:5">
-      <c r="A297" s="33"/>
-      <c r="B297" s="34"/>
-      <c r="C297" s="33"/>
-      <c r="D297" s="33"/>
-      <c r="E297" s="33"/>
+      <c r="A297" s="151"/>
+      <c r="B297" s="152"/>
+      <c r="C297" s="151"/>
+      <c r="D297" s="151"/>
+      <c r="E297" s="151"/>
     </row>
     <row r="298" spans="1:5">
-      <c r="A298" s="33"/>
-      <c r="B298" s="34"/>
-      <c r="C298" s="33"/>
-      <c r="D298" s="33"/>
-      <c r="E298" s="33"/>
+      <c r="A298" s="151"/>
+      <c r="B298" s="152"/>
+      <c r="C298" s="151"/>
+      <c r="D298" s="151"/>
+      <c r="E298" s="151"/>
     </row>
     <row r="299" spans="1:5">
-      <c r="A299" s="33"/>
-      <c r="B299" s="34"/>
-      <c r="C299" s="33"/>
-      <c r="D299" s="33"/>
-      <c r="E299" s="33"/>
+      <c r="A299" s="151"/>
+      <c r="B299" s="152"/>
+      <c r="C299" s="151"/>
+      <c r="D299" s="151"/>
+      <c r="E299" s="151"/>
     </row>
     <row r="300" spans="1:5">
-      <c r="A300" s="33"/>
-      <c r="B300" s="34"/>
-      <c r="C300" s="33"/>
-      <c r="D300" s="33"/>
-      <c r="E300" s="33"/>
+      <c r="A300" s="151"/>
+      <c r="B300" s="152"/>
+      <c r="C300" s="151"/>
+      <c r="D300" s="151"/>
+      <c r="E300" s="151"/>
     </row>
     <row r="301" spans="1:5">
-      <c r="A301" s="33"/>
-      <c r="B301" s="34"/>
-      <c r="C301" s="33"/>
-      <c r="D301" s="33"/>
-      <c r="E301" s="33"/>
+      <c r="A301" s="151"/>
+      <c r="B301" s="152"/>
+      <c r="C301" s="151"/>
+      <c r="D301" s="151"/>
+      <c r="E301" s="151"/>
     </row>
     <row r="302" spans="1:5">
-      <c r="A302" s="33"/>
-      <c r="B302" s="34"/>
-      <c r="C302" s="33"/>
-      <c r="D302" s="33"/>
-      <c r="E302" s="33"/>
+      <c r="A302" s="151"/>
+      <c r="B302" s="152"/>
+      <c r="C302" s="151"/>
+      <c r="D302" s="151"/>
+      <c r="E302" s="151"/>
     </row>
     <row r="303" spans="1:5">
-      <c r="A303" s="33"/>
-      <c r="B303" s="34"/>
-      <c r="C303" s="33"/>
-      <c r="D303" s="33"/>
-      <c r="E303" s="33"/>
+      <c r="A303" s="151"/>
+      <c r="B303" s="152"/>
+      <c r="C303" s="151"/>
+      <c r="D303" s="151"/>
+      <c r="E303" s="151"/>
     </row>
     <row r="304" spans="1:5">
-      <c r="A304" s="33"/>
-      <c r="B304" s="34"/>
-      <c r="C304" s="33"/>
-      <c r="D304" s="33"/>
-      <c r="E304" s="33"/>
+      <c r="A304" s="151"/>
+      <c r="B304" s="152"/>
+      <c r="C304" s="151"/>
+      <c r="D304" s="151"/>
+      <c r="E304" s="151"/>
     </row>
     <row r="305" spans="1:5">
-      <c r="A305" s="33"/>
-      <c r="B305" s="34"/>
-      <c r="C305" s="33"/>
-      <c r="D305" s="33"/>
-      <c r="E305" s="33"/>
+      <c r="A305" s="151"/>
+      <c r="B305" s="152"/>
+      <c r="C305" s="151"/>
+      <c r="D305" s="151"/>
+      <c r="E305" s="151"/>
     </row>
     <row r="306" spans="1:5">
-      <c r="A306" s="33"/>
-      <c r="B306" s="34"/>
-      <c r="C306" s="33"/>
-      <c r="D306" s="33"/>
-      <c r="E306" s="33"/>
+      <c r="A306" s="151"/>
+      <c r="B306" s="152"/>
+      <c r="C306" s="151"/>
+      <c r="D306" s="151"/>
+      <c r="E306" s="151"/>
     </row>
     <row r="307" spans="1:5">
-      <c r="A307" s="33"/>
-      <c r="B307" s="34"/>
-      <c r="C307" s="33"/>
-      <c r="D307" s="33"/>
-      <c r="E307" s="33"/>
+      <c r="A307" s="151"/>
+      <c r="B307" s="152"/>
+      <c r="C307" s="151"/>
+      <c r="D307" s="151"/>
+      <c r="E307" s="151"/>
     </row>
     <row r="308" spans="1:5">
-      <c r="A308" s="33"/>
-      <c r="B308" s="34"/>
-      <c r="C308" s="33"/>
-      <c r="D308" s="33"/>
-      <c r="E308" s="33"/>
+      <c r="A308" s="151"/>
+      <c r="B308" s="152"/>
+      <c r="C308" s="151"/>
+      <c r="D308" s="151"/>
+      <c r="E308" s="151"/>
     </row>
     <row r="309" spans="1:5">
-      <c r="A309" s="33"/>
-      <c r="B309" s="34"/>
-      <c r="C309" s="33"/>
-      <c r="D309" s="33"/>
-      <c r="E309" s="33"/>
+      <c r="A309" s="151"/>
+      <c r="B309" s="152"/>
+      <c r="C309" s="151"/>
+      <c r="D309" s="151"/>
+      <c r="E309" s="151"/>
     </row>
     <row r="310" spans="1:5">
-      <c r="A310" s="33"/>
-      <c r="B310" s="34"/>
-      <c r="C310" s="33"/>
-      <c r="D310" s="33"/>
-      <c r="E310" s="33"/>
+      <c r="A310" s="151"/>
+      <c r="B310" s="152"/>
+      <c r="C310" s="151"/>
+      <c r="D310" s="151"/>
+      <c r="E310" s="151"/>
     </row>
     <row r="311" spans="1:5">
-      <c r="A311" s="33"/>
-      <c r="B311" s="34"/>
-      <c r="C311" s="33"/>
-      <c r="D311" s="33"/>
-      <c r="E311" s="33"/>
+      <c r="A311" s="151"/>
+      <c r="B311" s="152"/>
+      <c r="C311" s="151"/>
+      <c r="D311" s="151"/>
+      <c r="E311" s="151"/>
     </row>
     <row r="312" spans="1:5">
-      <c r="A312" s="33"/>
-      <c r="B312" s="34"/>
-      <c r="C312" s="33"/>
-      <c r="D312" s="33"/>
-      <c r="E312" s="33"/>
+      <c r="A312" s="151"/>
+      <c r="B312" s="152"/>
+      <c r="C312" s="151"/>
+      <c r="D312" s="151"/>
+      <c r="E312" s="151"/>
     </row>
     <row r="313" spans="1:5">
-      <c r="A313" s="33"/>
-      <c r="B313" s="34"/>
-      <c r="C313" s="33"/>
-      <c r="D313" s="33"/>
-      <c r="E313" s="33"/>
+      <c r="A313" s="151"/>
+      <c r="B313" s="152"/>
+      <c r="C313" s="151"/>
+      <c r="D313" s="151"/>
+      <c r="E313" s="151"/>
     </row>
     <row r="314" spans="1:5">
-      <c r="A314" s="33"/>
-      <c r="B314" s="34"/>
-      <c r="C314" s="33"/>
-      <c r="D314" s="33"/>
-      <c r="E314" s="33"/>
+      <c r="A314" s="151"/>
+      <c r="B314" s="152"/>
+      <c r="C314" s="151"/>
+      <c r="D314" s="151"/>
+      <c r="E314" s="151"/>
     </row>
     <row r="315" spans="1:5">
-      <c r="A315" s="33"/>
-      <c r="B315" s="34"/>
-      <c r="C315" s="33"/>
-      <c r="D315" s="33"/>
-      <c r="E315" s="33"/>
+      <c r="A315" s="151"/>
+      <c r="B315" s="152"/>
+      <c r="C315" s="151"/>
+      <c r="D315" s="151"/>
+      <c r="E315" s="151"/>
     </row>
     <row r="316" spans="1:5">
-      <c r="A316" s="33"/>
-      <c r="B316" s="34"/>
-      <c r="C316" s="33"/>
-      <c r="D316" s="33"/>
-      <c r="E316" s="33"/>
+      <c r="A316" s="151"/>
+      <c r="B316" s="152"/>
+      <c r="C316" s="151"/>
+      <c r="D316" s="151"/>
+      <c r="E316" s="151"/>
     </row>
     <row r="317" spans="1:5">
-      <c r="A317" s="33"/>
-      <c r="B317" s="34"/>
-      <c r="C317" s="33"/>
-      <c r="D317" s="33"/>
-      <c r="E317" s="33"/>
+      <c r="A317" s="151"/>
+      <c r="B317" s="152"/>
+      <c r="C317" s="151"/>
+      <c r="D317" s="151"/>
+      <c r="E317" s="151"/>
     </row>
     <row r="318" spans="1:5">
-      <c r="A318" s="33"/>
-      <c r="B318" s="34"/>
-      <c r="C318" s="33"/>
-      <c r="D318" s="33"/>
-      <c r="E318" s="33"/>
+      <c r="A318" s="151"/>
+      <c r="B318" s="152"/>
+      <c r="C318" s="151"/>
+      <c r="D318" s="151"/>
+      <c r="E318" s="151"/>
     </row>
     <row r="319" spans="1:5">
-      <c r="A319" s="33"/>
-      <c r="B319" s="34"/>
-      <c r="C319" s="33"/>
-      <c r="D319" s="33"/>
-      <c r="E319" s="33"/>
+      <c r="A319" s="151"/>
+      <c r="B319" s="152"/>
+      <c r="C319" s="151"/>
+      <c r="D319" s="151"/>
+      <c r="E319" s="151"/>
     </row>
     <row r="320" spans="1:5">
-      <c r="A320" s="33"/>
-      <c r="B320" s="34"/>
-      <c r="C320" s="33"/>
-      <c r="D320" s="33"/>
-      <c r="E320" s="33"/>
+      <c r="A320" s="151"/>
+      <c r="B320" s="152"/>
+      <c r="C320" s="151"/>
+      <c r="D320" s="151"/>
+      <c r="E320" s="151"/>
     </row>
     <row r="321" spans="1:5">
-      <c r="A321" s="33"/>
-      <c r="B321" s="34"/>
-      <c r="C321" s="33"/>
-      <c r="D321" s="33"/>
-      <c r="E321" s="33"/>
+      <c r="A321" s="151"/>
+      <c r="B321" s="152"/>
+      <c r="C321" s="151"/>
+      <c r="D321" s="151"/>
+      <c r="E321" s="151"/>
     </row>
     <row r="322" spans="1:5">
-      <c r="A322" s="33"/>
-      <c r="B322" s="34"/>
-      <c r="C322" s="33"/>
-      <c r="D322" s="33"/>
-      <c r="E322" s="33"/>
+      <c r="A322" s="151"/>
+      <c r="B322" s="152"/>
+      <c r="C322" s="151"/>
+      <c r="D322" s="151"/>
+      <c r="E322" s="151"/>
     </row>
     <row r="323" spans="1:5">
-      <c r="A323" s="33"/>
-      <c r="B323" s="34"/>
-      <c r="C323" s="33"/>
-      <c r="D323" s="33"/>
-      <c r="E323" s="33"/>
+      <c r="A323" s="151"/>
+      <c r="B323" s="152"/>
+      <c r="C323" s="151"/>
+      <c r="D323" s="151"/>
+      <c r="E323" s="151"/>
     </row>
     <row r="324" spans="1:5">
-      <c r="A324" s="33"/>
-      <c r="B324" s="34"/>
-      <c r="C324" s="33"/>
-      <c r="D324" s="33"/>
-      <c r="E324" s="33"/>
+      <c r="A324" s="151"/>
+      <c r="B324" s="152"/>
+      <c r="C324" s="151"/>
+      <c r="D324" s="151"/>
+      <c r="E324" s="151"/>
     </row>
     <row r="325" spans="1:5">
-      <c r="A325" s="33"/>
-      <c r="B325" s="34"/>
-      <c r="C325" s="33"/>
-      <c r="D325" s="33"/>
-      <c r="E325" s="33"/>
+      <c r="A325" s="151"/>
+      <c r="B325" s="152"/>
+      <c r="C325" s="151"/>
+      <c r="D325" s="151"/>
+      <c r="E325" s="151"/>
     </row>
     <row r="326" spans="1:5">
-      <c r="A326" s="33"/>
-      <c r="B326" s="34"/>
-      <c r="C326" s="33"/>
-      <c r="D326" s="33"/>
-      <c r="E326" s="33"/>
+      <c r="A326" s="151"/>
+      <c r="B326" s="152"/>
+      <c r="C326" s="151"/>
+      <c r="D326" s="151"/>
+      <c r="E326" s="151"/>
     </row>
     <row r="327" spans="1:5">
-      <c r="A327" s="33"/>
-      <c r="B327" s="34"/>
-      <c r="C327" s="33"/>
-      <c r="D327" s="33"/>
-      <c r="E327" s="33"/>
+      <c r="A327" s="151"/>
+      <c r="B327" s="152"/>
+      <c r="C327" s="151"/>
+      <c r="D327" s="151"/>
+      <c r="E327" s="151"/>
     </row>
     <row r="328" spans="1:5">
-      <c r="A328" s="33"/>
-      <c r="B328" s="34"/>
-      <c r="C328" s="33"/>
-      <c r="D328" s="33"/>
-      <c r="E328" s="33"/>
+      <c r="A328" s="151"/>
+      <c r="B328" s="152"/>
+      <c r="C328" s="151"/>
+      <c r="D328" s="151"/>
+      <c r="E328" s="151"/>
     </row>
     <row r="329" spans="1:5">
-      <c r="A329" s="33"/>
-      <c r="B329" s="34"/>
-      <c r="C329" s="33"/>
-      <c r="D329" s="33"/>
-      <c r="E329" s="33"/>
+      <c r="A329" s="151"/>
+      <c r="B329" s="152"/>
+      <c r="C329" s="151"/>
+      <c r="D329" s="151"/>
+      <c r="E329" s="151"/>
     </row>
     <row r="330" spans="1:5">
-      <c r="A330" s="33"/>
-      <c r="B330" s="34"/>
-      <c r="C330" s="33"/>
-      <c r="D330" s="33"/>
-      <c r="E330" s="33"/>
+      <c r="A330" s="151"/>
+      <c r="B330" s="152"/>
+      <c r="C330" s="151"/>
+      <c r="D330" s="151"/>
+      <c r="E330" s="151"/>
     </row>
     <row r="331" spans="1:5">
-      <c r="A331" s="33"/>
-      <c r="B331" s="34"/>
-      <c r="C331" s="33"/>
-      <c r="D331" s="33"/>
-      <c r="E331" s="33"/>
+      <c r="A331" s="151"/>
+      <c r="B331" s="152"/>
+      <c r="C331" s="151"/>
+      <c r="D331" s="151"/>
+      <c r="E331" s="151"/>
     </row>
     <row r="332" spans="1:5">
-      <c r="A332" s="33"/>
-      <c r="B332" s="34"/>
-      <c r="C332" s="33"/>
-      <c r="D332" s="33"/>
-      <c r="E332" s="33"/>
+      <c r="A332" s="151"/>
+      <c r="B332" s="152"/>
+      <c r="C332" s="151"/>
+      <c r="D332" s="151"/>
+      <c r="E332" s="151"/>
     </row>
     <row r="333" spans="1:5">
-      <c r="A333" s="33"/>
-      <c r="B333" s="34"/>
-      <c r="C333" s="33"/>
-      <c r="D333" s="33"/>
-      <c r="E333" s="33"/>
+      <c r="A333" s="151"/>
+      <c r="B333" s="152"/>
+      <c r="C333" s="151"/>
+      <c r="D333" s="151"/>
+      <c r="E333" s="151"/>
     </row>
     <row r="334" spans="1:5">
-      <c r="A334" s="33"/>
-      <c r="B334" s="34"/>
-      <c r="C334" s="33"/>
-      <c r="D334" s="33"/>
-      <c r="E334" s="33"/>
+      <c r="A334" s="151"/>
+      <c r="B334" s="152"/>
+      <c r="C334" s="151"/>
+      <c r="D334" s="151"/>
+      <c r="E334" s="151"/>
     </row>
     <row r="335" spans="1:5">
-      <c r="A335" s="33"/>
-      <c r="B335" s="34"/>
-      <c r="C335" s="33"/>
-      <c r="D335" s="33"/>
-      <c r="E335" s="33"/>
+      <c r="A335" s="151"/>
+      <c r="B335" s="152"/>
+      <c r="C335" s="151"/>
+      <c r="D335" s="151"/>
+      <c r="E335" s="151"/>
     </row>
     <row r="336" spans="1:5">
-      <c r="A336" s="33"/>
-      <c r="B336" s="34"/>
-      <c r="C336" s="33"/>
-      <c r="D336" s="33"/>
-      <c r="E336" s="33"/>
+      <c r="A336" s="151"/>
+      <c r="B336" s="152"/>
+      <c r="C336" s="151"/>
+      <c r="D336" s="151"/>
+      <c r="E336" s="151"/>
     </row>
     <row r="337" spans="1:5">
-      <c r="A337" s="33"/>
-      <c r="B337" s="34"/>
-      <c r="C337" s="33"/>
-      <c r="D337" s="33"/>
-      <c r="E337" s="33"/>
+      <c r="A337" s="151"/>
+      <c r="B337" s="152"/>
+      <c r="C337" s="151"/>
+      <c r="D337" s="151"/>
+      <c r="E337" s="151"/>
     </row>
     <row r="338" spans="1:5">
-      <c r="A338" s="33"/>
-      <c r="B338" s="34"/>
-      <c r="C338" s="33"/>
-      <c r="D338" s="33"/>
-      <c r="E338" s="33"/>
+      <c r="A338" s="151"/>
+      <c r="B338" s="152"/>
+      <c r="C338" s="151"/>
+      <c r="D338" s="151"/>
+      <c r="E338" s="151"/>
     </row>
     <row r="339" spans="1:5">
-      <c r="A339" s="33"/>
-      <c r="B339" s="34"/>
-      <c r="C339" s="33"/>
-      <c r="D339" s="33"/>
-      <c r="E339" s="33"/>
+      <c r="A339" s="151"/>
+      <c r="B339" s="152"/>
+      <c r="C339" s="151"/>
+      <c r="D339" s="151"/>
+      <c r="E339" s="151"/>
     </row>
     <row r="340" spans="1:5">
-      <c r="A340" s="33"/>
-      <c r="B340" s="34"/>
-      <c r="C340" s="33"/>
-      <c r="D340" s="33"/>
-      <c r="E340" s="33"/>
+      <c r="A340" s="151"/>
+      <c r="B340" s="152"/>
+      <c r="C340" s="151"/>
+      <c r="D340" s="151"/>
+      <c r="E340" s="151"/>
     </row>
     <row r="341" spans="1:5">
-      <c r="A341" s="33"/>
-      <c r="B341" s="34"/>
-      <c r="C341" s="33"/>
-      <c r="D341" s="33"/>
-      <c r="E341" s="33"/>
+      <c r="A341" s="151"/>
+      <c r="B341" s="152"/>
+      <c r="C341" s="151"/>
+      <c r="D341" s="151"/>
+      <c r="E341" s="151"/>
     </row>
     <row r="342" spans="1:5">
-      <c r="A342" s="33"/>
-      <c r="B342" s="34"/>
-      <c r="C342" s="33"/>
-      <c r="D342" s="33"/>
-      <c r="E342" s="33"/>
+      <c r="A342" s="151"/>
+      <c r="B342" s="152"/>
+      <c r="C342" s="151"/>
+      <c r="D342" s="151"/>
+      <c r="E342" s="151"/>
     </row>
     <row r="343" spans="1:5">
-      <c r="A343" s="33"/>
-      <c r="B343" s="34"/>
-      <c r="C343" s="33"/>
-      <c r="D343" s="33"/>
-      <c r="E343" s="33"/>
+      <c r="A343" s="151"/>
+      <c r="B343" s="152"/>
+      <c r="C343" s="151"/>
+      <c r="D343" s="151"/>
+      <c r="E343" s="151"/>
     </row>
     <row r="344" spans="1:5">
-      <c r="A344" s="33"/>
-      <c r="B344" s="34"/>
-      <c r="C344" s="33"/>
-      <c r="D344" s="33"/>
-      <c r="E344" s="33"/>
+      <c r="A344" s="151"/>
+      <c r="B344" s="152"/>
+      <c r="C344" s="151"/>
+      <c r="D344" s="151"/>
+      <c r="E344" s="151"/>
     </row>
     <row r="345" spans="1:5">
-      <c r="A345" s="33"/>
-      <c r="B345" s="34"/>
-      <c r="C345" s="33"/>
-      <c r="D345" s="33"/>
-      <c r="E345" s="33"/>
+      <c r="A345" s="151"/>
+      <c r="B345" s="152"/>
+      <c r="C345" s="151"/>
+      <c r="D345" s="151"/>
+      <c r="E345" s="151"/>
     </row>
     <row r="346" spans="1:5">
-      <c r="A346" s="33"/>
-      <c r="B346" s="34"/>
-      <c r="C346" s="33"/>
-      <c r="D346" s="33"/>
-      <c r="E346" s="33"/>
+      <c r="A346" s="151"/>
+      <c r="B346" s="152"/>
+      <c r="C346" s="151"/>
+      <c r="D346" s="151"/>
+      <c r="E346" s="151"/>
     </row>
     <row r="347" spans="1:5">
-      <c r="A347" s="33"/>
-      <c r="B347" s="34"/>
-      <c r="C347" s="33"/>
-      <c r="D347" s="33"/>
-      <c r="E347" s="33"/>
+      <c r="A347" s="151"/>
+      <c r="B347" s="152"/>
+      <c r="C347" s="151"/>
+      <c r="D347" s="151"/>
+      <c r="E347" s="151"/>
     </row>
     <row r="348" spans="1:5">
-      <c r="A348" s="33"/>
-      <c r="B348" s="34"/>
-      <c r="C348" s="33"/>
-      <c r="D348" s="33"/>
-      <c r="E348" s="33"/>
+      <c r="A348" s="151"/>
+      <c r="B348" s="152"/>
+      <c r="C348" s="151"/>
+      <c r="D348" s="151"/>
+      <c r="E348" s="151"/>
     </row>
     <row r="349" spans="1:5">
-      <c r="A349" s="33"/>
-      <c r="B349" s="34"/>
-      <c r="C349" s="33"/>
-      <c r="D349" s="33"/>
-      <c r="E349" s="33"/>
+      <c r="A349" s="151"/>
+      <c r="B349" s="152"/>
+      <c r="C349" s="151"/>
+      <c r="D349" s="151"/>
+      <c r="E349" s="151"/>
     </row>
     <row r="350" spans="1:5">
-      <c r="A350" s="33"/>
-      <c r="B350" s="34"/>
-      <c r="C350" s="33"/>
-      <c r="D350" s="33"/>
-      <c r="E350" s="33"/>
+      <c r="A350" s="151"/>
+      <c r="B350" s="152"/>
+      <c r="C350" s="151"/>
+      <c r="D350" s="151"/>
+      <c r="E350" s="151"/>
     </row>
     <row r="351" spans="1:5">
-      <c r="A351" s="33"/>
-      <c r="B351" s="34"/>
-      <c r="C351" s="33"/>
-      <c r="D351" s="33"/>
-      <c r="E351" s="33"/>
+      <c r="A351" s="151"/>
+      <c r="B351" s="152"/>
+      <c r="C351" s="151"/>
+      <c r="D351" s="151"/>
+      <c r="E351" s="151"/>
     </row>
     <row r="352" spans="1:5">
-      <c r="A352" s="33"/>
-      <c r="B352" s="34"/>
-      <c r="C352" s="33"/>
-      <c r="D352" s="33"/>
-      <c r="E352" s="33"/>
+      <c r="A352" s="151"/>
+      <c r="B352" s="152"/>
+      <c r="C352" s="151"/>
+      <c r="D352" s="151"/>
+      <c r="E352" s="151"/>
     </row>
     <row r="353" spans="1:5">
-      <c r="A353" s="33"/>
-      <c r="B353" s="34"/>
-      <c r="C353" s="33"/>
-      <c r="D353" s="33"/>
-      <c r="E353" s="33"/>
+      <c r="A353" s="151"/>
+      <c r="B353" s="152"/>
+      <c r="C353" s="151"/>
+      <c r="D353" s="151"/>
+      <c r="E353" s="151"/>
     </row>
     <row r="354" spans="1:5">
-      <c r="A354" s="33"/>
-      <c r="B354" s="34"/>
-      <c r="C354" s="33"/>
-      <c r="D354" s="33"/>
-      <c r="E354" s="33"/>
+      <c r="A354" s="151"/>
+      <c r="B354" s="152"/>
+      <c r="C354" s="151"/>
+      <c r="D354" s="151"/>
+      <c r="E354" s="151"/>
     </row>
     <row r="355" spans="1:5">
-      <c r="A355" s="33"/>
-      <c r="B355" s="34"/>
-      <c r="C355" s="33"/>
-      <c r="D355" s="33"/>
-      <c r="E355" s="33"/>
+      <c r="A355" s="151"/>
+      <c r="B355" s="152"/>
+      <c r="C355" s="151"/>
+      <c r="D355" s="151"/>
+      <c r="E355" s="151"/>
     </row>
     <row r="356" spans="1:5">
-      <c r="A356" s="33"/>
-      <c r="B356" s="34"/>
-      <c r="C356" s="33"/>
-      <c r="D356" s="33"/>
-      <c r="E356" s="33"/>
+      <c r="A356" s="151"/>
+      <c r="B356" s="152"/>
+      <c r="C356" s="151"/>
+      <c r="D356" s="151"/>
+      <c r="E356" s="151"/>
     </row>
     <row r="357" spans="1:5">
-      <c r="A357" s="33"/>
-      <c r="B357" s="34"/>
-      <c r="C357" s="33"/>
-      <c r="D357" s="33"/>
-      <c r="E357" s="33"/>
+      <c r="A357" s="151"/>
+      <c r="B357" s="152"/>
+      <c r="C357" s="151"/>
+      <c r="D357" s="151"/>
+      <c r="E357" s="151"/>
     </row>
     <row r="358" spans="1:5">
-      <c r="A358" s="33"/>
-      <c r="B358" s="34"/>
-      <c r="C358" s="33"/>
-      <c r="D358" s="33"/>
-      <c r="E358" s="33"/>
+      <c r="A358" s="151"/>
+      <c r="B358" s="152"/>
+      <c r="C358" s="151"/>
+      <c r="D358" s="151"/>
+      <c r="E358" s="151"/>
     </row>
     <row r="359" spans="1:5">
-      <c r="A359" s="33"/>
-      <c r="B359" s="34"/>
-      <c r="C359" s="33"/>
-      <c r="D359" s="33"/>
-      <c r="E359" s="33"/>
+      <c r="A359" s="151"/>
+      <c r="B359" s="152"/>
+      <c r="C359" s="151"/>
+      <c r="D359" s="151"/>
+      <c r="E359" s="151"/>
     </row>
     <row r="360" spans="1:5">
-      <c r="A360" s="33"/>
-      <c r="B360" s="34"/>
-      <c r="C360" s="33"/>
-      <c r="D360" s="33"/>
-      <c r="E360" s="33"/>
+      <c r="A360" s="151"/>
+      <c r="B360" s="152"/>
+      <c r="C360" s="151"/>
+      <c r="D360" s="151"/>
+      <c r="E360" s="151"/>
     </row>
     <row r="361" spans="1:5">
-      <c r="A361" s="33"/>
-      <c r="B361" s="34"/>
-      <c r="C361" s="33"/>
-      <c r="D361" s="33"/>
-      <c r="E361" s="33"/>
+      <c r="A361" s="151"/>
+      <c r="B361" s="152"/>
+      <c r="C361" s="151"/>
+      <c r="D361" s="151"/>
+      <c r="E361" s="151"/>
     </row>
     <row r="362" spans="1:5">
-      <c r="A362" s="33"/>
-      <c r="B362" s="34"/>
-      <c r="C362" s="33"/>
-      <c r="D362" s="33"/>
-      <c r="E362" s="33"/>
+      <c r="A362" s="151"/>
+      <c r="B362" s="152"/>
+      <c r="C362" s="151"/>
+      <c r="D362" s="151"/>
+      <c r="E362" s="151"/>
     </row>
     <row r="363" spans="1:5">
-      <c r="A363" s="33"/>
-      <c r="B363" s="34"/>
-      <c r="C363" s="33"/>
-      <c r="D363" s="33"/>
-      <c r="E363" s="33"/>
+      <c r="A363" s="151"/>
+      <c r="B363" s="152"/>
+      <c r="C363" s="151"/>
+      <c r="D363" s="151"/>
+      <c r="E363" s="151"/>
     </row>
     <row r="364" spans="1:5">
-      <c r="A364" s="33"/>
-      <c r="B364" s="34"/>
-      <c r="C364" s="33"/>
-      <c r="D364" s="33"/>
-      <c r="E364" s="33"/>
+      <c r="A364" s="151"/>
+      <c r="B364" s="152"/>
+      <c r="C364" s="151"/>
+      <c r="D364" s="151"/>
+      <c r="E364" s="151"/>
     </row>
     <row r="365" spans="1:5">
-      <c r="A365" s="33"/>
-      <c r="B365" s="34"/>
-      <c r="C365" s="33"/>
-      <c r="D365" s="33"/>
-      <c r="E365" s="33"/>
+      <c r="A365" s="151"/>
+      <c r="B365" s="152"/>
+      <c r="C365" s="151"/>
+      <c r="D365" s="151"/>
+      <c r="E365" s="151"/>
     </row>
     <row r="366" spans="1:5">
-      <c r="A366" s="33"/>
-      <c r="B366" s="34"/>
-      <c r="C366" s="33"/>
-      <c r="D366" s="33"/>
-      <c r="E366" s="33"/>
+      <c r="A366" s="151"/>
+      <c r="B366" s="152"/>
+      <c r="C366" s="151"/>
+      <c r="D366" s="151"/>
+      <c r="E366" s="151"/>
     </row>
     <row r="367" spans="1:5">
-      <c r="A367" s="33"/>
-      <c r="B367" s="34"/>
-      <c r="C367" s="33"/>
-      <c r="D367" s="33"/>
-      <c r="E367" s="33"/>
+      <c r="A367" s="151"/>
+      <c r="B367" s="152"/>
+      <c r="C367" s="151"/>
+      <c r="D367" s="151"/>
+      <c r="E367" s="151"/>
     </row>
     <row r="368" spans="1:5">
-      <c r="A368" s="33"/>
-      <c r="B368" s="34"/>
-      <c r="C368" s="33"/>
-      <c r="D368" s="33"/>
-      <c r="E368" s="33"/>
+      <c r="A368" s="151"/>
+      <c r="B368" s="152"/>
+      <c r="C368" s="151"/>
+      <c r="D368" s="151"/>
+      <c r="E368" s="151"/>
     </row>
     <row r="369" spans="1:5">
-      <c r="A369" s="33"/>
-      <c r="B369" s="34"/>
-      <c r="C369" s="33"/>
-      <c r="D369" s="33"/>
-      <c r="E369" s="33"/>
+      <c r="A369" s="151"/>
+      <c r="B369" s="152"/>
+      <c r="C369" s="151"/>
+      <c r="D369" s="151"/>
+      <c r="E369" s="151"/>
     </row>
     <row r="370" spans="1:5">
-      <c r="A370" s="33"/>
-      <c r="B370" s="34"/>
-      <c r="C370" s="33"/>
-      <c r="D370" s="33"/>
-      <c r="E370" s="33"/>
+      <c r="A370" s="151"/>
+      <c r="B370" s="152"/>
+      <c r="C370" s="151"/>
+      <c r="D370" s="151"/>
+      <c r="E370" s="151"/>
     </row>
     <row r="371" spans="1:5">
-      <c r="A371" s="33"/>
-      <c r="B371" s="34"/>
-      <c r="C371" s="33"/>
-      <c r="D371" s="33"/>
-      <c r="E371" s="33"/>
+      <c r="A371" s="151"/>
+      <c r="B371" s="152"/>
+      <c r="C371" s="151"/>
+      <c r="D371" s="151"/>
+      <c r="E371" s="151"/>
     </row>
     <row r="372" spans="1:5">
-      <c r="A372" s="33"/>
-      <c r="B372" s="34"/>
-      <c r="C372" s="33"/>
-      <c r="D372" s="33"/>
-      <c r="E372" s="33"/>
+      <c r="A372" s="151"/>
+      <c r="B372" s="152"/>
+      <c r="C372" s="151"/>
+      <c r="D372" s="151"/>
+      <c r="E372" s="151"/>
     </row>
     <row r="373" spans="1:5">
-      <c r="A373" s="33"/>
-      <c r="B373" s="34"/>
-      <c r="C373" s="33"/>
-      <c r="D373" s="33"/>
-      <c r="E373" s="33"/>
+      <c r="A373" s="151"/>
+      <c r="B373" s="152"/>
+      <c r="C373" s="151"/>
+      <c r="D373" s="151"/>
+      <c r="E373" s="151"/>
     </row>
     <row r="374" spans="1:5">
-      <c r="A374" s="33"/>
-      <c r="B374" s="34"/>
-      <c r="C374" s="33"/>
-      <c r="D374" s="33"/>
-      <c r="E374" s="33"/>
+      <c r="A374" s="151"/>
+      <c r="B374" s="152"/>
+      <c r="C374" s="151"/>
+      <c r="D374" s="151"/>
+      <c r="E374" s="151"/>
     </row>
     <row r="375" spans="1:5">
-      <c r="A375" s="33"/>
-      <c r="B375" s="34"/>
-      <c r="C375" s="33"/>
-      <c r="D375" s="33"/>
-      <c r="E375" s="33"/>
+      <c r="A375" s="151"/>
+      <c r="B375" s="152"/>
+      <c r="C375" s="151"/>
+      <c r="D375" s="151"/>
+      <c r="E375" s="151"/>
     </row>
     <row r="376" spans="1:5">
-      <c r="A376" s="33"/>
-      <c r="B376" s="34"/>
-      <c r="C376" s="33"/>
-      <c r="D376" s="33"/>
-      <c r="E376" s="33"/>
+      <c r="A376" s="151"/>
+      <c r="B376" s="152"/>
+      <c r="C376" s="151"/>
+      <c r="D376" s="151"/>
+      <c r="E376" s="151"/>
     </row>
     <row r="377" spans="1:5">
-      <c r="A377" s="33"/>
-      <c r="B377" s="34"/>
-      <c r="C377" s="33"/>
-      <c r="D377" s="33"/>
-      <c r="E377" s="33"/>
+      <c r="A377" s="151"/>
+      <c r="B377" s="152"/>
+      <c r="C377" s="151"/>
+      <c r="D377" s="151"/>
+      <c r="E377" s="151"/>
     </row>
     <row r="378" spans="1:5">
-      <c r="A378" s="33"/>
-      <c r="B378" s="34"/>
-      <c r="C378" s="33"/>
-      <c r="D378" s="33"/>
-      <c r="E378" s="33"/>
+      <c r="A378" s="151"/>
+      <c r="B378" s="152"/>
+      <c r="C378" s="151"/>
+      <c r="D378" s="151"/>
+      <c r="E378" s="151"/>
     </row>
     <row r="379" spans="1:5">
-      <c r="A379" s="33"/>
-      <c r="B379" s="34"/>
-      <c r="C379" s="33"/>
-      <c r="D379" s="33"/>
-      <c r="E379" s="33"/>
+      <c r="A379" s="151"/>
+      <c r="B379" s="152"/>
+      <c r="C379" s="151"/>
+      <c r="D379" s="151"/>
+      <c r="E379" s="151"/>
     </row>
     <row r="380" spans="1:5">
-      <c r="A380" s="33"/>
-      <c r="B380" s="34"/>
-      <c r="C380" s="33"/>
-      <c r="D380" s="33"/>
-      <c r="E380" s="33"/>
+      <c r="A380" s="151"/>
+      <c r="B380" s="152"/>
+      <c r="C380" s="151"/>
+      <c r="D380" s="151"/>
+      <c r="E380" s="151"/>
     </row>
     <row r="381" spans="1:5">
-      <c r="A381" s="33"/>
-      <c r="B381" s="34"/>
-      <c r="C381" s="33"/>
-      <c r="D381" s="33"/>
-      <c r="E381" s="33"/>
+      <c r="A381" s="151"/>
+      <c r="B381" s="152"/>
+      <c r="C381" s="151"/>
+      <c r="D381" s="151"/>
+      <c r="E381" s="151"/>
     </row>
     <row r="382" spans="1:5">
-      <c r="A382" s="33"/>
-      <c r="B382" s="34"/>
-      <c r="C382" s="33"/>
-      <c r="D382" s="33"/>
-      <c r="E382" s="33"/>
+      <c r="A382" s="151"/>
+      <c r="B382" s="152"/>
+      <c r="C382" s="151"/>
+      <c r="D382" s="151"/>
+      <c r="E382" s="151"/>
     </row>
     <row r="383" spans="1:5">
-      <c r="A383" s="33"/>
-      <c r="B383" s="34"/>
-      <c r="C383" s="33"/>
-      <c r="D383" s="33"/>
-      <c r="E383" s="33"/>
+      <c r="A383" s="151"/>
+      <c r="B383" s="152"/>
+      <c r="C383" s="151"/>
+      <c r="D383" s="151"/>
+      <c r="E383" s="151"/>
     </row>
     <row r="384" spans="1:5">
-      <c r="A384" s="33"/>
-      <c r="B384" s="34"/>
-      <c r="C384" s="33"/>
-      <c r="D384" s="33"/>
-      <c r="E384" s="33"/>
+      <c r="A384" s="151"/>
+      <c r="B384" s="152"/>
+      <c r="C384" s="151"/>
+      <c r="D384" s="151"/>
+      <c r="E384" s="151"/>
     </row>
     <row r="385" spans="1:5">
-      <c r="A385" s="33"/>
-      <c r="B385" s="34"/>
-      <c r="C385" s="33"/>
-      <c r="D385" s="33"/>
-      <c r="E385" s="33"/>
+      <c r="A385" s="151"/>
+      <c r="B385" s="152"/>
+      <c r="C385" s="151"/>
+      <c r="D385" s="151"/>
+      <c r="E385" s="151"/>
     </row>
     <row r="386" spans="1:5">
-      <c r="A386" s="33"/>
-      <c r="B386" s="34"/>
-      <c r="C386" s="33"/>
-      <c r="D386" s="33"/>
-      <c r="E386" s="33"/>
+      <c r="A386" s="151"/>
+      <c r="B386" s="152"/>
+      <c r="C386" s="151"/>
+      <c r="D386" s="151"/>
+      <c r="E386" s="151"/>
     </row>
     <row r="387" spans="1:5">
-      <c r="A387" s="33"/>
-      <c r="B387" s="34"/>
-      <c r="C387" s="33"/>
-      <c r="D387" s="33"/>
-      <c r="E387" s="33"/>
+      <c r="A387" s="151"/>
+      <c r="B387" s="152"/>
+      <c r="C387" s="151"/>
+      <c r="D387" s="151"/>
+      <c r="E387" s="151"/>
     </row>
     <row r="388" spans="1:5">
-      <c r="A388" s="33"/>
-      <c r="B388" s="34"/>
-      <c r="C388" s="33"/>
-      <c r="D388" s="33"/>
-      <c r="E388" s="33"/>
+      <c r="A388" s="151"/>
+      <c r="B388" s="152"/>
+      <c r="C388" s="151"/>
+      <c r="D388" s="151"/>
+      <c r="E388" s="151"/>
     </row>
     <row r="389" spans="1:5">
-      <c r="A389" s="33"/>
-      <c r="B389" s="34"/>
-      <c r="C389" s="33"/>
-      <c r="D389" s="33"/>
-      <c r="E389" s="33"/>
+      <c r="A389" s="151"/>
+      <c r="B389" s="152"/>
+      <c r="C389" s="151"/>
+      <c r="D389" s="151"/>
+      <c r="E389" s="151"/>
     </row>
     <row r="390" spans="1:5">
-      <c r="A390" s="33"/>
-      <c r="B390" s="34"/>
-      <c r="C390" s="33"/>
-      <c r="D390" s="33"/>
-      <c r="E390" s="33"/>
+      <c r="A390" s="151"/>
+      <c r="B390" s="152"/>
+      <c r="C390" s="151"/>
+      <c r="D390" s="151"/>
+      <c r="E390" s="151"/>
     </row>
     <row r="391" spans="1:5">
-      <c r="A391" s="33"/>
-      <c r="B391" s="34"/>
-      <c r="C391" s="33"/>
-      <c r="D391" s="33"/>
-      <c r="E391" s="33"/>
+      <c r="A391" s="151"/>
+      <c r="B391" s="152"/>
+      <c r="C391" s="151"/>
+      <c r="D391" s="151"/>
+      <c r="E391" s="151"/>
     </row>
     <row r="392" spans="1:5">
-      <c r="A392" s="33"/>
-      <c r="B392" s="34"/>
-      <c r="C392" s="33"/>
-      <c r="D392" s="33"/>
-      <c r="E392" s="33"/>
+      <c r="A392" s="151"/>
+      <c r="B392" s="152"/>
+      <c r="C392" s="151"/>
+      <c r="D392" s="151"/>
+      <c r="E392" s="151"/>
     </row>
     <row r="393" spans="1:5">
-      <c r="A393" s="33"/>
-      <c r="B393" s="34"/>
-      <c r="C393" s="33"/>
-      <c r="D393" s="33"/>
-      <c r="E393" s="33"/>
+      <c r="A393" s="151"/>
+      <c r="B393" s="152"/>
+      <c r="C393" s="151"/>
+      <c r="D393" s="151"/>
+      <c r="E393" s="151"/>
     </row>
     <row r="394" spans="1:5">
-      <c r="A394" s="33"/>
-      <c r="B394" s="34"/>
-      <c r="C394" s="33"/>
-      <c r="D394" s="33"/>
-      <c r="E394" s="33"/>
+      <c r="A394" s="151"/>
+      <c r="B394" s="152"/>
+      <c r="C394" s="151"/>
+      <c r="D394" s="151"/>
+      <c r="E394" s="151"/>
     </row>
     <row r="395" spans="1:5">
-      <c r="A395" s="33"/>
-      <c r="B395" s="34"/>
-      <c r="C395" s="33"/>
-      <c r="D395" s="33"/>
-      <c r="E395" s="33"/>
+      <c r="A395" s="151"/>
+      <c r="B395" s="152"/>
+      <c r="C395" s="151"/>
+      <c r="D395" s="151"/>
+      <c r="E395" s="151"/>
     </row>
     <row r="396" spans="1:5">
-      <c r="A396" s="33"/>
-      <c r="B396" s="34"/>
-      <c r="C396" s="33"/>
-      <c r="D396" s="33"/>
-      <c r="E396" s="33"/>
+      <c r="A396" s="151"/>
+      <c r="B396" s="152"/>
+      <c r="C396" s="151"/>
+      <c r="D396" s="151"/>
+      <c r="E396" s="151"/>
     </row>
     <row r="397" spans="1:5">
-      <c r="A397" s="33"/>
-      <c r="B397" s="34"/>
-      <c r="C397" s="33"/>
-      <c r="D397" s="33"/>
-      <c r="E397" s="33"/>
+      <c r="A397" s="151"/>
+      <c r="B397" s="152"/>
+      <c r="C397" s="151"/>
+      <c r="D397" s="151"/>
+      <c r="E397" s="151"/>
     </row>
     <row r="398" spans="1:5">
-      <c r="A398" s="33"/>
-      <c r="B398" s="34"/>
-      <c r="C398" s="33"/>
-      <c r="D398" s="33"/>
-      <c r="E398" s="33"/>
+      <c r="A398" s="151"/>
+      <c r="B398" s="152"/>
+      <c r="C398" s="151"/>
+      <c r="D398" s="151"/>
+      <c r="E398" s="151"/>
     </row>
     <row r="399" spans="1:5">
-      <c r="A399" s="33"/>
-      <c r="B399" s="34"/>
-      <c r="C399" s="33"/>
-      <c r="D399" s="33"/>
-      <c r="E399" s="33"/>
+      <c r="A399" s="151"/>
+      <c r="B399" s="152"/>
+      <c r="C399" s="151"/>
+      <c r="D399" s="151"/>
+      <c r="E399" s="151"/>
     </row>
     <row r="400" spans="1:5">
-      <c r="A400" s="33"/>
-      <c r="B400" s="34"/>
-      <c r="C400" s="33"/>
-      <c r="D400" s="33"/>
-      <c r="E400" s="33"/>
+      <c r="A400" s="151"/>
+      <c r="B400" s="152"/>
+      <c r="C400" s="151"/>
+      <c r="D400" s="151"/>
+      <c r="E400" s="151"/>
     </row>
     <row r="401" spans="1:5">
-      <c r="A401" s="33"/>
-      <c r="B401" s="34"/>
-      <c r="C401" s="33"/>
-      <c r="D401" s="33"/>
-      <c r="E401" s="33"/>
+      <c r="A401" s="151"/>
+      <c r="B401" s="152"/>
+      <c r="C401" s="151"/>
+      <c r="D401" s="151"/>
+      <c r="E401" s="151"/>
     </row>
     <row r="402" spans="1:5">
-      <c r="A402" s="33"/>
-      <c r="B402" s="34"/>
-      <c r="C402" s="33"/>
-      <c r="D402" s="33"/>
-      <c r="E402" s="33"/>
+      <c r="A402" s="151"/>
+      <c r="B402" s="152"/>
+      <c r="C402" s="151"/>
+      <c r="D402" s="151"/>
+      <c r="E402" s="151"/>
     </row>
     <row r="403" spans="1:5">
-      <c r="A403" s="33"/>
-      <c r="B403" s="34"/>
-      <c r="C403" s="33"/>
-      <c r="D403" s="33"/>
-      <c r="E403" s="33"/>
+      <c r="A403" s="151"/>
+      <c r="B403" s="152"/>
+      <c r="C403" s="151"/>
+      <c r="D403" s="151"/>
+      <c r="E403" s="151"/>
     </row>
     <row r="404" spans="1:5">
-      <c r="A404" s="33"/>
-      <c r="B404" s="34"/>
-      <c r="C404" s="33"/>
-      <c r="D404" s="33"/>
-      <c r="E404" s="33"/>
+      <c r="A404" s="151"/>
+      <c r="B404" s="152"/>
+      <c r="C404" s="151"/>
+      <c r="D404" s="151"/>
+      <c r="E404" s="151"/>
     </row>
     <row r="405" spans="1:5">
-      <c r="A405" s="33"/>
-      <c r="B405" s="34"/>
-      <c r="C405" s="33"/>
-      <c r="D405" s="33"/>
-      <c r="E405" s="33"/>
+      <c r="A405" s="151"/>
+      <c r="B405" s="152"/>
+      <c r="C405" s="151"/>
+      <c r="D405" s="151"/>
+      <c r="E405" s="151"/>
     </row>
     <row r="406" spans="1:5">
-      <c r="A406" s="33"/>
-      <c r="B406" s="34"/>
-      <c r="C406" s="33"/>
-      <c r="D406" s="33"/>
-      <c r="E406" s="33"/>
+      <c r="A406" s="151"/>
+      <c r="B406" s="152"/>
+      <c r="C406" s="151"/>
+      <c r="D406" s="151"/>
+      <c r="E406" s="151"/>
     </row>
     <row r="407" spans="1:5">
-      <c r="A407" s="33"/>
-      <c r="B407" s="34"/>
-      <c r="C407" s="33"/>
-      <c r="D407" s="33"/>
-      <c r="E407" s="33"/>
+      <c r="A407" s="151"/>
+      <c r="B407" s="152"/>
+      <c r="C407" s="151"/>
+      <c r="D407" s="151"/>
+      <c r="E407" s="151"/>
     </row>
     <row r="408" spans="1:5">
-      <c r="A408" s="33"/>
-      <c r="B408" s="34"/>
-      <c r="C408" s="33"/>
-      <c r="D408" s="33"/>
-      <c r="E408" s="33"/>
+      <c r="A408" s="151"/>
+      <c r="B408" s="152"/>
+      <c r="C408" s="151"/>
+      <c r="D408" s="151"/>
+      <c r="E408" s="151"/>
     </row>
     <row r="409" spans="1:5">
-      <c r="A409" s="33"/>
-      <c r="B409" s="34"/>
-      <c r="C409" s="33"/>
-      <c r="D409" s="33"/>
-      <c r="E409" s="33"/>
+      <c r="A409" s="151"/>
+      <c r="B409" s="152"/>
+      <c r="C409" s="151"/>
+      <c r="D409" s="151"/>
+      <c r="E409" s="151"/>
     </row>
     <row r="410" spans="1:5">
-      <c r="A410" s="33"/>
-      <c r="B410" s="34"/>
-      <c r="C410" s="33"/>
-      <c r="D410" s="33"/>
-      <c r="E410" s="33"/>
+      <c r="A410" s="151"/>
+      <c r="B410" s="152"/>
+      <c r="C410" s="151"/>
+      <c r="D410" s="151"/>
+      <c r="E410" s="151"/>
     </row>
     <row r="411" spans="1:5">
-      <c r="A411" s="33"/>
-      <c r="B411" s="34"/>
-      <c r="C411" s="33"/>
-      <c r="D411" s="33"/>
-      <c r="E411" s="33"/>
+      <c r="A411" s="151"/>
+      <c r="B411" s="152"/>
+      <c r="C411" s="151"/>
+      <c r="D411" s="151"/>
+      <c r="E411" s="151"/>
     </row>
     <row r="412" spans="1:5">
-      <c r="A412" s="33"/>
-      <c r="B412" s="34"/>
-      <c r="C412" s="33"/>
-      <c r="D412" s="33"/>
-      <c r="E412" s="33"/>
+      <c r="A412" s="151"/>
+      <c r="B412" s="152"/>
+      <c r="C412" s="151"/>
+      <c r="D412" s="151"/>
+      <c r="E412" s="151"/>
     </row>
     <row r="413" spans="1:5">
-      <c r="A413" s="33"/>
-      <c r="B413" s="34"/>
-      <c r="C413" s="33"/>
-      <c r="D413" s="33"/>
-      <c r="E413" s="33"/>
+      <c r="A413" s="151"/>
+      <c r="B413" s="152"/>
+      <c r="C413" s="151"/>
+      <c r="D413" s="151"/>
+      <c r="E413" s="151"/>
     </row>
     <row r="414" spans="1:5">
-      <c r="A414" s="33"/>
-      <c r="B414" s="34"/>
-      <c r="C414" s="33"/>
-      <c r="D414" s="33"/>
-      <c r="E414" s="33"/>
+      <c r="A414" s="151"/>
+      <c r="B414" s="152"/>
+      <c r="C414" s="151"/>
+      <c r="D414" s="151"/>
+      <c r="E414" s="151"/>
     </row>
     <row r="415" spans="1:5">
-      <c r="A415" s="33"/>
-      <c r="B415" s="34"/>
-      <c r="C415" s="33"/>
-      <c r="D415" s="33"/>
-      <c r="E415" s="33"/>
+      <c r="A415" s="151"/>
+      <c r="B415" s="152"/>
+      <c r="C415" s="151"/>
+      <c r="D415" s="151"/>
+      <c r="E415" s="151"/>
     </row>
     <row r="416" spans="1:5">
-      <c r="A416" s="33"/>
-      <c r="B416" s="34"/>
-      <c r="C416" s="33"/>
-      <c r="D416" s="33"/>
-      <c r="E416" s="33"/>
+      <c r="A416" s="151"/>
+      <c r="B416" s="152"/>
+      <c r="C416" s="151"/>
+      <c r="D416" s="151"/>
+      <c r="E416" s="151"/>
     </row>
     <row r="417" spans="1:5">
-      <c r="A417" s="33"/>
-      <c r="B417" s="34"/>
-      <c r="C417" s="33"/>
-      <c r="D417" s="33"/>
-      <c r="E417" s="33"/>
+      <c r="A417" s="151"/>
+      <c r="B417" s="152"/>
+      <c r="C417" s="151"/>
+      <c r="D417" s="151"/>
+      <c r="E417" s="151"/>
     </row>
     <row r="418" spans="1:5">
-      <c r="A418" s="33"/>
-      <c r="B418" s="34"/>
-      <c r="C418" s="33"/>
-      <c r="D418" s="33"/>
-      <c r="E418" s="33"/>
+      <c r="A418" s="151"/>
+      <c r="B418" s="152"/>
+      <c r="C418" s="151"/>
+      <c r="D418" s="151"/>
+      <c r="E418" s="151"/>
     </row>
     <row r="419" spans="1:5">
-      <c r="A419" s="33"/>
-      <c r="B419" s="34"/>
-      <c r="C419" s="33"/>
-      <c r="D419" s="33"/>
-      <c r="E419" s="33"/>
+      <c r="A419" s="151"/>
+      <c r="B419" s="152"/>
+      <c r="C419" s="151"/>
+      <c r="D419" s="151"/>
+      <c r="E419" s="151"/>
     </row>
     <row r="420" spans="1:5">
-      <c r="A420" s="33"/>
-      <c r="B420" s="34"/>
-      <c r="C420" s="33"/>
-      <c r="D420" s="33"/>
-      <c r="E420" s="33"/>
+      <c r="A420" s="151"/>
+      <c r="B420" s="152"/>
+      <c r="C420" s="151"/>
+      <c r="D420" s="151"/>
+      <c r="E420" s="151"/>
     </row>
     <row r="421" spans="1:5">
-      <c r="A421" s="33"/>
-      <c r="B421" s="34"/>
-      <c r="C421" s="33"/>
-      <c r="D421" s="33"/>
-      <c r="E421" s="33"/>
+      <c r="A421" s="151"/>
+      <c r="B421" s="152"/>
+      <c r="C421" s="151"/>
+      <c r="D421" s="151"/>
+      <c r="E421" s="151"/>
     </row>
     <row r="422" spans="1:5">
-      <c r="A422" s="33"/>
-      <c r="B422" s="34"/>
-      <c r="C422" s="33"/>
-      <c r="D422" s="33"/>
-      <c r="E422" s="33"/>
+      <c r="A422" s="151"/>
+      <c r="B422" s="152"/>
+      <c r="C422" s="151"/>
+      <c r="D422" s="151"/>
+      <c r="E422" s="151"/>
     </row>
     <row r="423" spans="1:5">
-      <c r="A423" s="33"/>
-      <c r="B423" s="34"/>
-      <c r="C423" s="33"/>
-      <c r="D423" s="33"/>
-      <c r="E423" s="33"/>
+      <c r="A423" s="151"/>
+      <c r="B423" s="152"/>
+      <c r="C423" s="151"/>
+      <c r="D423" s="151"/>
+      <c r="E423" s="151"/>
     </row>
     <row r="424" spans="1:5">
-      <c r="A424" s="33"/>
-      <c r="B424" s="34"/>
-      <c r="C424" s="33"/>
-      <c r="D424" s="33"/>
-      <c r="E424" s="33"/>
+      <c r="A424" s="151"/>
+      <c r="B424" s="152"/>
+      <c r="C424" s="151"/>
+      <c r="D424" s="151"/>
+      <c r="E424" s="151"/>
     </row>
     <row r="425" spans="1:5">
-      <c r="A425" s="33"/>
-      <c r="B425" s="34"/>
-      <c r="C425" s="33"/>
-      <c r="D425" s="33"/>
-      <c r="E425" s="33"/>
+      <c r="A425" s="151"/>
+      <c r="B425" s="152"/>
+      <c r="C425" s="151"/>
+      <c r="D425" s="151"/>
+      <c r="E425" s="151"/>
     </row>
     <row r="426" spans="1:5">
-      <c r="A426" s="33"/>
-      <c r="B426" s="34"/>
-      <c r="C426" s="33"/>
-      <c r="D426" s="33"/>
-      <c r="E426" s="33"/>
+      <c r="A426" s="151"/>
+      <c r="B426" s="152"/>
+      <c r="C426" s="151"/>
+      <c r="D426" s="151"/>
+      <c r="E426" s="151"/>
     </row>
     <row r="427" spans="1:5">
-      <c r="A427" s="33"/>
-      <c r="B427" s="34"/>
-      <c r="C427" s="33"/>
-      <c r="D427" s="33"/>
-      <c r="E427" s="33"/>
+      <c r="A427" s="151"/>
+      <c r="B427" s="152"/>
+      <c r="C427" s="151"/>
+      <c r="D427" s="151"/>
+      <c r="E427" s="151"/>
     </row>
     <row r="428" spans="1:5">
-      <c r="A428" s="33"/>
-      <c r="B428" s="34"/>
-      <c r="C428" s="33"/>
-      <c r="D428" s="33"/>
-      <c r="E428" s="33"/>
+      <c r="A428" s="151"/>
+      <c r="B428" s="152"/>
+      <c r="C428" s="151"/>
+      <c r="D428" s="151"/>
+      <c r="E428" s="151"/>
     </row>
     <row r="429" spans="1:5">
-      <c r="A429" s="33"/>
-      <c r="B429" s="34"/>
-      <c r="C429" s="33"/>
-      <c r="D429" s="33"/>
-      <c r="E429" s="33"/>
+      <c r="A429" s="151"/>
+      <c r="B429" s="152"/>
+      <c r="C429" s="151"/>
+      <c r="D429" s="151"/>
+      <c r="E429" s="151"/>
     </row>
     <row r="430" spans="1:5">
-      <c r="A430" s="33"/>
-      <c r="B430" s="34"/>
-      <c r="C430" s="33"/>
-      <c r="D430" s="33"/>
-      <c r="E430" s="33"/>
+      <c r="A430" s="151"/>
+      <c r="B430" s="152"/>
+      <c r="C430" s="151"/>
+      <c r="D430" s="151"/>
+      <c r="E430" s="151"/>
     </row>
     <row r="431" spans="1:5">
-      <c r="A431" s="33"/>
-      <c r="B431" s="34"/>
-      <c r="C431" s="33"/>
-      <c r="D431" s="33"/>
-      <c r="E431" s="33"/>
+      <c r="A431" s="151"/>
+      <c r="B431" s="152"/>
+      <c r="C431" s="151"/>
+      <c r="D431" s="151"/>
+      <c r="E431" s="151"/>
     </row>
     <row r="432" spans="1:5">
-      <c r="A432" s="33"/>
-      <c r="B432" s="34"/>
-      <c r="C432" s="33"/>
-      <c r="D432" s="33"/>
-      <c r="E432" s="33"/>
+      <c r="A432" s="151"/>
+      <c r="B432" s="152"/>
+      <c r="C432" s="151"/>
+      <c r="D432" s="151"/>
+      <c r="E432" s="151"/>
     </row>
     <row r="433" spans="1:5">
-      <c r="A433" s="33"/>
-      <c r="B433" s="34"/>
-      <c r="C433" s="33"/>
-      <c r="D433" s="33"/>
-      <c r="E433" s="33"/>
+      <c r="A433" s="151"/>
+      <c r="B433" s="152"/>
+      <c r="C433" s="151"/>
+      <c r="D433" s="151"/>
+      <c r="E433" s="151"/>
     </row>
     <row r="434" spans="1:5">
-      <c r="A434" s="33"/>
-      <c r="B434" s="34"/>
-      <c r="C434" s="33"/>
-      <c r="D434" s="33"/>
-      <c r="E434" s="33"/>
+      <c r="A434" s="151"/>
+      <c r="B434" s="152"/>
+      <c r="C434" s="151"/>
+      <c r="D434" s="151"/>
+      <c r="E434" s="151"/>
     </row>
     <row r="435" spans="1:5">
-      <c r="A435" s="33"/>
-      <c r="B435" s="34"/>
-      <c r="C435" s="33"/>
-      <c r="D435" s="33"/>
-      <c r="E435" s="33"/>
+      <c r="A435" s="151"/>
+      <c r="B435" s="152"/>
+      <c r="C435" s="151"/>
+      <c r="D435" s="151"/>
+      <c r="E435" s="151"/>
     </row>
     <row r="436" spans="1:5">
-      <c r="A436" s="33"/>
-      <c r="B436" s="34"/>
-      <c r="C436" s="33"/>
-      <c r="D436" s="33"/>
-      <c r="E436" s="33"/>
+      <c r="A436" s="151"/>
+      <c r="B436" s="152"/>
+      <c r="C436" s="151"/>
+      <c r="D436" s="151"/>
+      <c r="E436" s="151"/>
     </row>
     <row r="437" spans="1:5">
-      <c r="A437" s="33"/>
-      <c r="B437" s="34"/>
-      <c r="C437" s="33"/>
-      <c r="D437" s="33"/>
-      <c r="E437" s="33"/>
+      <c r="A437" s="151"/>
+      <c r="B437" s="152"/>
+      <c r="C437" s="151"/>
+      <c r="D437" s="151"/>
+      <c r="E437" s="151"/>
     </row>
     <row r="438" spans="1:5">
-      <c r="A438" s="33"/>
-      <c r="B438" s="34"/>
-      <c r="C438" s="33"/>
-      <c r="D438" s="33"/>
-      <c r="E438" s="33"/>
+      <c r="A438" s="151"/>
+      <c r="B438" s="152"/>
+      <c r="C438" s="151"/>
+      <c r="D438" s="151"/>
+      <c r="E438" s="151"/>
     </row>
     <row r="439" spans="1:5">
-      <c r="A439" s="33"/>
-      <c r="B439" s="34"/>
-      <c r="C439" s="33"/>
-      <c r="D439" s="33"/>
-      <c r="E439" s="33"/>
+      <c r="A439" s="151"/>
+      <c r="B439" s="152"/>
+      <c r="C439" s="151"/>
+      <c r="D439" s="151"/>
+      <c r="E439" s="151"/>
     </row>
     <row r="440" spans="1:5">
-      <c r="A440" s="33"/>
-      <c r="B440" s="34"/>
-      <c r="C440" s="33"/>
-      <c r="D440" s="33"/>
-      <c r="E440" s="33"/>
+      <c r="A440" s="151"/>
+      <c r="B440" s="152"/>
+      <c r="C440" s="151"/>
+      <c r="D440" s="151"/>
+      <c r="E440" s="151"/>
     </row>
     <row r="441" spans="1:5">
-      <c r="A441" s="33"/>
-      <c r="B441" s="34"/>
-      <c r="C441" s="33"/>
-      <c r="D441" s="33"/>
-      <c r="E441" s="33"/>
+      <c r="A441" s="151"/>
+      <c r="B441" s="152"/>
+      <c r="C441" s="151"/>
+      <c r="D441" s="151"/>
+      <c r="E441" s="151"/>
     </row>
     <row r="442" spans="1:5">
-      <c r="A442" s="33"/>
-      <c r="B442" s="34"/>
-      <c r="C442" s="33"/>
-      <c r="D442" s="33"/>
-      <c r="E442" s="33"/>
+      <c r="A442" s="151"/>
+      <c r="B442" s="152"/>
+      <c r="C442" s="151"/>
+      <c r="D442" s="151"/>
+      <c r="E442" s="151"/>
     </row>
     <row r="443" spans="1:5">
-      <c r="A443" s="33"/>
-      <c r="B443" s="34"/>
-      <c r="C443" s="33"/>
-      <c r="D443" s="33"/>
-      <c r="E443" s="33"/>
+      <c r="A443" s="151"/>
+      <c r="B443" s="152"/>
+      <c r="C443" s="151"/>
+      <c r="D443" s="151"/>
+      <c r="E443" s="151"/>
     </row>
     <row r="444" spans="1:5">
-      <c r="A444" s="33"/>
-      <c r="B444" s="34"/>
-      <c r="C444" s="33"/>
-      <c r="D444" s="33"/>
-      <c r="E444" s="33"/>
+      <c r="A444" s="151"/>
+      <c r="B444" s="152"/>
+      <c r="C444" s="151"/>
+      <c r="D444" s="151"/>
+      <c r="E444" s="151"/>
     </row>
     <row r="445" spans="1:5">
-      <c r="A445" s="33"/>
-      <c r="B445" s="34"/>
-      <c r="C445" s="33"/>
-      <c r="D445" s="33"/>
-      <c r="E445" s="33"/>
+      <c r="A445" s="151"/>
+      <c r="B445" s="152"/>
+      <c r="C445" s="151"/>
+      <c r="D445" s="151"/>
+      <c r="E445" s="151"/>
     </row>
     <row r="446" spans="1:5">
-      <c r="A446" s="33"/>
-      <c r="B446" s="34"/>
-      <c r="C446" s="33"/>
-      <c r="D446" s="33"/>
-      <c r="E446" s="33"/>
+      <c r="A446" s="151"/>
+      <c r="B446" s="152"/>
+      <c r="C446" s="151"/>
+      <c r="D446" s="151"/>
+      <c r="E446" s="151"/>
     </row>
     <row r="447" spans="1:5">
-      <c r="A447" s="33"/>
-      <c r="B447" s="34"/>
-      <c r="C447" s="33"/>
-      <c r="D447" s="33"/>
-      <c r="E447" s="33"/>
+      <c r="A447" s="151"/>
+      <c r="B447" s="152"/>
+      <c r="C447" s="151"/>
+      <c r="D447" s="151"/>
+      <c r="E447" s="151"/>
     </row>
     <row r="448" spans="1:5">
-      <c r="A448" s="33"/>
-      <c r="B448" s="34"/>
-      <c r="C448" s="33"/>
-      <c r="D448" s="33"/>
-      <c r="E448" s="33"/>
+      <c r="A448" s="151"/>
+      <c r="B448" s="152"/>
+      <c r="C448" s="151"/>
+      <c r="D448" s="151"/>
+      <c r="E448" s="151"/>
     </row>
     <row r="449" spans="1:5">
-      <c r="A449" s="33"/>
-      <c r="B449" s="34"/>
-      <c r="C449" s="33"/>
-      <c r="D449" s="33"/>
-      <c r="E449" s="33"/>
+      <c r="A449" s="151"/>
+      <c r="B449" s="152"/>
+      <c r="C449" s="151"/>
+      <c r="D449" s="151"/>
+      <c r="E449" s="151"/>
     </row>
     <row r="450" spans="1:5">
-      <c r="A450" s="33"/>
-      <c r="B450" s="34"/>
-      <c r="C450" s="33"/>
-      <c r="D450" s="33"/>
-      <c r="E450" s="33"/>
+      <c r="A450" s="151"/>
+      <c r="B450" s="152"/>
+      <c r="C450" s="151"/>
+      <c r="D450" s="151"/>
+      <c r="E450" s="151"/>
     </row>
     <row r="451" spans="1:5">
-      <c r="A451" s="33"/>
-      <c r="B451" s="34"/>
-      <c r="C451" s="33"/>
-      <c r="D451" s="33"/>
-      <c r="E451" s="33"/>
+      <c r="A451" s="151"/>
+      <c r="B451" s="152"/>
+      <c r="C451" s="151"/>
+      <c r="D451" s="151"/>
+      <c r="E451" s="151"/>
     </row>
     <row r="452" spans="1:5">
-      <c r="A452" s="33"/>
-      <c r="B452" s="34"/>
-      <c r="C452" s="33"/>
-      <c r="D452" s="33"/>
-      <c r="E452" s="33"/>
+      <c r="A452" s="151"/>
+      <c r="B452" s="152"/>
+      <c r="C452" s="151"/>
+      <c r="D452" s="151"/>
+      <c r="E452" s="151"/>
     </row>
     <row r="453" spans="1:5">
-      <c r="A453" s="33"/>
-      <c r="B453" s="34"/>
-      <c r="C453" s="33"/>
-      <c r="D453" s="33"/>
-      <c r="E453" s="33"/>
+      <c r="A453" s="151"/>
+      <c r="B453" s="152"/>
+      <c r="C453" s="151"/>
+      <c r="D453" s="151"/>
+      <c r="E453" s="151"/>
     </row>
     <row r="454" spans="1:5">
-      <c r="A454" s="33"/>
-      <c r="B454" s="34"/>
-      <c r="C454" s="33"/>
-      <c r="D454" s="33"/>
-      <c r="E454" s="33"/>
+      <c r="A454" s="151"/>
+      <c r="B454" s="152"/>
+      <c r="C454" s="151"/>
+      <c r="D454" s="151"/>
+      <c r="E454" s="151"/>
     </row>
     <row r="455" spans="1:5">
-      <c r="A455" s="33"/>
-      <c r="B455" s="34"/>
-      <c r="C455" s="33"/>
-      <c r="D455" s="33"/>
-      <c r="E455" s="33"/>
+      <c r="A455" s="151"/>
+      <c r="B455" s="152"/>
+      <c r="C455" s="151"/>
+      <c r="D455" s="151"/>
+      <c r="E455" s="151"/>
     </row>
     <row r="456" spans="1:5">
-      <c r="A456" s="33"/>
-      <c r="B456" s="34"/>
-      <c r="C456" s="33"/>
-      <c r="D456" s="33"/>
-      <c r="E456" s="33"/>
+      <c r="A456" s="151"/>
+      <c r="B456" s="152"/>
+      <c r="C456" s="151"/>
+      <c r="D456" s="151"/>
+      <c r="E456" s="151"/>
     </row>
     <row r="457" spans="1:5">
-      <c r="A457" s="33"/>
-      <c r="B457" s="34"/>
-      <c r="C457" s="33"/>
-      <c r="D457" s="33"/>
-      <c r="E457" s="33"/>
+      <c r="A457" s="151"/>
+      <c r="B457" s="152"/>
+      <c r="C457" s="151"/>
+      <c r="D457" s="151"/>
+      <c r="E457" s="151"/>
     </row>
     <row r="458" spans="1:5">
-      <c r="A458" s="33"/>
-      <c r="B458" s="34"/>
-      <c r="C458" s="33"/>
-      <c r="D458" s="33"/>
-      <c r="E458" s="33"/>
+      <c r="A458" s="151"/>
+      <c r="B458" s="152"/>
+      <c r="C458" s="151"/>
+      <c r="D458" s="151"/>
+      <c r="E458" s="151"/>
     </row>
     <row r="459" spans="1:5">
-      <c r="A459" s="33"/>
-      <c r="B459" s="34"/>
-      <c r="C459" s="33"/>
-      <c r="D459" s="33"/>
-      <c r="E459" s="33"/>
+      <c r="A459" s="151"/>
+      <c r="B459" s="152"/>
+      <c r="C459" s="151"/>
+      <c r="D459" s="151"/>
+      <c r="E459" s="151"/>
     </row>
     <row r="460" spans="1:5">
-      <c r="A460" s="33"/>
-      <c r="B460" s="34"/>
-      <c r="C460" s="33"/>
-      <c r="D460" s="33"/>
-      <c r="E460" s="33"/>
+      <c r="A460" s="151"/>
+      <c r="B460" s="152"/>
+      <c r="C460" s="151"/>
+      <c r="D460" s="151"/>
+      <c r="E460" s="151"/>
     </row>
     <row r="461" spans="1:5">
-      <c r="A461" s="33"/>
-      <c r="B461" s="34"/>
-      <c r="C461" s="33"/>
-      <c r="D461" s="33"/>
-      <c r="E461" s="33"/>
+      <c r="A461" s="151"/>
+      <c r="B461" s="152"/>
+      <c r="C461" s="151"/>
+      <c r="D461" s="151"/>
+      <c r="E461" s="151"/>
     </row>
     <row r="462" spans="1:5">
-      <c r="A462" s="33"/>
-      <c r="B462" s="34"/>
-      <c r="C462" s="33"/>
-      <c r="D462" s="33"/>
-      <c r="E462" s="33"/>
+      <c r="A462" s="151"/>
+      <c r="B462" s="152"/>
+      <c r="C462" s="151"/>
+      <c r="D462" s="151"/>
+      <c r="E462" s="151"/>
     </row>
     <row r="463" spans="1:5">
-      <c r="A463" s="33"/>
-      <c r="B463" s="34"/>
-      <c r="C463" s="33"/>
-      <c r="D463" s="33"/>
-      <c r="E463" s="33"/>
+      <c r="A463" s="151"/>
+      <c r="B463" s="152"/>
+      <c r="C463" s="151"/>
+      <c r="D463" s="151"/>
+      <c r="E463" s="151"/>
     </row>
     <row r="464" spans="1:5">
-      <c r="A464" s="33"/>
-      <c r="B464" s="34"/>
-      <c r="C464" s="33"/>
-      <c r="D464" s="33"/>
-      <c r="E464" s="33"/>
+      <c r="A464" s="151"/>
+      <c r="B464" s="152"/>
+      <c r="C464" s="151"/>
+      <c r="D464" s="151"/>
+      <c r="E464" s="151"/>
     </row>
     <row r="465" spans="1:5">
-      <c r="A465" s="33"/>
-      <c r="B465" s="34"/>
-      <c r="C465" s="33"/>
-      <c r="D465" s="33"/>
-      <c r="E465" s="33"/>
+      <c r="A465" s="151"/>
+      <c r="B465" s="152"/>
+      <c r="C465" s="151"/>
+      <c r="D465" s="151"/>
+      <c r="E465" s="151"/>
     </row>
     <row r="466" spans="1:5">
-      <c r="A466" s="33"/>
-      <c r="B466" s="34"/>
-      <c r="C466" s="33"/>
-      <c r="D466" s="33"/>
-      <c r="E466" s="33"/>
+      <c r="A466" s="151"/>
+      <c r="B466" s="152"/>
+      <c r="C466" s="151"/>
+      <c r="D466" s="151"/>
+      <c r="E466" s="151"/>
     </row>
     <row r="467" spans="1:5">
-      <c r="A467" s="33"/>
-      <c r="B467" s="34"/>
-      <c r="C467" s="33"/>
-      <c r="D467" s="33"/>
-      <c r="E467" s="33"/>
+      <c r="A467" s="151"/>
+      <c r="B467" s="152"/>
+      <c r="C467" s="151"/>
+      <c r="D467" s="151"/>
+      <c r="E467" s="151"/>
     </row>
     <row r="468" spans="1:5">
-      <c r="A468" s="33"/>
-      <c r="B468" s="34"/>
-      <c r="C468" s="33"/>
-      <c r="D468" s="33"/>
-      <c r="E468" s="33"/>
+      <c r="A468" s="151"/>
+      <c r="B468" s="152"/>
+      <c r="C468" s="151"/>
+      <c r="D468" s="151"/>
+      <c r="E468" s="151"/>
     </row>
     <row r="469" spans="1:5">
-      <c r="A469" s="33"/>
-      <c r="B469" s="34"/>
-      <c r="C469" s="33"/>
-      <c r="D469" s="33"/>
-      <c r="E469" s="33"/>
+      <c r="A469" s="151"/>
+      <c r="B469" s="152"/>
+      <c r="C469" s="151"/>
+      <c r="D469" s="151"/>
+      <c r="E469" s="151"/>
     </row>
     <row r="470" spans="1:5">
-      <c r="A470" s="33"/>
-      <c r="B470" s="34"/>
-      <c r="C470" s="33"/>
-      <c r="D470" s="33"/>
-      <c r="E470" s="33"/>
+      <c r="A470" s="151"/>
+      <c r="B470" s="152"/>
+      <c r="C470" s="151"/>
+      <c r="D470" s="151"/>
+      <c r="E470" s="151"/>
     </row>
     <row r="471" spans="1:5">
-      <c r="A471" s="33"/>
-      <c r="B471" s="34"/>
-      <c r="C471" s="33"/>
-      <c r="D471" s="33"/>
-      <c r="E471" s="33"/>
+      <c r="A471" s="151"/>
+      <c r="B471" s="152"/>
+      <c r="C471" s="151"/>
+      <c r="D471" s="151"/>
+      <c r="E471" s="151"/>
     </row>
     <row r="472" spans="1:5">
-      <c r="A472" s="33"/>
-      <c r="B472" s="34"/>
-      <c r="C472" s="33"/>
-      <c r="D472" s="33"/>
-      <c r="E472" s="33"/>
+      <c r="A472" s="151"/>
+      <c r="B472" s="152"/>
+      <c r="C472" s="151"/>
+      <c r="D472" s="151"/>
+      <c r="E472" s="151"/>
     </row>
     <row r="473" spans="1:5">
-      <c r="A473" s="33"/>
-      <c r="B473" s="34"/>
-      <c r="C473" s="33"/>
-      <c r="D473" s="33"/>
-      <c r="E473" s="33"/>
+      <c r="A473" s="151"/>
+      <c r="B473" s="152"/>
+      <c r="C473" s="151"/>
+      <c r="D473" s="151"/>
+      <c r="E473" s="151"/>
     </row>
     <row r="474" spans="1:5">
-      <c r="A474" s="33"/>
-      <c r="B474" s="34"/>
-      <c r="C474" s="33"/>
-      <c r="D474" s="33"/>
-      <c r="E474" s="33"/>
+      <c r="A474" s="151"/>
+      <c r="B474" s="152"/>
+      <c r="C474" s="151"/>
+      <c r="D474" s="151"/>
+      <c r="E474" s="151"/>
     </row>
     <row r="475" spans="1:5">
-      <c r="A475" s="33"/>
-      <c r="B475" s="34"/>
-      <c r="C475" s="33"/>
-      <c r="D475" s="33"/>
-      <c r="E475" s="33"/>
+      <c r="A475" s="151"/>
+      <c r="B475" s="152"/>
+      <c r="C475" s="151"/>
+      <c r="D475" s="151"/>
+      <c r="E475" s="151"/>
     </row>
     <row r="476" spans="1:5">
-      <c r="A476" s="33"/>
-      <c r="B476" s="34"/>
-      <c r="C476" s="33"/>
-      <c r="D476" s="33"/>
-      <c r="E476" s="33"/>
+      <c r="A476" s="151"/>
+      <c r="B476" s="152"/>
+      <c r="C476" s="151"/>
+      <c r="D476" s="151"/>
+      <c r="E476" s="151"/>
     </row>
     <row r="477" spans="1:5">
-      <c r="A477" s="33"/>
-      <c r="B477" s="34"/>
-      <c r="C477" s="33"/>
-      <c r="D477" s="33"/>
-      <c r="E477" s="33"/>
+      <c r="A477" s="151"/>
+      <c r="B477" s="152"/>
+      <c r="C477" s="151"/>
+      <c r="D477" s="151"/>
+      <c r="E477" s="151"/>
     </row>
     <row r="478" spans="1:5">
-      <c r="A478" s="33"/>
-      <c r="B478" s="34"/>
-      <c r="C478" s="33"/>
-      <c r="D478" s="33"/>
-      <c r="E478" s="33"/>
+      <c r="A478" s="151"/>
+      <c r="B478" s="152"/>
+      <c r="C478" s="151"/>
+      <c r="D478" s="151"/>
+      <c r="E478" s="151"/>
     </row>
     <row r="479" spans="1:5">
-      <c r="A479" s="33"/>
-      <c r="B479" s="34"/>
-      <c r="C479" s="33"/>
-      <c r="D479" s="33"/>
-      <c r="E479" s="33"/>
+      <c r="A479" s="151"/>
+      <c r="B479" s="152"/>
+      <c r="C479" s="151"/>
+      <c r="D479" s="151"/>
+      <c r="E479" s="151"/>
     </row>
     <row r="480" spans="1:5">
-      <c r="A480" s="33"/>
-      <c r="B480" s="34"/>
-      <c r="C480" s="33"/>
-      <c r="D480" s="33"/>
-      <c r="E480" s="33"/>
+      <c r="A480" s="151"/>
+      <c r="B480" s="152"/>
+      <c r="C480" s="151"/>
+      <c r="D480" s="151"/>
+      <c r="E480" s="151"/>
     </row>
     <row r="481" spans="1:5">
-      <c r="A481" s="33"/>
-      <c r="B481" s="34"/>
-      <c r="C481" s="33"/>
-      <c r="D481" s="33"/>
-      <c r="E481" s="33"/>
+      <c r="A481" s="151"/>
+      <c r="B481" s="152"/>
+      <c r="C481" s="151"/>
+      <c r="D481" s="151"/>
+      <c r="E481" s="151"/>
     </row>
     <row r="482" spans="1:5">
-      <c r="A482" s="33"/>
-      <c r="B482" s="34"/>
-      <c r="C482" s="33"/>
-      <c r="D482" s="33"/>
-      <c r="E482" s="33"/>
+      <c r="A482" s="151"/>
+      <c r="B482" s="152"/>
+      <c r="C482" s="151"/>
+      <c r="D482" s="151"/>
+      <c r="E482" s="151"/>
     </row>
     <row r="483" spans="1:5">
-      <c r="A483" s="33"/>
-      <c r="B483" s="34"/>
-      <c r="C483" s="33"/>
-      <c r="D483" s="33"/>
-      <c r="E483" s="33"/>
+      <c r="A483" s="151"/>
+      <c r="B483" s="152"/>
+      <c r="C483" s="151"/>
+      <c r="D483" s="151"/>
+      <c r="E483" s="151"/>
     </row>
     <row r="484" spans="1:5">
-      <c r="A484" s="33"/>
-      <c r="B484" s="34"/>
-      <c r="C484" s="33"/>
-      <c r="D484" s="33"/>
-      <c r="E484" s="33"/>
+      <c r="A484" s="151"/>
+      <c r="B484" s="152"/>
+      <c r="C484" s="151"/>
+      <c r="D484" s="151"/>
+      <c r="E484" s="151"/>
     </row>
     <row r="485" spans="1:5">
-      <c r="A485" s="33"/>
-      <c r="B485" s="34"/>
-      <c r="C485" s="33"/>
-      <c r="D485" s="33"/>
-      <c r="E485" s="33"/>
+      <c r="A485" s="151"/>
+      <c r="B485" s="152"/>
+      <c r="C485" s="151"/>
+      <c r="D485" s="151"/>
+      <c r="E485" s="151"/>
     </row>
     <row r="486" spans="1:5">
-      <c r="A486" s="33"/>
-      <c r="B486" s="34"/>
-      <c r="C486" s="33"/>
-      <c r="D486" s="33"/>
-      <c r="E486" s="33"/>
+      <c r="A486" s="151"/>
+      <c r="B486" s="152"/>
+      <c r="C486" s="151"/>
+      <c r="D486" s="151"/>
+      <c r="E486" s="151"/>
     </row>
     <row r="487" spans="1:5">
-      <c r="A487" s="33"/>
-      <c r="B487" s="34"/>
-      <c r="C487" s="33"/>
-      <c r="D487" s="33"/>
-      <c r="E487" s="33"/>
+      <c r="A487" s="151"/>
+      <c r="B487" s="152"/>
+      <c r="C487" s="151"/>
+      <c r="D487" s="151"/>
+      <c r="E487" s="151"/>
     </row>
     <row r="488" spans="1:5">
-      <c r="A488" s="33"/>
-      <c r="B488" s="34"/>
-      <c r="C488" s="33"/>
-      <c r="D488" s="33"/>
-      <c r="E488" s="33"/>
+      <c r="A488" s="151"/>
+      <c r="B488" s="152"/>
+      <c r="C488" s="151"/>
+      <c r="D488" s="151"/>
+      <c r="E488" s="151"/>
     </row>
     <row r="489" spans="1:5">
-      <c r="A489" s="33"/>
-      <c r="B489" s="34"/>
-      <c r="C489" s="33"/>
-      <c r="D489" s="33"/>
-      <c r="E489" s="33"/>
+      <c r="A489" s="151"/>
+      <c r="B489" s="152"/>
+      <c r="C489" s="151"/>
+      <c r="D489" s="151"/>
+      <c r="E489" s="151"/>
     </row>
     <row r="490" spans="1:5">
-      <c r="A490" s="33"/>
-      <c r="B490" s="34"/>
-      <c r="C490" s="33"/>
-      <c r="D490" s="33"/>
-      <c r="E490" s="33"/>
+      <c r="A490" s="151"/>
+      <c r="B490" s="152"/>
+      <c r="C490" s="151"/>
+      <c r="D490" s="151"/>
+      <c r="E490" s="151"/>
     </row>
     <row r="491" spans="1:5">
-      <c r="A491" s="33"/>
-      <c r="B491" s="34"/>
-      <c r="C491" s="33"/>
-      <c r="D491" s="33"/>
-      <c r="E491" s="33"/>
+      <c r="A491" s="151"/>
+      <c r="B491" s="152"/>
+      <c r="C491" s="151"/>
+      <c r="D491" s="151"/>
+      <c r="E491" s="151"/>
     </row>
     <row r="492" spans="1:5">
-      <c r="A492" s="33"/>
-      <c r="B492" s="34"/>
-      <c r="C492" s="33"/>
-      <c r="D492" s="33"/>
-      <c r="E492" s="33"/>
+      <c r="A492" s="151"/>
+      <c r="B492" s="152"/>
+      <c r="C492" s="151"/>
+      <c r="D492" s="151"/>
+      <c r="E492" s="151"/>
     </row>
     <row r="493" spans="1:5">
-      <c r="A493" s="33"/>
-      <c r="B493" s="34"/>
-      <c r="C493" s="33"/>
-      <c r="D493" s="33"/>
-      <c r="E493" s="33"/>
+      <c r="A493" s="151"/>
+      <c r="B493" s="152"/>
+      <c r="C493" s="151"/>
+      <c r="D493" s="151"/>
+      <c r="E493" s="151"/>
     </row>
     <row r="494" spans="1:5">
-      <c r="A494" s="33"/>
-      <c r="B494" s="34"/>
-      <c r="C494" s="33"/>
-      <c r="D494" s="33"/>
-      <c r="E494" s="33"/>
+      <c r="A494" s="151"/>
+      <c r="B494" s="152"/>
+      <c r="C494" s="151"/>
+      <c r="D494" s="151"/>
+      <c r="E494" s="151"/>
     </row>
     <row r="495" spans="1:5">
-      <c r="A495" s="33"/>
-      <c r="B495" s="34"/>
-      <c r="C495" s="33"/>
-      <c r="D495" s="33"/>
-      <c r="E495" s="33"/>
+      <c r="A495" s="151"/>
+      <c r="B495" s="152"/>
+      <c r="C495" s="151"/>
+      <c r="D495" s="151"/>
+      <c r="E495" s="151"/>
     </row>
     <row r="496" spans="1:5">
-      <c r="A496" s="33"/>
-      <c r="B496" s="34"/>
-      <c r="C496" s="33"/>
-      <c r="D496" s="33"/>
-      <c r="E496" s="33"/>
+      <c r="A496" s="151"/>
+      <c r="B496" s="152"/>
+      <c r="C496" s="151"/>
+      <c r="D496" s="151"/>
+      <c r="E496" s="151"/>
     </row>
     <row r="497" spans="1:5">
-      <c r="A497" s="33"/>
-      <c r="B497" s="34"/>
-      <c r="C497" s="33"/>
-      <c r="D497" s="33"/>
-      <c r="E497" s="33"/>
+      <c r="A497" s="151"/>
+      <c r="B497" s="152"/>
+      <c r="C497" s="151"/>
+      <c r="D497" s="151"/>
+      <c r="E497" s="151"/>
     </row>
     <row r="498" spans="1:5">
-      <c r="A498" s="33"/>
-      <c r="B498" s="34"/>
-      <c r="C498" s="33"/>
-      <c r="D498" s="33"/>
-      <c r="E498" s="33"/>
+      <c r="A498" s="151"/>
+      <c r="B498" s="152"/>
+      <c r="C498" s="151"/>
+      <c r="D498" s="151"/>
+      <c r="E498" s="151"/>
     </row>
     <row r="499" spans="1:5">
-      <c r="A499" s="33"/>
-      <c r="B499" s="34"/>
-      <c r="C499" s="33"/>
-      <c r="D499" s="33"/>
-      <c r="E499" s="33"/>
+      <c r="A499" s="151"/>
+      <c r="B499" s="152"/>
+      <c r="C499" s="151"/>
+      <c r="D499" s="151"/>
+      <c r="E499" s="151"/>
     </row>
     <row r="500" spans="1:5">
-      <c r="A500" s="33"/>
-      <c r="B500" s="34"/>
-      <c r="C500" s="33"/>
-      <c r="D500" s="33"/>
-      <c r="E500" s="33"/>
+      <c r="A500" s="151"/>
+      <c r="B500" s="152"/>
+      <c r="C500" s="151"/>
+      <c r="D500" s="151"/>
+      <c r="E500" s="151"/>
     </row>
     <row r="501" spans="1:5">
-      <c r="A501" s="33"/>
-      <c r="B501" s="34"/>
-      <c r="C501" s="33"/>
-      <c r="D501" s="33"/>
-      <c r="E501" s="33"/>
+      <c r="A501" s="151"/>
+      <c r="B501" s="152"/>
+      <c r="C501" s="151"/>
+      <c r="D501" s="151"/>
+      <c r="E501" s="151"/>
     </row>
     <row r="502" spans="1:5">
-      <c r="A502" s="33"/>
-      <c r="B502" s="34"/>
-      <c r="C502" s="33"/>
-      <c r="D502" s="33"/>
-      <c r="E502" s="33"/>
+      <c r="A502" s="151"/>
+      <c r="B502" s="152"/>
+      <c r="C502" s="151"/>
+      <c r="D502" s="151"/>
+      <c r="E502" s="151"/>
     </row>
     <row r="503" spans="1:5">
-      <c r="A503" s="33"/>
-      <c r="B503" s="34"/>
-      <c r="C503" s="33"/>
-      <c r="D503" s="33"/>
-      <c r="E503" s="33"/>
+      <c r="A503" s="151"/>
+      <c r="B503" s="152"/>
+      <c r="C503" s="151"/>
+      <c r="D503" s="151"/>
+      <c r="E503" s="151"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:E7" etc:filterBottomFollowUsedRange="0">
@@ -12510,7 +12680,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P504"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.25" style="3" customWidth="1"/>

--- a/design/道具表.xlsx
+++ b/design/道具表.xlsx
@@ -793,7 +793,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="71">
+  <fonts count="73">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1200,6 +1200,18 @@
       <sz val="11"/>
       <color rgb="FF20364D"/>
       <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF20364D"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="83">
@@ -2489,7 +2501,7 @@
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2948,6 +2960,69 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="48" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="49" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="50" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="21" xfId="104" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="35" fillId="0" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="24" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="26" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="26" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="82" borderId="21" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="53">
@@ -3453,7 +3528,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:AM500"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="24" style="3" customWidth="1"/>
@@ -3463,7 +3538,7 @@
     <col min="5" max="6" width="17" style="3" customWidth="1"/>
     <col min="7" max="7" width="45" style="3" customWidth="1"/>
     <col min="8" max="8" width="17" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="38"/>
+    <col min="9" max="9" width="22" style="38" customWidth="1"/>
     <col min="10" max="10" width="55" style="38" customWidth="1"/>
     <col min="11" max="16384" width="9" style="38"/>
   </cols>
@@ -3493,7 +3568,9 @@
       <c r="H1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="36"/>
+      <c r="I1" s="173" t="str">
+        <v>授予技能ID（0为普通物品）</v>
+      </c>
       <c r="J1" s="40" t="s">
         <v>8</v>
       </c>
@@ -3552,7 +3629,9 @@
       <c r="H2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="36"/>
+      <c r="I2" s="173" t="str">
+        <v>int32</v>
+      </c>
       <c r="J2" s="42" t="s">
         <v>11</v>
       </c>
@@ -3611,7 +3690,9 @@
       <c r="H3" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="36"/>
+      <c r="I3" s="173" t="str">
+        <v>SkillIdx</v>
+      </c>
       <c r="J3" s="42"/>
       <c r="K3" s="36"/>
       <c r="L3" s="36"/>
@@ -3668,7 +3749,9 @@
       <c r="H4" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="36"/>
+      <c r="I4" s="173" t="str">
+        <v>server/client</v>
+      </c>
       <c r="J4" s="42"/>
       <c r="K4" s="36"/>
       <c r="L4" s="36"/>
@@ -3723,7 +3806,9 @@
       <c r="H5" s="43">
         <v>999999999</v>
       </c>
-      <c r="I5" s="38"/>
+      <c r="I5" s="104" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" s="42" t="s">
         <v>25</v>
       </c>
@@ -3758,15 +3843,21 @@
       <c r="D6" s="43">
         <v>1</v>
       </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
+      <c r="E6" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="110" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="44" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="43">
         <v>999999999</v>
       </c>
-      <c r="I6" s="38"/>
+      <c r="I6" s="104" t="n">
+        <v>0</v>
+      </c>
       <c r="J6" s="38"/>
       <c r="K6" s="38"/>
       <c r="L6" s="38"/>
@@ -3799,15 +3890,21 @@
       <c r="D7" s="43">
         <v>1</v>
       </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
+      <c r="E7" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="110" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" s="44" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="43">
         <v>999999999</v>
       </c>
-      <c r="I7" s="38"/>
+      <c r="I7" s="104" t="n">
+        <v>0</v>
+      </c>
       <c r="J7" s="38"/>
       <c r="K7" s="38"/>
       <c r="L7" s="38"/>
@@ -3840,15 +3937,21 @@
       <c r="D8" s="45">
         <v>1</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
+      <c r="E8" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="112" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" s="44" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="45">
         <v>999999999</v>
       </c>
-      <c r="I8" s="38"/>
+      <c r="I8" s="104" t="n">
+        <v>0</v>
+      </c>
       <c r="J8" s="38"/>
       <c r="K8" s="38"/>
       <c r="L8" s="38"/>
@@ -3907,6 +4010,9 @@
       <c r="H10" s="51">
         <v>5</v>
       </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:39">
       <c r="A11" s="43">
@@ -3931,6 +4037,9 @@
       <c r="H11" s="51">
         <v>5</v>
       </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:39">
       <c r="A12" s="45">
@@ -3954,6 +4063,9 @@
       </c>
       <c r="H12" s="51">
         <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" s="36" customFormat="1" ht="37" customHeight="1" spans="1:39">
@@ -3993,6 +4105,9 @@
       <c r="H14" s="51">
         <v>5</v>
       </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:39">
       <c r="A15" s="43">
@@ -4017,6 +4132,9 @@
       <c r="H15" s="51">
         <v>5</v>
       </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:39">
       <c r="A16" s="45">
@@ -4040,6 +4158,9 @@
       </c>
       <c r="H16" s="51">
         <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17" s="37" customFormat="1" ht="37" customHeight="1" spans="1:8">
@@ -4079,6 +4200,9 @@
       <c r="H18" s="51">
         <v>5</v>
       </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="54">
@@ -4103,6 +4227,9 @@
       <c r="H19" s="51">
         <v>5</v>
       </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="54">
@@ -4118,12 +4245,17 @@
       <c r="E20" s="54">
         <v>1</v>
       </c>
-      <c r="F20" s="54"/>
+      <c r="F20" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" s="61" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="51">
         <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4149,6 +4281,9 @@
       <c r="H21" s="54">
         <v>5</v>
       </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="54">
@@ -4164,12 +4299,17 @@
       <c r="E22" s="54">
         <v>2</v>
       </c>
-      <c r="F22" s="54"/>
+      <c r="F22" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="G22" s="53" t="s">
         <v>51</v>
       </c>
       <c r="H22" s="54">
         <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4195,6 +4335,9 @@
       <c r="H23" s="54">
         <v>5</v>
       </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="121" t="n">
@@ -4219,6 +4362,9 @@
       <c r="H24" s="121" t="n">
         <v>99</v>
       </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="121" t="n">
@@ -4242,6 +4388,9 @@
       </c>
       <c r="H25" s="121" t="n">
         <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4255,24 +4404,58 @@
       <c r="H26" s="54"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="54"/>
-      <c r="B27" s="53"/>
+      <c r="A27" s="121" t="n">
+        <v>2900001</v>
+      </c>
+      <c r="B27" s="120" t="str">
+        <v>军需官技能凭证</v>
+      </c>
       <c r="C27" s="53"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
+      <c r="D27" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="120" t="str">
+        <v>拾取立即获得技能4，撤离保留</v>
+      </c>
+      <c r="H27" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="54"/>
-      <c r="B28" s="53"/>
+      <c r="A28" s="121" t="n">
+        <v>2900002</v>
+      </c>
+      <c r="B28" s="120" t="str">
+        <v>医生技能凭证</v>
+      </c>
       <c r="C28" s="53"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
+      <c r="D28" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="120" t="str">
+        <v>拾取立即获得技能12，撤离保留</v>
+      </c>
+      <c r="H28" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="54"/>
@@ -12680,7 +12863,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:P504"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.25" style="3" customWidth="1"/>
@@ -12692,9 +12875,9 @@
     <col min="9" max="9" width="19.5" style="3" customWidth="1"/>
     <col min="10" max="10" width="20.25" style="3" customWidth="1"/>
     <col min="11" max="13" width="15.625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="7.125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="15.625" style="4"/>
-    <col min="16" max="16" width="55" style="4" customWidth="1"/>
+    <col min="14" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="22" style="4" customWidth="1"/>
+    <col min="16" max="16" width="22" style="4" customWidth="1"/>
     <col min="17" max="16384" width="15.625" style="4"/>
   </cols>
   <sheetData>
@@ -12738,11 +12921,17 @@
       <c r="M1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>8</v>
+      <c r="N1" s="159" t="str">
+        <v>单次补给次数</v>
+      </c>
+      <c r="O1" s="166" t="str">
+        <v>消耗品补给权重</v>
+      </c>
+      <c r="P1" s="166" t="str">
+        <v>运行启用（0/1）</v>
+      </c>
+      <c r="U1" t="str">
+        <v>配置模板 · 待接入</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="25" customHeight="1" spans="1:16">
@@ -12788,8 +12977,14 @@
       <c r="N2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="10" t="s">
-        <v>11</v>
+      <c r="O2" s="166" t="str">
+        <v>int32</v>
+      </c>
+      <c r="P2" s="170" t="str">
+        <v>int32</v>
+      </c>
+      <c r="U2" t="str">
+        <v>详见《配置表填写说明.md》</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="29" customHeight="1" spans="1:16">
@@ -12832,10 +13027,15 @@
       <c r="M3" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="N3" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="P3" s="10"/>
+      <c r="N3" s="162" t="str">
+        <v>RefillCount</v>
+      </c>
+      <c r="O3" s="166" t="str">
+        <v>SupplyWeight</v>
+      </c>
+      <c r="P3" s="170" t="str">
+        <v>Enabled</v>
+      </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="28" customHeight="1" spans="1:16">
       <c r="A4" s="11" t="s">
@@ -12877,10 +13077,15 @@
       <c r="M4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="P4" s="10"/>
+      <c r="N4" s="163" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="O4" s="166" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="P4" s="170" t="str">
+        <v>server/client</v>
+      </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="81" t="n">
@@ -12925,8 +13130,14 @@
       <c r="N5" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="10" t="s">
-        <v>25</v>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="str">
+        <v>资源空值表示待美术交付；新增数值为示例。</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -12970,12 +13181,18 @@
         <v>0</v>
       </c>
       <c r="N6" s="83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="13">
-        <v>3</v>
+      <c r="A7" s="81" t="n">
+        <v>30003</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>49</v>
@@ -13013,7 +13230,15 @@
       <c r="M7" s="13">
         <v>540</v>
       </c>
-      <c r="N7" s="13"/>
+      <c r="N7" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="83" t="n">
@@ -13058,10 +13283,16 @@
       <c r="N8" s="83" t="n">
         <v>0</v>
       </c>
+      <c r="O8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="17">
-        <v>5</v>
+      <c r="A9" s="85" t="n">
+        <v>30005</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>52</v>
@@ -13084,8 +13315,12 @@
       <c r="H9" s="17">
         <v>0</v>
       </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
+      <c r="I9" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="85" t="n">
+        <v>0</v>
+      </c>
       <c r="K9" s="17">
         <v>90</v>
       </c>
@@ -13095,7 +13330,15 @@
       <c r="M9" s="17">
         <v>7200</v>
       </c>
-      <c r="N9" s="17"/>
+      <c r="N9" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="85" t="n">
@@ -13139,6 +13382,12 @@
       </c>
       <c r="N10" s="85" t="n">
         <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:16">
